--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -62874,7 +62874,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="D2718" t="n">
-        <v>5.55999994277954</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="E2718" t="n">
         <v>5.63000011444092</v>
@@ -62883,6 +62883,29 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>18844</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>5.51000022888184</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>12736</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -62920,7 +62920,7 @@
         <v>5.75</v>
       </c>
       <c r="D2720" t="n">
-        <v>5.51999998092651</v>
+        <v>5.5</v>
       </c>
       <c r="E2720" t="n">
         <v>5.75</v>
@@ -62929,6 +62929,29 @@
         <v>5.5</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>6256</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>5.44999980926514</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>5.46999979019165</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>9748</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>5.53999996185303</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>32780</v>
+        <v>5783</v>
       </c>
       <c r="C2715" t="n">
-        <v>6.05999994277954</v>
+        <v>6</v>
       </c>
       <c r="D2715" t="n">
-        <v>5.80000019073486</v>
+        <v>5.84000015258789</v>
       </c>
       <c r="E2715" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="F2715" t="n">
         <v>6</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>5.90999984741211</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>49951</v>
+        <v>32780</v>
       </c>
       <c r="C2716" t="n">
-        <v>5.86999988555908</v>
+        <v>6.05999994277954</v>
       </c>
       <c r="D2716" t="n">
-        <v>5.61999988555908</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="E2716" t="n">
-        <v>5.86999988555908</v>
+        <v>6</v>
       </c>
       <c r="F2716" t="n">
-        <v>5.61999988555908</v>
+        <v>5.90999984741211</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>13690</v>
+        <v>49951</v>
       </c>
       <c r="C2717" t="n">
-        <v>5.67999982833862</v>
+        <v>5.86999988555908</v>
       </c>
       <c r="D2717" t="n">
-        <v>5.55000019073486</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="E2717" t="n">
-        <v>5.61999988555908</v>
+        <v>5.86999988555908</v>
       </c>
       <c r="F2717" t="n">
         <v>5.61999988555908</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>10573</v>
+        <v>13690</v>
       </c>
       <c r="C2718" t="n">
-        <v>5.69999980926514</v>
+        <v>5.67999982833862</v>
       </c>
       <c r="D2718" t="n">
         <v>5.55000019073486</v>
       </c>
       <c r="E2718" t="n">
-        <v>5.63000011444092</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="F2718" t="n">
-        <v>5.55000019073486</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>18844</v>
+        <v>10573</v>
       </c>
       <c r="C2719" t="n">
-        <v>5.76000022888184</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="D2719" t="n">
-        <v>5.51000022888184</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="E2719" t="n">
-        <v>5.76000022888184</v>
+        <v>5.63000011444092</v>
       </c>
       <c r="F2719" t="n">
-        <v>5.59999990463257</v>
+        <v>5.55000019073486</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>12736</v>
+        <v>18844</v>
       </c>
       <c r="C2720" t="n">
-        <v>5.75</v>
+        <v>5.76000022888184</v>
       </c>
       <c r="D2720" t="n">
-        <v>5.5</v>
+        <v>5.51000022888184</v>
       </c>
       <c r="E2720" t="n">
-        <v>5.75</v>
+        <v>5.76000022888184</v>
       </c>
       <c r="F2720" t="n">
-        <v>5.5</v>
+        <v>5.59999990463257</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>6256</v>
+        <v>12736</v>
       </c>
       <c r="C2721" t="n">
-        <v>5.65000009536743</v>
+        <v>5.75</v>
       </c>
       <c r="D2721" t="n">
-        <v>5.44999980926514</v>
+        <v>5.5</v>
       </c>
       <c r="E2721" t="n">
-        <v>5.65000009536743</v>
+        <v>5.75</v>
       </c>
       <c r="F2721" t="n">
-        <v>5.46999979019165</v>
+        <v>5.5</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>9748</v>
+        <v>6256</v>
       </c>
       <c r="C2722" t="n">
-        <v>5.69999980926514</v>
+        <v>5.65000009536743</v>
       </c>
       <c r="D2722" t="n">
-        <v>5.55000019073486</v>
+        <v>5.44999980926514</v>
       </c>
       <c r="E2722" t="n">
-        <v>5.69999980926514</v>
+        <v>5.65000009536743</v>
       </c>
       <c r="F2722" t="n">
-        <v>5.53999996185303</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>9942</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59127020835876</v>
+        <v>3.59126973152161</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60514259338379</v>
+        <v>3.60514235496521</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G4" t="n">
-        <v>3.51420450210571</v>
+        <v>3.51420402526855</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3893575668335</v>
+        <v>3.38935780525208</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G6" t="n">
-        <v>3.34620070457458</v>
+        <v>3.34620094299316</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2860894203186</v>
+        <v>3.28608918190002</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.39089894294739</v>
+        <v>3.39089918136597</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G10" t="n">
-        <v>3.37856817245483</v>
+        <v>3.37856793403625</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35853147506714</v>
+        <v>3.35853123664856</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G12" t="n">
-        <v>3.31229114532471</v>
+        <v>3.31229186058044</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33695292472839</v>
+        <v>3.33695340156555</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.22135448455811</v>
+        <v>3.22135424613953</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.14428806304932</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>3.19823431968689</v>
+        <v>3.19823479652405</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G19" t="n">
-        <v>3.12579274177551</v>
+        <v>3.12579250335693</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G20" t="n">
-        <v>3.06722235679626</v>
+        <v>3.06722211837769</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1597011089325</v>
+        <v>3.15970134735107</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09958982467651</v>
+        <v>3.09959006309509</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G23" t="n">
-        <v>3.10575556755066</v>
+        <v>3.10575532913208</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>3.00556945800781</v>
+        <v>3.00556969642639</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>3.08263564109802</v>
+        <v>3.08263540267944</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9855329990387</v>
+        <v>2.98553228378296</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.86685109138489</v>
+        <v>2.86685132980347</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85143756866455</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7743718624115</v>
+        <v>2.77437162399292</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G30" t="n">
-        <v>2.7666654586792</v>
+        <v>2.76666522026062</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G31" t="n">
-        <v>2.69422340393066</v>
+        <v>2.69422364234924</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6957643032074</v>
+        <v>2.69576478004456</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.69730615615845</v>
+        <v>2.69730591773987</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85143756866455</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86685109138489</v>
+        <v>2.86685132980347</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91925621032715</v>
+        <v>2.91925573348999</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.85143756866455</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.85143756866455</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93004512786865</v>
+        <v>2.93004488945007</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G42" t="n">
-        <v>2.99478030204773</v>
+        <v>2.99478054046631</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>2.92850399017334</v>
+        <v>2.92850375175476</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G47" t="n">
-        <v>2.94391679763794</v>
+        <v>2.94391703605652</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99786329269409</v>
+        <v>2.99786281585693</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08263564109802</v>
+        <v>3.08263540267944</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G54" t="n">
-        <v>3.03639578819275</v>
+        <v>3.03639602661133</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G55" t="n">
-        <v>3.07030487060547</v>
+        <v>3.07030510902405</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.14428806304932</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G57" t="n">
-        <v>3.22135448455811</v>
+        <v>3.22135424613953</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>3.26759338378906</v>
+        <v>3.26759314537048</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.23676681518555</v>
+        <v>3.23676705360413</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>3.17357349395752</v>
+        <v>3.17357301712036</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14428806304932</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05951595306396</v>
+        <v>3.05951547622681</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G66" t="n">
-        <v>3.13504028320312</v>
+        <v>3.13504004478455</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G67" t="n">
-        <v>3.03793692588806</v>
+        <v>3.03793716430664</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G69" t="n">
-        <v>3.07492899894714</v>
+        <v>3.07492876052856</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>2.98245024681091</v>
+        <v>2.98244976997375</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.93621063232422</v>
+        <v>2.93621039390564</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G73" t="n">
-        <v>3.02868962287903</v>
+        <v>3.02868938446045</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80211544036865</v>
+        <v>2.80211567878723</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.84835529327393</v>
+        <v>2.84835505485535</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G78" t="n">
-        <v>2.92233896255493</v>
+        <v>2.92233824729919</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.93775177001953</v>
+        <v>2.93775200843811</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G80" t="n">
-        <v>2.95162343978882</v>
+        <v>2.95162320137024</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G81" t="n">
-        <v>2.86530923843384</v>
+        <v>2.86530947685242</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85914492607117</v>
+        <v>2.85914421081543</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G84" t="n">
-        <v>2.75433468818665</v>
+        <v>2.75433492660522</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G85" t="n">
-        <v>2.75433468818665</v>
+        <v>2.75433492660522</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.78053760528564</v>
+        <v>2.78053689002991</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>2.74200439453125</v>
+        <v>2.74200415611267</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67110347747803</v>
+        <v>2.67110371589661</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59557938575745</v>
+        <v>2.59557914733887</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G90" t="n">
-        <v>2.62486433982849</v>
+        <v>2.62486410140991</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>2.65723156929016</v>
+        <v>2.65723180770874</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.70501255989075</v>
+        <v>2.70501208305359</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>2.7204258441925</v>
+        <v>2.72042608261108</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>2.53546762466431</v>
+        <v>2.53546786308289</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48152160644531</v>
+        <v>2.48152184486389</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55043363571167</v>
+        <v>2.55043339729309</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.53293228149414</v>
+        <v>2.53293204307556</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.50588417053223</v>
+        <v>2.50588464736938</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.55361580848694</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G106" t="n">
-        <v>2.5265679359436</v>
+        <v>2.52656817436218</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G107" t="n">
-        <v>2.5265679359436</v>
+        <v>2.52656817436218</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G109" t="n">
-        <v>2.66339731216431</v>
+        <v>2.66339659690857</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.76045036315918</v>
+        <v>2.7604501247406</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.74453997612</v>
+        <v>2.74454021453857</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G113" t="n">
-        <v>2.65703296661377</v>
+        <v>2.65703248977661</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.50588417053223</v>
+        <v>2.50588464736938</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>2.45019817352295</v>
+        <v>2.45019793510437</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35473561286926</v>
+        <v>2.35473585128784</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14790105819702</v>
+        <v>2.14790058135986</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.18767690658569</v>
+        <v>2.18767642974854</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G128" t="n">
-        <v>2.2258620262146</v>
+        <v>2.22586178779602</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.24336314201355</v>
+        <v>2.24336290359497</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="n">
-        <v>2.14631009101868</v>
+        <v>2.1463098526001</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25609135627747</v>
+        <v>2.25609159469604</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="n">
-        <v>2.28154826164246</v>
+        <v>2.2815477848053</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>2.27041077613831</v>
+        <v>2.27041053771973</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="n">
-        <v>2.27041077613831</v>
+        <v>2.27041053771973</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G141" t="n">
-        <v>2.33087015151978</v>
+        <v>2.33087038993835</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>2.4899742603302</v>
+        <v>2.48997378349304</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76045036315918</v>
+        <v>2.7604501247406</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G150" t="n">
-        <v>2.54088687896729</v>
+        <v>2.54088735580444</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>2.55361580848694</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G153" t="n">
-        <v>2.55043363571167</v>
+        <v>2.55043339729309</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179503440857</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179503440857</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="n">
-        <v>2.5186128616333</v>
+        <v>2.51861262321472</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="n">
-        <v>2.47883653640747</v>
+        <v>2.47883677482605</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G162" t="n">
-        <v>2.48360967636108</v>
+        <v>2.48360991477966</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="n">
-        <v>2.58066296577454</v>
+        <v>2.58066320419312</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>2.58066296577454</v>
+        <v>2.58066320419312</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225464820862</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="n">
-        <v>2.63475823402405</v>
+        <v>2.63475871086121</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.69840002059937</v>
+        <v>2.69839954376221</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="n">
-        <v>2.733402967453</v>
+        <v>2.73340272903442</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="n">
-        <v>2.733402967453</v>
+        <v>2.73340272903442</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G177" t="n">
-        <v>2.76045036315918</v>
+        <v>2.7604501247406</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134649276733</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>2.64907765388489</v>
+        <v>2.64907741546631</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66976118087769</v>
+        <v>2.66976141929626</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="n">
-        <v>2.71112775802612</v>
+        <v>2.71112847328186</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G188" t="n">
-        <v>2.74135828018188</v>
+        <v>2.74135804176331</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>2.64907765388489</v>
+        <v>2.64907741546631</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="n">
-        <v>2.63794016838074</v>
+        <v>2.63794040679932</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="n">
-        <v>2.61089277267456</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>2.55361580848694</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>2.56157088279724</v>
+        <v>2.56157064437866</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>2.55361580848694</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930204391479</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="n">
-        <v>2.54725170135498</v>
+        <v>2.5472514629364</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134649276733</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="n">
-        <v>2.62043905258179</v>
+        <v>2.62043952941895</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69680881500244</v>
+        <v>2.69680905342102</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66817021369934</v>
+        <v>2.66816997528076</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>2.76840543746948</v>
+        <v>2.76840591430664</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G213" t="n">
-        <v>2.70317316055298</v>
+        <v>2.7031729221344</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.63316702842712</v>
+        <v>2.63316750526428</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>2.55679726600647</v>
+        <v>2.55679774284363</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G222" t="n">
-        <v>2.6745343208313</v>
+        <v>2.67453455924988</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G225" t="n">
-        <v>2.61884808540344</v>
+        <v>2.61884784698486</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="n">
-        <v>2.5392963886261</v>
+        <v>2.53929567337036</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.50588417053223</v>
+        <v>2.50588464736938</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G232" t="n">
-        <v>2.4899742603302</v>
+        <v>2.48997378349304</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="n">
-        <v>2.49633860588074</v>
+        <v>2.49633812904358</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G234" t="n">
-        <v>2.45974397659302</v>
+        <v>2.45974445343018</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>2.35473561286926</v>
+        <v>2.35473585128784</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>2.50588417053223</v>
+        <v>2.50588464736938</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>2.50588417053223</v>
+        <v>2.50588464736938</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="n">
-        <v>2.5392963886261</v>
+        <v>2.53929567337036</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="n">
-        <v>2.5392963886261</v>
+        <v>2.53929567337036</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52975010871887</v>
+        <v>2.52974987030029</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>2.5758900642395</v>
+        <v>2.57588982582092</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179503440857</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930204391479</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930204391479</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63316702842712</v>
+        <v>2.63316750526428</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="n">
-        <v>2.66657900810242</v>
+        <v>2.666579246521</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="n">
-        <v>2.72385692596436</v>
+        <v>2.72385668754578</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71271944046021</v>
+        <v>2.71271920204163</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="n">
-        <v>2.64271354675293</v>
+        <v>2.64271378517151</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="n">
-        <v>2.66657900810242</v>
+        <v>2.666579246521</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G265" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>2.71430993080139</v>
+        <v>2.71431040763855</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="n">
-        <v>2.70635485649109</v>
+        <v>2.70635533332825</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="n">
-        <v>2.70635485649109</v>
+        <v>2.70635533332825</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134649276733</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G283" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="n">
-        <v>2.68726253509521</v>
+        <v>2.68726229667664</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.72067427635193</v>
+        <v>2.72067451477051</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68885374069214</v>
+        <v>2.68885350227356</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.65703296661377</v>
+        <v>2.65703248977661</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G292" t="n">
-        <v>2.63316702842712</v>
+        <v>2.63316750526428</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134649276733</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="n">
-        <v>2.62043905258179</v>
+        <v>2.62043952941895</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225464820862</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G300" t="n">
-        <v>2.54884266853333</v>
+        <v>2.54884219169617</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="n">
-        <v>2.57111692428589</v>
+        <v>2.57111716270447</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.59339141845703</v>
+        <v>2.59339165687561</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="n">
-        <v>2.61089277267456</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930204391479</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="n">
-        <v>2.63794016838074</v>
+        <v>2.63794040679932</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G309" t="n">
-        <v>2.61884808540344</v>
+        <v>2.61884784698486</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="n">
-        <v>2.62043905258179</v>
+        <v>2.62043952941895</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>2.64112281799316</v>
+        <v>2.64112234115601</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="n">
-        <v>2.66817021369934</v>
+        <v>2.66816997528076</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.74453997612</v>
+        <v>2.74454021453857</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G314" t="n">
-        <v>2.86068534851074</v>
+        <v>2.86068606376648</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G317" t="n">
-        <v>2.91159915924072</v>
+        <v>2.91159892082214</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="n">
-        <v>2.90682578086853</v>
+        <v>2.90682601928711</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G319" t="n">
-        <v>2.91159915924072</v>
+        <v>2.91159892082214</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87977814674377</v>
+        <v>2.8797779083252</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.87977814674377</v>
+        <v>2.8797779083252</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G324" t="n">
-        <v>2.86068534851074</v>
+        <v>2.86068606376648</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>2.83682012557983</v>
+        <v>2.83681988716125</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>2.81454563140869</v>
+        <v>2.81454586982727</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="n">
-        <v>2.78431582450867</v>
+        <v>2.78431606292725</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="n">
-        <v>2.85750341415405</v>
+        <v>2.85750365257263</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>2.85750341415405</v>
+        <v>2.85750365257263</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.86386752128601</v>
+        <v>2.86386799812317</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.87977814674377</v>
+        <v>2.8797779083252</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>2.92750930786133</v>
+        <v>2.92750954627991</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.85750341415405</v>
+        <v>2.85750365257263</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="n">
-        <v>2.8527307510376</v>
+        <v>2.85273051261902</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>2.86386752128601</v>
+        <v>2.86386799812317</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="n">
-        <v>2.85432147979736</v>
+        <v>2.85432124137878</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.87977814674377</v>
+        <v>2.8797779083252</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G346" t="n">
-        <v>2.89409732818604</v>
+        <v>2.89409756660461</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="n">
-        <v>2.889324426651</v>
+        <v>2.88932418823242</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="n">
-        <v>2.87977814674377</v>
+        <v>2.8797779083252</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.92750930786133</v>
+        <v>2.92750954627991</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G350" t="n">
-        <v>2.98478698730469</v>
+        <v>2.98478674888611</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="n">
-        <v>2.99115061759949</v>
+        <v>2.99115085601807</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="n">
-        <v>2.93228268623352</v>
+        <v>2.9322829246521</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G354" t="n">
-        <v>2.94341945648193</v>
+        <v>2.94341993331909</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03075194358826</v>
+        <v>3.03075218200684</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="n">
-        <v>3.1019115447998</v>
+        <v>3.10191178321838</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G360" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>3.11323237419128</v>
+        <v>3.11323213577271</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>3.14881253242493</v>
+        <v>3.14881229400635</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G367" t="n">
-        <v>3.10029458999634</v>
+        <v>3.10029411315918</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10029458999634</v>
+        <v>3.10029411315918</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G369" t="n">
-        <v>3.08735609054565</v>
+        <v>3.08735656738281</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352921485901</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G371" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>3.01134443283081</v>
+        <v>3.01134467124939</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="n">
-        <v>3.00972723960876</v>
+        <v>3.00972747802734</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="n">
-        <v>2.99355506896973</v>
+        <v>2.99355459213257</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G377" t="n">
-        <v>2.96929597854614</v>
+        <v>2.96929574012756</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="n">
-        <v>2.96120953559875</v>
+        <v>2.96120929718018</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="n">
-        <v>2.93048143386841</v>
+        <v>2.93048167228699</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="n">
-        <v>2.96120953559875</v>
+        <v>2.96120929718018</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>2.92724704742432</v>
+        <v>2.92724680900574</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="n">
-        <v>2.87549448013306</v>
+        <v>2.87549495697021</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328479766846</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>3.01457929611206</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="n">
-        <v>3.02266597747803</v>
+        <v>3.02266573905945</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="n">
-        <v>3.02104830741882</v>
+        <v>3.0210485458374</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>3.04207277297974</v>
+        <v>3.04207301139832</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="n">
-        <v>3.04530692100525</v>
+        <v>3.04530763626099</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="n">
-        <v>3.09705972671509</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>3.13749122619629</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G394" t="n">
-        <v>3.16175031661987</v>
+        <v>3.16175055503845</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>3.16498470306396</v>
+        <v>3.16498494148254</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="n">
-        <v>3.22482371330261</v>
+        <v>3.22482347488403</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="n">
-        <v>3.23776149749756</v>
+        <v>3.23776197433472</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22644090652466</v>
+        <v>3.22644066810608</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>3.18115758895874</v>
+        <v>3.18115735054016</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G403" t="n">
-        <v>3.12617039680481</v>
+        <v>3.12617087364197</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>3.11323237419128</v>
+        <v>3.11323213577271</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.75</v>
       </c>
       <c r="G406" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="n">
-        <v>3.09220790863037</v>
+        <v>3.09220767021179</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="n">
-        <v>3.0841212272644</v>
+        <v>3.08412146568298</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.75</v>
       </c>
       <c r="G411" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.75</v>
       </c>
       <c r="G412" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G413" t="n">
-        <v>2.98708581924438</v>
+        <v>2.98708558082581</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G415" t="n">
-        <v>3.01943135261536</v>
+        <v>3.01943111419678</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>3.11323237419128</v>
+        <v>3.11323213577271</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>3.06147980690002</v>
+        <v>3.0614800453186</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G419" t="n">
-        <v>3.04530692100525</v>
+        <v>3.04530763626099</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98708581924438</v>
+        <v>2.98708558082581</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G425" t="n">
-        <v>3.02590012550354</v>
+        <v>3.02590036392212</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G426" t="n">
-        <v>3.01457929611206</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.75</v>
       </c>
       <c r="G427" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>3.0647144317627</v>
+        <v>3.06471419334412</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G430" t="n">
-        <v>3.03883814811707</v>
+        <v>3.03883838653564</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G432" t="n">
-        <v>3.05501079559326</v>
+        <v>3.05501103401184</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>3.06956601142883</v>
+        <v>3.06956624984741</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06309747695923</v>
+        <v>3.06309723854065</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G437" t="n">
-        <v>3.07441806793213</v>
+        <v>3.07441830635071</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G438" t="n">
-        <v>3.09059071540833</v>
+        <v>3.09059047698975</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.11323237419128</v>
+        <v>3.11323213577271</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352921485901</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G442" t="n">
-        <v>3.08735609054565</v>
+        <v>3.08735656738281</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G443" t="n">
-        <v>3.11646676063538</v>
+        <v>3.11646723747253</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>3.09705972671509</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G451" t="n">
-        <v>3.03722143173218</v>
+        <v>3.03722095489502</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G453" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G456" t="n">
-        <v>3.01943135261536</v>
+        <v>3.01943111419678</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G458" t="n">
-        <v>3.05501079559326</v>
+        <v>3.05501103401184</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.75</v>
       </c>
       <c r="G462" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.75</v>
       </c>
       <c r="G463" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G465" t="n">
-        <v>2.88681530952454</v>
+        <v>2.88681554794312</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064242362976</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G467" t="n">
-        <v>2.77684164047241</v>
+        <v>2.77684140205383</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G471" t="n">
-        <v>2.84961891174316</v>
+        <v>2.84961843490601</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G472" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328479766846</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>2.87872886657715</v>
+        <v>2.87872934341431</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>2.82374215126038</v>
+        <v>2.82374238967896</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G477" t="n">
-        <v>2.78007578849792</v>
+        <v>2.7800760269165</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.76875567436218</v>
+        <v>2.7687554359436</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.73317551612854</v>
+        <v>2.73317527770996</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G484" t="n">
-        <v>2.75419998168945</v>
+        <v>2.75419974327087</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064242362976</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064242362976</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G488" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064242362976</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.91107416152954</v>
+        <v>2.9110746383667</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G490" t="n">
-        <v>2.87872886657715</v>
+        <v>2.87872934341431</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G491" t="n">
-        <v>2.90783953666687</v>
+        <v>2.90784025192261</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G492" t="n">
-        <v>2.91107416152954</v>
+        <v>2.9110746383667</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99032044410706</v>
+        <v>2.99032020568848</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G495" t="n">
-        <v>2.97576498985291</v>
+        <v>2.97576522827148</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G500" t="n">
-        <v>2.99355506896973</v>
+        <v>2.99355459213257</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G503" t="n">
-        <v>2.95959258079529</v>
+        <v>2.95959234237671</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G504" t="n">
-        <v>2.97253060340881</v>
+        <v>2.97253036499023</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G505" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G509" t="n">
-        <v>2.98870301246643</v>
+        <v>2.98870325088501</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G511" t="n">
-        <v>2.97576498985291</v>
+        <v>2.97576522827148</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>3.01296234130859</v>
+        <v>3.01296186447144</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0889732837677</v>
+        <v>3.08897352218628</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="n">
-        <v>3.0889732837677</v>
+        <v>3.08897352218628</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>3.16175031661987</v>
+        <v>3.16175055503845</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.09705972671509</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>3.11323237419128</v>
+        <v>3.11323213577271</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>3.1091890335083</v>
+        <v>3.10918927192688</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>3.12536191940308</v>
+        <v>3.1253616809845</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>3.18600916862488</v>
+        <v>3.18600940704346</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G531" t="n">
-        <v>3.15366387367249</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.75</v>
       </c>
       <c r="G533" t="n">
-        <v>3.0323691368103</v>
+        <v>3.03236889839172</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G535" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894533157349</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.9151177406311</v>
+        <v>2.91511797904968</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894533157349</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.86255621910095</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>2.81403851509094</v>
+        <v>2.81403875350952</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.86255621910095</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G546" t="n">
-        <v>3.0687575340271</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01215362548828</v>
+        <v>3.01215386390686</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.01215362548828</v>
+        <v>3.01215386390686</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G554" t="n">
-        <v>2.88681530952454</v>
+        <v>2.88681554794312</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.85851359367371</v>
+        <v>2.85851335525513</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.86255621910095</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>2.91107416152954</v>
+        <v>2.9110746383667</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.97576498985291</v>
+        <v>2.97576522827148</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.95554900169373</v>
+        <v>2.9555492401123</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G563" t="n">
-        <v>2.91107416152954</v>
+        <v>2.9110746383667</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G565" t="n">
-        <v>2.95554900169373</v>
+        <v>2.9555492401123</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>2.96363544464111</v>
+        <v>2.96363568305969</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.97980809211731</v>
+        <v>2.97980833053589</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G572" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G577" t="n">
-        <v>2.95554900169373</v>
+        <v>2.9555492401123</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G580" t="n">
-        <v>3.0687575340271</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.99193739891052</v>
+        <v>2.9919376373291</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>3.0687575340271</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>3.0647144317627</v>
+        <v>3.06471419334412</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>3.07280111312866</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>3.15366387367249</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G592" t="n">
-        <v>3.13749122619629</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G593" t="n">
-        <v>3.13749122619629</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>3.12536191940308</v>
+        <v>3.1253616809845</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G596" t="n">
-        <v>3.15366387367249</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>3.22644090652466</v>
+        <v>3.22644066810608</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G600" t="n">
-        <v>3.18196558952332</v>
+        <v>3.18196606636047</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G601" t="n">
-        <v>3.20622491836548</v>
+        <v>3.20622515678406</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G603" t="n">
-        <v>3.21431136131287</v>
+        <v>3.21431112289429</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G604" t="n">
-        <v>3.17792320251465</v>
+        <v>3.17792296409607</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>3.11727571487427</v>
+        <v>3.11727547645569</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G606" t="n">
-        <v>3.17792320251465</v>
+        <v>3.17792296409607</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G607" t="n">
-        <v>3.1091890335083</v>
+        <v>3.10918927192688</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.17490530014038</v>
+        <v>3.1749050617218</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>3.14204716682434</v>
+        <v>3.14204692840576</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>3.12151074409485</v>
+        <v>3.12151098251343</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>3.09686732292175</v>
+        <v>3.09686756134033</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>3.05579519271851</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="n">
-        <v>3.13794016838074</v>
+        <v>3.13793992996216</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18722724914551</v>
+        <v>3.18722748756409</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="n">
-        <v>3.05579519271851</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="n">
-        <v>3.00650763511658</v>
+        <v>3.00650787353516</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>3.11740398406982</v>
+        <v>3.11740374565125</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>3.11740398406982</v>
+        <v>3.11740374565125</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>3.1091890335083</v>
+        <v>3.10918927192688</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>3.0475800037384</v>
+        <v>3.04758024215698</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.75</v>
       </c>
       <c r="G629" t="n">
-        <v>3.08043837547302</v>
+        <v>3.08043813705444</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G631" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.08865261077881</v>
+        <v>3.08865284919739</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G633" t="n">
-        <v>3.1050820350647</v>
+        <v>3.10508179664612</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G634" t="n">
-        <v>3.09686732292175</v>
+        <v>3.09686756134033</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G635" t="n">
-        <v>3.01883006095886</v>
+        <v>3.01882982254028</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>3.04347324371338</v>
+        <v>3.04347348213196</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G639" t="n">
-        <v>3.09276032447815</v>
+        <v>3.09276056289673</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.75</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08043837547302</v>
+        <v>3.08043813705444</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G644" t="n">
-        <v>3.12151074409485</v>
+        <v>3.12151098251343</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>3.1461546421051</v>
+        <v>3.14615440368652</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>3.1461546421051</v>
+        <v>3.14615440368652</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>3.16669082641602</v>
+        <v>3.16669058799744</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G651" t="n">
-        <v>3.19544172286987</v>
+        <v>3.19544196128845</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>3.24062132835388</v>
+        <v>3.24062061309814</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.20776319503784</v>
+        <v>3.20776295661926</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>4</v>
       </c>
       <c r="G655" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.35151696205139</v>
+        <v>3.35151720046997</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>3.35151696205139</v>
+        <v>3.35151720046997</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>3.35973167419434</v>
+        <v>3.35973215103149</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="n">
-        <v>3.46652054786682</v>
+        <v>3.46652007102966</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G661" t="n">
-        <v>3.37616086006165</v>
+        <v>3.37616062164307</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>3.44187664985657</v>
+        <v>3.44187688827515</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.44187664985657</v>
+        <v>3.44187688827515</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="n">
-        <v>3.400803565979</v>
+        <v>3.40080428123474</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>3.3063371181488</v>
+        <v>3.30633735656738</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>3.35973167419434</v>
+        <v>3.35973215103149</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.24062132835388</v>
+        <v>3.24062061309814</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>3.24883580207825</v>
+        <v>3.24883556365967</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>3.26937198638916</v>
+        <v>3.26937222480774</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>3.20365595817566</v>
+        <v>3.20365619659424</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.24883580207825</v>
+        <v>3.24883556365967</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4</v>
       </c>
       <c r="G681" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>3.3268735408783</v>
+        <v>3.32687377929688</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.51170015335083</v>
+        <v>3.51169967651367</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>3.47473454475403</v>
+        <v>3.47473502159119</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="n">
-        <v>3.58562994003296</v>
+        <v>3.58563041687012</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>3.48294878005981</v>
+        <v>3.48294925689697</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="n">
-        <v>3.49116349220276</v>
+        <v>3.49116373062134</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54455804824829</v>
+        <v>3.54455757141113</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>3.70063400268555</v>
+        <v>3.70063304901123</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>3.64313173294067</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.60616612434387</v>
+        <v>3.60616588592529</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.71706223487854</v>
+        <v>3.71706247329712</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>3.70063400268555</v>
+        <v>3.70063304901123</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.74581336975098</v>
+        <v>3.74581384658813</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>3.75813436508179</v>
+        <v>3.75813484191895</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>3.86081647872925</v>
+        <v>3.86081624031067</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>3.93474626541138</v>
+        <v>3.93474721908569</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="n">
-        <v>3.84438681602478</v>
+        <v>3.84438729286194</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>3.73759937286377</v>
+        <v>3.73759889602661</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="n">
-        <v>3.71295499801636</v>
+        <v>3.71295475959778</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>3.7827787399292</v>
+        <v>3.78277850151062</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79509997367859</v>
+        <v>3.79510045051575</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G715" t="n">
-        <v>3.75813436508179</v>
+        <v>3.75813484191895</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>3.65545344352722</v>
+        <v>3.6554536819458</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224231719971</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G722" t="n">
-        <v>3.73759937286377</v>
+        <v>3.73759889602661</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G723" t="n">
-        <v>3.819744348526</v>
+        <v>3.81974387168884</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.86903047561646</v>
+        <v>3.86903095245361</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G725" t="n">
-        <v>3.90599656105042</v>
+        <v>3.90599632263184</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>3.9183177947998</v>
+        <v>3.91831731796265</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>3.9183177947998</v>
+        <v>3.91831731796265</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G729" t="n">
-        <v>3.79099249839783</v>
+        <v>3.79099225997925</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224231719971</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224231719971</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G735" t="n">
-        <v>3.64313173294067</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>3.58973789215088</v>
+        <v>3.5897376537323</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G738" t="n">
-        <v>3.51580691337585</v>
+        <v>3.51580739021301</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.25</v>
       </c>
       <c r="G739" t="n">
-        <v>3.49116349220276</v>
+        <v>3.49116373062134</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G740" t="n">
-        <v>3.48294878005981</v>
+        <v>3.48294925689697</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>3.45830535888672</v>
+        <v>3.45830583572388</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G742" t="n">
-        <v>3.60616612434387</v>
+        <v>3.60616588592529</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>3.62670278549194</v>
+        <v>3.62670302391052</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G745" t="n">
-        <v>3.56509447097778</v>
+        <v>3.56509375572205</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>3.73759937286377</v>
+        <v>3.73759889602661</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="n">
-        <v>3.63902425765991</v>
+        <v>3.63902449607849</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="n">
-        <v>3.62670278549194</v>
+        <v>3.62670302391052</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="n">
-        <v>3.56920146942139</v>
+        <v>3.56920123100281</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>3.64313173294067</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>3.63902425765991</v>
+        <v>3.63902449607849</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.63902425765991</v>
+        <v>3.63902449607849</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="n">
-        <v>3.6225950717926</v>
+        <v>3.62259554862976</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G759" t="n">
-        <v>3.65545344352722</v>
+        <v>3.6554536819458</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="n">
-        <v>3.63902425765991</v>
+        <v>3.63902449607849</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G764" t="n">
-        <v>3.73759937286377</v>
+        <v>3.73759889602661</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G765" t="n">
-        <v>3.72527694702148</v>
+        <v>3.72527670860291</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="n">
-        <v>3.70474052429199</v>
+        <v>3.70474100112915</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G768" t="n">
-        <v>3.65545344352722</v>
+        <v>3.6554536819458</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>3.65545344352722</v>
+        <v>3.6554536819458</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G770" t="n">
-        <v>3.65134620666504</v>
+        <v>3.6513466835022</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>3.66777539253235</v>
+        <v>3.66777563095093</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="n">
-        <v>3.63902425765991</v>
+        <v>3.63902449607849</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G773" t="n">
-        <v>3.57330870628357</v>
+        <v>3.57330846786499</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G774" t="n">
-        <v>3.51580691337585</v>
+        <v>3.51580739021301</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G779" t="n">
-        <v>3.819744348526</v>
+        <v>3.81974387168884</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="n">
-        <v>3.81152892112732</v>
+        <v>3.81152987480164</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G782" t="n">
-        <v>3.85260200500488</v>
+        <v>3.8526017665863</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>3.92242407798767</v>
+        <v>3.92242503166199</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>3.93474626541138</v>
+        <v>3.93474721908569</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5</v>
       </c>
       <c r="G788" t="n">
-        <v>4.10725164413452</v>
+        <v>4.10725069046021</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>4.14832401275635</v>
+        <v>4.14832353591919</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G792" t="n">
-        <v>4.01278448104858</v>
+        <v>4.01278495788574</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867795944214</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867795944214</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G796" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867795944214</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867795944214</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.99224829673767</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G799" t="n">
-        <v>4.01278448104858</v>
+        <v>4.01278495788574</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G802" t="n">
-        <v>3.99635553359985</v>
+        <v>3.99635601043701</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>3.99224829673767</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G804" t="n">
-        <v>3.9758198261261</v>
+        <v>3.97581934928894</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G805" t="n">
-        <v>3.99224829673767</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>4.30439901351929</v>
+        <v>4.30439853668213</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G808" t="n">
-        <v>4.42761707305908</v>
+        <v>4.42761659622192</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G809" t="n">
-        <v>4.40297365188599</v>
+        <v>4.40297317504883</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>4.48511838912964</v>
+        <v>4.4851188659668</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.3865442276001</v>
+        <v>4.38654375076294</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.48511838912964</v>
+        <v>4.4851188659668</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.52619075775146</v>
+        <v>4.52619123458862</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>4.60012197494507</v>
+        <v>4.60012149810791</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G816" t="n">
-        <v>4.60012197494507</v>
+        <v>4.60012149810791</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>4.60012197494507</v>
+        <v>4.60012149810791</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>4.56726360321045</v>
+        <v>4.56726312637329</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>4.53440475463867</v>
+        <v>4.53440570831299</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>4.34547185897827</v>
+        <v>4.34547233581543</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>4.37832927703857</v>
+        <v>4.37833023071289</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>4.50154733657837</v>
+        <v>4.50154781341553</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.5</v>
       </c>
       <c r="G829" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>5.5</v>
       </c>
       <c r="G831" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>5.5</v>
       </c>
       <c r="G832" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>5.25</v>
       </c>
       <c r="G834" t="n">
-        <v>4.31261444091797</v>
+        <v>4.31261396408081</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G835" t="n">
-        <v>4.43583154678345</v>
+        <v>4.43583106994629</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>4.48511838912964</v>
+        <v>4.4851188659668</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G837" t="n">
-        <v>4.52619075775146</v>
+        <v>4.52619123458862</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>4.65762233734131</v>
+        <v>4.65762281417847</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G839" t="n">
-        <v>4.70691013336182</v>
+        <v>4.70690965652466</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G840" t="n">
-        <v>4.64119386672974</v>
+        <v>4.64119338989258</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>4.59190702438354</v>
+        <v>4.5919075012207</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>4.48511838912964</v>
+        <v>4.4851188659668</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>4.48511838912964</v>
+        <v>4.4851188659668</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G847" t="n">
-        <v>4.44404554367065</v>
+        <v>4.44404602050781</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G850" t="n">
-        <v>4.37011480331421</v>
+        <v>4.37011528015137</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>4.3865442276001</v>
+        <v>4.38654375076294</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G852" t="n">
-        <v>4.37011480331421</v>
+        <v>4.37011528015137</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G858" t="n">
-        <v>4.2551121711731</v>
+        <v>4.25511169433594</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G866" t="n">
-        <v>4.17942762374878</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>4.22147512435913</v>
+        <v>4.22147464752197</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>4.28874969482422</v>
+        <v>4.28874921798706</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>4.36443328857422</v>
+        <v>4.36443376541138</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.26352167129517</v>
+        <v>4.26352214813232</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G877" t="n">
-        <v>4.29715871810913</v>
+        <v>4.29715919494629</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G878" t="n">
-        <v>4.35602378845215</v>
+        <v>4.35602331161499</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G882" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1415867805481</v>
+        <v>4.14158630371094</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>4.1752233505249</v>
+        <v>4.17522382736206</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487895965576</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>3.96078586578369</v>
+        <v>3.96078634262085</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G889" t="n">
-        <v>3.8977165222168</v>
+        <v>3.89771628379822</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94817280769348</v>
+        <v>3.94817185401917</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>3.86407923698425</v>
+        <v>3.86407876014709</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>3.90612626075745</v>
+        <v>3.90612578392029</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>3.90192127227783</v>
+        <v>3.90192174911499</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>3.88089776039124</v>
+        <v>3.88089728355408</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>3.90612626075745</v>
+        <v>3.90612578392029</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G899" t="n">
-        <v>3.84305620193481</v>
+        <v>3.84305572509766</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G900" t="n">
-        <v>3.86407923698425</v>
+        <v>3.86407876014709</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G902" t="n">
-        <v>4.00283288955688</v>
+        <v>4.00283241271973</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G903" t="n">
-        <v>4.0238561630249</v>
+        <v>4.02385663986206</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G904" t="n">
-        <v>4.17942762374878</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.20465612411499</v>
+        <v>4.20465564727783</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79260015487671</v>
+        <v>3.79260039329529</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G914" t="n">
-        <v>3.93555784225464</v>
+        <v>3.9355583190918</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G918" t="n">
-        <v>3.6916880607605</v>
+        <v>3.69168758392334</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>3.62441325187683</v>
+        <v>3.62441372871399</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G921" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>3.60759520530701</v>
+        <v>3.60759496688843</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.62861847877502</v>
+        <v>3.62861824035645</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G924" t="n">
-        <v>3.58657193183899</v>
+        <v>3.58657145500183</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.64123249053955</v>
+        <v>3.64123225212097</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G927" t="n">
-        <v>3.73373532295227</v>
+        <v>3.73373508453369</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.86828327178955</v>
+        <v>3.86828374862671</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G930" t="n">
-        <v>3.70430207252502</v>
+        <v>3.7043023109436</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.76316738128662</v>
+        <v>3.7631676197052</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G932" t="n">
-        <v>3.70009827613831</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70009827613831</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G940" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.25</v>
       </c>
       <c r="G941" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.25</v>
       </c>
       <c r="G942" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>3.62441325187683</v>
+        <v>3.62441372871399</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>3.64543676376343</v>
+        <v>3.64543747901917</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.76316738128662</v>
+        <v>3.7631676197052</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.70009827613831</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>3.70850658416748</v>
+        <v>3.70850682258606</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G948" t="n">
-        <v>3.56975317001343</v>
+        <v>3.56975340843201</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.25</v>
       </c>
       <c r="G949" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.59498167037964</v>
+        <v>3.5949809551239</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>3.70009827613831</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>3.54032063484192</v>
+        <v>3.5403208732605</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>3.49827432632446</v>
+        <v>3.49827408790588</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G957" t="n">
-        <v>3.56554841995239</v>
+        <v>3.56554865837097</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>3.57816243171692</v>
+        <v>3.57816290855408</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>3.64543676376343</v>
+        <v>3.64543747901917</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.60759520530701</v>
+        <v>3.60759496688843</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G964" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>3.70009827613831</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G966" t="n">
-        <v>3.88510227203369</v>
+        <v>3.88510274887085</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G971" t="n">
-        <v>3.88089776039124</v>
+        <v>3.88089728355408</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>4.01124238967896</v>
+        <v>4.0112419128418</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G976" t="n">
-        <v>4.05328893661499</v>
+        <v>4.05328845977783</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G977" t="n">
-        <v>4.15420007705688</v>
+        <v>4.15419960021973</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G978" t="n">
-        <v>4.15840482711792</v>
+        <v>4.15840578079224</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>4.33920574188232</v>
+        <v>4.33920526504517</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28874969482422</v>
+        <v>4.28874921798706</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G984" t="n">
-        <v>4.49057340621948</v>
+        <v>4.49057292938232</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>4.36443328857422</v>
+        <v>4.36443376541138</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>4.33920574188232</v>
+        <v>4.33920526504517</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898290634155</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G996" t="n">
-        <v>4.67557811737061</v>
+        <v>4.67557764053345</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G997" t="n">
-        <v>4.70921564102173</v>
+        <v>4.70921516418457</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>5.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40647983551025</v>
+        <v>4.4064793586731</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852685928345</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>5.25</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41488885879517</v>
+        <v>4.41488933563232</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852685928345</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852685928345</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.43170785903931</v>
+        <v>4.43170833587646</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.37284183502197</v>
+        <v>4.37284231185913</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.56625652313232</v>
+        <v>4.56625699996948</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.63353157043457</v>
+        <v>4.63353204727173</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852685928345</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.35602378845215</v>
+        <v>4.35602331161499</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.14579105377197</v>
+        <v>4.14579153060913</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1037" t="n">
-        <v>4.07010793685913</v>
+        <v>4.07010746002197</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.11215400695801</v>
+        <v>4.11215353012085</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.14579105377197</v>
+        <v>4.14579153060913</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.56625652313232</v>
+        <v>4.56625699996948</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.50739240646362</v>
+        <v>4.50739145278931</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898290634155</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898290634155</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487895965576</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487895965576</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.90192127227783</v>
+        <v>3.90192174911499</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.67066431045532</v>
+        <v>3.67066502571106</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59498167037964</v>
+        <v>3.5949809551239</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.75</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349197387695</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.85496163368225</v>
+        <v>2.85496187210083</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.67416167259216</v>
+        <v>2.67416143417358</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.61109161376953</v>
+        <v>2.61109137535095</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.55643081665039</v>
+        <v>2.55643129348755</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.85916614532471</v>
+        <v>2.85916638374329</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.75404977798462</v>
+        <v>2.7540500164032</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.60268211364746</v>
+        <v>2.60268235206604</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.78348278999329</v>
+        <v>2.78348255157471</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70779895782471</v>
+        <v>2.70779871940613</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.72882175445557</v>
+        <v>2.72882199287415</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.64893412590027</v>
+        <v>2.64893388748169</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.86757588386536</v>
+        <v>2.86757564544678</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.85916614532471</v>
+        <v>2.85916638374329</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.87598538398743</v>
+        <v>2.87598490715027</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.91803193092346</v>
+        <v>2.9180314540863</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.91803193092346</v>
+        <v>2.9180314540863</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.88439440727234</v>
+        <v>2.88439393043518</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.9768967628479</v>
+        <v>2.97689652442932</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.98530578613281</v>
+        <v>2.98530554771423</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848726272583</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.02735257148743</v>
+        <v>3.02735280990601</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.98530578613281</v>
+        <v>2.98530554771423</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>3.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349197387695</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.08201289176941</v>
+        <v>3.08201313018799</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.06939935684204</v>
+        <v>3.06939911842346</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.05258083343506</v>
+        <v>3.05258059501648</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349197387695</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.38895297050476</v>
+        <v>3.38895320892334</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.40577220916748</v>
+        <v>3.4057719707489</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.24599432945251</v>
+        <v>3.24599456787109</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.12826442718506</v>
+        <v>3.12826418876648</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.3090648651123</v>
+        <v>3.30906462669373</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.30486011505127</v>
+        <v>3.30485987663269</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.30065536499023</v>
+        <v>3.30065512657166</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.3090648651123</v>
+        <v>3.30906462669373</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.54032063484192</v>
+        <v>3.5403208732605</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.25</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.6788170337677</v>
+        <v>3.67881727218628</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.63553643226624</v>
+        <v>3.63553690910339</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1148" t="n">
-        <v>3.50569677352905</v>
+        <v>3.50569653511047</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.2892951965332</v>
+        <v>3.28929543495178</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.31526350975037</v>
+        <v>3.31526327133179</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.34555983543396</v>
+        <v>3.3455593585968</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1158" t="n">
-        <v>3.26765561103821</v>
+        <v>3.26765537261963</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.75</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.24601531028748</v>
+        <v>3.2460150718689</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.21139097213745</v>
+        <v>3.21139073371887</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1162" t="n">
-        <v>3.15945506095886</v>
+        <v>3.15945482254028</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1163" t="n">
-        <v>3.15945506095886</v>
+        <v>3.15945482254028</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.625</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.13781452178955</v>
+        <v>3.13781476020813</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.09886264801025</v>
+        <v>3.09886240959167</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.09020614624023</v>
+        <v>3.09020638465881</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1178" t="n">
-        <v>3.07289409637451</v>
+        <v>3.07289385795593</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1179" t="n">
-        <v>3.07289409637451</v>
+        <v>3.07289385795593</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.07289409637451</v>
+        <v>3.07289385795593</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.02528619766235</v>
+        <v>3.02528643608093</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.00364637374878</v>
+        <v>3.00364589691162</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.99066185951233</v>
+        <v>2.99066209793091</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>3.375</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.92141342163086</v>
+        <v>2.92141389846802</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.84350919723511</v>
+        <v>2.84350943565369</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.80888509750366</v>
+        <v>2.80888533592224</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.75262117385864</v>
+        <v>2.75262093544006</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.78724503517151</v>
+        <v>2.78724479675293</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.78724503517151</v>
+        <v>2.78724479675293</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.85649299621582</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.85649299621582</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.00364637374878</v>
+        <v>3.00364589691162</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.76127696037292</v>
+        <v>2.7612771987915</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.73963689804077</v>
+        <v>2.73963713645935</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.70068454742432</v>
+        <v>2.7006847858429</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.66606020927429</v>
+        <v>2.66606044769287</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.627108335495</v>
+        <v>2.62710809707642</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.57949995994568</v>
+        <v>2.57950019836426</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.56218838691711</v>
+        <v>2.56218814849854</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.49293947219849</v>
+        <v>2.49293994903564</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.51025199890137</v>
+        <v>2.51025176048279</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.49726724624634</v>
+        <v>2.4972677230835</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.51890802383423</v>
+        <v>2.51890778541565</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.85649299621582</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.89111733436584</v>
+        <v>2.89111709594727</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.93872570991516</v>
+        <v>2.93872594833374</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1241" t="n">
-        <v>3.07289409637451</v>
+        <v>3.07289385795593</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.625</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.13781452178955</v>
+        <v>3.13781476020813</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.09886264801025</v>
+        <v>3.09886240959167</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.10319042205811</v>
+        <v>3.10319066047668</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10319042205811</v>
+        <v>3.10319066047668</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12483024597168</v>
+        <v>3.12483072280884</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617469787598</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.22004723548889</v>
+        <v>3.22004699707031</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.22870302200317</v>
+        <v>3.22870326042175</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3.75</v>
       </c>
       <c r="G1254" t="n">
-        <v>3.24601531028748</v>
+        <v>3.2460150718689</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.31526350975037</v>
+        <v>3.31526327133179</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.40615200996399</v>
+        <v>3.40615177154541</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.34123134613037</v>
+        <v>3.34123158454895</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.41913604736328</v>
+        <v>3.4191358089447</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.43644785881042</v>
+        <v>3.436448097229</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.34123134613037</v>
+        <v>3.34123158454895</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.41913604736328</v>
+        <v>3.4191358089447</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.47972822189331</v>
+        <v>3.47972846031189</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.60091304779053</v>
+        <v>3.60091280937195</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.60091304779053</v>
+        <v>3.60091280937195</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>4.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.6788170337677</v>
+        <v>3.67881727218628</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.64419293403625</v>
+        <v>3.64419317245483</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.72209763526917</v>
+        <v>3.72209739685059</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.64419293403625</v>
+        <v>3.64419317245483</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.58360028266907</v>
+        <v>3.5836009979248</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.57494449615479</v>
+        <v>3.57494497299194</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.5316641330719</v>
+        <v>3.53166484832764</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.43644785881042</v>
+        <v>3.436448097229</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1295" t="n">
-        <v>3.43211984634399</v>
+        <v>3.43212008476257</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.47972822189331</v>
+        <v>3.47972846031189</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.5316641330719</v>
+        <v>3.53166484832764</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.50569677352905</v>
+        <v>3.50569653511047</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.50569677352905</v>
+        <v>3.50569653511047</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.60091304779053</v>
+        <v>3.60091280937195</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.65284943580627</v>
+        <v>3.65284895896912</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.75672197341919</v>
+        <v>3.75672149658203</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.60524129867554</v>
+        <v>3.6052405834198</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045709609985</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045709609985</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.68314504623413</v>
+        <v>3.68314552307129</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.69180130958557</v>
+        <v>3.69180083274841</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.6398651599884</v>
+        <v>3.63986539840698</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.63553643226624</v>
+        <v>3.63553690910339</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.64419293403625</v>
+        <v>3.64419317245483</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.68314504623413</v>
+        <v>3.68314552307129</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.57494449615479</v>
+        <v>3.57494497299194</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.54032063484192</v>
+        <v>3.54032111167908</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.47972822189331</v>
+        <v>3.47972846031189</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.64419293403625</v>
+        <v>3.64419317245483</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.58792853355408</v>
+        <v>3.58792877197266</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.60091304779053</v>
+        <v>3.60091280937195</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.70478534698486</v>
+        <v>3.70478558540344</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.75672197341919</v>
+        <v>3.75672149658203</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.84328246116638</v>
+        <v>3.84328198432922</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.91253018379211</v>
+        <v>3.91252970695496</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.65500020980835</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.08359384536743</v>
+        <v>4.08359432220459</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>4.07482147216797</v>
+        <v>4.07482099533081</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.94323396682739</v>
+        <v>3.94323348999023</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.9695508480072</v>
+        <v>3.96955132484436</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.00025510787964</v>
+        <v>4.0002555847168</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.90375733375549</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.86866736412048</v>
+        <v>3.86866784095764</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.10552406311035</v>
+        <v>4.10552453994751</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.10552406311035</v>
+        <v>4.10552453994751</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.06166315078735</v>
+        <v>4.0616626739502</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1388" t="n">
-        <v>4.06166315078735</v>
+        <v>4.0616626739502</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.95200657844543</v>
+        <v>3.95200610160828</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.97832345962524</v>
+        <v>3.9783239364624</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1394" t="n">
-        <v>4.10552406311035</v>
+        <v>4.10552453994751</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.14061450958252</v>
+        <v>4.14061498641968</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.14061450958252</v>
+        <v>4.14061498641968</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.84235072135925</v>
+        <v>3.84235024452209</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>4.25</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.72830748558044</v>
+        <v>3.7283079624176</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.58794832229614</v>
+        <v>3.58794856071472</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.75023913383484</v>
+        <v>3.75023889541626</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.85112261772156</v>
+        <v>3.8511221408844</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.91253018379211</v>
+        <v>3.91253066062927</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.9607789516449</v>
+        <v>3.96077847480774</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.90814399719238</v>
+        <v>3.90814352035522</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.95200657844543</v>
+        <v>3.95200610160828</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.90375733375549</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.93884778022766</v>
+        <v>3.9388473033905</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.84235072135925</v>
+        <v>3.84235024452209</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.77217078208923</v>
+        <v>3.77217054367065</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.90814399719238</v>
+        <v>3.90814352035522</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.94323396682739</v>
+        <v>3.94323348999023</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.90375733375549</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.88621234893799</v>
+        <v>3.88621282577515</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.88621234893799</v>
+        <v>3.88621282577515</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.06166315078735</v>
+        <v>4.0616626739502</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.01341342926025</v>
+        <v>4.01341390609741</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.06604957580566</v>
+        <v>4.06604862213135</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.13622903823853</v>
+        <v>4.13622856140137</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.04411745071411</v>
+        <v>4.04411697387695</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.01780033111572</v>
+        <v>4.01779985427856</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.01341342926025</v>
+        <v>4.01341390609741</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.06604957580566</v>
+        <v>4.06604862213135</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1471" t="n">
-        <v>4.14061450958252</v>
+        <v>4.14061498641968</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.14061450958252</v>
+        <v>4.14061498641968</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.20202207565308</v>
+        <v>4.20202255249023</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>5</v>
       </c>
       <c r="G1476" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.43887948989868</v>
+        <v>4.43887996673584</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.41256237030029</v>
+        <v>4.41256189346313</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>5</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1484" t="n">
-        <v>4.40378952026367</v>
+        <v>4.40378904342651</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.41256237030029</v>
+        <v>4.41256189346313</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1490" t="n">
-        <v>4.5002875328064</v>
+        <v>4.50028705596924</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.38185787200928</v>
+        <v>4.38185834884644</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>5</v>
       </c>
       <c r="G1498" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5</v>
       </c>
       <c r="G1502" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.18447780609131</v>
+        <v>4.18447732925415</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.49151468276978</v>
+        <v>4.49151515960693</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>4.78977918624878</v>
+        <v>4.78977966308594</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.94768381118774</v>
+        <v>4.94768333435059</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.91259431838989</v>
+        <v>4.91259384155273</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.03540897369385</v>
+        <v>5.03540849685669</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1525" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.16699647903442</v>
+        <v>5.16699600219727</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1534" t="n">
-        <v>5.18454122543335</v>
+        <v>5.18454170227051</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1535" t="n">
-        <v>5.18454122543335</v>
+        <v>5.18454170227051</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.08804368972778</v>
+        <v>5.08804416656494</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1537" t="n">
-        <v>5.07049942016602</v>
+        <v>5.0704984664917</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1539" t="n">
-        <v>4.96522903442383</v>
+        <v>4.96522855758667</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.98277378082275</v>
+        <v>4.98277425765991</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1543" t="n">
-        <v>4.78977918624878</v>
+        <v>4.78977966308594</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1545" t="n">
-        <v>4.78977918624878</v>
+        <v>4.78977966308594</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.64941883087158</v>
+        <v>4.6494197845459</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1547" t="n">
-        <v>4.70205450057983</v>
+        <v>4.70205402374268</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1550" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.91259431838989</v>
+        <v>4.91259384155273</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1560" t="n">
-        <v>4.78977918624878</v>
+        <v>4.78977966308594</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.64941883087158</v>
+        <v>4.6494197845459</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1563" t="n">
-        <v>4.64064645767212</v>
+        <v>4.64064693450928</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>5</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.32483673095703</v>
+        <v>4.32483720779419</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.14061450958252</v>
+        <v>4.14061498641968</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.1493878364563</v>
+        <v>4.14938735961914</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.40378952026367</v>
+        <v>4.40378904342651</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>5</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.38624477386475</v>
+        <v>4.38624429702759</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.49151468276978</v>
+        <v>4.49151515960693</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>4.80732393264771</v>
+        <v>4.80732440948486</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1589" t="n">
-        <v>5.08804368972778</v>
+        <v>5.08804416656494</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1591" t="n">
-        <v>5.19331407546997</v>
+        <v>5.19331359863281</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1593" t="n">
-        <v>5.30735635757446</v>
+        <v>5.3073558807373</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>5.19331407546997</v>
+        <v>5.19331359863281</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1598" t="n">
-        <v>5.30735635757446</v>
+        <v>5.3073558807373</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1601" t="n">
-        <v>5.5091233253479</v>
+        <v>5.50912284851074</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>5.35877418518066</v>
+        <v>5.35877466201782</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>5.68083763122559</v>
+        <v>5.68083810806274</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1616" t="n">
-        <v>5.28720474243164</v>
+        <v>5.2872052192688</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1623" t="n">
-        <v>5.77924633026123</v>
+        <v>5.77924680709839</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1628" t="n">
-        <v>5.91343975067139</v>
+        <v>5.91343927383423</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1631" t="n">
-        <v>5.78819227218628</v>
+        <v>5.78819274902344</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1636" t="n">
-        <v>5.55559206008911</v>
+        <v>5.55559158325195</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.57348346710205</v>
+        <v>5.57348394393921</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.30509805679321</v>
+        <v>5.30509757995605</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1644" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1655" t="n">
-        <v>5.10828113555908</v>
+        <v>5.10828065872192</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1662" t="n">
-        <v>4.91146469116211</v>
+        <v>4.91146421432495</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1671" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1672" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1674" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.35877418518066</v>
+        <v>5.35877466201782</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.35877418518066</v>
+        <v>5.35877466201782</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1683" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1684" t="n">
-        <v>5.10828113555908</v>
+        <v>5.10828065872192</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1685" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1689" t="n">
-        <v>5.03671169281006</v>
+        <v>5.0367112159729</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1692" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.75043344497681</v>
+        <v>4.75043296813965</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1698" t="n">
-        <v>4.7235951423645</v>
+        <v>4.72359466552734</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.65202522277832</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1701" t="n">
-        <v>4.59834718704224</v>
+        <v>4.59834766387939</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.61624050140381</v>
+        <v>4.61624002456665</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1705" t="n">
-        <v>4.74148654937744</v>
+        <v>4.7414870262146</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1706" t="n">
-        <v>4.70570182800293</v>
+        <v>4.70570230484009</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1707" t="n">
-        <v>4.65202522277832</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.65202522277832</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.62518644332886</v>
+        <v>4.6251859664917</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.57150936126709</v>
+        <v>4.57150983810425</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.59834718704224</v>
+        <v>4.59834766387939</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G1745" t="n">
-        <v>4.38811254501343</v>
+        <v>4.38811206817627</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1746" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1747" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1755" t="n">
-        <v>4.65202522277832</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.70570182800293</v>
+        <v>4.70570230484009</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1757" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1764" t="n">
-        <v>5.10828113555908</v>
+        <v>5.10828065872192</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1771" t="n">
-        <v>5.2693133354187</v>
+        <v>5.26931285858154</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1779" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.70570182800293</v>
+        <v>4.70570230484009</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.75043344497681</v>
+        <v>4.75043296813965</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1790" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1793" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1796" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.82200288772583</v>
+        <v>4.82200241088867</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1803" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1808" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.88462591171265</v>
+        <v>4.8846263885498</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1828" t="n">
-        <v>5.09038877487183</v>
+        <v>5.09038925170898</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1829" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1830" t="n">
-        <v>5.09038877487183</v>
+        <v>5.09038925170898</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.90251874923706</v>
+        <v>4.90251922607422</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1843" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1845" t="n">
-        <v>5.09933471679688</v>
+        <v>5.09933519363403</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1855" t="n">
-        <v>5.16195821762085</v>
+        <v>5.16195869445801</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1857" t="n">
-        <v>5.30509805679321</v>
+        <v>5.30509757995605</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.20668983459473</v>
+        <v>5.20668935775757</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1861" t="n">
-        <v>5.16053104400635</v>
+        <v>5.16053152084351</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.8928108215332</v>
+        <v>4.89281129837036</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1869" t="n">
-        <v>5.05898189544678</v>
+        <v>5.05898237228394</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1871" t="n">
-        <v>5.16053104400635</v>
+        <v>5.16053152084351</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1885" t="n">
-        <v>5.26207971572876</v>
+        <v>5.26208019256592</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1888" t="n">
-        <v>5.05898189544678</v>
+        <v>5.05898237228394</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1889" t="n">
-        <v>5.06821346282959</v>
+        <v>5.06821298599243</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.8928108215332</v>
+        <v>4.89281129837036</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1902" t="n">
-        <v>5.04051828384399</v>
+        <v>5.04051876068115</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1906" t="n">
-        <v>5.04051828384399</v>
+        <v>5.04051876068115</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.95743274688721</v>
+        <v>4.95743322372437</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.8928108215332</v>
+        <v>4.89281129837036</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.8004937171936</v>
+        <v>4.80049324035645</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.8004937171936</v>
+        <v>4.80049324035645</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.85588407516479</v>
+        <v>4.85588455200195</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.75433492660522</v>
+        <v>4.75433540344238</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.69894552230835</v>
+        <v>4.69894504547119</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.42199325561523</v>
+        <v>4.42199373245239</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.5235424041748</v>
+        <v>4.52354288101196</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1939" t="n">
-        <v>4.38045072555542</v>
+        <v>4.38045024871826</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.52815866470337</v>
+        <v>4.52815818786621</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1954" t="n">
-        <v>4.578932762146</v>
+        <v>4.57893228530884</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1957" t="n">
-        <v>4.5235424041748</v>
+        <v>4.52354288101196</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.5235424041748</v>
+        <v>4.52354288101196</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.5235424041748</v>
+        <v>4.52354288101196</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.5235424041748</v>
+        <v>4.52354288101196</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.578932762146</v>
+        <v>4.57893228530884</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1967" t="n">
-        <v>4.50507926940918</v>
+        <v>4.50507879257202</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.38045072555542</v>
+        <v>4.38045024871826</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.50507926940918</v>
+        <v>4.50507879257202</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1979" t="n">
-        <v>4.32044410705566</v>
+        <v>4.32044458389282</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G1983" t="n">
-        <v>4.38045072555542</v>
+        <v>4.38045024871826</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1984" t="n">
-        <v>4.32044410705566</v>
+        <v>4.32044458389282</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1996" t="n">
-        <v>4.14504194259644</v>
+        <v>4.14504146575928</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1997" t="n">
-        <v>4.02502918243408</v>
+        <v>4.02502965927124</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.96963953971863</v>
+        <v>3.96963906288147</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.02041387557983</v>
+        <v>4.02041339874268</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.96963953971863</v>
+        <v>3.96963906288147</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>4.25</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.92348027229309</v>
+        <v>3.92348074913025</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.9142484664917</v>
+        <v>3.91424822807312</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.02502918243408</v>
+        <v>4.02502965927124</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.09426736831665</v>
+        <v>4.09426689147949</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.17735290527344</v>
+        <v>4.1773533821106</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.26505422592163</v>
+        <v>4.26505374908447</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.26505422592163</v>
+        <v>4.26505374908447</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>4.90500020980835</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.52815866470337</v>
+        <v>4.52815818786621</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.17735290527344</v>
+        <v>4.1773533821106</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.26505422592163</v>
+        <v>4.26505374908447</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.14504194259644</v>
+        <v>4.14504146575928</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.11273097991943</v>
+        <v>4.11273050308228</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2073" t="n">
-        <v>3.93732786178589</v>
+        <v>3.93732810020447</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.02502918243408</v>
+        <v>4.02502965927124</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.06195640563965</v>
+        <v>4.06195592880249</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.02041387557983</v>
+        <v>4.02041339874268</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.02502918243408</v>
+        <v>4.02502965927124</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G2079" t="n">
-        <v>3.84501099586487</v>
+        <v>3.84501075744629</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.02502918243408</v>
+        <v>4.02502965927124</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2084" t="n">
-        <v>3.96963953971863</v>
+        <v>3.96963906288147</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G2086" t="n">
-        <v>3.93732786178589</v>
+        <v>3.93732810020447</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>4.30499982833862</v>
       </c>
       <c r="G2088" t="n">
-        <v>3.9742546081543</v>
+        <v>3.97425508499146</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G2090" t="n">
-        <v>3.81731629371643</v>
+        <v>3.81731605529785</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2091" t="n">
-        <v>3.85885810852051</v>
+        <v>3.85885858535767</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G2099" t="n">
-        <v>3.7619252204895</v>
+        <v>3.76192498207092</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2105" t="n">
-        <v>3.64652895927429</v>
+        <v>3.64652919769287</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2106" t="n">
-        <v>3.6834557056427</v>
+        <v>3.68345594406128</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G2109" t="n">
-        <v>3.50805330276489</v>
+        <v>3.50805306434631</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -71262,7 +71262,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="D2727" t="n">
-        <v>5.55000019073486</v>
+        <v>5.53999996185303</v>
       </c>
       <c r="E2727" t="n">
         <v>5.76000022888184</v>
@@ -71274,6 +71274,32 @@
         <v>5.53999996185303</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>13075</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>5.51999998092651</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -63265,13 +63265,36 @@
         <v>5.30000019073486</v>
       </c>
       <c r="D2735" t="n">
-        <v>5.03000020980835</v>
+        <v>5</v>
       </c>
       <c r="E2735" t="n">
         <v>5.30000019073486</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>5</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>18751</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>5.28999996185303</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>5.09999990463257</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>5.28000020980835</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>10376</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>5.36999988555908</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>5.36999988555908</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>5.36999988555908</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>5.1399998664856</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>10856</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>5.07999992370605</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>5.03000020980835</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>11463</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>24589</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>5.17000007629395</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>4.94999980926514</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59127068519592</v>
+        <v>3.59127044677734</v>
       </c>
       <c r="H2" t="n">
         <v>72929</v>
@@ -485,7 +485,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G4" t="n">
-        <v>3.51420450210571</v>
+        <v>3.51420378684998</v>
       </c>
       <c r="H4" t="n">
         <v>44293</v>
@@ -514,7 +514,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3893575668335</v>
+        <v>3.38935708999634</v>
       </c>
       <c r="H5" t="n">
         <v>181917</v>
@@ -543,7 +543,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G6" t="n">
-        <v>3.34620094299316</v>
+        <v>3.34620141983032</v>
       </c>
       <c r="H6" t="n">
         <v>71336</v>
@@ -572,7 +572,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G7" t="n">
-        <v>3.28608965873718</v>
+        <v>3.28608894348145</v>
       </c>
       <c r="H7" t="n">
         <v>56010</v>
@@ -601,7 +601,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G8" t="n">
-        <v>3.37240314483643</v>
+        <v>3.372403383255</v>
       </c>
       <c r="H8" t="n">
         <v>62861</v>
@@ -659,7 +659,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G10" t="n">
-        <v>3.37856864929199</v>
+        <v>3.37856793403625</v>
       </c>
       <c r="H10" t="n">
         <v>50536</v>
@@ -717,7 +717,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G12" t="n">
-        <v>3.31229138374329</v>
+        <v>3.31229186058044</v>
       </c>
       <c r="H12" t="n">
         <v>77310</v>
@@ -775,7 +775,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05026793479919</v>
+        <v>3.05026817321777</v>
       </c>
       <c r="H14" t="n">
         <v>232026</v>
@@ -804,7 +804,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G15" t="n">
-        <v>3.17203259468079</v>
+        <v>3.17203187942505</v>
       </c>
       <c r="H15" t="n">
         <v>196273</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.22135400772095</v>
+        <v>3.22135376930237</v>
       </c>
       <c r="H16" t="n">
         <v>58469</v>
@@ -862,7 +862,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1442883014679</v>
+        <v>3.14428806304932</v>
       </c>
       <c r="H17" t="n">
         <v>52350</v>
@@ -891,7 +891,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>3.19823455810547</v>
+        <v>3.19823479652405</v>
       </c>
       <c r="H18" t="n">
         <v>61482</v>
@@ -920,7 +920,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G19" t="n">
-        <v>3.12579250335693</v>
+        <v>3.12579298019409</v>
       </c>
       <c r="H19" t="n">
         <v>16969</v>
@@ -978,7 +978,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15970087051392</v>
+        <v>3.15970134735107</v>
       </c>
       <c r="H21" t="n">
         <v>25718</v>
@@ -1007,7 +1007,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09959006309509</v>
+        <v>3.09958958625793</v>
       </c>
       <c r="H22" t="n">
         <v>45339</v>
@@ -1065,7 +1065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>3.00556993484497</v>
+        <v>3.00556945800781</v>
       </c>
       <c r="H24" t="n">
         <v>130754</v>
@@ -1123,7 +1123,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9855329990387</v>
+        <v>2.98553276062012</v>
       </c>
       <c r="H26" t="n">
         <v>72543</v>
@@ -1181,7 +1181,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85143804550171</v>
+        <v>2.85143828392029</v>
       </c>
       <c r="H28" t="n">
         <v>67495</v>
@@ -1210,7 +1210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.77437233924866</v>
+        <v>2.77437162399292</v>
       </c>
       <c r="H29" t="n">
         <v>80936</v>
@@ -1268,7 +1268,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G31" t="n">
-        <v>2.69422340393066</v>
+        <v>2.69422316551208</v>
       </c>
       <c r="H31" t="n">
         <v>107730</v>
@@ -1326,7 +1326,7 @@
         <v>3.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.69730639457703</v>
+        <v>2.69730615615845</v>
       </c>
       <c r="H33" t="n">
         <v>38029</v>
@@ -1355,7 +1355,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85143804550171</v>
+        <v>2.85143828392029</v>
       </c>
       <c r="H34" t="n">
         <v>57855</v>
@@ -1384,7 +1384,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83294177055359</v>
+        <v>2.83294224739075</v>
       </c>
       <c r="H35" t="n">
         <v>30597</v>
@@ -1442,7 +1442,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91925621032715</v>
+        <v>2.91925573348999</v>
       </c>
       <c r="H37" t="n">
         <v>20925</v>
@@ -1471,7 +1471,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G38" t="n">
-        <v>2.89921879768372</v>
+        <v>2.89921855926514</v>
       </c>
       <c r="H38" t="n">
         <v>57547</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.85143804550171</v>
+        <v>2.85143828392029</v>
       </c>
       <c r="H39" t="n">
         <v>25330</v>
@@ -1529,7 +1529,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.85143804550171</v>
+        <v>2.85143828392029</v>
       </c>
       <c r="H40" t="n">
         <v>31248</v>
@@ -1616,7 +1616,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.04410243034363</v>
+        <v>3.04410314559937</v>
       </c>
       <c r="H43" t="n">
         <v>31054</v>
@@ -1645,7 +1645,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G44" t="n">
-        <v>3.00402855873108</v>
+        <v>3.00402808189392</v>
       </c>
       <c r="H44" t="n">
         <v>22788</v>
@@ -1674,7 +1674,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G45" t="n">
-        <v>2.90075993537903</v>
+        <v>2.90076017379761</v>
       </c>
       <c r="H45" t="n">
         <v>67040</v>
@@ -1703,7 +1703,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>2.92850351333618</v>
+        <v>2.92850399017334</v>
       </c>
       <c r="H46" t="n">
         <v>57615</v>
@@ -1732,7 +1732,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G47" t="n">
-        <v>2.94391679763794</v>
+        <v>2.94391703605652</v>
       </c>
       <c r="H47" t="n">
         <v>29987</v>
@@ -1819,7 +1819,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>3.05180931091309</v>
+        <v>3.05180907249451</v>
       </c>
       <c r="H50" t="n">
         <v>43916</v>
@@ -1848,7 +1848,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>3.11346173286438</v>
+        <v>3.11346197128296</v>
       </c>
       <c r="H51" t="n">
         <v>32052</v>
@@ -1906,7 +1906,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>3.11346173286438</v>
+        <v>3.11346197128296</v>
       </c>
       <c r="H53" t="n">
         <v>14628</v>
@@ -1964,7 +1964,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G55" t="n">
-        <v>3.07030487060547</v>
+        <v>3.07030510902405</v>
       </c>
       <c r="H55" t="n">
         <v>14032</v>
@@ -1993,7 +1993,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.1442883014679</v>
+        <v>3.14428806304932</v>
       </c>
       <c r="H56" t="n">
         <v>126601</v>
@@ -2022,7 +2022,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G57" t="n">
-        <v>3.22135400772095</v>
+        <v>3.22135376930237</v>
       </c>
       <c r="H57" t="n">
         <v>62497</v>
@@ -2080,7 +2080,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>3.26759362220764</v>
+        <v>3.26759314537048</v>
       </c>
       <c r="H59" t="n">
         <v>68882</v>
@@ -2109,7 +2109,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.23676657676697</v>
+        <v>3.23676729202271</v>
       </c>
       <c r="H60" t="n">
         <v>54892</v>
@@ -2138,7 +2138,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17511391639709</v>
+        <v>3.17511439323425</v>
       </c>
       <c r="H61" t="n">
         <v>11417</v>
@@ -2167,7 +2167,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>3.17357301712036</v>
+        <v>3.17357325553894</v>
       </c>
       <c r="H62" t="n">
         <v>15210</v>
@@ -2196,7 +2196,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>3.1442883014679</v>
+        <v>3.14428806304932</v>
       </c>
       <c r="H63" t="n">
         <v>22488</v>
@@ -2225,7 +2225,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05951571464539</v>
+        <v>3.05951595306396</v>
       </c>
       <c r="H64" t="n">
         <v>70519</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.12887477874756</v>
+        <v>3.12887501716614</v>
       </c>
       <c r="H65" t="n">
         <v>34918</v>
@@ -2283,7 +2283,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G66" t="n">
-        <v>3.13504004478455</v>
+        <v>3.13504028320312</v>
       </c>
       <c r="H66" t="n">
         <v>37530</v>
@@ -2312,7 +2312,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G67" t="n">
-        <v>3.03793692588806</v>
+        <v>3.03793740272522</v>
       </c>
       <c r="H67" t="n">
         <v>20927</v>
@@ -2341,7 +2341,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G68" t="n">
-        <v>3.04718518257141</v>
+        <v>3.04718494415283</v>
       </c>
       <c r="H68" t="n">
         <v>20107</v>
@@ -2370,7 +2370,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G69" t="n">
-        <v>3.0749294757843</v>
+        <v>3.07492852210999</v>
       </c>
       <c r="H69" t="n">
         <v>21306</v>
@@ -2457,7 +2457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G72" t="n">
-        <v>2.8976776599884</v>
+        <v>2.89767742156982</v>
       </c>
       <c r="H72" t="n">
         <v>32000</v>
@@ -2515,7 +2515,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>2.90538430213928</v>
+        <v>2.90538382530212</v>
       </c>
       <c r="H74" t="n">
         <v>47297</v>
@@ -2544,7 +2544,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80211544036865</v>
+        <v>2.80211567878723</v>
       </c>
       <c r="H75" t="n">
         <v>55881</v>
@@ -2573,7 +2573,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>2.81290507316589</v>
+        <v>2.81290483474731</v>
       </c>
       <c r="H76" t="n">
         <v>95558</v>
@@ -2631,7 +2631,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G78" t="n">
-        <v>2.92233872413635</v>
+        <v>2.92233848571777</v>
       </c>
       <c r="H78" t="n">
         <v>48703</v>
@@ -2660,7 +2660,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.93775129318237</v>
+        <v>2.93775177001953</v>
       </c>
       <c r="H79" t="n">
         <v>15380</v>
@@ -2689,7 +2689,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G80" t="n">
-        <v>2.95162343978882</v>
+        <v>2.9516236782074</v>
       </c>
       <c r="H80" t="n">
         <v>20848</v>
@@ -2747,7 +2747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85914444923401</v>
+        <v>2.85914421081543</v>
       </c>
       <c r="H82" t="n">
         <v>23339</v>
@@ -2776,7 +2776,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>2.79749178886414</v>
+        <v>2.79749155044556</v>
       </c>
       <c r="H83" t="n">
         <v>43312</v>
@@ -2805,7 +2805,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G84" t="n">
-        <v>2.75433444976807</v>
+        <v>2.75433492660522</v>
       </c>
       <c r="H84" t="n">
         <v>21266</v>
@@ -2834,7 +2834,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G85" t="n">
-        <v>2.75433444976807</v>
+        <v>2.75433492660522</v>
       </c>
       <c r="H85" t="n">
         <v>24473</v>
@@ -2863,7 +2863,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.78053712844849</v>
+        <v>2.78053760528564</v>
       </c>
       <c r="H86" t="n">
         <v>36406</v>
@@ -2892,7 +2892,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>2.74200415611267</v>
+        <v>2.74200439453125</v>
       </c>
       <c r="H87" t="n">
         <v>25791</v>
@@ -2921,7 +2921,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67110347747803</v>
+        <v>2.67110371589661</v>
       </c>
       <c r="H88" t="n">
         <v>11008</v>
@@ -2950,7 +2950,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59557938575745</v>
+        <v>2.59557914733887</v>
       </c>
       <c r="H89" t="n">
         <v>60448</v>
@@ -2979,7 +2979,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G90" t="n">
-        <v>2.62486410140991</v>
+        <v>2.62486386299133</v>
       </c>
       <c r="H90" t="n">
         <v>31513</v>
@@ -3008,7 +3008,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>2.65723204612732</v>
+        <v>2.65723180770874</v>
       </c>
       <c r="H91" t="n">
         <v>18592</v>
@@ -3037,7 +3037,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.70501303672791</v>
+        <v>2.70501255989075</v>
       </c>
       <c r="H92" t="n">
         <v>35213</v>
@@ -3095,7 +3095,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G94" t="n">
-        <v>2.66647958755493</v>
+        <v>2.66647934913635</v>
       </c>
       <c r="H94" t="n">
         <v>45599</v>
@@ -3124,7 +3124,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>2.53546738624573</v>
+        <v>2.53546786308289</v>
       </c>
       <c r="H95" t="n">
         <v>173451</v>
@@ -3153,7 +3153,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48152160644531</v>
+        <v>2.48152184486389</v>
       </c>
       <c r="H96" t="n">
         <v>102059</v>
@@ -3211,7 +3211,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.42757558822632</v>
+        <v>2.4275758266449</v>
       </c>
       <c r="H98" t="n">
         <v>26401</v>
@@ -3240,7 +3240,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>2.46610832214355</v>
+        <v>2.46610879898071</v>
       </c>
       <c r="H99" t="n">
         <v>80928</v>
@@ -3443,7 +3443,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G106" t="n">
-        <v>2.52656769752502</v>
+        <v>2.52656745910645</v>
       </c>
       <c r="H106" t="n">
         <v>37323</v>
@@ -3472,7 +3472,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G107" t="n">
-        <v>2.52656769752502</v>
+        <v>2.52656745910645</v>
       </c>
       <c r="H107" t="n">
         <v>41652</v>
@@ -3501,7 +3501,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G108" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H108" t="n">
         <v>16496</v>
@@ -3559,7 +3559,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.76045083999634</v>
+        <v>2.76045036315918</v>
       </c>
       <c r="H110" t="n">
         <v>125977</v>
@@ -3588,7 +3588,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.74453973770142</v>
+        <v>2.74454021453857</v>
       </c>
       <c r="H111" t="n">
         <v>312957</v>
@@ -3617,7 +3617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H112" t="n">
         <v>290102</v>
@@ -3704,7 +3704,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.39451193809509</v>
+        <v>2.39451169967651</v>
       </c>
       <c r="H115" t="n">
         <v>82760</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.34678077697754</v>
+        <v>2.34678101539612</v>
       </c>
       <c r="H116" t="n">
         <v>57327</v>
@@ -3762,7 +3762,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.39451193809509</v>
+        <v>2.39451169967651</v>
       </c>
       <c r="H117" t="n">
         <v>48701</v>
@@ -3791,7 +3791,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.34678077697754</v>
+        <v>2.34678101539612</v>
       </c>
       <c r="H118" t="n">
         <v>55466</v>
@@ -3820,7 +3820,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>2.45019793510437</v>
+        <v>2.45019817352295</v>
       </c>
       <c r="H119" t="n">
         <v>187802</v>
@@ -3849,7 +3849,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G120" t="n">
-        <v>2.42315030097961</v>
+        <v>2.42315053939819</v>
       </c>
       <c r="H120" t="n">
         <v>40122</v>
@@ -3907,7 +3907,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406315803528</v>
       </c>
       <c r="H122" t="n">
         <v>106354</v>
@@ -3936,7 +3936,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G123" t="n">
-        <v>2.45497131347656</v>
+        <v>2.45497107505798</v>
       </c>
       <c r="H123" t="n">
         <v>154366</v>
@@ -3965,7 +3965,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>2.354736328125</v>
+        <v>2.35473585128784</v>
       </c>
       <c r="H124" t="n">
         <v>319100</v>
@@ -3994,7 +3994,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14790105819702</v>
+        <v>2.1479012966156</v>
       </c>
       <c r="H125" t="n">
         <v>176396</v>
@@ -4081,7 +4081,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G128" t="n">
-        <v>2.22586178779602</v>
+        <v>2.2258620262146</v>
       </c>
       <c r="H128" t="n">
         <v>117167</v>
@@ -4110,7 +4110,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.30700469017029</v>
+        <v>2.30700492858887</v>
       </c>
       <c r="H129" t="n">
         <v>136895</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.32291531562805</v>
+        <v>2.32291483879089</v>
       </c>
       <c r="H130" t="n">
         <v>32482</v>
@@ -4168,7 +4168,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.24336290359497</v>
+        <v>2.24336314201355</v>
       </c>
       <c r="H131" t="n">
         <v>19361</v>
@@ -4197,7 +4197,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1463098526001</v>
+        <v>2.14631009101868</v>
       </c>
       <c r="H132" t="n">
         <v>157907</v>
@@ -4226,7 +4226,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="n">
-        <v>2.17813062667847</v>
+        <v>2.17813038825989</v>
       </c>
       <c r="H133" t="n">
         <v>87599</v>
@@ -4284,7 +4284,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25609159469604</v>
+        <v>2.25609135627747</v>
       </c>
       <c r="H135" t="n">
         <v>36502</v>
@@ -4313,7 +4313,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="n">
-        <v>2.28154850006104</v>
+        <v>2.28154802322388</v>
       </c>
       <c r="H136" t="n">
         <v>119374</v>
@@ -4371,7 +4371,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>2.28313899040222</v>
+        <v>2.2831392288208</v>
       </c>
       <c r="H138" t="n">
         <v>109004</v>
@@ -4400,7 +4400,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>2.27041053771973</v>
+        <v>2.27041077613831</v>
       </c>
       <c r="H139" t="n">
         <v>22031</v>
@@ -4429,7 +4429,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="n">
-        <v>2.27041053771973</v>
+        <v>2.27041077613831</v>
       </c>
       <c r="H140" t="n">
         <v>51795</v>
@@ -4545,7 +4545,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51383948326111</v>
+        <v>2.51383972167969</v>
       </c>
       <c r="H144" t="n">
         <v>31905</v>
@@ -4574,7 +4574,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G145" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H145" t="n">
         <v>74728</v>
@@ -4632,7 +4632,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="n">
-        <v>2.77795195579529</v>
+        <v>2.77795171737671</v>
       </c>
       <c r="H147" t="n">
         <v>193727</v>
@@ -4661,7 +4661,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76045083999634</v>
+        <v>2.76045036315918</v>
       </c>
       <c r="H148" t="n">
         <v>65327</v>
@@ -4690,7 +4690,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H149" t="n">
         <v>491545</v>
@@ -4748,7 +4748,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G151" t="n">
-        <v>2.51383948326111</v>
+        <v>2.51383972167969</v>
       </c>
       <c r="H151" t="n">
         <v>124544</v>
@@ -4864,7 +4864,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179479598999</v>
       </c>
       <c r="H155" t="n">
         <v>53869</v>
@@ -4893,7 +4893,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179479598999</v>
       </c>
       <c r="H156" t="n">
         <v>14282</v>
@@ -4951,7 +4951,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G158" t="n">
-        <v>2.51383948326111</v>
+        <v>2.51383972167969</v>
       </c>
       <c r="H158" t="n">
         <v>36996</v>
@@ -5009,7 +5009,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="n">
-        <v>2.47883653640747</v>
+        <v>2.47883677482605</v>
       </c>
       <c r="H160" t="n">
         <v>74187</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406315803528</v>
       </c>
       <c r="H161" t="n">
         <v>18301</v>
@@ -5067,7 +5067,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G162" t="n">
-        <v>2.48360967636108</v>
+        <v>2.48360991477966</v>
       </c>
       <c r="H162" t="n">
         <v>17964</v>
@@ -5125,7 +5125,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406315803528</v>
       </c>
       <c r="H164" t="n">
         <v>47798</v>
@@ -5154,7 +5154,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406315803528</v>
       </c>
       <c r="H165" t="n">
         <v>44840</v>
@@ -5212,7 +5212,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G167" t="n">
-        <v>2.57429909706116</v>
+        <v>2.57429885864258</v>
       </c>
       <c r="H167" t="n">
         <v>72831</v>
@@ -5270,7 +5270,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.59020924568176</v>
+        <v>2.59020972251892</v>
       </c>
       <c r="H169" t="n">
         <v>13943</v>
@@ -5299,7 +5299,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>2.59657382965088</v>
+        <v>2.5965735912323</v>
       </c>
       <c r="H170" t="n">
         <v>50663</v>
@@ -5328,7 +5328,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225440979004</v>
       </c>
       <c r="H171" t="n">
         <v>48256</v>
@@ -5357,7 +5357,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543610572815</v>
       </c>
       <c r="H172" t="n">
         <v>51149</v>
@@ -5386,7 +5386,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="n">
-        <v>2.63475847244263</v>
+        <v>2.63475823402405</v>
       </c>
       <c r="H173" t="n">
         <v>113264</v>
@@ -5415,7 +5415,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.69839978218079</v>
+        <v>2.69840025901794</v>
       </c>
       <c r="H174" t="n">
         <v>40940</v>
@@ -5444,7 +5444,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="n">
-        <v>2.73340272903442</v>
+        <v>2.73340249061584</v>
       </c>
       <c r="H175" t="n">
         <v>109716</v>
@@ -5473,7 +5473,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73340272903442</v>
+        <v>2.73340249061584</v>
       </c>
       <c r="H176" t="n">
         <v>20242</v>
@@ -5502,7 +5502,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G177" t="n">
-        <v>2.76045083999634</v>
+        <v>2.76045036315918</v>
       </c>
       <c r="H177" t="n">
         <v>60761</v>
@@ -5531,7 +5531,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.7047643661499</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H178" t="n">
         <v>27763</v>
@@ -5589,7 +5589,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G180" t="n">
-        <v>2.5981650352478</v>
+        <v>2.59816479682922</v>
       </c>
       <c r="H180" t="n">
         <v>128255</v>
@@ -5647,7 +5647,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G182" t="n">
-        <v>2.68408036231995</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H182" t="n">
         <v>23673</v>
@@ -5705,7 +5705,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>2.64907741546631</v>
+        <v>2.64907765388489</v>
       </c>
       <c r="H184" t="n">
         <v>14160</v>
@@ -5734,7 +5734,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66976165771484</v>
+        <v>2.66976094245911</v>
       </c>
       <c r="H185" t="n">
         <v>14080</v>
@@ -5821,7 +5821,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G188" t="n">
-        <v>2.74135828018188</v>
+        <v>2.74135804176331</v>
       </c>
       <c r="H188" t="n">
         <v>34809</v>
@@ -5850,7 +5850,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>2.64907741546631</v>
+        <v>2.64907765388489</v>
       </c>
       <c r="H189" t="n">
         <v>47560</v>
@@ -5879,7 +5879,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="n">
-        <v>2.63794040679932</v>
+        <v>2.6379406452179</v>
       </c>
       <c r="H190" t="n">
         <v>53442</v>
@@ -5937,7 +5937,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.59180021286011</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H192" t="n">
         <v>29200</v>
@@ -5966,7 +5966,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>2.56952595710754</v>
+        <v>2.56952571868896</v>
       </c>
       <c r="H193" t="n">
         <v>54687</v>
@@ -6053,7 +6053,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>2.56157088279724</v>
+        <v>2.56157064437866</v>
       </c>
       <c r="H196" t="n">
         <v>30767</v>
@@ -6082,7 +6082,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G197" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H197" t="n">
         <v>55307</v>
@@ -6140,7 +6140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="n">
-        <v>2.60930156707764</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H199" t="n">
         <v>6143</v>
@@ -6169,7 +6169,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748103141785</v>
       </c>
       <c r="H200" t="n">
         <v>17873</v>
@@ -6227,7 +6227,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="n">
-        <v>2.54725122451782</v>
+        <v>2.54725170135498</v>
       </c>
       <c r="H202" t="n">
         <v>36814</v>
@@ -6285,7 +6285,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="n">
-        <v>2.62043929100037</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H204" t="n">
         <v>8159</v>
@@ -6314,7 +6314,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G205" t="n">
-        <v>2.65226030349731</v>
+        <v>2.65226006507874</v>
       </c>
       <c r="H205" t="n">
         <v>17577</v>
@@ -6343,7 +6343,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.7047643661499</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H206" t="n">
         <v>52437</v>
@@ -6401,7 +6401,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>2.6681706905365</v>
+        <v>2.66817021369934</v>
       </c>
       <c r="H208" t="n">
         <v>47680</v>
@@ -6430,7 +6430,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H209" t="n">
         <v>24860</v>
@@ -6488,7 +6488,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G211" t="n">
-        <v>2.68567156791687</v>
+        <v>2.68567132949829</v>
       </c>
       <c r="H211" t="n">
         <v>106947</v>
@@ -6517,7 +6517,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G212" t="n">
-        <v>2.68408036231995</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H212" t="n">
         <v>173832</v>
@@ -6546,7 +6546,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G213" t="n">
-        <v>2.7031729221344</v>
+        <v>2.70317316055298</v>
       </c>
       <c r="H213" t="n">
         <v>130799</v>
@@ -6575,7 +6575,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H214" t="n">
         <v>41273</v>
@@ -6604,7 +6604,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H215" t="n">
         <v>9359</v>
@@ -6633,7 +6633,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G216" t="n">
-        <v>2.64748668670654</v>
+        <v>2.6474871635437</v>
       </c>
       <c r="H216" t="n">
         <v>40967</v>
@@ -6691,7 +6691,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543610572815</v>
       </c>
       <c r="H218" t="n">
         <v>23540</v>
@@ -6720,7 +6720,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406315803528</v>
       </c>
       <c r="H219" t="n">
         <v>18537</v>
@@ -6749,7 +6749,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>2.55679750442505</v>
+        <v>2.55679726600647</v>
       </c>
       <c r="H220" t="n">
         <v>41230</v>
@@ -6778,7 +6778,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H221" t="n">
         <v>43595</v>
@@ -6836,7 +6836,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H223" t="n">
         <v>18854</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H224" t="n">
         <v>33279</v>
@@ -6923,7 +6923,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G226" t="n">
-        <v>2.56793451309204</v>
+        <v>2.56793475151062</v>
       </c>
       <c r="H226" t="n">
         <v>41172</v>
@@ -6952,7 +6952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>2.56952595710754</v>
+        <v>2.56952571868896</v>
       </c>
       <c r="H227" t="n">
         <v>32264</v>
@@ -7039,7 +7039,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G230" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H230" t="n">
         <v>15493</v>
@@ -7068,7 +7068,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="n">
-        <v>2.49952030181885</v>
+        <v>2.49952006340027</v>
       </c>
       <c r="H231" t="n">
         <v>16357</v>
@@ -7126,7 +7126,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="n">
-        <v>2.49633836746216</v>
+        <v>2.49633860588074</v>
       </c>
       <c r="H233" t="n">
         <v>28235</v>
@@ -7184,7 +7184,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>2.41519522666931</v>
+        <v>2.41519546508789</v>
       </c>
       <c r="H235" t="n">
         <v>57120</v>
@@ -7213,7 +7213,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G236" t="n">
-        <v>2.41519522666931</v>
+        <v>2.41519546508789</v>
       </c>
       <c r="H236" t="n">
         <v>18231</v>
@@ -7242,7 +7242,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>2.354736328125</v>
+        <v>2.35473585128784</v>
       </c>
       <c r="H237" t="n">
         <v>69110</v>
@@ -7271,7 +7271,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="n">
-        <v>2.4486072063446</v>
+        <v>2.44860696792603</v>
       </c>
       <c r="H238" t="n">
         <v>62898</v>
@@ -7329,7 +7329,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.56952595710754</v>
+        <v>2.56952571868896</v>
       </c>
       <c r="H240" t="n">
         <v>34467</v>
@@ -7445,7 +7445,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52975010871887</v>
+        <v>2.52974987030029</v>
       </c>
       <c r="H244" t="n">
         <v>12347</v>
@@ -7474,7 +7474,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>2.57588958740234</v>
+        <v>2.57588982582092</v>
       </c>
       <c r="H245" t="n">
         <v>38786</v>
@@ -7503,7 +7503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>2.52179455757141</v>
+        <v>2.52179479598999</v>
       </c>
       <c r="H246" t="n">
         <v>26112</v>
@@ -7532,7 +7532,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748103141785</v>
       </c>
       <c r="H247" t="n">
         <v>41148</v>
@@ -7561,7 +7561,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748103141785</v>
       </c>
       <c r="H248" t="n">
         <v>27007</v>
@@ -7590,7 +7590,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543610572815</v>
       </c>
       <c r="H249" t="n">
         <v>43074</v>
@@ -7619,7 +7619,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G250" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H250" t="n">
         <v>19353</v>
@@ -7648,7 +7648,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748103141785</v>
       </c>
       <c r="H251" t="n">
         <v>8970</v>
@@ -7677,7 +7677,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.60930156707764</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H252" t="n">
         <v>9879</v>
@@ -7735,7 +7735,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="n">
-        <v>2.61248350143433</v>
+        <v>2.61248397827148</v>
       </c>
       <c r="H254" t="n">
         <v>26246</v>
@@ -7764,7 +7764,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="n">
-        <v>2.60930156707764</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H255" t="n">
         <v>17200</v>
@@ -7822,7 +7822,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="n">
-        <v>2.666579246521</v>
+        <v>2.66657948493958</v>
       </c>
       <c r="H257" t="n">
         <v>25863</v>
@@ -7851,7 +7851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H258" t="n">
         <v>80602</v>
@@ -7880,7 +7880,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H259" t="n">
         <v>50582</v>
@@ -7909,7 +7909,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="n">
-        <v>2.7238564491272</v>
+        <v>2.72385621070862</v>
       </c>
       <c r="H260" t="n">
         <v>42845</v>
@@ -7967,7 +7967,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="n">
-        <v>2.71908354759216</v>
+        <v>2.71908330917358</v>
       </c>
       <c r="H262" t="n">
         <v>25385</v>
@@ -7996,7 +7996,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="n">
-        <v>2.64271378517151</v>
+        <v>2.64271354675293</v>
       </c>
       <c r="H263" t="n">
         <v>56966</v>
@@ -8025,7 +8025,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="n">
-        <v>2.666579246521</v>
+        <v>2.66657948493958</v>
       </c>
       <c r="H264" t="n">
         <v>9951</v>
@@ -8083,7 +8083,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H266" t="n">
         <v>13826</v>
@@ -8141,7 +8141,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="n">
-        <v>2.70635533332825</v>
+        <v>2.70635485649109</v>
       </c>
       <c r="H268" t="n">
         <v>26397</v>
@@ -8170,7 +8170,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="n">
-        <v>2.70635533332825</v>
+        <v>2.70635485649109</v>
       </c>
       <c r="H269" t="n">
         <v>22982</v>
@@ -8199,7 +8199,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G270" t="n">
-        <v>2.66021513938904</v>
+        <v>2.66021490097046</v>
       </c>
       <c r="H270" t="n">
         <v>35417</v>
@@ -8228,7 +8228,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H271" t="n">
         <v>41308</v>
@@ -8286,7 +8286,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H273" t="n">
         <v>35545</v>
@@ -8315,7 +8315,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G274" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.6252121925354</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H275" t="n">
         <v>42217</v>
@@ -8402,7 +8402,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G277" t="n">
-        <v>2.57429909706116</v>
+        <v>2.57429885864258</v>
       </c>
       <c r="H277" t="n">
         <v>41281</v>
@@ -8431,7 +8431,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543610572815</v>
       </c>
       <c r="H278" t="n">
         <v>57674</v>
@@ -8460,7 +8460,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>2.56952595710754</v>
+        <v>2.56952571868896</v>
       </c>
       <c r="H279" t="n">
         <v>36848</v>
@@ -8489,7 +8489,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="n">
-        <v>2.59180021286011</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H280" t="n">
         <v>23457</v>
@@ -8518,7 +8518,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H281" t="n">
         <v>74481</v>
@@ -8547,7 +8547,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G282" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H282" t="n">
         <v>100666</v>
@@ -8605,7 +8605,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089842796326</v>
       </c>
       <c r="H284" t="n">
         <v>57420</v>
@@ -8663,7 +8663,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="n">
-        <v>2.68726277351379</v>
+        <v>2.68726253509521</v>
       </c>
       <c r="H286" t="n">
         <v>17879</v>
@@ -8692,7 +8692,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>2.68408036231995</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H287" t="n">
         <v>42726</v>
@@ -8721,7 +8721,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>2.7047643661499</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H288" t="n">
         <v>50895</v>
@@ -8750,7 +8750,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.72067427635193</v>
+        <v>2.72067451477051</v>
       </c>
       <c r="H289" t="n">
         <v>25565</v>
@@ -8779,7 +8779,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.6888542175293</v>
+        <v>2.68885397911072</v>
       </c>
       <c r="H290" t="n">
         <v>82866</v>
@@ -8866,7 +8866,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H293" t="n">
         <v>34605</v>
@@ -8895,7 +8895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H294" t="n">
         <v>25347</v>
@@ -8953,7 +8953,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="n">
-        <v>2.62043929100037</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H296" t="n">
         <v>18722</v>
@@ -8982,7 +8982,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G297" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H297" t="n">
         <v>139127</v>
@@ -9011,7 +9011,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225440979004</v>
       </c>
       <c r="H298" t="n">
         <v>32196</v>
@@ -9040,7 +9040,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.54566025733948</v>
+        <v>2.54566073417664</v>
       </c>
       <c r="H299" t="n">
         <v>38610</v>
@@ -9069,7 +9069,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G300" t="n">
-        <v>2.54884219169617</v>
+        <v>2.54884243011475</v>
       </c>
       <c r="H300" t="n">
         <v>21232</v>
@@ -9098,7 +9098,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="n">
-        <v>2.57111740112305</v>
+        <v>2.57111692428589</v>
       </c>
       <c r="H301" t="n">
         <v>13644</v>
@@ -9185,7 +9185,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543610572815</v>
       </c>
       <c r="H304" t="n">
         <v>15734</v>
@@ -9214,7 +9214,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.60930156707764</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H305" t="n">
         <v>49411</v>
@@ -9243,7 +9243,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G306" t="n">
-        <v>2.63634920120239</v>
+        <v>2.63634967803955</v>
       </c>
       <c r="H306" t="n">
         <v>16972</v>
@@ -9272,7 +9272,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="n">
-        <v>2.63794040679932</v>
+        <v>2.6379406452179</v>
       </c>
       <c r="H307" t="n">
         <v>62268</v>
@@ -9301,7 +9301,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="n">
-        <v>2.61248350143433</v>
+        <v>2.61248397827148</v>
       </c>
       <c r="H308" t="n">
         <v>66425</v>
@@ -9359,7 +9359,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="n">
-        <v>2.62043929100037</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H310" t="n">
         <v>89281</v>
@@ -9388,7 +9388,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>2.64112234115601</v>
+        <v>2.64112257957458</v>
       </c>
       <c r="H311" t="n">
         <v>41340</v>
@@ -9417,7 +9417,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="n">
-        <v>2.6681706905365</v>
+        <v>2.66817021369934</v>
       </c>
       <c r="H312" t="n">
         <v>57404</v>
@@ -9446,7 +9446,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.74453973770142</v>
+        <v>2.74454021453857</v>
       </c>
       <c r="H313" t="n">
         <v>87119</v>
@@ -9504,7 +9504,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>2.82409143447876</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H315" t="n">
         <v>207351</v>
@@ -9649,7 +9649,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G320" t="n">
-        <v>2.90046191215515</v>
+        <v>2.90046167373657</v>
       </c>
       <c r="H320" t="n">
         <v>117232</v>
@@ -9678,7 +9678,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H321" t="n">
         <v>95397</v>
@@ -9707,7 +9707,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H322" t="n">
         <v>104092</v>
@@ -9736,7 +9736,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87182259559631</v>
+        <v>2.87182283401489</v>
       </c>
       <c r="H323" t="n">
         <v>35190</v>
@@ -9794,7 +9794,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>2.83682036399841</v>
+        <v>2.83682012557983</v>
       </c>
       <c r="H325" t="n">
         <v>158724</v>
@@ -9823,7 +9823,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="n">
-        <v>2.82409143447876</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H326" t="n">
         <v>89204</v>
@@ -9852,7 +9852,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G327" t="n">
-        <v>2.83045601844788</v>
+        <v>2.83045625686646</v>
       </c>
       <c r="H327" t="n">
         <v>60679</v>
@@ -9881,7 +9881,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G328" t="n">
-        <v>2.83045601844788</v>
+        <v>2.83045625686646</v>
       </c>
       <c r="H328" t="n">
         <v>32120</v>
@@ -9910,7 +9910,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="n">
-        <v>2.81772756576538</v>
+        <v>2.81772804260254</v>
       </c>
       <c r="H329" t="n">
         <v>82116</v>
@@ -9939,7 +9939,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>2.81454586982727</v>
+        <v>2.81454610824585</v>
       </c>
       <c r="H330" t="n">
         <v>69337</v>
@@ -9968,7 +9968,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="n">
-        <v>2.78431630134583</v>
+        <v>2.78431582450867</v>
       </c>
       <c r="H331" t="n">
         <v>81473</v>
@@ -10026,7 +10026,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G333" t="n">
-        <v>2.78908920288086</v>
+        <v>2.78908896446228</v>
       </c>
       <c r="H333" t="n">
         <v>69352</v>
@@ -10055,7 +10055,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H334" t="n">
         <v>92029</v>
@@ -10084,7 +10084,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H335" t="n">
         <v>53661</v>
@@ -10113,7 +10113,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.86386799812317</v>
+        <v>2.86386752128601</v>
       </c>
       <c r="H336" t="n">
         <v>58841</v>
@@ -10142,7 +10142,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H337" t="n">
         <v>70066</v>
@@ -10200,7 +10200,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H339" t="n">
         <v>238858</v>
@@ -10229,7 +10229,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="n">
-        <v>2.8527307510376</v>
+        <v>2.85273051261902</v>
       </c>
       <c r="H340" t="n">
         <v>51846</v>
@@ -10258,7 +10258,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>2.86386799812317</v>
+        <v>2.86386752128601</v>
       </c>
       <c r="H341" t="n">
         <v>32664</v>
@@ -10287,7 +10287,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>2.82409143447876</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H342" t="n">
         <v>125438</v>
@@ -10345,7 +10345,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H344" t="n">
         <v>89264</v>
@@ -10374,7 +10374,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.89568877220154</v>
+        <v>2.89568901062012</v>
       </c>
       <c r="H345" t="n">
         <v>92728</v>
@@ -10432,7 +10432,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="n">
-        <v>2.889324426651</v>
+        <v>2.88932466506958</v>
       </c>
       <c r="H347" t="n">
         <v>90670</v>
@@ -10461,7 +10461,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H348" t="n">
         <v>136711</v>
@@ -10519,7 +10519,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G350" t="n">
-        <v>2.98478698730469</v>
+        <v>2.98478674888611</v>
       </c>
       <c r="H350" t="n">
         <v>415056</v>
@@ -10548,7 +10548,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="n">
-        <v>2.99115109443665</v>
+        <v>2.99115085601807</v>
       </c>
       <c r="H351" t="n">
         <v>119094</v>
@@ -10606,7 +10606,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="n">
-        <v>2.91637182235718</v>
+        <v>2.91637206077576</v>
       </c>
       <c r="H353" t="n">
         <v>182186</v>
@@ -10664,7 +10664,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G355" t="n">
-        <v>3.03075170516968</v>
+        <v>3.03075194358826</v>
       </c>
       <c r="H355" t="n">
         <v>122912</v>
@@ -10838,7 +10838,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131834030151</v>
       </c>
       <c r="H361" t="n">
         <v>119655</v>
@@ -10867,7 +10867,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131834030151</v>
       </c>
       <c r="H362" t="n">
         <v>67746</v>
@@ -10896,7 +10896,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131834030151</v>
       </c>
       <c r="H363" t="n">
         <v>54604</v>
@@ -10925,7 +10925,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>3.11323189735413</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H364" t="n">
         <v>34631</v>
@@ -10983,7 +10983,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>3.14881229400635</v>
+        <v>3.14881205558777</v>
       </c>
       <c r="H366" t="n">
         <v>119264</v>
@@ -11012,7 +11012,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G367" t="n">
-        <v>3.10029435157776</v>
+        <v>3.10029411315918</v>
       </c>
       <c r="H367" t="n">
         <v>142843</v>
@@ -11041,7 +11041,7 @@
         <v>3.83400011062622</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10029435157776</v>
+        <v>3.10029411315918</v>
       </c>
       <c r="H368" t="n">
         <v>55165</v>
@@ -11070,7 +11070,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G369" t="n">
-        <v>3.08735609054565</v>
+        <v>3.08735632896423</v>
       </c>
       <c r="H369" t="n">
         <v>54287</v>
@@ -11099,7 +11099,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352849960327</v>
       </c>
       <c r="H370" t="n">
         <v>81503</v>
@@ -11157,7 +11157,7 @@
         <v>3.72399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>3.01134443283081</v>
+        <v>3.01134467124939</v>
       </c>
       <c r="H372" t="n">
         <v>94889</v>
@@ -11186,7 +11186,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="n">
-        <v>3.00972747802734</v>
+        <v>3.00972771644592</v>
       </c>
       <c r="H373" t="n">
         <v>103670</v>
@@ -11215,7 +11215,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>2.91916036605835</v>
+        <v>2.91916060447693</v>
       </c>
       <c r="H374" t="n">
         <v>188128</v>
@@ -11244,7 +11244,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="n">
-        <v>2.99355483055115</v>
+        <v>2.99355530738831</v>
       </c>
       <c r="H375" t="n">
         <v>71434</v>
@@ -11360,7 +11360,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="n">
-        <v>2.93048191070557</v>
+        <v>2.93048167228699</v>
       </c>
       <c r="H379" t="n">
         <v>42441</v>
@@ -11418,7 +11418,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>2.92724704742432</v>
+        <v>2.92724680900574</v>
       </c>
       <c r="H381" t="n">
         <v>55506</v>
@@ -11534,7 +11534,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>3.01457929611206</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H385" t="n">
         <v>107145</v>
@@ -11563,7 +11563,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="n">
-        <v>3.02266550064087</v>
+        <v>3.02266597747803</v>
       </c>
       <c r="H386" t="n">
         <v>111467</v>
@@ -11592,7 +11592,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="n">
-        <v>3.02104830741882</v>
+        <v>3.0210485458374</v>
       </c>
       <c r="H387" t="n">
         <v>12744</v>
@@ -11621,7 +11621,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>3.04207301139832</v>
+        <v>3.04207277297974</v>
       </c>
       <c r="H388" t="n">
         <v>35930</v>
@@ -11650,7 +11650,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="n">
-        <v>3.04530692100525</v>
+        <v>3.04530715942383</v>
       </c>
       <c r="H389" t="n">
         <v>32337</v>
@@ -11679,7 +11679,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>3.08088707923889</v>
+        <v>3.08088731765747</v>
       </c>
       <c r="H390" t="n">
         <v>53039</v>
@@ -11737,7 +11737,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H392" t="n">
         <v>163352</v>
@@ -11911,7 +11911,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="n">
-        <v>3.23776173591614</v>
+        <v>3.23776197433472</v>
       </c>
       <c r="H398" t="n">
         <v>119030</v>
@@ -11940,7 +11940,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>3.20218205451965</v>
+        <v>3.20218181610107</v>
       </c>
       <c r="H399" t="n">
         <v>37055</v>
@@ -11969,7 +11969,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22644138336182</v>
+        <v>3.22644090652466</v>
       </c>
       <c r="H400" t="n">
         <v>53278</v>
@@ -11998,7 +11998,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G401" t="n">
-        <v>3.15528130531311</v>
+        <v>3.15528082847595</v>
       </c>
       <c r="H401" t="n">
         <v>69013</v>
@@ -12085,7 +12085,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>3.11323189735413</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H404" t="n">
         <v>51569</v>
@@ -12114,7 +12114,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>3.19409537315369</v>
+        <v>3.19409584999084</v>
       </c>
       <c r="H405" t="n">
         <v>91838</v>
@@ -12230,7 +12230,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>3.10676336288452</v>
+        <v>3.10676312446594</v>
       </c>
       <c r="H409" t="n">
         <v>23654</v>
@@ -12259,7 +12259,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="n">
-        <v>3.08412170410156</v>
+        <v>3.08412146568298</v>
       </c>
       <c r="H410" t="n">
         <v>32920</v>
@@ -12346,7 +12346,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G413" t="n">
-        <v>2.98708558082581</v>
+        <v>2.98708581924438</v>
       </c>
       <c r="H413" t="n">
         <v>59913</v>
@@ -12433,7 +12433,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>3.11323189735413</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H416" t="n">
         <v>101420</v>
@@ -12462,7 +12462,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>3.0614800453186</v>
+        <v>3.06148052215576</v>
       </c>
       <c r="H417" t="n">
         <v>8655</v>
@@ -12520,7 +12520,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G419" t="n">
-        <v>3.04530692100525</v>
+        <v>3.04530715942383</v>
       </c>
       <c r="H419" t="n">
         <v>10728</v>
@@ -12578,7 +12578,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H421" t="n">
         <v>65985</v>
@@ -12607,7 +12607,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G422" t="n">
-        <v>2.98708558082581</v>
+        <v>2.98708581924438</v>
       </c>
       <c r="H422" t="n">
         <v>74305</v>
@@ -12636,7 +12636,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G423" t="n">
-        <v>3.02913475036621</v>
+        <v>3.02913451194763</v>
       </c>
       <c r="H423" t="n">
         <v>46896</v>
@@ -12694,7 +12694,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G425" t="n">
-        <v>3.0259006023407</v>
+        <v>3.02590036392212</v>
       </c>
       <c r="H425" t="n">
         <v>42343</v>
@@ -12723,7 +12723,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G426" t="n">
-        <v>3.01457929611206</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H426" t="n">
         <v>6672</v>
@@ -12810,7 +12810,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>3.04369020462036</v>
+        <v>3.04368996620178</v>
       </c>
       <c r="H429" t="n">
         <v>15285</v>
@@ -12926,7 +12926,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>3.06956624984741</v>
+        <v>3.06956648826599</v>
       </c>
       <c r="H433" t="n">
         <v>12085</v>
@@ -12955,7 +12955,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G434" t="n">
-        <v>3.07926988601685</v>
+        <v>3.079270362854</v>
       </c>
       <c r="H434" t="n">
         <v>22989</v>
@@ -12984,7 +12984,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06309747695923</v>
+        <v>3.06309723854065</v>
       </c>
       <c r="H435" t="n">
         <v>4662</v>
@@ -13013,7 +13013,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>3.08088707923889</v>
+        <v>3.08088731765747</v>
       </c>
       <c r="H436" t="n">
         <v>15381</v>
@@ -13071,7 +13071,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G438" t="n">
-        <v>3.0905909538269</v>
+        <v>3.09059071540833</v>
       </c>
       <c r="H438" t="n">
         <v>71142</v>
@@ -13100,7 +13100,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.11323189735413</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H439" t="n">
         <v>36940</v>
@@ -13158,7 +13158,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352849960327</v>
       </c>
       <c r="H441" t="n">
         <v>27948</v>
@@ -13187,7 +13187,7 @@
         <v>3.81800007820129</v>
       </c>
       <c r="G442" t="n">
-        <v>3.08735609054565</v>
+        <v>3.08735632896423</v>
       </c>
       <c r="H442" t="n">
         <v>15798</v>
@@ -13274,7 +13274,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G445" t="n">
-        <v>3.01619696617126</v>
+        <v>3.01619672775269</v>
       </c>
       <c r="H445" t="n">
         <v>51333</v>
@@ -13419,7 +13419,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G450" t="n">
-        <v>3.03560376167297</v>
+        <v>3.03560352325439</v>
       </c>
       <c r="H450" t="n">
         <v>23747</v>
@@ -13448,7 +13448,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G451" t="n">
-        <v>3.03722071647644</v>
+        <v>3.0372211933136</v>
       </c>
       <c r="H451" t="n">
         <v>275365</v>
@@ -13738,7 +13738,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G461" t="n">
-        <v>3.02428317070007</v>
+        <v>3.02428293228149</v>
       </c>
       <c r="H461" t="n">
         <v>43036</v>
@@ -13825,7 +13825,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H464" t="n">
         <v>73977</v>
@@ -13854,7 +13854,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G465" t="n">
-        <v>2.88681554794312</v>
+        <v>2.88681578636169</v>
       </c>
       <c r="H465" t="n">
         <v>179816</v>
@@ -13883,7 +13883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.87064242362976</v>
+        <v>2.8706431388855</v>
       </c>
       <c r="H466" t="n">
         <v>17745</v>
@@ -13912,7 +13912,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G467" t="n">
-        <v>2.77684140205383</v>
+        <v>2.77684187889099</v>
       </c>
       <c r="H467" t="n">
         <v>63791</v>
@@ -13941,7 +13941,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G468" t="n">
-        <v>2.82050728797913</v>
+        <v>2.82050752639771</v>
       </c>
       <c r="H468" t="n">
         <v>38921</v>
@@ -14028,7 +14028,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G471" t="n">
-        <v>2.84961867332458</v>
+        <v>2.84961819648743</v>
       </c>
       <c r="H471" t="n">
         <v>23748</v>
@@ -14086,7 +14086,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G473" t="n">
-        <v>2.88358116149902</v>
+        <v>2.88358092308044</v>
       </c>
       <c r="H473" t="n">
         <v>34493</v>
@@ -14115,7 +14115,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G474" t="n">
-        <v>2.87872910499573</v>
+        <v>2.87872886657715</v>
       </c>
       <c r="H474" t="n">
         <v>69047</v>
@@ -14260,7 +14260,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G479" t="n">
-        <v>2.75258231163025</v>
+        <v>2.75258255004883</v>
       </c>
       <c r="H479" t="n">
         <v>44104</v>
@@ -14347,7 +14347,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.74934840202332</v>
+        <v>2.74934792518616</v>
       </c>
       <c r="H482" t="n">
         <v>54279</v>
@@ -14405,7 +14405,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G484" t="n">
-        <v>2.75419974327087</v>
+        <v>2.75419950485229</v>
       </c>
       <c r="H484" t="n">
         <v>28027</v>
@@ -14463,7 +14463,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>2.87064242362976</v>
+        <v>2.8706431388855</v>
       </c>
       <c r="H486" t="n">
         <v>33962</v>
@@ -14492,7 +14492,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>2.87064242362976</v>
+        <v>2.8706431388855</v>
       </c>
       <c r="H487" t="n">
         <v>64425</v>
@@ -14521,7 +14521,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G488" t="n">
-        <v>2.87064242362976</v>
+        <v>2.8706431388855</v>
       </c>
       <c r="H488" t="n">
         <v>43070</v>
@@ -14550,7 +14550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.9110746383667</v>
+        <v>2.91107416152954</v>
       </c>
       <c r="H489" t="n">
         <v>28572</v>
@@ -14579,7 +14579,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G490" t="n">
-        <v>2.87872910499573</v>
+        <v>2.87872886657715</v>
       </c>
       <c r="H490" t="n">
         <v>24549</v>
@@ -14608,7 +14608,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G491" t="n">
-        <v>2.90783977508545</v>
+        <v>2.90783953666687</v>
       </c>
       <c r="H491" t="n">
         <v>93467</v>
@@ -14637,7 +14637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G492" t="n">
-        <v>2.9110746383667</v>
+        <v>2.91107416152954</v>
       </c>
       <c r="H492" t="n">
         <v>17258</v>
@@ -14666,7 +14666,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H493" t="n">
         <v>35897</v>
@@ -14695,7 +14695,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99032020568848</v>
+        <v>2.99032044410706</v>
       </c>
       <c r="H494" t="n">
         <v>72971</v>
@@ -14753,7 +14753,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H496" t="n">
         <v>27203</v>
@@ -14782,7 +14782,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H497" t="n">
         <v>17713</v>
@@ -14811,7 +14811,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H498" t="n">
         <v>4819</v>
@@ -14869,7 +14869,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G500" t="n">
-        <v>2.99355483055115</v>
+        <v>2.99355530738831</v>
       </c>
       <c r="H500" t="n">
         <v>24148</v>
@@ -14898,7 +14898,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G501" t="n">
-        <v>3.00487589836121</v>
+        <v>3.00487565994263</v>
       </c>
       <c r="H501" t="n">
         <v>23092</v>
@@ -14927,7 +14927,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.99840712547302</v>
+        <v>2.99840664863586</v>
       </c>
       <c r="H502" t="n">
         <v>19534</v>
@@ -14985,7 +14985,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G504" t="n">
-        <v>2.97253036499023</v>
+        <v>2.97253060340881</v>
       </c>
       <c r="H504" t="n">
         <v>26794</v>
@@ -15043,7 +15043,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H506" t="n">
         <v>25108</v>
@@ -15072,7 +15072,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H507" t="n">
         <v>9640</v>
@@ -15101,7 +15101,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G508" t="n">
-        <v>2.96444392204285</v>
+        <v>2.96444416046143</v>
       </c>
       <c r="H508" t="n">
         <v>14705</v>
@@ -15130,7 +15130,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G509" t="n">
-        <v>2.98870301246643</v>
+        <v>2.98870325088501</v>
       </c>
       <c r="H509" t="n">
         <v>34208</v>
@@ -15217,7 +15217,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>3.01296186447144</v>
+        <v>3.01296234130859</v>
       </c>
       <c r="H512" t="n">
         <v>26911</v>
@@ -15246,7 +15246,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G513" t="n">
-        <v>3.02428317070007</v>
+        <v>3.02428293228149</v>
       </c>
       <c r="H513" t="n">
         <v>32857</v>
@@ -15420,7 +15420,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="n">
-        <v>3.0889732837677</v>
+        <v>3.08897376060486</v>
       </c>
       <c r="H519" t="n">
         <v>42643</v>
@@ -15449,7 +15449,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="n">
-        <v>3.0889732837677</v>
+        <v>3.08897376060486</v>
       </c>
       <c r="H520" t="n">
         <v>95749</v>
@@ -15507,7 +15507,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G522" t="n">
-        <v>3.14962100982666</v>
+        <v>3.14962077140808</v>
       </c>
       <c r="H522" t="n">
         <v>45939</v>
@@ -15565,7 +15565,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>3.11323189735413</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H524" t="n">
         <v>23639</v>
@@ -15594,7 +15594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G525" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131834030151</v>
       </c>
       <c r="H525" t="n">
         <v>23093</v>
@@ -15710,7 +15710,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131834030151</v>
       </c>
       <c r="H529" t="n">
         <v>31820</v>
@@ -15768,7 +15768,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G531" t="n">
-        <v>3.15366435050964</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H531" t="n">
         <v>22393</v>
@@ -15855,7 +15855,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G534" t="n">
-        <v>3.01619696617126</v>
+        <v>3.01619672775269</v>
       </c>
       <c r="H534" t="n">
         <v>16781</v>
@@ -15913,7 +15913,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H536" t="n">
         <v>30939</v>
@@ -15942,7 +15942,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894485473633</v>
       </c>
       <c r="H537" t="n">
         <v>43032</v>
@@ -15971,7 +15971,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.9151177406311</v>
+        <v>2.91511750221252</v>
       </c>
       <c r="H538" t="n">
         <v>26193</v>
@@ -16000,7 +16000,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894485473633</v>
       </c>
       <c r="H539" t="n">
         <v>13819</v>
@@ -16029,7 +16029,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.86255645751953</v>
+        <v>2.86255621910095</v>
       </c>
       <c r="H540" t="n">
         <v>15401</v>
@@ -16087,7 +16087,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>2.81403875350952</v>
+        <v>2.81403851509094</v>
       </c>
       <c r="H542" t="n">
         <v>15169</v>
@@ -16116,7 +16116,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.86255645751953</v>
+        <v>2.86255621910095</v>
       </c>
       <c r="H543" t="n">
         <v>7373</v>
@@ -16348,7 +16348,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G551" t="n">
-        <v>2.98789405822754</v>
+        <v>2.9878945350647</v>
       </c>
       <c r="H551" t="n">
         <v>4194</v>
@@ -16377,7 +16377,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G552" t="n">
-        <v>2.97172164916992</v>
+        <v>2.9717218875885</v>
       </c>
       <c r="H552" t="n">
         <v>16110</v>
@@ -16435,7 +16435,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G554" t="n">
-        <v>2.88681554794312</v>
+        <v>2.88681578636169</v>
       </c>
       <c r="H554" t="n">
         <v>37669</v>
@@ -16493,7 +16493,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.86255645751953</v>
+        <v>2.86255621910095</v>
       </c>
       <c r="H556" t="n">
         <v>683</v>
@@ -16551,7 +16551,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>2.9110746383667</v>
+        <v>2.91107416152954</v>
       </c>
       <c r="H558" t="n">
         <v>15867</v>
@@ -16638,7 +16638,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G561" t="n">
-        <v>3.01619696617126</v>
+        <v>3.01619672775269</v>
       </c>
       <c r="H561" t="n">
         <v>1864</v>
@@ -16696,7 +16696,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G563" t="n">
-        <v>2.9110746383667</v>
+        <v>2.91107416152954</v>
       </c>
       <c r="H563" t="n">
         <v>19539</v>
@@ -16725,7 +16725,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G564" t="n">
-        <v>2.97172164916992</v>
+        <v>2.9717218875885</v>
       </c>
       <c r="H564" t="n">
         <v>5144</v>
@@ -16812,7 +16812,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>2.96363520622253</v>
+        <v>2.96363496780396</v>
       </c>
       <c r="H567" t="n">
         <v>14348</v>
@@ -16841,7 +16841,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G568" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H568" t="n">
         <v>33482</v>
@@ -16899,7 +16899,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G570" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H570" t="n">
         <v>12542</v>
@@ -16928,7 +16928,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.97980809211731</v>
+        <v>2.97980833053589</v>
       </c>
       <c r="H571" t="n">
         <v>12871</v>
@@ -16957,7 +16957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G572" t="n">
-        <v>2.95150637626648</v>
+        <v>2.9515061378479</v>
       </c>
       <c r="H572" t="n">
         <v>14977</v>
@@ -16986,7 +16986,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H573" t="n">
         <v>29946</v>
@@ -17044,7 +17044,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H575" t="n">
         <v>72092</v>
@@ -17073,7 +17073,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H576" t="n">
         <v>19331</v>
@@ -17160,7 +17160,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G579" t="n">
-        <v>3.08088707923889</v>
+        <v>3.08088731765747</v>
       </c>
       <c r="H579" t="n">
         <v>44576</v>
@@ -17276,7 +17276,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G583" t="n">
-        <v>3.08088707923889</v>
+        <v>3.08088731765747</v>
       </c>
       <c r="H583" t="n">
         <v>8012</v>
@@ -17305,7 +17305,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>3.0849301815033</v>
+        <v>3.08493041992188</v>
       </c>
       <c r="H584" t="n">
         <v>11079</v>
@@ -17479,7 +17479,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>3.15366435050964</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H590" t="n">
         <v>72655</v>
@@ -17537,7 +17537,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G592" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H592" t="n">
         <v>11711</v>
@@ -17566,7 +17566,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G593" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749170303345</v>
       </c>
       <c r="H593" t="n">
         <v>18941</v>
@@ -17624,7 +17624,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G595" t="n">
-        <v>3.0849301815033</v>
+        <v>3.08493041992188</v>
       </c>
       <c r="H595" t="n">
         <v>33246</v>
@@ -17653,7 +17653,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G596" t="n">
-        <v>3.15366435050964</v>
+        <v>3.15366411209106</v>
       </c>
       <c r="H596" t="n">
         <v>94311</v>
@@ -17682,7 +17682,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G597" t="n">
-        <v>3.19409537315369</v>
+        <v>3.19409584999084</v>
       </c>
       <c r="H597" t="n">
         <v>252878</v>
@@ -17740,7 +17740,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>3.22644138336182</v>
+        <v>3.22644090652466</v>
       </c>
       <c r="H599" t="n">
         <v>44669</v>
@@ -17798,7 +17798,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G601" t="n">
-        <v>3.20622515678406</v>
+        <v>3.20622491836548</v>
       </c>
       <c r="H601" t="n">
         <v>22587</v>
@@ -17827,7 +17827,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>3.20218205451965</v>
+        <v>3.20218181610107</v>
       </c>
       <c r="H602" t="n">
         <v>31738</v>
@@ -17914,7 +17914,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>3.11727571487427</v>
+        <v>3.11727547645569</v>
       </c>
       <c r="H605" t="n">
         <v>16652</v>
@@ -18001,7 +18001,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.17490530014038</v>
+        <v>3.1749050617218</v>
       </c>
       <c r="H608" t="n">
         <v>10245</v>
@@ -18117,7 +18117,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>3.15436863899231</v>
+        <v>3.15436887741089</v>
       </c>
       <c r="H612" t="n">
         <v>23103</v>
@@ -18204,7 +18204,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>3.05579495429993</v>
+        <v>3.05579519271851</v>
       </c>
       <c r="H615" t="n">
         <v>8889</v>
@@ -18262,7 +18262,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="n">
-        <v>3.13793992996216</v>
+        <v>3.13793969154358</v>
       </c>
       <c r="H617" t="n">
         <v>25576</v>
@@ -18291,7 +18291,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G618" t="n">
-        <v>3.18722724914551</v>
+        <v>3.18722701072693</v>
       </c>
       <c r="H618" t="n">
         <v>25648</v>
@@ -18320,7 +18320,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G619" t="n">
-        <v>3.17901206016541</v>
+        <v>3.17901229858398</v>
       </c>
       <c r="H619" t="n">
         <v>18705</v>
@@ -18349,7 +18349,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G620" t="n">
-        <v>3.03936648368835</v>
+        <v>3.0393660068512</v>
       </c>
       <c r="H620" t="n">
         <v>108303</v>
@@ -18378,7 +18378,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="n">
-        <v>3.05579495429993</v>
+        <v>3.05579519271851</v>
       </c>
       <c r="H621" t="n">
         <v>34890</v>
@@ -18407,7 +18407,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="n">
-        <v>3.00650811195374</v>
+        <v>3.00650787353516</v>
       </c>
       <c r="H622" t="n">
         <v>72011</v>
@@ -18494,7 +18494,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G625" t="n">
-        <v>3.1091890335083</v>
+        <v>3.10918927192688</v>
       </c>
       <c r="H625" t="n">
         <v>32725</v>
@@ -18523,7 +18523,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>3.04758048057556</v>
+        <v>3.04758071899414</v>
       </c>
       <c r="H626" t="n">
         <v>17502</v>
@@ -18697,7 +18697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.08865332603455</v>
+        <v>3.08865308761597</v>
       </c>
       <c r="H632" t="n">
         <v>27479</v>
@@ -18784,7 +18784,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G635" t="n">
-        <v>3.0188295841217</v>
+        <v>3.01882982254028</v>
       </c>
       <c r="H635" t="n">
         <v>12728</v>
@@ -18842,7 +18842,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>3.10097455978394</v>
+        <v>3.10097479820251</v>
       </c>
       <c r="H637" t="n">
         <v>55066</v>
@@ -18871,7 +18871,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>3.04347324371338</v>
+        <v>3.0434730052948</v>
       </c>
       <c r="H638" t="n">
         <v>11711</v>
@@ -18900,7 +18900,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G639" t="n">
-        <v>3.09276056289673</v>
+        <v>3.09276032447815</v>
       </c>
       <c r="H639" t="n">
         <v>8567</v>
@@ -19074,7 +19074,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>3.14615440368652</v>
+        <v>3.1461546421051</v>
       </c>
       <c r="H645" t="n">
         <v>21823</v>
@@ -19103,7 +19103,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>3.14615440368652</v>
+        <v>3.1461546421051</v>
       </c>
       <c r="H646" t="n">
         <v>5310</v>
@@ -19190,7 +19190,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G649" t="n">
-        <v>3.15436863899231</v>
+        <v>3.15436887741089</v>
       </c>
       <c r="H649" t="n">
         <v>17423</v>
@@ -19248,7 +19248,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G651" t="n">
-        <v>3.19544148445129</v>
+        <v>3.19544196128845</v>
       </c>
       <c r="H651" t="n">
         <v>16643</v>
@@ -19277,7 +19277,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>3.25294327735901</v>
+        <v>3.25294280052185</v>
       </c>
       <c r="H652" t="n">
         <v>25210</v>
@@ -19306,7 +19306,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>3.24062132835388</v>
+        <v>3.2406210899353</v>
       </c>
       <c r="H653" t="n">
         <v>22467</v>
@@ -19335,7 +19335,7 @@
         <v>3.90499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.20776319503784</v>
+        <v>3.20776295661926</v>
       </c>
       <c r="H654" t="n">
         <v>10186</v>
@@ -19422,7 +19422,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>3.41723275184631</v>
+        <v>3.41723299026489</v>
       </c>
       <c r="H657" t="n">
         <v>159806</v>
@@ -19480,7 +19480,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>3.35973191261292</v>
+        <v>3.35973167419434</v>
       </c>
       <c r="H659" t="n">
         <v>76457</v>
@@ -19509,7 +19509,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="n">
-        <v>3.46652030944824</v>
+        <v>3.46651983261108</v>
       </c>
       <c r="H660" t="n">
         <v>178638</v>
@@ -19567,7 +19567,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.40901851654053</v>
+        <v>3.40901899337769</v>
       </c>
       <c r="H662" t="n">
         <v>49274</v>
@@ -19596,7 +19596,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>3.44187664985657</v>
+        <v>3.44187712669373</v>
       </c>
       <c r="H663" t="n">
         <v>198699</v>
@@ -19625,7 +19625,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.44187664985657</v>
+        <v>3.44187712669373</v>
       </c>
       <c r="H664" t="n">
         <v>37222</v>
@@ -19654,7 +19654,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="n">
-        <v>3.40080380439758</v>
+        <v>3.40080404281616</v>
       </c>
       <c r="H665" t="n">
         <v>30309</v>
@@ -19683,7 +19683,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>3.38437461853027</v>
+        <v>3.38437485694885</v>
       </c>
       <c r="H666" t="n">
         <v>18534</v>
@@ -19770,7 +19770,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>3.30633759498596</v>
+        <v>3.30633735656738</v>
       </c>
       <c r="H669" t="n">
         <v>28585</v>
@@ -19799,7 +19799,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G670" t="n">
-        <v>3.39669728279114</v>
+        <v>3.39669704437256</v>
       </c>
       <c r="H670" t="n">
         <v>29687</v>
@@ -19828,7 +19828,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>3.35973191261292</v>
+        <v>3.35973167419434</v>
       </c>
       <c r="H671" t="n">
         <v>31771</v>
@@ -19857,7 +19857,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.24062132835388</v>
+        <v>3.2406210899353</v>
       </c>
       <c r="H672" t="n">
         <v>62324</v>
@@ -19886,7 +19886,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>3.23240661621094</v>
+        <v>3.23240685462952</v>
       </c>
       <c r="H673" t="n">
         <v>26792</v>
@@ -19915,7 +19915,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>3.24883556365967</v>
+        <v>3.24883604049683</v>
       </c>
       <c r="H674" t="n">
         <v>28539</v>
@@ -19973,7 +19973,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>3.26937198638916</v>
+        <v>3.26937222480774</v>
       </c>
       <c r="H676" t="n">
         <v>11711</v>
@@ -20031,7 +20031,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.24883556365967</v>
+        <v>3.24883604049683</v>
       </c>
       <c r="H678" t="n">
         <v>14565</v>
@@ -20060,7 +20060,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G679" t="n">
-        <v>3.2118706703186</v>
+        <v>3.21187090873718</v>
       </c>
       <c r="H679" t="n">
         <v>7737</v>
@@ -20147,7 +20147,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>3.32687377929688</v>
+        <v>3.32687401771545</v>
       </c>
       <c r="H682" t="n">
         <v>18076</v>
@@ -20176,7 +20176,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G683" t="n">
-        <v>3.4993782043457</v>
+        <v>3.49937844276428</v>
       </c>
       <c r="H683" t="n">
         <v>123793</v>
@@ -20205,7 +20205,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.51169967651367</v>
+        <v>3.51169991493225</v>
       </c>
       <c r="H684" t="n">
         <v>122153</v>
@@ -20234,7 +20234,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>3.47473454475403</v>
+        <v>3.47473430633545</v>
       </c>
       <c r="H685" t="n">
         <v>79386</v>
@@ -20263,7 +20263,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G686" t="n">
-        <v>3.50348567962646</v>
+        <v>3.50348520278931</v>
       </c>
       <c r="H686" t="n">
         <v>53010</v>
@@ -20292,7 +20292,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>3.50759291648865</v>
+        <v>3.50759220123291</v>
       </c>
       <c r="H687" t="n">
         <v>48640</v>
@@ -20321,7 +20321,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="n">
-        <v>3.58562994003296</v>
+        <v>3.58563041687012</v>
       </c>
       <c r="H688" t="n">
         <v>104807</v>
@@ -20350,7 +20350,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G689" t="n">
-        <v>3.48294878005981</v>
+        <v>3.48294901847839</v>
       </c>
       <c r="H689" t="n">
         <v>76703</v>
@@ -20408,7 +20408,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54455804824829</v>
+        <v>3.54455780982971</v>
       </c>
       <c r="H691" t="n">
         <v>144454</v>
@@ -20466,7 +20466,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>3.80331540107727</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H693" t="n">
         <v>166131</v>
@@ -20495,7 +20495,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313173294067</v>
       </c>
       <c r="H694" t="n">
         <v>169087</v>
@@ -20524,7 +20524,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420433998108</v>
       </c>
       <c r="H695" t="n">
         <v>99219</v>
@@ -20553,7 +20553,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.60616660118103</v>
+        <v>3.60616636276245</v>
       </c>
       <c r="H696" t="n">
         <v>72075</v>
@@ -20582,7 +20582,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.71706223487854</v>
+        <v>3.71706199645996</v>
       </c>
       <c r="H697" t="n">
         <v>63187</v>
@@ -20640,7 +20640,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.74581360816956</v>
+        <v>3.74581289291382</v>
       </c>
       <c r="H699" t="n">
         <v>33160</v>
@@ -20669,7 +20669,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G700" t="n">
-        <v>3.72116994857788</v>
+        <v>3.72117042541504</v>
       </c>
       <c r="H700" t="n">
         <v>52446</v>
@@ -20698,7 +20698,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>3.7581353187561</v>
+        <v>3.75813508033752</v>
       </c>
       <c r="H701" t="n">
         <v>61208</v>
@@ -20727,7 +20727,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>3.83617305755615</v>
+        <v>3.83617281913757</v>
       </c>
       <c r="H702" t="n">
         <v>109153</v>
@@ -20785,7 +20785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>3.86081576347351</v>
+        <v>3.86081624031067</v>
       </c>
       <c r="H704" t="n">
         <v>73408</v>
@@ -20814,7 +20814,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G705" t="n">
-        <v>3.97992634773254</v>
+        <v>3.97992587089539</v>
       </c>
       <c r="H705" t="n">
         <v>192175</v>
@@ -20843,7 +20843,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>3.93474745750427</v>
+        <v>3.93474650382996</v>
       </c>
       <c r="H706" t="n">
         <v>142470</v>
@@ -20872,7 +20872,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="n">
-        <v>3.84438705444336</v>
+        <v>3.84438681602478</v>
       </c>
       <c r="H707" t="n">
         <v>138036</v>
@@ -20901,7 +20901,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>3.80331540107727</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H708" t="n">
         <v>105500</v>
@@ -20930,7 +20930,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>3.7868857383728</v>
+        <v>3.78688526153564</v>
       </c>
       <c r="H709" t="n">
         <v>40785</v>
@@ -20959,7 +20959,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759865760803</v>
       </c>
       <c r="H710" t="n">
         <v>53135</v>
@@ -20988,7 +20988,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="n">
-        <v>3.77867102622986</v>
+        <v>3.77867126464844</v>
       </c>
       <c r="H711" t="n">
         <v>108765</v>
@@ -21017,7 +21017,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="n">
-        <v>3.71295475959778</v>
+        <v>3.71295523643494</v>
       </c>
       <c r="H712" t="n">
         <v>30961</v>
@@ -21046,7 +21046,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78277826309204</v>
+        <v>3.78277802467346</v>
       </c>
       <c r="H713" t="n">
         <v>86200</v>
@@ -21075,7 +21075,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79510021209717</v>
+        <v>3.79509997367859</v>
       </c>
       <c r="H714" t="n">
         <v>15542</v>
@@ -21104,7 +21104,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G715" t="n">
-        <v>3.7581353187561</v>
+        <v>3.75813508033752</v>
       </c>
       <c r="H715" t="n">
         <v>24403</v>
@@ -21133,7 +21133,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>3.65545344352722</v>
+        <v>3.65545392036438</v>
       </c>
       <c r="H716" t="n">
         <v>26171</v>
@@ -21162,7 +21162,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>3.77867102622986</v>
+        <v>3.77867126464844</v>
       </c>
       <c r="H717" t="n">
         <v>37906</v>
@@ -21191,7 +21191,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H718" t="n">
         <v>69227</v>
@@ -21220,7 +21220,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G719" t="n">
-        <v>3.72116994857788</v>
+        <v>3.72117042541504</v>
       </c>
       <c r="H719" t="n">
         <v>48205</v>
@@ -21249,7 +21249,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G720" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420433998108</v>
       </c>
       <c r="H720" t="n">
         <v>34708</v>
@@ -21278,7 +21278,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H721" t="n">
         <v>50647</v>
@@ -21307,7 +21307,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G722" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759865760803</v>
       </c>
       <c r="H722" t="n">
         <v>55674</v>
@@ -21336,7 +21336,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G723" t="n">
-        <v>3.81974363327026</v>
+        <v>3.81974339485168</v>
       </c>
       <c r="H723" t="n">
         <v>107484</v>
@@ -21423,7 +21423,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>3.91831707954407</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H726" t="n">
         <v>134986</v>
@@ -21452,7 +21452,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>3.91831707954407</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H727" t="n">
         <v>82607</v>
@@ -21481,7 +21481,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>3.83206534385681</v>
+        <v>3.83206510543823</v>
       </c>
       <c r="H728" t="n">
         <v>39212</v>
@@ -21510,7 +21510,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G729" t="n">
-        <v>3.79099321365356</v>
+        <v>3.79099345207214</v>
       </c>
       <c r="H729" t="n">
         <v>43175</v>
@@ -21539,7 +21539,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>3.83617305755615</v>
+        <v>3.83617281913757</v>
       </c>
       <c r="H730" t="n">
         <v>32787</v>
@@ -21597,7 +21597,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H732" t="n">
         <v>33541</v>
@@ -21626,7 +21626,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H733" t="n">
         <v>41957</v>
@@ -21655,7 +21655,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420433998108</v>
       </c>
       <c r="H734" t="n">
         <v>31529</v>
@@ -21684,7 +21684,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G735" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313173294067</v>
       </c>
       <c r="H735" t="n">
         <v>140609</v>
@@ -21713,7 +21713,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>3.58973693847656</v>
+        <v>3.58973741531372</v>
       </c>
       <c r="H736" t="n">
         <v>43867</v>
@@ -21742,7 +21742,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G737" t="n">
-        <v>3.59795260429382</v>
+        <v>3.59795212745667</v>
       </c>
       <c r="H737" t="n">
         <v>45226</v>
@@ -21771,7 +21771,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G738" t="n">
-        <v>3.51580739021301</v>
+        <v>3.51580715179443</v>
       </c>
       <c r="H738" t="n">
         <v>53675</v>
@@ -21829,7 +21829,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G740" t="n">
-        <v>3.48294878005981</v>
+        <v>3.48294901847839</v>
       </c>
       <c r="H740" t="n">
         <v>52847</v>
@@ -21858,7 +21858,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>3.4583055973053</v>
+        <v>3.45830583572388</v>
       </c>
       <c r="H741" t="n">
         <v>79422</v>
@@ -21887,7 +21887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G742" t="n">
-        <v>3.60616660118103</v>
+        <v>3.60616636276245</v>
       </c>
       <c r="H742" t="n">
         <v>62698</v>
@@ -21916,7 +21916,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>3.6267032623291</v>
+        <v>3.62670302391052</v>
       </c>
       <c r="H743" t="n">
         <v>33077</v>
@@ -21945,7 +21945,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H744" t="n">
         <v>69787</v>
@@ -22003,7 +22003,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H746" t="n">
         <v>38382</v>
@@ -22032,7 +22032,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759865760803</v>
       </c>
       <c r="H747" t="n">
         <v>117156</v>
@@ -22061,7 +22061,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.77867102622986</v>
+        <v>3.77867126464844</v>
       </c>
       <c r="H748" t="n">
         <v>166234</v>
@@ -22090,7 +22090,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="n">
-        <v>3.69652652740479</v>
+        <v>3.69652628898621</v>
       </c>
       <c r="H749" t="n">
         <v>52912</v>
@@ -22119,7 +22119,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H750" t="n">
         <v>155173</v>
@@ -22148,7 +22148,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="n">
-        <v>3.6267032623291</v>
+        <v>3.62670302391052</v>
       </c>
       <c r="H751" t="n">
         <v>10478</v>
@@ -22177,7 +22177,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="n">
-        <v>3.56920170783997</v>
+        <v>3.56920123100281</v>
       </c>
       <c r="H752" t="n">
         <v>67819</v>
@@ -22206,7 +22206,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313173294067</v>
       </c>
       <c r="H753" t="n">
         <v>47802</v>
@@ -22235,7 +22235,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H754" t="n">
         <v>101246</v>
@@ -22264,7 +22264,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H755" t="n">
         <v>21557</v>
@@ -22293,7 +22293,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="n">
-        <v>3.6225950717926</v>
+        <v>3.62259554862976</v>
       </c>
       <c r="H756" t="n">
         <v>15999</v>
@@ -22322,7 +22322,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>3.60205984115601</v>
+        <v>3.60205960273743</v>
       </c>
       <c r="H757" t="n">
         <v>20408</v>
@@ -22351,7 +22351,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H758" t="n">
         <v>12169</v>
@@ -22380,7 +22380,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G759" t="n">
-        <v>3.65545344352722</v>
+        <v>3.65545392036438</v>
       </c>
       <c r="H759" t="n">
         <v>30287</v>
@@ -22409,7 +22409,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G760" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H760" t="n">
         <v>42084</v>
@@ -22438,7 +22438,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59795260429382</v>
+        <v>3.59795212745667</v>
       </c>
       <c r="H761" t="n">
         <v>69033</v>
@@ -22467,7 +22467,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G762" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438083648682</v>
       </c>
       <c r="H762" t="n">
         <v>26366</v>
@@ -22496,7 +22496,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H763" t="n">
         <v>36511</v>
@@ -22525,7 +22525,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G764" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759865760803</v>
       </c>
       <c r="H764" t="n">
         <v>23380</v>
@@ -22583,7 +22583,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="n">
-        <v>3.70474076271057</v>
+        <v>3.70474052429199</v>
       </c>
       <c r="H766" t="n">
         <v>203274</v>
@@ -22612,7 +22612,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G767" t="n">
-        <v>3.61848878860474</v>
+        <v>3.61848855018616</v>
       </c>
       <c r="H767" t="n">
         <v>70522</v>
@@ -22641,7 +22641,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G768" t="n">
-        <v>3.65545344352722</v>
+        <v>3.65545392036438</v>
       </c>
       <c r="H768" t="n">
         <v>32231</v>
@@ -22670,7 +22670,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>3.65545344352722</v>
+        <v>3.65545392036438</v>
       </c>
       <c r="H769" t="n">
         <v>21973</v>
@@ -22728,7 +22728,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>3.66777539253235</v>
+        <v>3.66777563095093</v>
       </c>
       <c r="H771" t="n">
         <v>29437</v>
@@ -22757,7 +22757,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H772" t="n">
         <v>27013</v>
@@ -22815,7 +22815,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G774" t="n">
-        <v>3.51580739021301</v>
+        <v>3.51580715179443</v>
       </c>
       <c r="H774" t="n">
         <v>26465</v>
@@ -22844,7 +22844,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.58152294158936</v>
+        <v>3.58152318000793</v>
       </c>
       <c r="H775" t="n">
         <v>34176</v>
@@ -22873,7 +22873,7 @@
         <v>4.5</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69652652740479</v>
+        <v>3.69652628898621</v>
       </c>
       <c r="H776" t="n">
         <v>190049</v>
@@ -22902,7 +22902,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G777" t="n">
-        <v>3.80331540107727</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H777" t="n">
         <v>32135</v>
@@ -22931,7 +22931,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G778" t="n">
-        <v>3.7745635509491</v>
+        <v>3.77456402778625</v>
       </c>
       <c r="H778" t="n">
         <v>20632</v>
@@ -22960,7 +22960,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G779" t="n">
-        <v>3.81974363327026</v>
+        <v>3.81974339485168</v>
       </c>
       <c r="H779" t="n">
         <v>22277</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="n">
-        <v>3.8115291595459</v>
+        <v>3.81152844429016</v>
       </c>
       <c r="H780" t="n">
         <v>11208</v>
@@ -23018,7 +23018,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>3.77867102622986</v>
+        <v>3.77867126464844</v>
       </c>
       <c r="H781" t="n">
         <v>27055</v>
@@ -23047,7 +23047,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G782" t="n">
-        <v>3.8526017665863</v>
+        <v>3.85260128974915</v>
       </c>
       <c r="H782" t="n">
         <v>102037</v>
@@ -23105,7 +23105,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>3.93474745750427</v>
+        <v>3.93474650382996</v>
       </c>
       <c r="H784" t="n">
         <v>66709</v>
@@ -23163,7 +23163,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>4.02510643005371</v>
+        <v>4.02510595321655</v>
       </c>
       <c r="H786" t="n">
         <v>75165</v>
@@ -23221,7 +23221,7 @@
         <v>5</v>
       </c>
       <c r="G788" t="n">
-        <v>4.10725116729736</v>
+        <v>4.10725212097168</v>
       </c>
       <c r="H788" t="n">
         <v>112810</v>
@@ -23250,7 +23250,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>4.14832448959351</v>
+        <v>4.14832401275635</v>
       </c>
       <c r="H789" t="n">
         <v>91901</v>
@@ -23308,7 +23308,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G791" t="n">
-        <v>4.02510643005371</v>
+        <v>4.02510595321655</v>
       </c>
       <c r="H791" t="n">
         <v>11802</v>
@@ -23366,7 +23366,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H793" t="n">
         <v>168992</v>
@@ -23395,7 +23395,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H794" t="n">
         <v>137854</v>
@@ -23424,7 +23424,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.02510643005371</v>
+        <v>4.02510595321655</v>
       </c>
       <c r="H795" t="n">
         <v>36342</v>
@@ -23453,7 +23453,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G796" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H796" t="n">
         <v>31628</v>
@@ -23482,7 +23482,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H797" t="n">
         <v>68646</v>
@@ -23511,7 +23511,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.99224877357483</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H798" t="n">
         <v>11876</v>
@@ -23569,7 +23569,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G800" t="n">
-        <v>4.05796480178833</v>
+        <v>4.05796337127686</v>
       </c>
       <c r="H800" t="n">
         <v>40001</v>
@@ -23598,7 +23598,7 @@
         <v>4.875</v>
       </c>
       <c r="G801" t="n">
-        <v>4.00456953048706</v>
+        <v>4.00457000732422</v>
       </c>
       <c r="H801" t="n">
         <v>32198</v>
@@ -23656,7 +23656,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>3.99224877357483</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H803" t="n">
         <v>28200</v>
@@ -23714,7 +23714,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G805" t="n">
-        <v>3.99224877357483</v>
+        <v>3.99224781990051</v>
       </c>
       <c r="H805" t="n">
         <v>37583</v>
@@ -23772,7 +23772,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>4.30439949035645</v>
+        <v>4.30439901351929</v>
       </c>
       <c r="H807" t="n">
         <v>103293</v>
@@ -23888,7 +23888,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.38654470443726</v>
+        <v>4.3865442276001</v>
       </c>
       <c r="H811" t="n">
         <v>220416</v>
@@ -24120,7 +24120,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>4.58369207382202</v>
+        <v>4.58369255065918</v>
       </c>
       <c r="H819" t="n">
         <v>21467</v>
@@ -24236,7 +24236,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>4.34547138214111</v>
+        <v>4.34547185897827</v>
       </c>
       <c r="H823" t="n">
         <v>26602</v>
@@ -24265,7 +24265,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>4.37832975387573</v>
+        <v>4.37833023071289</v>
       </c>
       <c r="H824" t="n">
         <v>64270</v>
@@ -24410,7 +24410,7 @@
         <v>5.5</v>
       </c>
       <c r="G829" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H829" t="n">
         <v>26241</v>
@@ -24439,7 +24439,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G830" t="n">
-        <v>4.50976181030273</v>
+        <v>4.50976133346558</v>
       </c>
       <c r="H830" t="n">
         <v>34366</v>
@@ -24468,7 +24468,7 @@
         <v>5.5</v>
       </c>
       <c r="G831" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H831" t="n">
         <v>15842</v>
@@ -24497,7 +24497,7 @@
         <v>5.5</v>
       </c>
       <c r="G832" t="n">
-        <v>4.51797676086426</v>
+        <v>4.5179762840271</v>
       </c>
       <c r="H832" t="n">
         <v>17003</v>
@@ -24671,7 +24671,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>4.65762329101562</v>
+        <v>4.65762281417847</v>
       </c>
       <c r="H838" t="n">
         <v>101495</v>
@@ -24758,7 +24758,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>4.59190702438354</v>
+        <v>4.5919075012207</v>
       </c>
       <c r="H841" t="n">
         <v>100209</v>
@@ -24787,7 +24787,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.55904960632324</v>
+        <v>4.55904912948608</v>
       </c>
       <c r="H842" t="n">
         <v>31144</v>
@@ -24816,7 +24816,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.55904960632324</v>
+        <v>4.55904912948608</v>
       </c>
       <c r="H843" t="n">
         <v>17460</v>
@@ -24874,7 +24874,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G845" t="n">
-        <v>4.41118860244751</v>
+        <v>4.41118764877319</v>
       </c>
       <c r="H845" t="n">
         <v>32376</v>
@@ -24932,7 +24932,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G847" t="n">
-        <v>4.44404554367065</v>
+        <v>4.44404602050781</v>
       </c>
       <c r="H847" t="n">
         <v>22993</v>
@@ -24961,7 +24961,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G848" t="n">
-        <v>4.50976181030273</v>
+        <v>4.50976133346558</v>
       </c>
       <c r="H848" t="n">
         <v>59088</v>
@@ -25048,7 +25048,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>4.38654470443726</v>
+        <v>4.3865442276001</v>
       </c>
       <c r="H851" t="n">
         <v>33576</v>
@@ -25135,7 +25135,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G854" t="n">
-        <v>4.32082843780518</v>
+        <v>4.32082891464233</v>
       </c>
       <c r="H854" t="n">
         <v>47263</v>
@@ -25164,7 +25164,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G855" t="n">
-        <v>4.32082843780518</v>
+        <v>4.32082891464233</v>
       </c>
       <c r="H855" t="n">
         <v>22155</v>
@@ -25193,7 +25193,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.29618453979492</v>
+        <v>4.29618501663208</v>
       </c>
       <c r="H856" t="n">
         <v>40838</v>
@@ -25251,7 +25251,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G858" t="n">
-        <v>4.25511264801025</v>
+        <v>4.2551121711731</v>
       </c>
       <c r="H858" t="n">
         <v>12748</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H859" t="n">
         <v>42714</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H860" t="n">
         <v>14810</v>
@@ -25338,7 +25338,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G861" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329931259155</v>
       </c>
       <c r="H861" t="n">
         <v>12608</v>
@@ -25367,7 +25367,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H862" t="n">
         <v>65534</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H863" t="n">
         <v>47863</v>
@@ -25454,7 +25454,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G865" t="n">
-        <v>4.2130651473999</v>
+        <v>4.21306562423706</v>
       </c>
       <c r="H865" t="n">
         <v>52335</v>
@@ -25512,7 +25512,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23829364776611</v>
+        <v>4.23829412460327</v>
       </c>
       <c r="H867" t="n">
         <v>20899</v>
@@ -25541,7 +25541,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>4.22147512435913</v>
+        <v>4.22147464752197</v>
       </c>
       <c r="H868" t="n">
         <v>27277</v>
@@ -25628,7 +25628,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>4.34761428833008</v>
+        <v>4.34761476516724</v>
       </c>
       <c r="H871" t="n">
         <v>29518</v>
@@ -25657,7 +25657,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>4.36443281173706</v>
+        <v>4.36443328857422</v>
       </c>
       <c r="H872" t="n">
         <v>27044</v>
@@ -25686,7 +25686,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H873" t="n">
         <v>58805</v>
@@ -25715,7 +25715,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H874" t="n">
         <v>14233</v>
@@ -25773,7 +25773,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.26352167129517</v>
+        <v>4.26352119445801</v>
       </c>
       <c r="H876" t="n">
         <v>9240</v>
@@ -25802,7 +25802,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G877" t="n">
-        <v>4.29715967178345</v>
+        <v>4.29715919494629</v>
       </c>
       <c r="H877" t="n">
         <v>37216</v>
@@ -25860,7 +25860,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H879" t="n">
         <v>24765</v>
@@ -25889,7 +25889,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G880" t="n">
-        <v>4.32238674163818</v>
+        <v>4.32238626480103</v>
       </c>
       <c r="H880" t="n">
         <v>25241</v>
@@ -25918,7 +25918,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>4.32238674163818</v>
+        <v>4.32238626480103</v>
       </c>
       <c r="H881" t="n">
         <v>32823</v>
@@ -25947,7 +25947,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G882" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H882" t="n">
         <v>25721</v>
@@ -26005,7 +26005,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1415867805481</v>
+        <v>4.14158630371094</v>
       </c>
       <c r="H884" t="n">
         <v>38616</v>
@@ -26092,7 +26092,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>3.96078634262085</v>
+        <v>3.96078586578369</v>
       </c>
       <c r="H887" t="n">
         <v>207235</v>
@@ -26179,7 +26179,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94817185401917</v>
+        <v>3.94817280769348</v>
       </c>
       <c r="H890" t="n">
         <v>44423</v>
@@ -26208,7 +26208,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>3.86407876014709</v>
+        <v>3.86407899856567</v>
       </c>
       <c r="H891" t="n">
         <v>164930</v>
@@ -26266,7 +26266,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G893" t="n">
-        <v>3.90192103385925</v>
+        <v>3.90192055702209</v>
       </c>
       <c r="H893" t="n">
         <v>71211</v>
@@ -26295,7 +26295,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.85987401008606</v>
+        <v>3.85987496376038</v>
       </c>
       <c r="H894" t="n">
         <v>35895</v>
@@ -26324,7 +26324,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>3.88089776039124</v>
+        <v>3.88089847564697</v>
       </c>
       <c r="H895" t="n">
         <v>65152</v>
@@ -26353,7 +26353,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G896" t="n">
-        <v>3.8766930103302</v>
+        <v>3.87669277191162</v>
       </c>
       <c r="H896" t="n">
         <v>16496</v>
@@ -26382,7 +26382,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H897" t="n">
         <v>93698</v>
@@ -26440,7 +26440,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G899" t="n">
-        <v>3.84305620193481</v>
+        <v>3.84305644035339</v>
       </c>
       <c r="H899" t="n">
         <v>20737</v>
@@ -26469,7 +26469,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G900" t="n">
-        <v>3.86407876014709</v>
+        <v>3.86407899856567</v>
       </c>
       <c r="H900" t="n">
         <v>83258</v>
@@ -26498,7 +26498,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.9860143661499</v>
+        <v>3.98601388931274</v>
       </c>
       <c r="H901" t="n">
         <v>70917</v>
@@ -26527,7 +26527,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G902" t="n">
-        <v>4.00283336639404</v>
+        <v>4.00283288955688</v>
       </c>
       <c r="H902" t="n">
         <v>58188</v>
@@ -26614,7 +26614,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.17101907730103</v>
+        <v>4.17101955413818</v>
       </c>
       <c r="H905" t="n">
         <v>138288</v>
@@ -26643,7 +26643,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G906" t="n">
-        <v>4.2298846244812</v>
+        <v>4.22988414764404</v>
       </c>
       <c r="H906" t="n">
         <v>68752</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.20465612411499</v>
+        <v>4.20465707778931</v>
       </c>
       <c r="H907" t="n">
         <v>181979</v>
@@ -26701,7 +26701,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>3.94396805763245</v>
+        <v>3.94396710395813</v>
       </c>
       <c r="H908" t="n">
         <v>146640</v>
@@ -26759,7 +26759,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79260039329529</v>
+        <v>3.79259991645813</v>
       </c>
       <c r="H910" t="n">
         <v>75174</v>
@@ -26788,7 +26788,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>3.80521416664124</v>
+        <v>3.80521368980408</v>
       </c>
       <c r="H911" t="n">
         <v>41711</v>
@@ -26817,7 +26817,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G912" t="n">
-        <v>3.9860143661499</v>
+        <v>3.98601388931274</v>
       </c>
       <c r="H912" t="n">
         <v>85224</v>
@@ -26846,7 +26846,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91873955726624</v>
+        <v>3.91874003410339</v>
       </c>
       <c r="H913" t="n">
         <v>95858</v>
@@ -26904,7 +26904,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>3.85146546363831</v>
+        <v>3.85146498680115</v>
       </c>
       <c r="H915" t="n">
         <v>58796</v>
@@ -26933,7 +26933,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>3.80521416664124</v>
+        <v>3.80521368980408</v>
       </c>
       <c r="H916" t="n">
         <v>31648</v>
@@ -26962,7 +26962,7 @@
         <v>4.5</v>
       </c>
       <c r="G917" t="n">
-        <v>3.7841911315918</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H917" t="n">
         <v>18106</v>
@@ -26991,7 +26991,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G918" t="n">
-        <v>3.69168829917908</v>
+        <v>3.6916880607605</v>
       </c>
       <c r="H918" t="n">
         <v>28446</v>
@@ -27020,7 +27020,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G919" t="n">
-        <v>3.63702774047852</v>
+        <v>3.63702750205994</v>
       </c>
       <c r="H919" t="n">
         <v>43334</v>
@@ -27049,7 +27049,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441396713257</v>
       </c>
       <c r="H920" t="n">
         <v>59927</v>
@@ -27078,7 +27078,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G921" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H921" t="n">
         <v>22149</v>
@@ -27107,7 +27107,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>3.60759520530701</v>
+        <v>3.60759568214417</v>
       </c>
       <c r="H922" t="n">
         <v>27438</v>
@@ -27136,7 +27136,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.62861824035645</v>
+        <v>3.62861847877502</v>
       </c>
       <c r="H923" t="n">
         <v>30278</v>
@@ -27165,7 +27165,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G924" t="n">
-        <v>3.58657217025757</v>
+        <v>3.58657169342041</v>
       </c>
       <c r="H924" t="n">
         <v>24138</v>
@@ -27194,7 +27194,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G925" t="n">
-        <v>3.58236718177795</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H925" t="n">
         <v>14205</v>
@@ -27223,7 +27223,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.64123201370239</v>
+        <v>3.64123225212097</v>
       </c>
       <c r="H926" t="n">
         <v>20911</v>
@@ -27281,7 +27281,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.86828351020813</v>
+        <v>3.86828374862671</v>
       </c>
       <c r="H928" t="n">
         <v>29744</v>
@@ -27310,7 +27310,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>3.77578067779541</v>
+        <v>3.77578139305115</v>
       </c>
       <c r="H929" t="n">
         <v>66248</v>
@@ -27339,7 +27339,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G930" t="n">
-        <v>3.70430278778076</v>
+        <v>3.70430254936218</v>
       </c>
       <c r="H930" t="n">
         <v>32087</v>
@@ -27368,7 +27368,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.7631676197052</v>
+        <v>3.76316714286804</v>
       </c>
       <c r="H931" t="n">
         <v>100882</v>
@@ -27397,7 +27397,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G932" t="n">
-        <v>3.70009803771973</v>
+        <v>3.70009756088257</v>
       </c>
       <c r="H932" t="n">
         <v>23120</v>
@@ -27484,7 +27484,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G935" t="n">
-        <v>3.6538462638855</v>
+        <v>3.65384602546692</v>
       </c>
       <c r="H935" t="n">
         <v>28600</v>
@@ -27513,7 +27513,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>3.63282322883606</v>
+        <v>3.63282346725464</v>
       </c>
       <c r="H936" t="n">
         <v>17927</v>
@@ -27542,7 +27542,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>3.52350211143494</v>
+        <v>3.52350282669067</v>
       </c>
       <c r="H937" t="n">
         <v>99290</v>
@@ -27571,7 +27571,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70009803771973</v>
+        <v>3.70009756088257</v>
       </c>
       <c r="H938" t="n">
         <v>45841</v>
@@ -27600,7 +27600,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G939" t="n">
-        <v>3.67486906051636</v>
+        <v>3.67486977577209</v>
       </c>
       <c r="H939" t="n">
         <v>41467</v>
@@ -27629,7 +27629,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G940" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H940" t="n">
         <v>27931</v>
@@ -27658,7 +27658,7 @@
         <v>4.25</v>
       </c>
       <c r="G941" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H941" t="n">
         <v>38506</v>
@@ -27687,7 +27687,7 @@
         <v>4.25</v>
       </c>
       <c r="G942" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H942" t="n">
         <v>119394</v>
@@ -27716,7 +27716,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441396713257</v>
       </c>
       <c r="H943" t="n">
         <v>74050</v>
@@ -27745,7 +27745,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>3.64543724060059</v>
+        <v>3.64543676376343</v>
       </c>
       <c r="H944" t="n">
         <v>39832</v>
@@ -27774,7 +27774,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.7631676197052</v>
+        <v>3.76316714286804</v>
       </c>
       <c r="H945" t="n">
         <v>65323</v>
@@ -27803,7 +27803,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.70009803771973</v>
+        <v>3.70009756088257</v>
       </c>
       <c r="H946" t="n">
         <v>42387</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>3.7085063457489</v>
+        <v>3.70850682258606</v>
       </c>
       <c r="H947" t="n">
         <v>16961</v>
@@ -27861,7 +27861,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G948" t="n">
-        <v>3.56975340843201</v>
+        <v>3.56975317001343</v>
       </c>
       <c r="H948" t="n">
         <v>60667</v>
@@ -27890,7 +27890,7 @@
         <v>4.25</v>
       </c>
       <c r="G949" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H949" t="n">
         <v>21673</v>
@@ -27919,7 +27919,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G950" t="n">
-        <v>3.58236718177795</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H950" t="n">
         <v>25708</v>
@@ -27948,7 +27948,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.59077715873718</v>
+        <v>3.59077620506287</v>
       </c>
       <c r="H951" t="n">
         <v>11470</v>
@@ -27977,7 +27977,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.59498119354248</v>
+        <v>3.59498143196106</v>
       </c>
       <c r="H952" t="n">
         <v>29620</v>
@@ -28006,7 +28006,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>3.70009803771973</v>
+        <v>3.70009756088257</v>
       </c>
       <c r="H953" t="n">
         <v>62364</v>
@@ -28035,7 +28035,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G954" t="n">
-        <v>3.63282322883606</v>
+        <v>3.63282346725464</v>
       </c>
       <c r="H954" t="n">
         <v>27595</v>
@@ -28122,7 +28122,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G957" t="n">
-        <v>3.56554818153381</v>
+        <v>3.56554841995239</v>
       </c>
       <c r="H957" t="n">
         <v>24322</v>
@@ -28151,7 +28151,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>3.57816243171692</v>
+        <v>3.5781626701355</v>
       </c>
       <c r="H958" t="n">
         <v>20043</v>
@@ -28180,7 +28180,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G959" t="n">
-        <v>3.64543724060059</v>
+        <v>3.64543676376343</v>
       </c>
       <c r="H959" t="n">
         <v>27997</v>
@@ -28238,7 +28238,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>3.59077715873718</v>
+        <v>3.59077620506287</v>
       </c>
       <c r="H961" t="n">
         <v>24349</v>
@@ -28267,7 +28267,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G962" t="n">
-        <v>3.6538462638855</v>
+        <v>3.65384602546692</v>
       </c>
       <c r="H962" t="n">
         <v>34756</v>
@@ -28296,7 +28296,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.60759520530701</v>
+        <v>3.60759568214417</v>
       </c>
       <c r="H963" t="n">
         <v>21774</v>
@@ -28325,7 +28325,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G964" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H964" t="n">
         <v>44956</v>
@@ -28354,7 +28354,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>3.70009803771973</v>
+        <v>3.70009756088257</v>
       </c>
       <c r="H965" t="n">
         <v>68023</v>
@@ -28383,7 +28383,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G966" t="n">
-        <v>3.88510203361511</v>
+        <v>3.88510227203369</v>
       </c>
       <c r="H966" t="n">
         <v>222789</v>
@@ -28412,7 +28412,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G967" t="n">
-        <v>3.87248826026917</v>
+        <v>3.87248802185059</v>
       </c>
       <c r="H967" t="n">
         <v>98632</v>
@@ -28441,7 +28441,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G968" t="n">
-        <v>3.81782817840576</v>
+        <v>3.81782793998718</v>
       </c>
       <c r="H968" t="n">
         <v>70923</v>
@@ -28499,7 +28499,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85146546363831</v>
+        <v>3.85146498680115</v>
       </c>
       <c r="H970" t="n">
         <v>35812</v>
@@ -28528,7 +28528,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G971" t="n">
-        <v>3.88089776039124</v>
+        <v>3.88089847564697</v>
       </c>
       <c r="H971" t="n">
         <v>36901</v>
@@ -28557,7 +28557,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H972" t="n">
         <v>52932</v>
@@ -28615,7 +28615,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H974" t="n">
         <v>60311</v>
@@ -28673,7 +28673,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G976" t="n">
-        <v>4.05328941345215</v>
+        <v>4.05328893661499</v>
       </c>
       <c r="H976" t="n">
         <v>72505</v>
@@ -28702,7 +28702,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G977" t="n">
-        <v>4.15420055389404</v>
+        <v>4.15419960021973</v>
       </c>
       <c r="H977" t="n">
         <v>70913</v>
@@ -28847,7 +28847,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G982" t="n">
-        <v>4.33079624176025</v>
+        <v>4.3307957649231</v>
       </c>
       <c r="H982" t="n">
         <v>72363</v>
@@ -28876,7 +28876,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G983" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329931259155</v>
       </c>
       <c r="H983" t="n">
         <v>86583</v>
@@ -28905,7 +28905,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G984" t="n">
-        <v>4.49057340621948</v>
+        <v>4.49057292938232</v>
       </c>
       <c r="H984" t="n">
         <v>101974</v>
@@ -28934,7 +28934,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G985" t="n">
-        <v>4.48216342926025</v>
+        <v>4.48216438293457</v>
       </c>
       <c r="H985" t="n">
         <v>121569</v>
@@ -28992,7 +28992,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G987" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329931259155</v>
       </c>
       <c r="H987" t="n">
         <v>79916</v>
@@ -29021,7 +29021,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H988" t="n">
         <v>168462</v>
@@ -29050,7 +29050,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G989" t="n">
-        <v>4.36443281173706</v>
+        <v>4.36443328857422</v>
       </c>
       <c r="H989" t="n">
         <v>72713</v>
@@ -29137,7 +29137,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G992" t="n">
-        <v>4.33079624176025</v>
+        <v>4.3307957649231</v>
       </c>
       <c r="H992" t="n">
         <v>32809</v>
@@ -29166,7 +29166,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G993" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H993" t="n">
         <v>33595</v>
@@ -29224,7 +29224,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H995" t="n">
         <v>97656</v>
@@ -29253,7 +29253,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G996" t="n">
-        <v>4.67557764053345</v>
+        <v>4.67557811737061</v>
       </c>
       <c r="H996" t="n">
         <v>413404</v>
@@ -29311,7 +29311,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G998" t="n">
-        <v>4.59989356994629</v>
+        <v>4.59989404678345</v>
       </c>
       <c r="H998" t="n">
         <v>233224</v>
@@ -29340,7 +29340,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>4.54943752288818</v>
+        <v>4.54943799972534</v>
       </c>
       <c r="H999" t="n">
         <v>155283</v>
@@ -29369,7 +29369,7 @@
         <v>5.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1000" t="n">
         <v>96233</v>
@@ -29427,7 +29427,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1002" t="n">
         <v>75122</v>
@@ -29456,7 +29456,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1003" t="n">
         <v>47533</v>
@@ -29485,7 +29485,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.58307552337646</v>
+        <v>4.58307504653931</v>
       </c>
       <c r="H1004" t="n">
         <v>68308</v>
@@ -29514,7 +29514,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.6083025932312</v>
+        <v>4.60830354690552</v>
       </c>
       <c r="H1005" t="n">
         <v>64087</v>
@@ -29601,7 +29601,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.46534538269043</v>
+        <v>4.46534490585327</v>
       </c>
       <c r="H1008" t="n">
         <v>238585</v>
@@ -29688,7 +29688,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.40647983551025</v>
+        <v>4.4064793586731</v>
       </c>
       <c r="H1011" t="n">
         <v>25970</v>
@@ -29717,7 +29717,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.44852685928345</v>
+        <v>4.44852638244629</v>
       </c>
       <c r="H1012" t="n">
         <v>79806</v>
@@ -29804,7 +29804,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H1015" t="n">
         <v>17780</v>
@@ -29833,7 +29833,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.44852685928345</v>
+        <v>4.44852638244629</v>
       </c>
       <c r="H1016" t="n">
         <v>24939</v>
@@ -29862,7 +29862,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.44852685928345</v>
+        <v>4.44852638244629</v>
       </c>
       <c r="H1017" t="n">
         <v>14038</v>
@@ -29891,7 +29891,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H1018" t="n">
         <v>21777</v>
@@ -29920,7 +29920,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.43170785903931</v>
+        <v>4.43170738220215</v>
       </c>
       <c r="H1019" t="n">
         <v>24998</v>
@@ -29949,7 +29949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H1020" t="n">
         <v>43906</v>
@@ -30007,7 +30007,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.6083025932312</v>
+        <v>4.60830354690552</v>
       </c>
       <c r="H1022" t="n">
         <v>88961</v>
@@ -30065,7 +30065,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1024" t="n">
         <v>28268</v>
@@ -30123,7 +30123,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.51580142974854</v>
+        <v>4.51580095291138</v>
       </c>
       <c r="H1026" t="n">
         <v>28134</v>
@@ -30152,7 +30152,7 @@
         <v>5.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1027" t="n">
         <v>38338</v>
@@ -30181,7 +30181,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1028" t="n">
-        <v>4.63353109359741</v>
+        <v>4.63353157043457</v>
       </c>
       <c r="H1028" t="n">
         <v>22315</v>
@@ -30268,7 +30268,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44852685928345</v>
+        <v>4.44852638244629</v>
       </c>
       <c r="H1031" t="n">
         <v>41499</v>
@@ -30297,7 +30297,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1032" t="n">
         <v>19972</v>
@@ -30326,7 +30326,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1033" t="n">
-        <v>4.33079624176025</v>
+        <v>4.3307957649231</v>
       </c>
       <c r="H1033" t="n">
         <v>75406</v>
@@ -30500,7 +30500,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.2298846244812</v>
+        <v>4.22988414764404</v>
       </c>
       <c r="H1039" t="n">
         <v>28178</v>
@@ -30529,7 +30529,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.2130651473999</v>
+        <v>4.21306562423706</v>
       </c>
       <c r="H1040" t="n">
         <v>14580</v>
@@ -30558,7 +30558,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.27193069458008</v>
+        <v>4.27193117141724</v>
       </c>
       <c r="H1041" t="n">
         <v>18713</v>
@@ -30587,7 +30587,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.17101907730103</v>
+        <v>4.17101955413818</v>
       </c>
       <c r="H1042" t="n">
         <v>65972</v>
@@ -30645,7 +30645,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H1044" t="n">
         <v>27804</v>
@@ -30674,7 +30674,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H1045" t="n">
         <v>37700</v>
@@ -30703,7 +30703,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1046" t="n">
-        <v>4.33079624176025</v>
+        <v>4.3307957649231</v>
       </c>
       <c r="H1046" t="n">
         <v>38633</v>
@@ -30732,7 +30732,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1047" t="n">
         <v>436016</v>
@@ -30790,7 +30790,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1049" t="n">
         <v>28796</v>
@@ -30848,7 +30848,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H1051" t="n">
         <v>25958</v>
@@ -30877,7 +30877,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H1052" t="n">
         <v>39312</v>
@@ -30935,7 +30935,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.0280613899231</v>
+        <v>4.02806043624878</v>
       </c>
       <c r="H1054" t="n">
         <v>87604</v>
@@ -30993,7 +30993,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.90192103385925</v>
+        <v>3.90192055702209</v>
       </c>
       <c r="H1056" t="n">
         <v>38689</v>
@@ -31022,7 +31022,7 @@
         <v>4.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.7841911315918</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H1057" t="n">
         <v>100789</v>
@@ -31051,7 +31051,7 @@
         <v>4.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.7841911315918</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H1058" t="n">
         <v>46961</v>
@@ -31080,7 +31080,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.67066431045532</v>
+        <v>3.67066502571106</v>
       </c>
       <c r="H1059" t="n">
         <v>45415</v>
@@ -31109,7 +31109,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59498119354248</v>
+        <v>3.59498143196106</v>
       </c>
       <c r="H1060" t="n">
         <v>98196</v>
@@ -31138,7 +31138,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.39736223220825</v>
+        <v>3.39736247062683</v>
       </c>
       <c r="H1061" t="n">
         <v>100807</v>
@@ -31196,7 +31196,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.24178981781006</v>
+        <v>3.24179005622864</v>
       </c>
       <c r="H1063" t="n">
         <v>77522</v>
@@ -31254,7 +31254,7 @@
         <v>3.75</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1065" t="n">
         <v>78435</v>
@@ -31283,7 +31283,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1066" t="n">
-        <v>2.74564075469971</v>
+        <v>2.74564051628113</v>
       </c>
       <c r="H1066" t="n">
         <v>66186</v>
@@ -31312,7 +31312,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.85496139526367</v>
+        <v>2.85496163368225</v>
       </c>
       <c r="H1067" t="n">
         <v>105436</v>
@@ -31341,7 +31341,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.80450582504272</v>
+        <v>2.80450558662415</v>
       </c>
       <c r="H1068" t="n">
         <v>103875</v>
@@ -31370,7 +31370,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.82552909851074</v>
+        <v>2.82552886009216</v>
       </c>
       <c r="H1069" t="n">
         <v>56249</v>
@@ -31399,7 +31399,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.67416167259216</v>
+        <v>2.67416143417358</v>
       </c>
       <c r="H1070" t="n">
         <v>30926</v>
@@ -31428,7 +31428,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.61109161376953</v>
+        <v>2.61109137535095</v>
       </c>
       <c r="H1071" t="n">
         <v>53793</v>
@@ -31486,7 +31486,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.55643105506897</v>
+        <v>2.55643081665039</v>
       </c>
       <c r="H1073" t="n">
         <v>102932</v>
@@ -31544,7 +31544,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.85916662216187</v>
+        <v>2.85916614532471</v>
       </c>
       <c r="H1075" t="n">
         <v>144588</v>
@@ -31573,7 +31573,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.7540500164032</v>
+        <v>2.75405025482178</v>
       </c>
       <c r="H1076" t="n">
         <v>49244</v>
@@ -31602,7 +31602,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.6447286605835</v>
+        <v>2.64472842216492</v>
       </c>
       <c r="H1077" t="n">
         <v>47482</v>
@@ -31660,7 +31660,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.78348255157471</v>
+        <v>2.78348231315613</v>
       </c>
       <c r="H1079" t="n">
         <v>225795</v>
@@ -31689,7 +31689,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70779895782471</v>
+        <v>2.70779848098755</v>
       </c>
       <c r="H1080" t="n">
         <v>66327</v>
@@ -31718,7 +31718,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.72882223129272</v>
+        <v>2.72882175445557</v>
       </c>
       <c r="H1081" t="n">
         <v>47993</v>
@@ -31805,7 +31805,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.79189157485962</v>
+        <v>2.79189205169678</v>
       </c>
       <c r="H1084" t="n">
         <v>378419</v>
@@ -31834,7 +31834,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.82973384857178</v>
+        <v>2.8297336101532</v>
       </c>
       <c r="H1085" t="n">
         <v>42050</v>
@@ -31892,7 +31892,7 @@
         <v>3.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.94325947761536</v>
+        <v>2.94325923919678</v>
       </c>
       <c r="H1087" t="n">
         <v>73870</v>
@@ -31921,7 +31921,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1088" t="n">
         <v>43109</v>
@@ -31950,7 +31950,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.85916662216187</v>
+        <v>2.85916614532471</v>
       </c>
       <c r="H1089" t="n">
         <v>24628</v>
@@ -32008,7 +32008,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1091" t="n">
         <v>12591</v>
@@ -32037,7 +32037,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.91803169250488</v>
+        <v>2.91803121566772</v>
       </c>
       <c r="H1092" t="n">
         <v>30394</v>
@@ -32066,7 +32066,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.91803169250488</v>
+        <v>2.91803121566772</v>
       </c>
       <c r="H1093" t="n">
         <v>14421</v>
@@ -32095,7 +32095,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1094" t="n">
         <v>44042</v>
@@ -32124,7 +32124,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.94746422767639</v>
+        <v>2.94746398925781</v>
       </c>
       <c r="H1095" t="n">
         <v>24986</v>
@@ -32153,7 +32153,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1096" t="n">
         <v>16579</v>
@@ -32211,7 +32211,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1098" t="n">
         <v>8697</v>
@@ -32240,7 +32240,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91382670402527</v>
+        <v>2.91382694244385</v>
       </c>
       <c r="H1099" t="n">
         <v>11932</v>
@@ -32298,7 +32298,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1101" t="n">
         <v>15640</v>
@@ -32327,7 +32327,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1102" t="n">
         <v>34379</v>
@@ -32356,7 +32356,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.03996634483337</v>
+        <v>3.03996658325195</v>
       </c>
       <c r="H1103" t="n">
         <v>107338</v>
@@ -32414,7 +32414,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.98530554771423</v>
+        <v>2.98530602455139</v>
       </c>
       <c r="H1105" t="n">
         <v>51255</v>
@@ -32443,7 +32443,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.01894307136536</v>
+        <v>3.01894330978394</v>
       </c>
       <c r="H1106" t="n">
         <v>7512</v>
@@ -32501,7 +32501,7 @@
         <v>3.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.94325947761536</v>
+        <v>2.94325923919678</v>
       </c>
       <c r="H1108" t="n">
         <v>45095</v>
@@ -32530,7 +32530,7 @@
         <v>3.5</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.94325947761536</v>
+        <v>2.94325923919678</v>
       </c>
       <c r="H1109" t="n">
         <v>23980</v>
@@ -32588,7 +32588,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.02735257148743</v>
+        <v>3.02735233306885</v>
       </c>
       <c r="H1111" t="n">
         <v>23141</v>
@@ -32617,7 +32617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.98530554771423</v>
+        <v>2.98530602455139</v>
       </c>
       <c r="H1112" t="n">
         <v>12893</v>
@@ -32675,7 +32675,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.17871999740601</v>
+        <v>3.17872023582458</v>
       </c>
       <c r="H1114" t="n">
         <v>30466</v>
@@ -32704,7 +32704,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.09462714195251</v>
+        <v>3.09462738037109</v>
       </c>
       <c r="H1115" t="n">
         <v>483852</v>
@@ -32733,7 +32733,7 @@
         <v>3.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1116" t="n">
         <v>16895</v>
@@ -32762,7 +32762,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.08201313018799</v>
+        <v>3.08201289176941</v>
       </c>
       <c r="H1117" t="n">
         <v>31713</v>
@@ -32791,7 +32791,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.11565041542053</v>
+        <v>3.11564993858337</v>
       </c>
       <c r="H1118" t="n">
         <v>31970</v>
@@ -32820,7 +32820,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.06939935684204</v>
+        <v>3.06939911842346</v>
       </c>
       <c r="H1119" t="n">
         <v>81350</v>
@@ -32849,7 +32849,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.05258059501648</v>
+        <v>3.0525803565979</v>
       </c>
       <c r="H1120" t="n">
         <v>87073</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1121" t="n">
         <v>125597</v>
@@ -32907,7 +32907,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.2375853061676</v>
+        <v>3.23758554458618</v>
       </c>
       <c r="H1122" t="n">
         <v>41019</v>
@@ -32936,7 +32936,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.31326937675476</v>
+        <v>3.31326913833618</v>
       </c>
       <c r="H1123" t="n">
         <v>33940</v>
@@ -32994,7 +32994,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.40997624397278</v>
+        <v>3.40997648239136</v>
       </c>
       <c r="H1125" t="n">
         <v>96671</v>
@@ -33052,7 +33052,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.40577173233032</v>
+        <v>3.4057719707489</v>
       </c>
       <c r="H1127" t="n">
         <v>28852</v>
@@ -33139,7 +33139,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1130" t="n">
-        <v>3.12826442718506</v>
+        <v>3.12826466560364</v>
       </c>
       <c r="H1130" t="n">
         <v>12825</v>
@@ -33197,7 +33197,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.30906462669373</v>
+        <v>3.3090648651123</v>
       </c>
       <c r="H1132" t="n">
         <v>20072</v>
@@ -33226,7 +33226,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.30485987663269</v>
+        <v>3.30486011505127</v>
       </c>
       <c r="H1133" t="n">
         <v>9929</v>
@@ -33255,7 +33255,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.2796323299408</v>
+        <v>3.27963209152222</v>
       </c>
       <c r="H1134" t="n">
         <v>191541</v>
@@ -33313,7 +33313,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.31326937675476</v>
+        <v>3.31326913833618</v>
       </c>
       <c r="H1136" t="n">
         <v>55970</v>
@@ -33342,7 +33342,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.30906462669373</v>
+        <v>3.3090648651123</v>
       </c>
       <c r="H1137" t="n">
         <v>62999</v>
@@ -33429,7 +33429,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.3679301738739</v>
+        <v>3.36792969703674</v>
       </c>
       <c r="H1140" t="n">
         <v>16770</v>
@@ -33458,7 +33458,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.37213444709778</v>
+        <v>3.37213468551636</v>
       </c>
       <c r="H1141" t="n">
         <v>74328</v>
@@ -33516,7 +33516,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.59077715873718</v>
+        <v>3.59077620506287</v>
       </c>
       <c r="H1143" t="n">
         <v>68123</v>
@@ -33574,7 +33574,7 @@
         <v>4.25</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.67881727218628</v>
+        <v>3.67881751060486</v>
       </c>
       <c r="H1145" t="n">
         <v>32568</v>
@@ -33603,7 +33603,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.63553690910339</v>
+        <v>3.63553667068481</v>
       </c>
       <c r="H1146" t="n">
         <v>107743</v>
@@ -33632,7 +33632,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.55330443382263</v>
+        <v>3.55330467224121</v>
       </c>
       <c r="H1147" t="n">
         <v>68563</v>
@@ -33748,7 +33748,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1151" t="n">
         <v>12775</v>
@@ -33777,7 +33777,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1152" t="n">
         <v>25808</v>
@@ -33806,7 +33806,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1153" t="n">
         <v>7570</v>
@@ -33864,7 +33864,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.31526374816895</v>
+        <v>3.31526327133179</v>
       </c>
       <c r="H1155" t="n">
         <v>18868</v>
@@ -33893,7 +33893,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.34555983543396</v>
+        <v>3.34555959701538</v>
       </c>
       <c r="H1156" t="n">
         <v>8521</v>
@@ -34009,7 +34009,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.20273494720459</v>
+        <v>3.20273542404175</v>
       </c>
       <c r="H1160" t="n">
         <v>25674</v>
@@ -34125,7 +34125,7 @@
         <v>3.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.02961397171021</v>
+        <v>3.02961421012878</v>
       </c>
       <c r="H1164" t="n">
         <v>28095</v>
@@ -34154,7 +34154,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.20273494720459</v>
+        <v>3.20273542404175</v>
       </c>
       <c r="H1165" t="n">
         <v>58772</v>
@@ -34183,7 +34183,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.20273494720459</v>
+        <v>3.20273542404175</v>
       </c>
       <c r="H1166" t="n">
         <v>25203</v>
@@ -34212,7 +34212,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1167" t="n">
         <v>39750</v>
@@ -34241,7 +34241,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18542265892029</v>
+        <v>3.18542313575745</v>
       </c>
       <c r="H1168" t="n">
         <v>60306</v>
@@ -34270,7 +34270,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1169" t="n">
         <v>42338</v>
@@ -34299,7 +34299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1170" t="n">
         <v>11674</v>
@@ -34328,7 +34328,7 @@
         <v>3.625</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.13781476020813</v>
+        <v>3.13781452178955</v>
       </c>
       <c r="H1171" t="n">
         <v>37987</v>
@@ -34357,7 +34357,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1172" t="n">
         <v>44555</v>
@@ -34415,7 +34415,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1174" t="n">
         <v>16845</v>
@@ -34444,7 +34444,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1175" t="n">
         <v>11249</v>
@@ -34473,7 +34473,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1176" t="n">
         <v>14163</v>
@@ -34618,7 +34618,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1181" t="n">
-        <v>3.03826975822449</v>
+        <v>3.03827023506165</v>
       </c>
       <c r="H1181" t="n">
         <v>16656</v>
@@ -34647,7 +34647,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1182" t="n">
-        <v>3.03394222259521</v>
+        <v>3.03394198417664</v>
       </c>
       <c r="H1182" t="n">
         <v>6267</v>
@@ -34705,7 +34705,7 @@
         <v>3.5</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.02961397171021</v>
+        <v>3.02961421012878</v>
       </c>
       <c r="H1184" t="n">
         <v>10267</v>
@@ -34734,7 +34734,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.98200559616089</v>
+        <v>2.98200607299805</v>
       </c>
       <c r="H1185" t="n">
         <v>22437</v>
@@ -34763,7 +34763,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.01230216026306</v>
+        <v>3.01230239868164</v>
       </c>
       <c r="H1186" t="n">
         <v>33766</v>
@@ -34792,7 +34792,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.99498987197876</v>
+        <v>2.99499011039734</v>
       </c>
       <c r="H1187" t="n">
         <v>18282</v>
@@ -34821,7 +34821,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.91708540916443</v>
+        <v>2.91708588600159</v>
       </c>
       <c r="H1188" t="n">
         <v>19683</v>
@@ -34850,7 +34850,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.89977359771729</v>
+        <v>2.89977383613586</v>
       </c>
       <c r="H1189" t="n">
         <v>17643</v>
@@ -34937,7 +34937,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.87380528450012</v>
+        <v>2.87380504608154</v>
       </c>
       <c r="H1192" t="n">
         <v>11152</v>
@@ -34966,7 +34966,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.87380528450012</v>
+        <v>2.87380504608154</v>
       </c>
       <c r="H1193" t="n">
         <v>5142</v>
@@ -35024,7 +35024,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.00364589691162</v>
+        <v>3.0036461353302</v>
       </c>
       <c r="H1195" t="n">
         <v>8450</v>
@@ -35082,7 +35082,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.99066233634949</v>
+        <v>2.99066209793091</v>
       </c>
       <c r="H1197" t="n">
         <v>20958</v>
@@ -35140,7 +35140,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.84350943565369</v>
+        <v>2.84350919723511</v>
       </c>
       <c r="H1199" t="n">
         <v>24636</v>
@@ -35169,7 +35169,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.7742612361908</v>
+        <v>2.77426099777222</v>
       </c>
       <c r="H1200" t="n">
         <v>14812</v>
@@ -35198,7 +35198,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.7742612361908</v>
+        <v>2.77426099777222</v>
       </c>
       <c r="H1201" t="n">
         <v>11373</v>
@@ -35256,7 +35256,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.74396467208862</v>
+        <v>2.7439649105072</v>
       </c>
       <c r="H1203" t="n">
         <v>13783</v>
@@ -35285,7 +35285,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.7179970741272</v>
+        <v>2.71799683570862</v>
       </c>
       <c r="H1204" t="n">
         <v>20689</v>
@@ -35314,7 +35314,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.75262117385864</v>
+        <v>2.75262093544006</v>
       </c>
       <c r="H1205" t="n">
         <v>14823</v>
@@ -35517,7 +35517,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.89977359771729</v>
+        <v>2.89977383613586</v>
       </c>
       <c r="H1212" t="n">
         <v>28258</v>
@@ -35575,7 +35575,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.00364589691162</v>
+        <v>3.0036461353302</v>
       </c>
       <c r="H1214" t="n">
         <v>29476</v>
@@ -35604,7 +35604,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.89977359771729</v>
+        <v>2.89977383613586</v>
       </c>
       <c r="H1215" t="n">
         <v>17211</v>
@@ -35720,7 +35720,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.76127696037292</v>
+        <v>2.7612771987915</v>
       </c>
       <c r="H1219" t="n">
         <v>16948</v>
@@ -35749,7 +35749,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.73963665962219</v>
+        <v>2.73963689804077</v>
       </c>
       <c r="H1220" t="n">
         <v>13723</v>
@@ -35836,7 +35836,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.66606044769287</v>
+        <v>2.66606068611145</v>
       </c>
       <c r="H1223" t="n">
         <v>27695</v>
@@ -35865,7 +35865,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.65740442276001</v>
+        <v>2.65740466117859</v>
       </c>
       <c r="H1224" t="n">
         <v>30810</v>
@@ -35894,7 +35894,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.62710857391357</v>
+        <v>2.62710809707642</v>
       </c>
       <c r="H1225" t="n">
         <v>18880</v>
@@ -35952,7 +35952,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.56218814849854</v>
+        <v>2.56218791007996</v>
       </c>
       <c r="H1227" t="n">
         <v>33991</v>
@@ -36010,7 +36010,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.49293971061707</v>
+        <v>2.49293994903564</v>
       </c>
       <c r="H1229" t="n">
         <v>42711</v>
@@ -36039,7 +36039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.51025176048279</v>
+        <v>2.51025199890137</v>
       </c>
       <c r="H1230" t="n">
         <v>25737</v>
@@ -36068,7 +36068,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.49726724624634</v>
+        <v>2.49726748466492</v>
       </c>
       <c r="H1231" t="n">
         <v>24442</v>
@@ -36126,7 +36126,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.44100308418274</v>
+        <v>2.44100332260132</v>
       </c>
       <c r="H1233" t="n">
         <v>71628</v>
@@ -36271,7 +36271,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.89111733436584</v>
+        <v>2.89111757278442</v>
       </c>
       <c r="H1238" t="n">
         <v>43412</v>
@@ -36387,7 +36387,7 @@
         <v>3.625</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.13781476020813</v>
+        <v>3.13781452178955</v>
       </c>
       <c r="H1242" t="n">
         <v>286519</v>
@@ -36416,7 +36416,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1243" t="n">
         <v>42158</v>
@@ -36445,7 +36445,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1244" t="n">
         <v>82441</v>
@@ -36503,7 +36503,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.11184668540955</v>
+        <v>3.11184644699097</v>
       </c>
       <c r="H1246" t="n">
         <v>111943</v>
@@ -36532,7 +36532,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1247" t="n">
         <v>61470</v>
@@ -36619,7 +36619,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12483048439026</v>
+        <v>3.12483024597168</v>
       </c>
       <c r="H1250" t="n">
         <v>43905</v>
@@ -36648,7 +36648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1251" t="n">
         <v>44851</v>
@@ -36677,7 +36677,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.22004675865173</v>
+        <v>3.22004699707031</v>
       </c>
       <c r="H1252" t="n">
         <v>180885</v>
@@ -36706,7 +36706,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.22870302200317</v>
+        <v>3.22870326042175</v>
       </c>
       <c r="H1253" t="n">
         <v>120927</v>
@@ -36764,7 +36764,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.31526374816895</v>
+        <v>3.31526327133179</v>
       </c>
       <c r="H1255" t="n">
         <v>104398</v>
@@ -36793,7 +36793,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.40615200996399</v>
+        <v>3.40615224838257</v>
       </c>
       <c r="H1256" t="n">
         <v>82291</v>
@@ -36822,7 +36822,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1257" t="n">
-        <v>3.34123182296753</v>
+        <v>3.34123134613037</v>
       </c>
       <c r="H1257" t="n">
         <v>79877</v>
@@ -36851,7 +36851,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.410480260849</v>
+        <v>3.41048002243042</v>
       </c>
       <c r="H1258" t="n">
         <v>37054</v>
@@ -36880,7 +36880,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1259" t="n">
         <v>47087</v>
@@ -36909,7 +36909,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1260" t="n">
         <v>50431</v>
@@ -36996,7 +36996,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.436448097229</v>
+        <v>3.43644833564758</v>
       </c>
       <c r="H1263" t="n">
         <v>51384</v>
@@ -37025,7 +37025,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G1264" t="n">
-        <v>3.37152791023254</v>
+        <v>3.37152767181396</v>
       </c>
       <c r="H1264" t="n">
         <v>57150</v>
@@ -37054,7 +37054,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.34123182296753</v>
+        <v>3.34123134613037</v>
       </c>
       <c r="H1265" t="n">
         <v>80505</v>
@@ -37112,7 +37112,7 @@
         <v>3.875</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.3542160987854</v>
+        <v>3.35421562194824</v>
       </c>
       <c r="H1267" t="n">
         <v>46313</v>
@@ -37170,7 +37170,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.60091257095337</v>
+        <v>3.60091233253479</v>
       </c>
       <c r="H1269" t="n">
         <v>155508</v>
@@ -37199,7 +37199,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.60091257095337</v>
+        <v>3.60091233253479</v>
       </c>
       <c r="H1270" t="n">
         <v>61290</v>
@@ -37228,7 +37228,7 @@
         <v>4.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.67881727218628</v>
+        <v>3.67881751060486</v>
       </c>
       <c r="H1271" t="n">
         <v>52340</v>
@@ -37257,7 +37257,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.64419341087341</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1272" t="n">
         <v>61245</v>
@@ -37286,7 +37286,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.670161485672</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1273" t="n">
         <v>44391</v>
@@ -37315,7 +37315,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.670161485672</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1274" t="n">
         <v>37048</v>
@@ -37344,7 +37344,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.72209787368774</v>
+        <v>3.72209763526917</v>
       </c>
       <c r="H1275" t="n">
         <v>48291</v>
@@ -37373,7 +37373,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.64419341087341</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1276" t="n">
         <v>24944</v>
@@ -37402,7 +37402,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.57927322387695</v>
+        <v>3.57927298545837</v>
       </c>
       <c r="H1277" t="n">
         <v>32707</v>
@@ -37460,7 +37460,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.57494473457336</v>
+        <v>3.57494497299194</v>
       </c>
       <c r="H1279" t="n">
         <v>24582</v>
@@ -37489,7 +37489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.5489764213562</v>
+        <v>3.54897665977478</v>
       </c>
       <c r="H1280" t="n">
         <v>34859</v>
@@ -37518,7 +37518,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1281" t="n">
-        <v>3.5489764213562</v>
+        <v>3.54897665977478</v>
       </c>
       <c r="H1281" t="n">
         <v>13955</v>
@@ -37576,7 +37576,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1283" t="n">
-        <v>3.47107219696045</v>
+        <v>3.47107243537903</v>
       </c>
       <c r="H1283" t="n">
         <v>33763</v>
@@ -37692,7 +37692,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.436448097229</v>
+        <v>3.43644833564758</v>
       </c>
       <c r="H1287" t="n">
         <v>22323</v>
@@ -37779,7 +37779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.410480260849</v>
+        <v>3.41048002243042</v>
       </c>
       <c r="H1290" t="n">
         <v>5711</v>
@@ -37808,7 +37808,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.410480260849</v>
+        <v>3.41048002243042</v>
       </c>
       <c r="H1291" t="n">
         <v>9392</v>
@@ -37866,7 +37866,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.47107219696045</v>
+        <v>3.47107243537903</v>
       </c>
       <c r="H1293" t="n">
         <v>5161</v>
@@ -37982,7 +37982,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1297" t="n">
-        <v>3.51435256004333</v>
+        <v>3.51435232162476</v>
       </c>
       <c r="H1297" t="n">
         <v>64111</v>
@@ -38214,7 +38214,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.5489764213562</v>
+        <v>3.54897665977478</v>
       </c>
       <c r="H1305" t="n">
         <v>135344</v>
@@ -38243,7 +38243,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.60091257095337</v>
+        <v>3.60091233253479</v>
       </c>
       <c r="H1306" t="n">
         <v>44032</v>
@@ -38272,7 +38272,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.66583347320557</v>
+        <v>3.66583323478699</v>
       </c>
       <c r="H1307" t="n">
         <v>53680</v>
@@ -38301,7 +38301,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1308" t="n">
         <v>14769</v>
@@ -38330,7 +38330,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.6528491973877</v>
+        <v>3.65284895896912</v>
       </c>
       <c r="H1309" t="n">
         <v>21085</v>
@@ -38359,7 +38359,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.62688159942627</v>
+        <v>3.62688088417053</v>
       </c>
       <c r="H1310" t="n">
         <v>13519</v>
@@ -38388,7 +38388,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1311" t="n">
         <v>35922</v>
@@ -38446,7 +38446,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.75672221183777</v>
+        <v>3.75672173500061</v>
       </c>
       <c r="H1313" t="n">
         <v>17797</v>
@@ -38475,7 +38475,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.62688159942627</v>
+        <v>3.62688088417053</v>
       </c>
       <c r="H1314" t="n">
         <v>40501</v>
@@ -38504,7 +38504,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.60524082183838</v>
+        <v>3.60524034500122</v>
       </c>
       <c r="H1315" t="n">
         <v>18680</v>
@@ -38533,7 +38533,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.670161485672</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1316" t="n">
         <v>18719</v>
@@ -38562,7 +38562,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.68747353553772</v>
+        <v>3.6874737739563</v>
       </c>
       <c r="H1317" t="n">
         <v>37495</v>
@@ -38591,7 +38591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1318" t="n">
         <v>19255</v>
@@ -38620,7 +38620,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045733451843</v>
       </c>
       <c r="H1319" t="n">
         <v>16480</v>
@@ -38649,7 +38649,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045733451843</v>
       </c>
       <c r="H1320" t="n">
         <v>33947</v>
@@ -38707,7 +38707,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.69180154800415</v>
+        <v>3.69180083274841</v>
       </c>
       <c r="H1322" t="n">
         <v>21036</v>
@@ -38765,7 +38765,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.63553690910339</v>
+        <v>3.63553667068481</v>
       </c>
       <c r="H1324" t="n">
         <v>15167</v>
@@ -38794,7 +38794,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.64419341087341</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1325" t="n">
         <v>19724</v>
@@ -38823,7 +38823,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.60956883430481</v>
+        <v>3.60956907272339</v>
       </c>
       <c r="H1326" t="n">
         <v>14439</v>
@@ -38881,7 +38881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.57494473457336</v>
+        <v>3.57494497299194</v>
       </c>
       <c r="H1328" t="n">
         <v>44132</v>
@@ -38968,7 +38968,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.47107219696045</v>
+        <v>3.47107243537903</v>
       </c>
       <c r="H1331" t="n">
         <v>18501</v>
@@ -39026,7 +39026,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.62688159942627</v>
+        <v>3.62688088417053</v>
       </c>
       <c r="H1333" t="n">
         <v>62690</v>
@@ -39055,7 +39055,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.64419341087341</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1334" t="n">
         <v>227618</v>
@@ -39113,7 +39113,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.60091257095337</v>
+        <v>3.60091233253479</v>
       </c>
       <c r="H1336" t="n">
         <v>26849</v>
@@ -39142,7 +39142,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.63120889663696</v>
+        <v>3.63120913505554</v>
       </c>
       <c r="H1337" t="n">
         <v>162714</v>
@@ -39171,7 +39171,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.60956883430481</v>
+        <v>3.60956907272339</v>
       </c>
       <c r="H1338" t="n">
         <v>11457</v>
@@ -39200,7 +39200,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.70478558540344</v>
+        <v>3.7047860622406</v>
       </c>
       <c r="H1339" t="n">
         <v>37701</v>
@@ -39229,7 +39229,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.75672221183777</v>
+        <v>3.75672173500061</v>
       </c>
       <c r="H1340" t="n">
         <v>106019</v>
@@ -39287,7 +39287,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1342" t="n">
-        <v>3.85626649856567</v>
+        <v>3.85626578330994</v>
       </c>
       <c r="H1342" t="n">
         <v>37160</v>
@@ -39345,7 +39345,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.92568922042847</v>
+        <v>3.92568874359131</v>
       </c>
       <c r="H1344" t="n">
         <v>82068</v>
@@ -39374,7 +39374,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1345" t="n">
         <v>105839</v>
@@ -39432,7 +39432,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G1347" t="n">
-        <v>4.07482099533081</v>
+        <v>4.07482147216797</v>
       </c>
       <c r="H1347" t="n">
         <v>21670</v>
@@ -39490,7 +39490,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.10991144180298</v>
+        <v>4.10991096496582</v>
       </c>
       <c r="H1349" t="n">
         <v>30388</v>
@@ -39548,7 +39548,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.05289030075073</v>
+        <v>4.05288982391357</v>
       </c>
       <c r="H1351" t="n">
         <v>28011</v>
@@ -39577,7 +39577,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1352" t="n">
         <v>154295</v>
@@ -39606,7 +39606,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1353" t="n">
         <v>85873</v>
@@ -39693,7 +39693,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1356" t="n">
         <v>107419</v>
@@ -39722,7 +39722,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.94323396682739</v>
+        <v>3.94323348999023</v>
       </c>
       <c r="H1357" t="n">
         <v>27194</v>
@@ -39925,7 +39925,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.91691613197327</v>
+        <v>3.91691660881042</v>
       </c>
       <c r="H1364" t="n">
         <v>14269</v>
@@ -39983,7 +39983,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1366" t="n">
         <v>23565</v>
@@ -40041,7 +40041,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.90375709533691</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1368" t="n">
         <v>11714</v>
@@ -40070,7 +40070,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.86866807937622</v>
+        <v>3.86866760253906</v>
       </c>
       <c r="H1369" t="n">
         <v>41469</v>
@@ -40186,7 +40186,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.92568922042847</v>
+        <v>3.92568874359131</v>
       </c>
       <c r="H1373" t="n">
         <v>28128</v>
@@ -40215,7 +40215,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.95639324188232</v>
+        <v>3.95639276504517</v>
       </c>
       <c r="H1374" t="n">
         <v>105079</v>
@@ -40331,7 +40331,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1378" t="n">
         <v>83837</v>
@@ -40360,7 +40360,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1379" t="n">
         <v>71974</v>
@@ -40447,7 +40447,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.97393727302551</v>
+        <v>3.97393774986267</v>
       </c>
       <c r="H1382" t="n">
         <v>31872</v>
@@ -40505,7 +40505,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.10552453994751</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1384" t="n">
         <v>114987</v>
@@ -40534,7 +40534,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.10552453994751</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1385" t="n">
         <v>70506</v>
@@ -40650,7 +40650,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.03534460067749</v>
+        <v>4.03534507751465</v>
       </c>
       <c r="H1389" t="n">
         <v>36588</v>
@@ -40766,7 +40766,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G1393" t="n">
-        <v>3.9783239364624</v>
+        <v>3.97832441329956</v>
       </c>
       <c r="H1393" t="n">
         <v>21167</v>
@@ -40795,7 +40795,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1394" t="n">
-        <v>4.10552453994751</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1394" t="n">
         <v>234889</v>
@@ -40824,7 +40824,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.1186842918396</v>
+        <v>4.11868381500244</v>
       </c>
       <c r="H1395" t="n">
         <v>60827</v>
@@ -40998,7 +40998,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1401" t="n">
-        <v>4.1186842918396</v>
+        <v>4.11868381500244</v>
       </c>
       <c r="H1401" t="n">
         <v>55006</v>
@@ -41085,7 +41085,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.84235072135925</v>
+        <v>3.84235024452209</v>
       </c>
       <c r="H1404" t="n">
         <v>27674</v>
@@ -41114,7 +41114,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.82480549812317</v>
+        <v>3.82480525970459</v>
       </c>
       <c r="H1405" t="n">
         <v>22741</v>
@@ -41143,7 +41143,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.79848790168762</v>
+        <v>3.79848766326904</v>
       </c>
       <c r="H1406" t="n">
         <v>16201</v>
@@ -41172,7 +41172,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.79410147666931</v>
+        <v>3.79410171508789</v>
       </c>
       <c r="H1407" t="n">
         <v>67590</v>
@@ -41201,7 +41201,7 @@
         <v>4.25</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.7283079624176</v>
+        <v>3.72830820083618</v>
       </c>
       <c r="H1408" t="n">
         <v>35407</v>
@@ -41259,7 +41259,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.58794808387756</v>
+        <v>3.58794856071472</v>
       </c>
       <c r="H1410" t="n">
         <v>22462</v>
@@ -41288,7 +41288,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.75023937225342</v>
+        <v>3.75023913383484</v>
       </c>
       <c r="H1411" t="n">
         <v>54658</v>
@@ -41317,7 +41317,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.85112237930298</v>
+        <v>3.85112261772156</v>
       </c>
       <c r="H1412" t="n">
         <v>88072</v>
@@ -41375,7 +41375,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.91253042221069</v>
+        <v>3.91253066062927</v>
       </c>
       <c r="H1414" t="n">
         <v>28276</v>
@@ -41404,7 +41404,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.79848790168762</v>
+        <v>3.79848766326904</v>
       </c>
       <c r="H1415" t="n">
         <v>26744</v>
@@ -41433,7 +41433,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.8598952293396</v>
+        <v>3.85989546775818</v>
       </c>
       <c r="H1416" t="n">
         <v>36258</v>
@@ -41462,7 +41462,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.96077847480774</v>
+        <v>3.9607789516449</v>
       </c>
       <c r="H1417" t="n">
         <v>78205</v>
@@ -41578,7 +41578,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.90375709533691</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1421" t="n">
         <v>21700</v>
@@ -41607,7 +41607,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1422" t="n">
         <v>19394</v>
@@ -41636,7 +41636,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.89937233924866</v>
+        <v>3.89937162399292</v>
       </c>
       <c r="H1423" t="n">
         <v>17002</v>
@@ -41694,7 +41694,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.91691613197327</v>
+        <v>3.91691660881042</v>
       </c>
       <c r="H1425" t="n">
         <v>15425</v>
@@ -41752,7 +41752,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.95639324188232</v>
+        <v>3.95639276504517</v>
       </c>
       <c r="H1427" t="n">
         <v>12378</v>
@@ -41839,7 +41839,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.82480549812317</v>
+        <v>3.82480525970459</v>
       </c>
       <c r="H1430" t="n">
         <v>16207</v>
@@ -41897,7 +41897,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.84235072135925</v>
+        <v>3.84235024452209</v>
       </c>
       <c r="H1432" t="n">
         <v>45332</v>
@@ -41955,7 +41955,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.84673666954041</v>
+        <v>3.84673714637756</v>
       </c>
       <c r="H1434" t="n">
         <v>22564</v>
@@ -42013,7 +42013,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1436" t="n">
-        <v>3.8598952293396</v>
+        <v>3.85989546775818</v>
       </c>
       <c r="H1436" t="n">
         <v>12738</v>
@@ -42042,7 +42042,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.94323396682739</v>
+        <v>3.94323348999023</v>
       </c>
       <c r="H1437" t="n">
         <v>11785</v>
@@ -42071,7 +42071,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.8598952293396</v>
+        <v>3.85989546775818</v>
       </c>
       <c r="H1438" t="n">
         <v>17876</v>
@@ -42100,7 +42100,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.90375709533691</v>
+        <v>3.90375781059265</v>
       </c>
       <c r="H1439" t="n">
         <v>14721</v>
@@ -42158,7 +42158,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.88621306419373</v>
+        <v>3.88621258735657</v>
       </c>
       <c r="H1441" t="n">
         <v>31839</v>
@@ -42187,7 +42187,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.88621306419373</v>
+        <v>3.88621258735657</v>
       </c>
       <c r="H1442" t="n">
         <v>11973</v>
@@ -42216,7 +42216,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1443" t="n">
         <v>22458</v>
@@ -42245,7 +42245,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>4.03534460067749</v>
+        <v>4.03534507751465</v>
       </c>
       <c r="H1444" t="n">
         <v>36796</v>
@@ -42303,7 +42303,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.95639324188232</v>
+        <v>3.95639276504517</v>
       </c>
       <c r="H1446" t="n">
         <v>25409</v>
@@ -42361,7 +42361,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.95639324188232</v>
+        <v>3.95639276504517</v>
       </c>
       <c r="H1448" t="n">
         <v>17459</v>
@@ -42448,7 +42448,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.00902795791626</v>
+        <v>4.0090274810791</v>
       </c>
       <c r="H1451" t="n">
         <v>19832</v>
@@ -42477,7 +42477,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.06604909896851</v>
+        <v>4.06604862213135</v>
       </c>
       <c r="H1452" t="n">
         <v>31528</v>
@@ -42535,7 +42535,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.00464105606079</v>
+        <v>4.00464153289795</v>
       </c>
       <c r="H1454" t="n">
         <v>29105</v>
@@ -42593,7 +42593,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.13622856140137</v>
+        <v>4.13622903823853</v>
       </c>
       <c r="H1456" t="n">
         <v>26452</v>
@@ -42622,7 +42622,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1457" t="n">
-        <v>4.17570543289185</v>
+        <v>4.17570495605469</v>
       </c>
       <c r="H1457" t="n">
         <v>34032</v>
@@ -42651,7 +42651,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.15377378463745</v>
+        <v>4.15377330780029</v>
       </c>
       <c r="H1458" t="n">
         <v>22649</v>
@@ -42709,7 +42709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.01779985427856</v>
+        <v>4.01780033111572</v>
       </c>
       <c r="H1460" t="n">
         <v>22508</v>
@@ -42738,7 +42738,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1461" t="n">
-        <v>4.03973197937012</v>
+        <v>4.03973150253296</v>
       </c>
       <c r="H1461" t="n">
         <v>19434</v>
@@ -42883,7 +42883,7 @@
         <v>4.63500022888184</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.06604909896851</v>
+        <v>4.06604862213135</v>
       </c>
       <c r="H1466" t="n">
         <v>15403</v>
@@ -42912,7 +42912,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G1467" t="n">
-        <v>4.1186842918396</v>
+        <v>4.11868381500244</v>
       </c>
       <c r="H1467" t="n">
         <v>11126</v>
@@ -42941,7 +42941,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.10991144180298</v>
+        <v>4.10991096496582</v>
       </c>
       <c r="H1468" t="n">
         <v>15292</v>
@@ -42970,7 +42970,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1469" t="n">
-        <v>4.1581597328186</v>
+        <v>4.15816020965576</v>
       </c>
       <c r="H1469" t="n">
         <v>8104</v>
@@ -42999,7 +42999,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.10113859176636</v>
+        <v>4.10113906860352</v>
       </c>
       <c r="H1470" t="n">
         <v>15953</v>
@@ -43115,7 +43115,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.31167840957642</v>
+        <v>4.31167793273926</v>
       </c>
       <c r="H1474" t="n">
         <v>44409</v>
@@ -43260,7 +43260,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>4.46519756317139</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1479" t="n">
         <v>16097</v>
@@ -43318,7 +43318,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.3599271774292</v>
+        <v>4.35992670059204</v>
       </c>
       <c r="H1481" t="n">
         <v>16300</v>
@@ -43434,7 +43434,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1485" t="n">
-        <v>4.39501810073853</v>
+        <v>4.39501714706421</v>
       </c>
       <c r="H1485" t="n">
         <v>24688</v>
@@ -43521,7 +43521,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.39501810073853</v>
+        <v>4.39501714706421</v>
       </c>
       <c r="H1488" t="n">
         <v>43372</v>
@@ -43608,7 +43608,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.38185834884644</v>
+        <v>4.38185882568359</v>
       </c>
       <c r="H1491" t="n">
         <v>146082</v>
@@ -43753,7 +43753,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1496" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1496" t="n">
         <v>59614</v>
@@ -43782,7 +43782,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1497" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1497" t="n">
         <v>45722</v>
@@ -43840,7 +43840,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1499" t="n">
-        <v>4.39501810073853</v>
+        <v>4.39501714706421</v>
       </c>
       <c r="H1499" t="n">
         <v>22226</v>
@@ -43898,7 +43898,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.35554075241089</v>
+        <v>4.35554122924805</v>
       </c>
       <c r="H1501" t="n">
         <v>50486</v>
@@ -44014,7 +44014,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1505" t="n">
-        <v>4.46519756317139</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1505" t="n">
         <v>56559</v>
@@ -44072,7 +44072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1507" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1507" t="n">
         <v>74370</v>
@@ -44246,7 +44246,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.6581916809082</v>
+        <v>4.65819215774536</v>
       </c>
       <c r="H1513" t="n">
         <v>68965</v>
@@ -44275,7 +44275,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1514" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1514" t="n">
         <v>37612</v>
@@ -44420,7 +44420,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.91259384155273</v>
+        <v>4.91259336471558</v>
       </c>
       <c r="H1519" t="n">
         <v>299942</v>
@@ -44536,7 +44536,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.24594926834106</v>
+        <v>5.24594879150391</v>
       </c>
       <c r="H1523" t="n">
         <v>95208</v>
@@ -44565,7 +44565,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1524" t="n">
-        <v>5.05295419692993</v>
+        <v>5.05295372009277</v>
       </c>
       <c r="H1524" t="n">
         <v>126230</v>
@@ -44623,7 +44623,7 @@
         <v>5.75</v>
       </c>
       <c r="G1526" t="n">
-        <v>5.04418134689331</v>
+        <v>5.04418087005615</v>
       </c>
       <c r="H1526" t="n">
         <v>57227</v>
@@ -44739,7 +44739,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1530" t="n">
-        <v>5.35999059677124</v>
+        <v>5.3599910736084</v>
       </c>
       <c r="H1530" t="n">
         <v>88930</v>
@@ -44797,7 +44797,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.24594926834106</v>
+        <v>5.24594879150391</v>
       </c>
       <c r="H1532" t="n">
         <v>85593</v>
@@ -45000,7 +45000,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1539" t="n">
-        <v>4.96522808074951</v>
+        <v>4.96522855758667</v>
       </c>
       <c r="H1539" t="n">
         <v>57313</v>
@@ -45029,7 +45029,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.98277378082275</v>
+        <v>4.98277425765991</v>
       </c>
       <c r="H1540" t="n">
         <v>44589</v>
@@ -45087,7 +45087,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.6581916809082</v>
+        <v>4.65819215774536</v>
       </c>
       <c r="H1542" t="n">
         <v>138270</v>
@@ -45203,7 +45203,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.6494197845459</v>
+        <v>4.64941930770874</v>
       </c>
       <c r="H1546" t="n">
         <v>24508</v>
@@ -45261,7 +45261,7 @@
         <v>5.5</v>
       </c>
       <c r="G1548" t="n">
-        <v>4.82486915588379</v>
+        <v>4.82486963272095</v>
       </c>
       <c r="H1548" t="n">
         <v>56796</v>
@@ -45348,7 +45348,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1551" t="n">
-        <v>4.86873197555542</v>
+        <v>4.86873149871826</v>
       </c>
       <c r="H1551" t="n">
         <v>56002</v>
@@ -45377,7 +45377,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1552" t="n">
-        <v>4.79855155944824</v>
+        <v>4.7985520362854</v>
       </c>
       <c r="H1552" t="n">
         <v>60085</v>
@@ -45406,7 +45406,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1553" t="n">
-        <v>4.76346158981323</v>
+        <v>4.76346111297607</v>
       </c>
       <c r="H1553" t="n">
         <v>42098</v>
@@ -45435,7 +45435,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1554" t="n">
-        <v>4.76346158981323</v>
+        <v>4.76346111297607</v>
       </c>
       <c r="H1554" t="n">
         <v>70872</v>
@@ -45464,7 +45464,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1555" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1555" t="n">
         <v>105080</v>
@@ -45493,7 +45493,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.93013954162598</v>
+        <v>4.93013906478882</v>
       </c>
       <c r="H1556" t="n">
         <v>107233</v>
@@ -45522,7 +45522,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1557" t="n">
-        <v>4.85118675231934</v>
+        <v>4.85118722915649</v>
       </c>
       <c r="H1557" t="n">
         <v>110467</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.82486915588379</v>
+        <v>4.82486963272095</v>
       </c>
       <c r="H1558" t="n">
         <v>69670</v>
@@ -45580,7 +45580,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.91259384155273</v>
+        <v>4.91259336471558</v>
       </c>
       <c r="H1559" t="n">
         <v>7855</v>
@@ -45667,7 +45667,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.6494197845459</v>
+        <v>4.64941930770874</v>
       </c>
       <c r="H1562" t="n">
         <v>39032</v>
@@ -45899,7 +45899,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.32483673095703</v>
+        <v>4.32483720779419</v>
       </c>
       <c r="H1570" t="n">
         <v>67064</v>
@@ -45928,7 +45928,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.2722020149231</v>
+        <v>4.27220249176025</v>
       </c>
       <c r="H1571" t="n">
         <v>83986</v>
@@ -45986,7 +45986,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.14938735961914</v>
+        <v>4.1493878364563</v>
       </c>
       <c r="H1573" t="n">
         <v>71533</v>
@@ -46131,7 +46131,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.3599271774292</v>
+        <v>4.35992670059204</v>
       </c>
       <c r="H1578" t="n">
         <v>23588</v>
@@ -46160,7 +46160,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.46519756317139</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1579" t="n">
         <v>44797</v>
@@ -46247,7 +46247,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.75468921661377</v>
+        <v>4.75468873977661</v>
       </c>
       <c r="H1582" t="n">
         <v>34531</v>
@@ -46276,7 +46276,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1583" t="n">
         <v>50824</v>
@@ -46421,7 +46421,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>5.0090913772583</v>
+        <v>5.00909185409546</v>
       </c>
       <c r="H1588" t="n">
         <v>44967</v>
@@ -46479,7 +46479,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1590" t="n">
-        <v>5.11436176300049</v>
+        <v>5.11436128616333</v>
       </c>
       <c r="H1590" t="n">
         <v>40558</v>
@@ -46537,7 +46537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>5.24594926834106</v>
+        <v>5.24594879150391</v>
       </c>
       <c r="H1592" t="n">
         <v>29800</v>
@@ -46566,7 +46566,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1593" t="n">
-        <v>5.30735635757446</v>
+        <v>5.3073558807373</v>
       </c>
       <c r="H1593" t="n">
         <v>61562</v>
@@ -46653,7 +46653,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1596" t="n">
-        <v>5.17576837539673</v>
+        <v>5.17576885223389</v>
       </c>
       <c r="H1596" t="n">
         <v>21731</v>
@@ -46682,7 +46682,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1597" t="n">
-        <v>5.31612873077393</v>
+        <v>5.31612777709961</v>
       </c>
       <c r="H1597" t="n">
         <v>23692</v>
@@ -46711,7 +46711,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1598" t="n">
-        <v>5.30735635757446</v>
+        <v>5.3073558807373</v>
       </c>
       <c r="H1598" t="n">
         <v>42196</v>
@@ -46740,7 +46740,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1599" t="n">
-        <v>5.43894338607788</v>
+        <v>5.43894243240356</v>
       </c>
       <c r="H1599" t="n">
         <v>45303</v>
@@ -46769,7 +46769,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>5.43894338607788</v>
+        <v>5.43894243240356</v>
       </c>
       <c r="H1600" t="n">
         <v>73046</v>
@@ -46798,7 +46798,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1601" t="n">
-        <v>5.50912380218506</v>
+        <v>5.5091233253479</v>
       </c>
       <c r="H1601" t="n">
         <v>60060</v>
@@ -46827,7 +46827,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1602" t="n">
-        <v>5.40385293960571</v>
+        <v>5.40385341644287</v>
       </c>
       <c r="H1602" t="n">
         <v>58864</v>
@@ -46856,7 +46856,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1603" t="n">
-        <v>5.50035095214844</v>
+        <v>5.50035047531128</v>
       </c>
       <c r="H1603" t="n">
         <v>48186</v>
@@ -46914,7 +46914,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1605" t="n">
         <v>28457</v>
@@ -46943,7 +46943,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1606" t="n">
         <v>39120</v>
@@ -47059,7 +47059,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>5.51980638504028</v>
+        <v>5.51980686187744</v>
       </c>
       <c r="H1610" t="n">
         <v>31666</v>
@@ -47117,7 +47117,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>5.68083810806274</v>
+        <v>5.68083763122559</v>
       </c>
       <c r="H1612" t="n">
         <v>24162</v>
@@ -47204,7 +47204,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1615" t="n">
         <v>61746</v>
@@ -47291,7 +47291,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1618" t="n">
-        <v>5.49296760559082</v>
+        <v>5.49296808242798</v>
       </c>
       <c r="H1618" t="n">
         <v>39274</v>
@@ -47320,7 +47320,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>5.69872999191284</v>
+        <v>5.69873046875</v>
       </c>
       <c r="H1619" t="n">
         <v>40676</v>
@@ -47610,7 +47610,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1629" t="n">
-        <v>5.75240802764893</v>
+        <v>5.75240755081177</v>
       </c>
       <c r="H1629" t="n">
         <v>17311</v>
@@ -47639,7 +47639,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1630" t="n">
-        <v>5.9492244720459</v>
+        <v>5.94922399520874</v>
       </c>
       <c r="H1630" t="n">
         <v>7878</v>
@@ -47668,7 +47668,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1631" t="n">
-        <v>5.78819227218628</v>
+        <v>5.78819274902344</v>
       </c>
       <c r="H1631" t="n">
         <v>23406</v>
@@ -47755,7 +47755,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.66294622421265</v>
+        <v>5.66294574737549</v>
       </c>
       <c r="H1634" t="n">
         <v>15666</v>
@@ -47784,7 +47784,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1635" t="n">
-        <v>5.60926818847656</v>
+        <v>5.60926866531372</v>
       </c>
       <c r="H1635" t="n">
         <v>34799</v>
@@ -47813,7 +47813,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1636" t="n">
-        <v>5.55559110641479</v>
+        <v>5.55559062957764</v>
       </c>
       <c r="H1636" t="n">
         <v>21394</v>
@@ -47958,7 +47958,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1641" t="n">
-        <v>5.31404399871826</v>
+        <v>5.31404447555542</v>
       </c>
       <c r="H1641" t="n">
         <v>23288</v>
@@ -48132,7 +48132,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1647" t="n">
         <v>20118</v>
@@ -48161,7 +48161,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1648" t="n">
-        <v>5.19774341583252</v>
+        <v>5.19774293899536</v>
       </c>
       <c r="H1648" t="n">
         <v>10022</v>
@@ -48277,7 +48277,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1652" t="n">
-        <v>5.25142049789429</v>
+        <v>5.25142002105713</v>
       </c>
       <c r="H1652" t="n">
         <v>6670</v>
@@ -48335,7 +48335,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1654" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1654" t="n">
         <v>3429</v>
@@ -48393,7 +48393,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1656" t="n">
-        <v>5.04565715789795</v>
+        <v>5.04565811157227</v>
       </c>
       <c r="H1656" t="n">
         <v>10347</v>
@@ -48451,7 +48451,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1658" t="n">
-        <v>5.04565715789795</v>
+        <v>5.04565811157227</v>
       </c>
       <c r="H1658" t="n">
         <v>9242</v>
@@ -48480,7 +48480,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1659" t="n">
         <v>14998</v>
@@ -48538,7 +48538,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.92935705184937</v>
+        <v>4.92935752868652</v>
       </c>
       <c r="H1661" t="n">
         <v>7539</v>
@@ -48596,7 +48596,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1663" t="n">
         <v>4884</v>
@@ -48625,7 +48625,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1664" t="n">
         <v>3654</v>
@@ -48654,7 +48654,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1665" t="n">
         <v>1766</v>
@@ -48799,7 +48799,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1670" t="n">
         <v>2178</v>
@@ -48857,7 +48857,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1672" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1672" t="n">
         <v>1617</v>
@@ -48915,7 +48915,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1674" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1674" t="n">
         <v>32862</v>
@@ -48944,7 +48944,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1675" t="n">
         <v>15998</v>
@@ -49002,7 +49002,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1677" t="n">
         <v>61662</v>
@@ -49031,7 +49031,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1678" t="n">
         <v>48833</v>
@@ -49089,7 +49089,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1680" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1680" t="n">
         <v>3893</v>
@@ -49118,7 +49118,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1681" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1681" t="n">
         <v>2943</v>
@@ -49263,7 +49263,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1686" t="n">
-        <v>5.05460405349731</v>
+        <v>5.05460357666016</v>
       </c>
       <c r="H1686" t="n">
         <v>2708</v>
@@ -49292,7 +49292,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1687" t="n">
-        <v>5.05460405349731</v>
+        <v>5.05460357666016</v>
       </c>
       <c r="H1687" t="n">
         <v>5457</v>
@@ -49321,7 +49321,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1688" t="n">
-        <v>5.05460405349731</v>
+        <v>5.05460357666016</v>
       </c>
       <c r="H1688" t="n">
         <v>1970</v>
@@ -49466,7 +49466,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1693" t="n">
-        <v>4.83094930648804</v>
+        <v>4.8309497833252</v>
       </c>
       <c r="H1693" t="n">
         <v>15155</v>
@@ -49524,7 +49524,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1695" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1695" t="n">
         <v>11114</v>
@@ -49553,7 +49553,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1696" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1696" t="n">
         <v>46629</v>
@@ -49640,7 +49640,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1699" t="n">
-        <v>4.63413286209106</v>
+        <v>4.63413238525391</v>
       </c>
       <c r="H1699" t="n">
         <v>17103</v>
@@ -49756,7 +49756,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.61623954772949</v>
+        <v>4.61624002456665</v>
       </c>
       <c r="H1703" t="n">
         <v>10989</v>
@@ -49814,7 +49814,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1705" t="n">
-        <v>4.7414870262146</v>
+        <v>4.74148750305176</v>
       </c>
       <c r="H1705" t="n">
         <v>16296</v>
@@ -49843,7 +49843,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1706" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1706" t="n">
         <v>30524</v>
@@ -50017,7 +50017,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.57150888442993</v>
+        <v>4.57150936126709</v>
       </c>
       <c r="H1712" t="n">
         <v>15323</v>
@@ -50191,7 +50191,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1718" t="n">
-        <v>4.4641547203064</v>
+        <v>4.46415424346924</v>
       </c>
       <c r="H1718" t="n">
         <v>28499</v>
@@ -50220,7 +50220,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1719" t="n">
-        <v>4.4909930229187</v>
+        <v>4.49099349975586</v>
       </c>
       <c r="H1719" t="n">
         <v>18528</v>
@@ -50278,7 +50278,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1721" t="n">
-        <v>4.4909930229187</v>
+        <v>4.49099349975586</v>
       </c>
       <c r="H1721" t="n">
         <v>12048</v>
@@ -50539,7 +50539,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1730" t="n">
-        <v>4.44178915023804</v>
+        <v>4.4417896270752</v>
       </c>
       <c r="H1730" t="n">
         <v>9172</v>
@@ -50626,7 +50626,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1733" t="n">
-        <v>4.40600490570068</v>
+        <v>4.40600442886353</v>
       </c>
       <c r="H1733" t="n">
         <v>19415</v>
@@ -50829,7 +50829,7 @@
         <v>4.875</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.36127376556396</v>
+        <v>4.36127328872681</v>
       </c>
       <c r="H1740" t="n">
         <v>10091</v>
@@ -50858,7 +50858,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1741" t="n">
-        <v>4.27628421783447</v>
+        <v>4.27628469467163</v>
       </c>
       <c r="H1741" t="n">
         <v>16027</v>
@@ -50945,7 +50945,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363933563232</v>
       </c>
       <c r="H1744" t="n">
         <v>42697</v>
@@ -51003,7 +51003,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1746" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363933563232</v>
       </c>
       <c r="H1746" t="n">
         <v>25541</v>
@@ -51032,7 +51032,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1747" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363933563232</v>
       </c>
       <c r="H1747" t="n">
         <v>14611</v>
@@ -51061,7 +51061,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.63413286209106</v>
+        <v>4.63413238525391</v>
       </c>
       <c r="H1748" t="n">
         <v>24894</v>
@@ -51148,7 +51148,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1751" t="n">
         <v>17367</v>
@@ -51177,7 +51177,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>4.73254108428955</v>
+        <v>4.73254060745239</v>
       </c>
       <c r="H1752" t="n">
         <v>15553</v>
@@ -51293,7 +51293,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1756" t="n">
         <v>11240</v>
@@ -51409,7 +51409,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1760" t="n">
         <v>46326</v>
@@ -51467,7 +51467,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1762" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1762" t="n">
         <v>17489</v>
@@ -51496,7 +51496,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1763" t="n">
         <v>15553</v>
@@ -51554,7 +51554,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1765" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1765" t="n">
         <v>16423</v>
@@ -51583,7 +51583,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1766" t="n">
-        <v>5.19774341583252</v>
+        <v>5.19774293899536</v>
       </c>
       <c r="H1766" t="n">
         <v>9552</v>
@@ -51641,7 +51641,7 @@
         <v>5.75</v>
       </c>
       <c r="G1768" t="n">
-        <v>5.14406585693359</v>
+        <v>5.14406633377075</v>
       </c>
       <c r="H1768" t="n">
         <v>8149</v>
@@ -51670,7 +51670,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1769" t="n">
         <v>11761</v>
@@ -51699,7 +51699,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1770" t="n">
-        <v>5.25142049789429</v>
+        <v>5.25142002105713</v>
       </c>
       <c r="H1770" t="n">
         <v>14837</v>
@@ -51728,7 +51728,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1771" t="n">
-        <v>5.26931238174438</v>
+        <v>5.26931285858154</v>
       </c>
       <c r="H1771" t="n">
         <v>7138</v>
@@ -51786,7 +51786,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.86673402786255</v>
+        <v>4.86673355102539</v>
       </c>
       <c r="H1773" t="n">
         <v>21989</v>
@@ -51844,7 +51844,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1775" t="n">
-        <v>5.05460405349731</v>
+        <v>5.05460357666016</v>
       </c>
       <c r="H1775" t="n">
         <v>5926</v>
@@ -51902,7 +51902,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1777" t="n">
         <v>7772</v>
@@ -51931,7 +51931,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1778" t="n">
         <v>5909</v>
@@ -51960,7 +51960,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1779" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1779" t="n">
         <v>8483</v>
@@ -51989,7 +51989,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1780" t="n">
         <v>77215</v>
@@ -52018,7 +52018,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.71464824676514</v>
+        <v>4.71464872360229</v>
       </c>
       <c r="H1781" t="n">
         <v>40274</v>
@@ -52192,7 +52192,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1787" t="n">
         <v>14425</v>
@@ -52221,7 +52221,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.89357233047485</v>
+        <v>4.8935718536377</v>
       </c>
       <c r="H1788" t="n">
         <v>6623</v>
@@ -52279,7 +52279,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1790" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1790" t="n">
         <v>2351</v>
@@ -52337,7 +52337,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1792" t="n">
-        <v>4.98303508758545</v>
+        <v>4.98303461074829</v>
       </c>
       <c r="H1792" t="n">
         <v>4626</v>
@@ -52540,7 +52540,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.82200288772583</v>
+        <v>4.82200241088867</v>
       </c>
       <c r="H1799" t="n">
         <v>13335</v>
@@ -52569,7 +52569,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1800" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1800" t="n">
         <v>20596</v>
@@ -52598,7 +52598,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.89357233047485</v>
+        <v>4.8935718536377</v>
       </c>
       <c r="H1801" t="n">
         <v>5302</v>
@@ -52714,7 +52714,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1805" t="n">
-        <v>4.83094930648804</v>
+        <v>4.8309497833252</v>
       </c>
       <c r="H1805" t="n">
         <v>9600</v>
@@ -52801,7 +52801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1808" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1808" t="n">
         <v>30637</v>
@@ -52830,7 +52830,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1809" t="n">
         <v>25456</v>
@@ -52888,7 +52888,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1811" t="n">
         <v>17032</v>
@@ -52917,7 +52917,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1812" t="n">
         <v>44688</v>
@@ -52946,7 +52946,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>5.00987339019775</v>
+        <v>5.0098729133606</v>
       </c>
       <c r="H1813" t="n">
         <v>24148</v>
@@ -53004,7 +53004,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1815" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1815" t="n">
         <v>27733</v>
@@ -53033,7 +53033,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1816" t="n">
-        <v>4.98303508758545</v>
+        <v>4.98303461074829</v>
       </c>
       <c r="H1816" t="n">
         <v>53268</v>
@@ -53062,7 +53062,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.95619583129883</v>
+        <v>4.95619630813599</v>
       </c>
       <c r="H1817" t="n">
         <v>4275</v>
@@ -53149,7 +53149,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.95619583129883</v>
+        <v>4.95619630813599</v>
       </c>
       <c r="H1820" t="n">
         <v>3266</v>
@@ -53207,7 +53207,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.8846263885498</v>
+        <v>4.88462686538696</v>
       </c>
       <c r="H1822" t="n">
         <v>5688</v>
@@ -53265,7 +53265,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1824" t="n">
-        <v>5.18879699707031</v>
+        <v>5.18879747390747</v>
       </c>
       <c r="H1824" t="n">
         <v>44682</v>
@@ -53294,7 +53294,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1825" t="n">
         <v>33072</v>
@@ -53323,7 +53323,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.95619583129883</v>
+        <v>4.95619630813599</v>
       </c>
       <c r="H1826" t="n">
         <v>29371</v>
@@ -53352,7 +53352,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1827" t="n">
-        <v>5.04565715789795</v>
+        <v>5.04565811157227</v>
       </c>
       <c r="H1827" t="n">
         <v>9238</v>
@@ -53381,7 +53381,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1828" t="n">
-        <v>5.09038877487183</v>
+        <v>5.09038925170898</v>
       </c>
       <c r="H1828" t="n">
         <v>6484</v>
@@ -53439,7 +53439,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1830" t="n">
-        <v>5.09038877487183</v>
+        <v>5.09038925170898</v>
       </c>
       <c r="H1830" t="n">
         <v>4884</v>
@@ -53555,7 +53555,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092697143555</v>
       </c>
       <c r="H1834" t="n">
         <v>23025</v>
@@ -53845,7 +53845,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1844" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1844" t="n">
         <v>8797</v>
@@ -53990,7 +53990,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1849" t="n">
-        <v>5.05460405349731</v>
+        <v>5.05460357666016</v>
       </c>
       <c r="H1849" t="n">
         <v>5075</v>
@@ -54048,7 +54048,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1851" t="n">
         <v>10038</v>
@@ -54077,7 +54077,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1852" t="n">
-        <v>5.12617349624634</v>
+        <v>5.12617301940918</v>
       </c>
       <c r="H1852" t="n">
         <v>4188</v>
@@ -54106,7 +54106,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1853" t="n">
-        <v>5.12617349624634</v>
+        <v>5.12617301940918</v>
       </c>
       <c r="H1853" t="n">
         <v>6700</v>
@@ -54135,7 +54135,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1854" t="n">
         <v>8009</v>
@@ -54193,7 +54193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1856" t="n">
         <v>18091</v>
@@ -54251,7 +54251,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1858" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1858" t="n">
         <v>6450</v>
@@ -54280,7 +54280,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1859" t="n">
-        <v>5.19774341583252</v>
+        <v>5.19774293899536</v>
       </c>
       <c r="H1859" t="n">
         <v>3843</v>
@@ -54309,7 +54309,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1860" t="n">
-        <v>5.20669031143188</v>
+        <v>5.20668983459473</v>
       </c>
       <c r="H1860" t="n">
         <v>6979</v>
@@ -80009,6 +80009,35 @@
         <v>36108</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>4.92000007629395</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>4.83500003814697</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>19240</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59126996994019</v>
+        <v>3.59127044677734</v>
       </c>
       <c r="H2" t="n">
         <v>72929</v>
@@ -456,7 +456,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60514211654663</v>
+        <v>3.60514235496521</v>
       </c>
       <c r="H3" t="n">
         <v>46376</v>
@@ -485,7 +485,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G4" t="n">
-        <v>3.51420450210571</v>
+        <v>3.51420426368713</v>
       </c>
       <c r="H4" t="n">
         <v>44293</v>
@@ -514,7 +514,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>3.38935732841492</v>
+        <v>3.3893575668335</v>
       </c>
       <c r="H5" t="n">
         <v>181917</v>
@@ -543,7 +543,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G6" t="n">
-        <v>3.34620118141174</v>
+        <v>3.34620094299316</v>
       </c>
       <c r="H6" t="n">
         <v>71336</v>
@@ -572,7 +572,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G7" t="n">
-        <v>3.28608918190002</v>
+        <v>3.2860894203186</v>
       </c>
       <c r="H7" t="n">
         <v>56010</v>
@@ -630,7 +630,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.39089870452881</v>
+        <v>3.39089918136597</v>
       </c>
       <c r="H9" t="n">
         <v>38098</v>
@@ -659,7 +659,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G10" t="n">
-        <v>3.37856793403625</v>
+        <v>3.37856841087341</v>
       </c>
       <c r="H10" t="n">
         <v>50536</v>
@@ -717,7 +717,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G12" t="n">
-        <v>3.31229138374329</v>
+        <v>3.31229186058044</v>
       </c>
       <c r="H12" t="n">
         <v>77310</v>
@@ -746,7 +746,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33695244789124</v>
+        <v>3.33695292472839</v>
       </c>
       <c r="H13" t="n">
         <v>58756</v>
@@ -775,7 +775,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05026793479919</v>
+        <v>3.05026769638062</v>
       </c>
       <c r="H14" t="n">
         <v>232026</v>
@@ -804,7 +804,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G15" t="n">
-        <v>3.17203235626221</v>
+        <v>3.17203211784363</v>
       </c>
       <c r="H15" t="n">
         <v>196273</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.22135400772095</v>
+        <v>3.22135353088379</v>
       </c>
       <c r="H16" t="n">
         <v>58469</v>
@@ -862,7 +862,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.14428853988647</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H17" t="n">
         <v>52350</v>
@@ -891,7 +891,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>3.19823455810547</v>
+        <v>3.19823479652405</v>
       </c>
       <c r="H18" t="n">
         <v>61482</v>
@@ -920,7 +920,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G19" t="n">
-        <v>3.12579274177551</v>
+        <v>3.12579250335693</v>
       </c>
       <c r="H19" t="n">
         <v>16969</v>
@@ -978,7 +978,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>3.15970134735107</v>
+        <v>3.15970158576965</v>
       </c>
       <c r="H21" t="n">
         <v>25718</v>
@@ -1007,7 +1007,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09958982467651</v>
+        <v>3.09959006309509</v>
       </c>
       <c r="H22" t="n">
         <v>45339</v>
@@ -1036,7 +1036,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G23" t="n">
-        <v>3.10575532913208</v>
+        <v>3.10575556755066</v>
       </c>
       <c r="H23" t="n">
         <v>42488</v>
@@ -1123,7 +1123,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G26" t="n">
-        <v>2.98553276062012</v>
+        <v>2.98553252220154</v>
       </c>
       <c r="H26" t="n">
         <v>72543</v>
@@ -1181,7 +1181,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85143828392029</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H28" t="n">
         <v>67495</v>
@@ -1210,7 +1210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7743718624115</v>
+        <v>2.77437233924866</v>
       </c>
       <c r="H29" t="n">
         <v>80936</v>
@@ -1239,7 +1239,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76666522026062</v>
+        <v>2.76666569709778</v>
       </c>
       <c r="H30" t="n">
         <v>152737</v>
@@ -1268,7 +1268,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G31" t="n">
-        <v>2.69422340393066</v>
+        <v>2.69422364234924</v>
       </c>
       <c r="H31" t="n">
         <v>107730</v>
@@ -1297,7 +1297,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G32" t="n">
-        <v>2.69576454162598</v>
+        <v>2.69576501846313</v>
       </c>
       <c r="H32" t="n">
         <v>156635</v>
@@ -1326,7 +1326,7 @@
         <v>3.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.69730615615845</v>
+        <v>2.69730639457703</v>
       </c>
       <c r="H33" t="n">
         <v>38029</v>
@@ -1355,7 +1355,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85143828392029</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H34" t="n">
         <v>57855</v>
@@ -1384,7 +1384,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G35" t="n">
-        <v>2.83294224739075</v>
+        <v>2.83294200897217</v>
       </c>
       <c r="H35" t="n">
         <v>30597</v>
@@ -1442,7 +1442,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91925573348999</v>
+        <v>2.91925597190857</v>
       </c>
       <c r="H37" t="n">
         <v>20925</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.85143828392029</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H39" t="n">
         <v>25330</v>
@@ -1529,7 +1529,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.85143828392029</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H40" t="n">
         <v>31248</v>
@@ -1558,7 +1558,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93004536628723</v>
+        <v>2.93004512786865</v>
       </c>
       <c r="H41" t="n">
         <v>36631</v>
@@ -1587,7 +1587,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G42" t="n">
-        <v>2.99478030204773</v>
+        <v>2.99478054046631</v>
       </c>
       <c r="H42" t="n">
         <v>55878</v>
@@ -1616,7 +1616,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.04410243034363</v>
+        <v>3.04410290718079</v>
       </c>
       <c r="H43" t="n">
         <v>31054</v>
@@ -1645,7 +1645,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G44" t="n">
-        <v>3.00402808189392</v>
+        <v>3.0040283203125</v>
       </c>
       <c r="H44" t="n">
         <v>22788</v>
@@ -1674,7 +1674,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G45" t="n">
-        <v>2.90075993537903</v>
+        <v>2.90076017379761</v>
       </c>
       <c r="H45" t="n">
         <v>67040</v>
@@ -1732,7 +1732,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G47" t="n">
-        <v>2.94391679763794</v>
+        <v>2.94391703605652</v>
       </c>
       <c r="H47" t="n">
         <v>29987</v>
@@ -1790,7 +1790,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99786305427551</v>
+        <v>2.99786281585693</v>
       </c>
       <c r="H49" t="n">
         <v>12452</v>
@@ -1935,7 +1935,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G54" t="n">
-        <v>3.03639626502991</v>
+        <v>3.03639578819275</v>
       </c>
       <c r="H54" t="n">
         <v>44709</v>
@@ -1964,7 +1964,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G55" t="n">
-        <v>3.07030510902405</v>
+        <v>3.07030487060547</v>
       </c>
       <c r="H55" t="n">
         <v>14032</v>
@@ -1993,7 +1993,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.14428853988647</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H56" t="n">
         <v>126601</v>
@@ -2022,7 +2022,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G57" t="n">
-        <v>3.22135400772095</v>
+        <v>3.22135353088379</v>
       </c>
       <c r="H57" t="n">
         <v>62497</v>
@@ -2080,7 +2080,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>3.26759362220764</v>
+        <v>3.26759338378906</v>
       </c>
       <c r="H59" t="n">
         <v>68882</v>
@@ -2138,7 +2138,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G61" t="n">
-        <v>3.17511391639709</v>
+        <v>3.17511439323425</v>
       </c>
       <c r="H61" t="n">
         <v>11417</v>
@@ -2167,7 +2167,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G62" t="n">
-        <v>3.17357349395752</v>
+        <v>3.17357301712036</v>
       </c>
       <c r="H62" t="n">
         <v>15210</v>
@@ -2196,7 +2196,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14428853988647</v>
+        <v>3.14428782463074</v>
       </c>
       <c r="H63" t="n">
         <v>22488</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.12887477874756</v>
+        <v>3.12887525558472</v>
       </c>
       <c r="H65" t="n">
         <v>34918</v>
@@ -2283,7 +2283,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G66" t="n">
-        <v>3.13504004478455</v>
+        <v>3.13504028320312</v>
       </c>
       <c r="H66" t="n">
         <v>37530</v>
@@ -2312,7 +2312,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G67" t="n">
-        <v>3.03793740272522</v>
+        <v>3.03793716430664</v>
       </c>
       <c r="H67" t="n">
         <v>20927</v>
@@ -2341,7 +2341,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G68" t="n">
-        <v>3.04718494415283</v>
+        <v>3.04718518257141</v>
       </c>
       <c r="H68" t="n">
         <v>20107</v>
@@ -2370,7 +2370,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G69" t="n">
-        <v>3.07492876052856</v>
+        <v>3.07492852210999</v>
       </c>
       <c r="H69" t="n">
         <v>21306</v>
@@ -2457,7 +2457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G72" t="n">
-        <v>2.89767718315125</v>
+        <v>2.8976776599884</v>
       </c>
       <c r="H72" t="n">
         <v>32000</v>
@@ -2544,7 +2544,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G75" t="n">
-        <v>2.80211544036865</v>
+        <v>2.80211567878723</v>
       </c>
       <c r="H75" t="n">
         <v>55881</v>
@@ -2631,7 +2631,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G78" t="n">
-        <v>2.92233896255493</v>
+        <v>2.92233848571777</v>
       </c>
       <c r="H78" t="n">
         <v>48703</v>
@@ -2660,7 +2660,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G79" t="n">
-        <v>2.93775177001953</v>
+        <v>2.93775153160095</v>
       </c>
       <c r="H79" t="n">
         <v>15380</v>
@@ -2747,7 +2747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85914468765259</v>
+        <v>2.85914444923401</v>
       </c>
       <c r="H82" t="n">
         <v>23339</v>
@@ -2776,7 +2776,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>2.79749202728271</v>
+        <v>2.79749178886414</v>
       </c>
       <c r="H83" t="n">
         <v>43312</v>
@@ -2863,7 +2863,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.78053760528564</v>
+        <v>2.78053736686707</v>
       </c>
       <c r="H86" t="n">
         <v>36406</v>
@@ -2921,7 +2921,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67110300064087</v>
+        <v>2.67110395431519</v>
       </c>
       <c r="H88" t="n">
         <v>11008</v>
@@ -2950,7 +2950,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>2.59557867050171</v>
+        <v>2.59557914733887</v>
       </c>
       <c r="H89" t="n">
         <v>60448</v>
@@ -3008,7 +3008,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>2.65723180770874</v>
+        <v>2.65723156929016</v>
       </c>
       <c r="H91" t="n">
         <v>18592</v>
@@ -3037,7 +3037,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.70501303672791</v>
+        <v>2.70501279830933</v>
       </c>
       <c r="H92" t="n">
         <v>35213</v>
@@ -3095,7 +3095,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G94" t="n">
-        <v>2.66647934913635</v>
+        <v>2.66647958755493</v>
       </c>
       <c r="H94" t="n">
         <v>45599</v>
@@ -3124,7 +3124,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>2.53546810150146</v>
+        <v>2.53546786308289</v>
       </c>
       <c r="H95" t="n">
         <v>173451</v>
@@ -3153,7 +3153,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48152160644531</v>
+        <v>2.48152184486389</v>
       </c>
       <c r="H96" t="n">
         <v>102059</v>
@@ -3182,7 +3182,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G97" t="n">
-        <v>2.44144725799561</v>
+        <v>2.44144701957703</v>
       </c>
       <c r="H97" t="n">
         <v>17204</v>
@@ -3211,7 +3211,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.42757534980774</v>
+        <v>2.42757511138916</v>
       </c>
       <c r="H98" t="n">
         <v>26401</v>
@@ -3240,7 +3240,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>2.46610856056213</v>
+        <v>2.46610832214355</v>
       </c>
       <c r="H99" t="n">
         <v>80928</v>
@@ -3269,7 +3269,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55043387413025</v>
+        <v>2.55043363571167</v>
       </c>
       <c r="H100" t="n">
         <v>23573</v>
@@ -3298,7 +3298,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.53293180465698</v>
+        <v>2.53293204307556</v>
       </c>
       <c r="H101" t="n">
         <v>61597</v>
@@ -3356,7 +3356,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G103" t="n">
-        <v>2.50747561454773</v>
+        <v>2.50747537612915</v>
       </c>
       <c r="H103" t="n">
         <v>38471</v>
@@ -3385,7 +3385,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.55361557006836</v>
+        <v>2.55361580848694</v>
       </c>
       <c r="H104" t="n">
         <v>41372</v>
@@ -3414,7 +3414,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G105" t="n">
-        <v>2.53770518302917</v>
+        <v>2.53770542144775</v>
       </c>
       <c r="H105" t="n">
         <v>43480</v>
@@ -3530,7 +3530,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G109" t="n">
-        <v>2.66339707374573</v>
+        <v>2.66339683532715</v>
       </c>
       <c r="H109" t="n">
         <v>176680</v>
@@ -3559,7 +3559,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H110" t="n">
         <v>125977</v>
@@ -3617,7 +3617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H112" t="n">
         <v>290102</v>
@@ -3646,7 +3646,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G113" t="n">
-        <v>2.65703296661377</v>
+        <v>2.65703272819519</v>
       </c>
       <c r="H113" t="n">
         <v>21063</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.34678030014038</v>
+        <v>2.34678077697754</v>
       </c>
       <c r="H116" t="n">
         <v>57327</v>
@@ -3791,7 +3791,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.34678030014038</v>
+        <v>2.34678077697754</v>
       </c>
       <c r="H118" t="n">
         <v>55466</v>
@@ -3820,7 +3820,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>2.45019817352295</v>
+        <v>2.45019769668579</v>
       </c>
       <c r="H119" t="n">
         <v>187802</v>
@@ -3878,7 +3878,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>2.46610856056213</v>
+        <v>2.46610832214355</v>
       </c>
       <c r="H121" t="n">
         <v>45232</v>
@@ -3907,7 +3907,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G122" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H122" t="n">
         <v>106354</v>
@@ -3994,7 +3994,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14790058135986</v>
+        <v>2.14790105819702</v>
       </c>
       <c r="H125" t="n">
         <v>176396</v>
@@ -4023,7 +4023,7 @@
         <v>2.75</v>
       </c>
       <c r="G126" t="n">
-        <v>2.18767714500427</v>
+        <v>2.18767690658569</v>
       </c>
       <c r="H126" t="n">
         <v>311230</v>
@@ -4110,7 +4110,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.30700469017029</v>
+        <v>2.30700492858887</v>
       </c>
       <c r="H129" t="n">
         <v>136895</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.32291531562805</v>
+        <v>2.32291483879089</v>
       </c>
       <c r="H130" t="n">
         <v>32482</v>
@@ -4197,7 +4197,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="n">
-        <v>2.1463098526001</v>
+        <v>2.14631009101868</v>
       </c>
       <c r="H132" t="n">
         <v>157907</v>
@@ -4226,7 +4226,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="n">
-        <v>2.17813038825989</v>
+        <v>2.17813062667847</v>
       </c>
       <c r="H133" t="n">
         <v>87599</v>
@@ -4342,7 +4342,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G137" t="n">
-        <v>2.28632140159607</v>
+        <v>2.28632116317749</v>
       </c>
       <c r="H137" t="n">
         <v>96462</v>
@@ -4371,7 +4371,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>2.28313851356506</v>
+        <v>2.28313899040222</v>
       </c>
       <c r="H138" t="n">
         <v>109004</v>
@@ -4400,7 +4400,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>2.27041053771973</v>
+        <v>2.27041077613831</v>
       </c>
       <c r="H139" t="n">
         <v>22031</v>
@@ -4429,7 +4429,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="n">
-        <v>2.27041053771973</v>
+        <v>2.27041077613831</v>
       </c>
       <c r="H140" t="n">
         <v>51795</v>
@@ -4487,7 +4487,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>2.48201870918274</v>
+        <v>2.48201847076416</v>
       </c>
       <c r="H142" t="n">
         <v>81818</v>
@@ -4545,7 +4545,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51383996009827</v>
+        <v>2.51383948326111</v>
       </c>
       <c r="H144" t="n">
         <v>31905</v>
@@ -4574,7 +4574,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G145" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H145" t="n">
         <v>74728</v>
@@ -4603,7 +4603,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G146" t="n">
-        <v>2.83522891998291</v>
+        <v>2.83522915840149</v>
       </c>
       <c r="H146" t="n">
         <v>321439</v>
@@ -4632,7 +4632,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="n">
-        <v>2.77795171737671</v>
+        <v>2.77795219421387</v>
       </c>
       <c r="H147" t="n">
         <v>193727</v>
@@ -4661,7 +4661,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H148" t="n">
         <v>65327</v>
@@ -4690,7 +4690,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H149" t="n">
         <v>491545</v>
@@ -4719,7 +4719,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G150" t="n">
-        <v>2.54088759422302</v>
+        <v>2.54088735580444</v>
       </c>
       <c r="H150" t="n">
         <v>248346</v>
@@ -4748,7 +4748,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G151" t="n">
-        <v>2.51383996009827</v>
+        <v>2.51383948326111</v>
       </c>
       <c r="H151" t="n">
         <v>124544</v>
@@ -4777,7 +4777,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>2.55361557006836</v>
+        <v>2.55361580848694</v>
       </c>
       <c r="H152" t="n">
         <v>45450</v>
@@ -4806,7 +4806,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G153" t="n">
-        <v>2.55043387413025</v>
+        <v>2.55043363571167</v>
       </c>
       <c r="H153" t="n">
         <v>144787</v>
@@ -4835,7 +4835,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G154" t="n">
-        <v>2.53770518302917</v>
+        <v>2.53770542144775</v>
       </c>
       <c r="H154" t="n">
         <v>74990</v>
@@ -4864,7 +4864,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G155" t="n">
-        <v>2.52179479598999</v>
+        <v>2.52179455757141</v>
       </c>
       <c r="H155" t="n">
         <v>53869</v>
@@ -4893,7 +4893,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>2.52179479598999</v>
+        <v>2.52179455757141</v>
       </c>
       <c r="H156" t="n">
         <v>14282</v>
@@ -4922,7 +4922,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="n">
-        <v>2.51861238479614</v>
+        <v>2.51861262321472</v>
       </c>
       <c r="H157" t="n">
         <v>42162</v>
@@ -4951,7 +4951,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G158" t="n">
-        <v>2.51383996009827</v>
+        <v>2.51383948326111</v>
       </c>
       <c r="H158" t="n">
         <v>36996</v>
@@ -4980,7 +4980,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G159" t="n">
-        <v>2.51224851608276</v>
+        <v>2.51224827766418</v>
       </c>
       <c r="H159" t="n">
         <v>72706</v>
@@ -5009,7 +5009,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G160" t="n">
-        <v>2.47883677482605</v>
+        <v>2.47883629798889</v>
       </c>
       <c r="H160" t="n">
         <v>74187</v>
@@ -5038,7 +5038,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H161" t="n">
         <v>18301</v>
@@ -5096,7 +5096,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G163" t="n">
-        <v>2.46610856056213</v>
+        <v>2.46610832214355</v>
       </c>
       <c r="H163" t="n">
         <v>61075</v>
@@ -5125,7 +5125,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H164" t="n">
         <v>47798</v>
@@ -5154,7 +5154,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G165" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H165" t="n">
         <v>44840</v>
@@ -5183,7 +5183,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="n">
-        <v>2.58066320419312</v>
+        <v>2.58066296577454</v>
       </c>
       <c r="H166" t="n">
         <v>115779</v>
@@ -5212,7 +5212,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G167" t="n">
-        <v>2.57429909706116</v>
+        <v>2.57429885864258</v>
       </c>
       <c r="H167" t="n">
         <v>72831</v>
@@ -5241,7 +5241,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>2.58066320419312</v>
+        <v>2.58066296577454</v>
       </c>
       <c r="H168" t="n">
         <v>37331</v>
@@ -5270,7 +5270,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.59020948410034</v>
+        <v>2.59020924568176</v>
       </c>
       <c r="H169" t="n">
         <v>13943</v>
@@ -5299,7 +5299,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>2.59657382965088</v>
+        <v>2.5965735912323</v>
       </c>
       <c r="H170" t="n">
         <v>50663</v>
@@ -5328,7 +5328,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="n">
-        <v>2.58225440979004</v>
+        <v>2.58225417137146</v>
       </c>
       <c r="H171" t="n">
         <v>48256</v>
@@ -5357,7 +5357,7 @@
         <v>3.25</v>
       </c>
       <c r="G172" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H172" t="n">
         <v>51149</v>
@@ -5386,7 +5386,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="n">
-        <v>2.63475823402405</v>
+        <v>2.63475871086121</v>
       </c>
       <c r="H173" t="n">
         <v>113264</v>
@@ -5415,7 +5415,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.69839978218079</v>
+        <v>2.69840002059937</v>
       </c>
       <c r="H174" t="n">
         <v>40940</v>
@@ -5502,7 +5502,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G177" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H177" t="n">
         <v>60761</v>
@@ -5531,7 +5531,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H178" t="n">
         <v>27763</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H179" t="n">
         <v>62837</v>
@@ -5589,7 +5589,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G180" t="n">
-        <v>2.59816479682922</v>
+        <v>2.59816455841064</v>
       </c>
       <c r="H180" t="n">
         <v>128255</v>
@@ -5618,7 +5618,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G181" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134696960449</v>
       </c>
       <c r="H181" t="n">
         <v>55933</v>
@@ -5647,7 +5647,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G182" t="n">
-        <v>2.68408012390137</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H182" t="n">
         <v>23673</v>
@@ -5676,7 +5676,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G183" t="n">
-        <v>2.70953679084778</v>
+        <v>2.70953726768494</v>
       </c>
       <c r="H183" t="n">
         <v>54185</v>
@@ -5705,7 +5705,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>2.64907789230347</v>
+        <v>2.64907813072205</v>
       </c>
       <c r="H184" t="n">
         <v>14160</v>
@@ -5792,7 +5792,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="n">
-        <v>2.7111279964447</v>
+        <v>2.71112847328186</v>
       </c>
       <c r="H187" t="n">
         <v>39220</v>
@@ -5850,7 +5850,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>2.64907789230347</v>
+        <v>2.64907813072205</v>
       </c>
       <c r="H189" t="n">
         <v>47560</v>
@@ -5908,7 +5908,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="n">
-        <v>2.61089324951172</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H191" t="n">
         <v>9182</v>
@@ -5937,7 +5937,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.59180068969727</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H192" t="n">
         <v>29200</v>
@@ -5966,7 +5966,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G193" t="n">
-        <v>2.56952571868896</v>
+        <v>2.56952595710754</v>
       </c>
       <c r="H193" t="n">
         <v>54687</v>
@@ -6024,7 +6024,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>2.55361557006836</v>
+        <v>2.55361580848694</v>
       </c>
       <c r="H195" t="n">
         <v>12196</v>
@@ -6053,7 +6053,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>2.56157088279724</v>
+        <v>2.56157040596008</v>
       </c>
       <c r="H196" t="n">
         <v>30767</v>
@@ -6111,7 +6111,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>2.55361557006836</v>
+        <v>2.55361580848694</v>
       </c>
       <c r="H198" t="n">
         <v>11245</v>
@@ -6140,7 +6140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="n">
-        <v>2.60930204391479</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H199" t="n">
         <v>6143</v>
@@ -6169,7 +6169,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748079299927</v>
       </c>
       <c r="H200" t="n">
         <v>17873</v>
@@ -6198,7 +6198,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G201" t="n">
-        <v>2.63157653808594</v>
+        <v>2.63157629966736</v>
       </c>
       <c r="H201" t="n">
         <v>48572</v>
@@ -6227,7 +6227,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="n">
-        <v>2.5472514629364</v>
+        <v>2.54725122451782</v>
       </c>
       <c r="H202" t="n">
         <v>36814</v>
@@ -6256,7 +6256,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134696960449</v>
       </c>
       <c r="H203" t="n">
         <v>21183</v>
@@ -6314,7 +6314,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G205" t="n">
-        <v>2.65226006507874</v>
+        <v>2.65225982666016</v>
       </c>
       <c r="H205" t="n">
         <v>17577</v>
@@ -6343,7 +6343,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H206" t="n">
         <v>52437</v>
@@ -6401,7 +6401,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66817045211792</v>
+        <v>2.66817021369934</v>
       </c>
       <c r="H208" t="n">
         <v>47680</v>
@@ -6430,7 +6430,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H209" t="n">
         <v>24860</v>
@@ -6459,7 +6459,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>2.76840567588806</v>
+        <v>2.76840591430664</v>
       </c>
       <c r="H210" t="n">
         <v>76075</v>
@@ -6517,7 +6517,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G212" t="n">
-        <v>2.68408012390137</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H212" t="n">
         <v>173832</v>
@@ -6633,7 +6633,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G216" t="n">
-        <v>2.64748668670654</v>
+        <v>2.6474871635437</v>
       </c>
       <c r="H216" t="n">
         <v>40967</v>
@@ -6691,7 +6691,7 @@
         <v>3.25</v>
       </c>
       <c r="G218" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H218" t="n">
         <v>23540</v>
@@ -6720,7 +6720,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G219" t="n">
-        <v>2.47406339645386</v>
+        <v>2.47406363487244</v>
       </c>
       <c r="H219" t="n">
         <v>18537</v>
@@ -6749,7 +6749,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>2.55679774284363</v>
+        <v>2.55679726600647</v>
       </c>
       <c r="H220" t="n">
         <v>41230</v>
@@ -6778,7 +6778,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H221" t="n">
         <v>43595</v>
@@ -6836,7 +6836,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H223" t="n">
         <v>18854</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H224" t="n">
         <v>33279</v>
@@ -6952,7 +6952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G227" t="n">
-        <v>2.56952571868896</v>
+        <v>2.56952595710754</v>
       </c>
       <c r="H227" t="n">
         <v>32264</v>
@@ -6981,7 +6981,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="n">
-        <v>2.53929662704468</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H228" t="n">
         <v>26610</v>
@@ -7068,7 +7068,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="n">
-        <v>2.49952006340027</v>
+        <v>2.49952030181885</v>
       </c>
       <c r="H231" t="n">
         <v>16357</v>
@@ -7126,7 +7126,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G233" t="n">
-        <v>2.49633836746216</v>
+        <v>2.49633812904358</v>
       </c>
       <c r="H233" t="n">
         <v>28235</v>
@@ -7271,7 +7271,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="n">
-        <v>2.4486072063446</v>
+        <v>2.44860696792603</v>
       </c>
       <c r="H238" t="n">
         <v>62898</v>
@@ -7329,7 +7329,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G240" t="n">
-        <v>2.56952571868896</v>
+        <v>2.56952595710754</v>
       </c>
       <c r="H240" t="n">
         <v>34467</v>
@@ -7387,7 +7387,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="n">
-        <v>2.53929662704468</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H242" t="n">
         <v>14106</v>
@@ -7416,7 +7416,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="n">
-        <v>2.53929662704468</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H243" t="n">
         <v>21628</v>
@@ -7474,7 +7474,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>2.57588958740234</v>
+        <v>2.57588982582092</v>
       </c>
       <c r="H245" t="n">
         <v>38786</v>
@@ -7503,7 +7503,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>2.52179479598999</v>
+        <v>2.52179455757141</v>
       </c>
       <c r="H246" t="n">
         <v>26112</v>
@@ -7532,7 +7532,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748079299927</v>
       </c>
       <c r="H247" t="n">
         <v>41148</v>
@@ -7561,7 +7561,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748079299927</v>
       </c>
       <c r="H248" t="n">
         <v>27007</v>
@@ -7590,7 +7590,7 @@
         <v>3.25</v>
       </c>
       <c r="G249" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H249" t="n">
         <v>43074</v>
@@ -7648,7 +7648,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>2.57748126983643</v>
+        <v>2.57748079299927</v>
       </c>
       <c r="H251" t="n">
         <v>8970</v>
@@ -7677,7 +7677,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.60930204391479</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H252" t="n">
         <v>9879</v>
@@ -7706,7 +7706,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G253" t="n">
-        <v>2.59975528717041</v>
+        <v>2.59975576400757</v>
       </c>
       <c r="H253" t="n">
         <v>45016</v>
@@ -7735,7 +7735,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="n">
-        <v>2.61248397827148</v>
+        <v>2.61248373985291</v>
       </c>
       <c r="H254" t="n">
         <v>26246</v>
@@ -7764,7 +7764,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="n">
-        <v>2.60930204391479</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H255" t="n">
         <v>17200</v>
@@ -7822,7 +7822,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G257" t="n">
-        <v>2.666579246521</v>
+        <v>2.66657948493958</v>
       </c>
       <c r="H257" t="n">
         <v>25863</v>
@@ -7851,7 +7851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H258" t="n">
         <v>80602</v>
@@ -7880,7 +7880,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>2.75249528884888</v>
+        <v>2.7524950504303</v>
       </c>
       <c r="H259" t="n">
         <v>50582</v>
@@ -7967,7 +7967,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="n">
-        <v>2.71908330917358</v>
+        <v>2.719083070755</v>
       </c>
       <c r="H262" t="n">
         <v>25385</v>
@@ -7996,7 +7996,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G263" t="n">
-        <v>2.64271378517151</v>
+        <v>2.64271354675293</v>
       </c>
       <c r="H263" t="n">
         <v>56966</v>
@@ -8025,7 +8025,7 @@
         <v>3.35199999809265</v>
       </c>
       <c r="G264" t="n">
-        <v>2.666579246521</v>
+        <v>2.66657948493958</v>
       </c>
       <c r="H264" t="n">
         <v>9951</v>
@@ -8054,7 +8054,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G265" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H265" t="n">
         <v>40393</v>
@@ -8112,7 +8112,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>2.71430993080139</v>
+        <v>2.71431016921997</v>
       </c>
       <c r="H267" t="n">
         <v>19300</v>
@@ -8199,7 +8199,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G270" t="n">
-        <v>2.66021513938904</v>
+        <v>2.66021490097046</v>
       </c>
       <c r="H270" t="n">
         <v>35417</v>
@@ -8228,7 +8228,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H271" t="n">
         <v>41308</v>
@@ -8257,7 +8257,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G272" t="n">
-        <v>2.63157653808594</v>
+        <v>2.63157629966736</v>
       </c>
       <c r="H272" t="n">
         <v>44211</v>
@@ -8286,7 +8286,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H273" t="n">
         <v>35545</v>
@@ -8315,7 +8315,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G274" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62521243095398</v>
+        <v>2.62521195411682</v>
       </c>
       <c r="H275" t="n">
         <v>42217</v>
@@ -8373,7 +8373,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134696960449</v>
       </c>
       <c r="H276" t="n">
         <v>44136</v>
@@ -8402,7 +8402,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G277" t="n">
-        <v>2.57429909706116</v>
+        <v>2.57429885864258</v>
       </c>
       <c r="H277" t="n">
         <v>41281</v>
@@ -8431,7 +8431,7 @@
         <v>3.25</v>
       </c>
       <c r="G278" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H278" t="n">
         <v>57674</v>
@@ -8460,7 +8460,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G279" t="n">
-        <v>2.56952571868896</v>
+        <v>2.56952595710754</v>
       </c>
       <c r="H279" t="n">
         <v>36848</v>
@@ -8489,7 +8489,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="n">
-        <v>2.59180068969727</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H280" t="n">
         <v>23457</v>
@@ -8576,7 +8576,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G283" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H283" t="n">
         <v>63086</v>
@@ -8634,7 +8634,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>2.67294311523438</v>
+        <v>2.67294335365295</v>
       </c>
       <c r="H285" t="n">
         <v>26822</v>
@@ -8692,7 +8692,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G287" t="n">
-        <v>2.68408012390137</v>
+        <v>2.6840808391571</v>
       </c>
       <c r="H287" t="n">
         <v>42726</v>
@@ -8721,7 +8721,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>2.70476412773132</v>
+        <v>2.7047643661499</v>
       </c>
       <c r="H288" t="n">
         <v>50895</v>
@@ -8779,7 +8779,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68885374069214</v>
+        <v>2.68885350227356</v>
       </c>
       <c r="H290" t="n">
         <v>82866</v>
@@ -8808,7 +8808,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G291" t="n">
-        <v>2.65703296661377</v>
+        <v>2.65703272819519</v>
       </c>
       <c r="H291" t="n">
         <v>54377</v>
@@ -8866,7 +8866,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H293" t="n">
         <v>34605</v>
@@ -8895,7 +8895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H294" t="n">
         <v>25347</v>
@@ -8924,7 +8924,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>2.60134673118591</v>
+        <v>2.60134696960449</v>
       </c>
       <c r="H295" t="n">
         <v>68336</v>
@@ -9011,7 +9011,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="n">
-        <v>2.58225440979004</v>
+        <v>2.58225417137146</v>
       </c>
       <c r="H298" t="n">
         <v>32196</v>
@@ -9098,7 +9098,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G301" t="n">
-        <v>2.57111740112305</v>
+        <v>2.57111716270447</v>
       </c>
       <c r="H301" t="n">
         <v>13644</v>
@@ -9127,7 +9127,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.59339165687561</v>
+        <v>2.59339141845703</v>
       </c>
       <c r="H302" t="n">
         <v>13538</v>
@@ -9156,7 +9156,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="n">
-        <v>2.61089324951172</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H303" t="n">
         <v>10504</v>
@@ -9185,7 +9185,7 @@
         <v>3.25</v>
       </c>
       <c r="G304" t="n">
-        <v>2.58543634414673</v>
+        <v>2.58543658256531</v>
       </c>
       <c r="H304" t="n">
         <v>15734</v>
@@ -9214,7 +9214,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.60930204391479</v>
+        <v>2.60930180549622</v>
       </c>
       <c r="H305" t="n">
         <v>49411</v>
@@ -9243,7 +9243,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G306" t="n">
-        <v>2.63634920120239</v>
+        <v>2.63634967803955</v>
       </c>
       <c r="H306" t="n">
         <v>16972</v>
@@ -9301,7 +9301,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="n">
-        <v>2.61248397827148</v>
+        <v>2.61248373985291</v>
       </c>
       <c r="H308" t="n">
         <v>66425</v>
@@ -9417,7 +9417,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="n">
-        <v>2.66817045211792</v>
+        <v>2.66817021369934</v>
       </c>
       <c r="H312" t="n">
         <v>57404</v>
@@ -9504,7 +9504,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>2.82409167289734</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H315" t="n">
         <v>207351</v>
@@ -9533,7 +9533,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93546438217163</v>
+        <v>2.93546462059021</v>
       </c>
       <c r="H316" t="n">
         <v>182578</v>
@@ -9591,7 +9591,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="n">
-        <v>2.90682578086853</v>
+        <v>2.90682625770569</v>
       </c>
       <c r="H318" t="n">
         <v>132386</v>
@@ -9649,7 +9649,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G320" t="n">
-        <v>2.90046119689941</v>
+        <v>2.90046167373657</v>
       </c>
       <c r="H320" t="n">
         <v>117232</v>
@@ -9794,7 +9794,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>2.83681988716125</v>
+        <v>2.83682036399841</v>
       </c>
       <c r="H325" t="n">
         <v>158724</v>
@@ -9823,7 +9823,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="n">
-        <v>2.82409167289734</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H326" t="n">
         <v>89204</v>
@@ -9910,7 +9910,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="n">
-        <v>2.81772780418396</v>
+        <v>2.81772756576538</v>
       </c>
       <c r="H329" t="n">
         <v>82116</v>
@@ -9939,7 +9939,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>2.81454610824585</v>
+        <v>2.81454563140869</v>
       </c>
       <c r="H330" t="n">
         <v>69337</v>
@@ -9968,7 +9968,7 @@
         <v>3.5</v>
       </c>
       <c r="G331" t="n">
-        <v>2.78431582450867</v>
+        <v>2.78431558609009</v>
       </c>
       <c r="H331" t="n">
         <v>81473</v>
@@ -10026,7 +10026,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G333" t="n">
-        <v>2.78908920288086</v>
+        <v>2.78908896446228</v>
       </c>
       <c r="H333" t="n">
         <v>69352</v>
@@ -10055,7 +10055,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750389099121</v>
       </c>
       <c r="H334" t="n">
         <v>92029</v>
@@ -10084,7 +10084,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750389099121</v>
       </c>
       <c r="H335" t="n">
         <v>53661</v>
@@ -10113,7 +10113,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.86386752128601</v>
+        <v>2.86386775970459</v>
       </c>
       <c r="H336" t="n">
         <v>58841</v>
@@ -10171,7 +10171,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G338" t="n">
-        <v>2.92750906944275</v>
+        <v>2.92750883102417</v>
       </c>
       <c r="H338" t="n">
         <v>157660</v>
@@ -10200,7 +10200,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750389099121</v>
       </c>
       <c r="H339" t="n">
         <v>238858</v>
@@ -10229,7 +10229,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="n">
-        <v>2.8527307510376</v>
+        <v>2.85273051261902</v>
       </c>
       <c r="H340" t="n">
         <v>51846</v>
@@ -10258,7 +10258,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>2.86386752128601</v>
+        <v>2.86386775970459</v>
       </c>
       <c r="H341" t="n">
         <v>32664</v>
@@ -10287,7 +10287,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>2.82409167289734</v>
+        <v>2.82409191131592</v>
       </c>
       <c r="H342" t="n">
         <v>125438</v>
@@ -10316,7 +10316,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="n">
-        <v>2.85432195663452</v>
+        <v>2.85432171821594</v>
       </c>
       <c r="H343" t="n">
         <v>124053</v>
@@ -10374,7 +10374,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G345" t="n">
-        <v>2.89568877220154</v>
+        <v>2.89568829536438</v>
       </c>
       <c r="H345" t="n">
         <v>92728</v>
@@ -10403,7 +10403,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G346" t="n">
-        <v>2.89409780502319</v>
+        <v>2.89409756660461</v>
       </c>
       <c r="H346" t="n">
         <v>92958</v>
@@ -10432,7 +10432,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="n">
-        <v>2.88932466506958</v>
+        <v>2.889324426651</v>
       </c>
       <c r="H347" t="n">
         <v>90670</v>
@@ -10490,7 +10490,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G349" t="n">
-        <v>2.92750906944275</v>
+        <v>2.92750883102417</v>
       </c>
       <c r="H349" t="n">
         <v>77708</v>
@@ -10548,7 +10548,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G351" t="n">
-        <v>2.99115061759949</v>
+        <v>2.99115085601807</v>
       </c>
       <c r="H351" t="n">
         <v>119094</v>
@@ -10577,7 +10577,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="n">
-        <v>2.93228268623352</v>
+        <v>2.93228244781494</v>
       </c>
       <c r="H352" t="n">
         <v>138348</v>
@@ -10606,7 +10606,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="n">
-        <v>2.91637206077576</v>
+        <v>2.91637182235718</v>
       </c>
       <c r="H353" t="n">
         <v>182186</v>
@@ -10693,7 +10693,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G356" t="n">
-        <v>3.05015897750854</v>
+        <v>3.05015921592712</v>
       </c>
       <c r="H356" t="n">
         <v>57659</v>
@@ -10722,7 +10722,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="n">
-        <v>3.1019115447998</v>
+        <v>3.10191178321838</v>
       </c>
       <c r="H357" t="n">
         <v>147407</v>
@@ -10751,7 +10751,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H358" t="n">
         <v>116685</v>
@@ -10780,7 +10780,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G359" t="n">
-        <v>3.07765221595764</v>
+        <v>3.07765245437622</v>
       </c>
       <c r="H359" t="n">
         <v>16616</v>
@@ -10809,7 +10809,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G360" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H360" t="n">
         <v>56986</v>
@@ -10838,7 +10838,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H361" t="n">
         <v>119655</v>
@@ -10867,7 +10867,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H362" t="n">
         <v>67746</v>
@@ -10896,7 +10896,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H363" t="n">
         <v>54604</v>
@@ -10954,7 +10954,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17954039573669</v>
+        <v>3.17954015731812</v>
       </c>
       <c r="H365" t="n">
         <v>125080</v>
@@ -10983,7 +10983,7 @@
         <v>3.89400005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>3.14881253242493</v>
+        <v>3.14881229400635</v>
       </c>
       <c r="H366" t="n">
         <v>119264</v>
@@ -11099,7 +11099,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352921485901</v>
       </c>
       <c r="H370" t="n">
         <v>81503</v>
@@ -11128,7 +11128,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G371" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H371" t="n">
         <v>96375</v>
@@ -11186,7 +11186,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G373" t="n">
-        <v>3.00972771644592</v>
+        <v>3.00972747802734</v>
       </c>
       <c r="H373" t="n">
         <v>103670</v>
@@ -11215,7 +11215,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>2.91916060447693</v>
+        <v>2.91916036605835</v>
       </c>
       <c r="H374" t="n">
         <v>188128</v>
@@ -11244,7 +11244,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G375" t="n">
-        <v>2.99355483055115</v>
+        <v>2.99355459213257</v>
       </c>
       <c r="H375" t="n">
         <v>71434</v>
@@ -11331,7 +11331,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="n">
-        <v>2.96120977401733</v>
+        <v>2.96120953559875</v>
       </c>
       <c r="H378" t="n">
         <v>38971</v>
@@ -11360,7 +11360,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G379" t="n">
-        <v>2.93048167228699</v>
+        <v>2.93048143386841</v>
       </c>
       <c r="H379" t="n">
         <v>42441</v>
@@ -11389,7 +11389,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="n">
-        <v>2.96120977401733</v>
+        <v>2.96120953559875</v>
       </c>
       <c r="H380" t="n">
         <v>35420</v>
@@ -11418,7 +11418,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>2.92724704742432</v>
+        <v>2.92724680900574</v>
       </c>
       <c r="H381" t="n">
         <v>55506</v>
@@ -11476,7 +11476,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="n">
-        <v>2.87549471855164</v>
+        <v>2.87549495697021</v>
       </c>
       <c r="H383" t="n">
         <v>35865</v>
@@ -11505,7 +11505,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328503608704</v>
       </c>
       <c r="H384" t="n">
         <v>31658</v>
@@ -11534,7 +11534,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>3.01457953453064</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H385" t="n">
         <v>107145</v>
@@ -11563,7 +11563,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="n">
-        <v>3.02266550064087</v>
+        <v>3.02266573905945</v>
       </c>
       <c r="H386" t="n">
         <v>111467</v>
@@ -11592,7 +11592,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="n">
-        <v>3.02104806900024</v>
+        <v>3.02104878425598</v>
       </c>
       <c r="H387" t="n">
         <v>12744</v>
@@ -11679,7 +11679,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>3.08088731765747</v>
+        <v>3.08088707923889</v>
       </c>
       <c r="H390" t="n">
         <v>53039</v>
@@ -11708,7 +11708,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705972671509</v>
       </c>
       <c r="H391" t="n">
         <v>49004</v>
@@ -11737,7 +11737,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G392" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749122619629</v>
       </c>
       <c r="H392" t="n">
         <v>163352</v>
@@ -11766,7 +11766,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.14557790756226</v>
+        <v>3.14557766914368</v>
       </c>
       <c r="H393" t="n">
         <v>58156</v>
@@ -11795,7 +11795,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G394" t="n">
-        <v>3.16175055503845</v>
+        <v>3.16175007820129</v>
       </c>
       <c r="H394" t="n">
         <v>52642</v>
@@ -11824,7 +11824,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>3.16498446464539</v>
+        <v>3.16498470306396</v>
       </c>
       <c r="H395" t="n">
         <v>152673</v>
@@ -11882,7 +11882,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="n">
-        <v>3.22482371330261</v>
+        <v>3.22482347488403</v>
       </c>
       <c r="H397" t="n">
         <v>116628</v>
@@ -11969,7 +11969,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22644090652466</v>
+        <v>3.22644114494324</v>
       </c>
       <c r="H400" t="n">
         <v>53278</v>
@@ -11998,7 +11998,7 @@
         <v>3.90199995040894</v>
       </c>
       <c r="G401" t="n">
-        <v>3.15528130531311</v>
+        <v>3.15528106689453</v>
       </c>
       <c r="H401" t="n">
         <v>69013</v>
@@ -12027,7 +12027,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>3.18115735054016</v>
+        <v>3.18115758895874</v>
       </c>
       <c r="H402" t="n">
         <v>78520</v>
@@ -12172,7 +12172,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="n">
-        <v>3.09220743179321</v>
+        <v>3.09220790863037</v>
       </c>
       <c r="H407" t="n">
         <v>101028</v>
@@ -12259,7 +12259,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="n">
-        <v>3.0841212272644</v>
+        <v>3.08412146568298</v>
       </c>
       <c r="H410" t="n">
         <v>32920</v>
@@ -12375,7 +12375,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H414" t="n">
         <v>65128</v>
@@ -12404,7 +12404,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G415" t="n">
-        <v>3.0194308757782</v>
+        <v>3.01943111419678</v>
       </c>
       <c r="H415" t="n">
         <v>8634</v>
@@ -12462,7 +12462,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>3.0614800453186</v>
+        <v>3.06148028373718</v>
       </c>
       <c r="H417" t="n">
         <v>8655</v>
@@ -12491,7 +12491,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G418" t="n">
-        <v>3.05015897750854</v>
+        <v>3.05015921592712</v>
       </c>
       <c r="H418" t="n">
         <v>11880</v>
@@ -12578,7 +12578,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H421" t="n">
         <v>65985</v>
@@ -12665,7 +12665,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G424" t="n">
-        <v>3.0081102848053</v>
+        <v>3.00811052322388</v>
       </c>
       <c r="H424" t="n">
         <v>6957</v>
@@ -12723,7 +12723,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G426" t="n">
-        <v>3.01457953453064</v>
+        <v>3.01457905769348</v>
       </c>
       <c r="H426" t="n">
         <v>6672</v>
@@ -12781,7 +12781,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>3.0647144317627</v>
+        <v>3.06471419334412</v>
       </c>
       <c r="H428" t="n">
         <v>23324</v>
@@ -12868,7 +12868,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H431" t="n">
         <v>40561</v>
@@ -12897,7 +12897,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G432" t="n">
-        <v>3.05501079559326</v>
+        <v>3.05501103401184</v>
       </c>
       <c r="H432" t="n">
         <v>10256</v>
@@ -12926,7 +12926,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>3.06956624984741</v>
+        <v>3.06956648826599</v>
       </c>
       <c r="H433" t="n">
         <v>12085</v>
@@ -12955,7 +12955,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G434" t="n">
-        <v>3.07927012443542</v>
+        <v>3.07926988601685</v>
       </c>
       <c r="H434" t="n">
         <v>22989</v>
@@ -12984,7 +12984,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06309723854065</v>
+        <v>3.06309747695923</v>
       </c>
       <c r="H435" t="n">
         <v>4662</v>
@@ -13013,7 +13013,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G436" t="n">
-        <v>3.08088731765747</v>
+        <v>3.08088707923889</v>
       </c>
       <c r="H436" t="n">
         <v>15381</v>
@@ -13129,7 +13129,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G440" t="n">
-        <v>3.14557790756226</v>
+        <v>3.14557766914368</v>
       </c>
       <c r="H440" t="n">
         <v>45982</v>
@@ -13158,7 +13158,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="n">
-        <v>3.10352897644043</v>
+        <v>3.10352921485901</v>
       </c>
       <c r="H441" t="n">
         <v>27948</v>
@@ -13216,7 +13216,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G443" t="n">
-        <v>3.11646699905396</v>
+        <v>3.11646676063538</v>
       </c>
       <c r="H443" t="n">
         <v>51853</v>
@@ -13245,7 +13245,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H444" t="n">
         <v>73276</v>
@@ -13390,7 +13390,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705972671509</v>
       </c>
       <c r="H449" t="n">
         <v>21094</v>
@@ -13448,7 +13448,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G451" t="n">
-        <v>3.03722095489502</v>
+        <v>3.0372211933136</v>
       </c>
       <c r="H451" t="n">
         <v>275365</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662798881531</v>
       </c>
       <c r="H452" t="n">
         <v>18836</v>
@@ -13506,7 +13506,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G453" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H453" t="n">
         <v>19982</v>
@@ -13535,7 +13535,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H454" t="n">
         <v>47525</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662798881531</v>
       </c>
       <c r="H455" t="n">
         <v>20763</v>
@@ -13593,7 +13593,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G456" t="n">
-        <v>3.0194308757782</v>
+        <v>3.01943111419678</v>
       </c>
       <c r="H456" t="n">
         <v>33701</v>
@@ -13622,7 +13622,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G457" t="n">
-        <v>3.0081102848053</v>
+        <v>3.00811052322388</v>
       </c>
       <c r="H457" t="n">
         <v>14859</v>
@@ -13651,7 +13651,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G458" t="n">
-        <v>3.05501079559326</v>
+        <v>3.05501103401184</v>
       </c>
       <c r="H458" t="n">
         <v>48138</v>
@@ -13680,7 +13680,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G459" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H459" t="n">
         <v>19240</v>
@@ -13709,7 +13709,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G460" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H460" t="n">
         <v>46537</v>
@@ -13738,7 +13738,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G461" t="n">
-        <v>3.02428293228149</v>
+        <v>3.02428317070007</v>
       </c>
       <c r="H461" t="n">
         <v>43036</v>
@@ -13825,7 +13825,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H464" t="n">
         <v>73977</v>
@@ -13854,7 +13854,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G465" t="n">
-        <v>2.88681578636169</v>
+        <v>2.88681554794312</v>
       </c>
       <c r="H465" t="n">
         <v>179816</v>
@@ -13883,7 +13883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G466" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064266204834</v>
       </c>
       <c r="H466" t="n">
         <v>17745</v>
@@ -13970,7 +13970,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H469" t="n">
         <v>29990</v>
@@ -13999,7 +13999,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H470" t="n">
         <v>14253</v>
@@ -14057,7 +14057,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G472" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328503608704</v>
       </c>
       <c r="H472" t="n">
         <v>73459</v>
@@ -14144,7 +14144,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G475" t="n">
-        <v>2.90298819541931</v>
+        <v>2.90298795700073</v>
       </c>
       <c r="H475" t="n">
         <v>8119</v>
@@ -14173,7 +14173,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G476" t="n">
-        <v>2.82374215126038</v>
+        <v>2.82374238967896</v>
       </c>
       <c r="H476" t="n">
         <v>62343</v>
@@ -14231,7 +14231,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.76875519752502</v>
+        <v>2.7687554359436</v>
       </c>
       <c r="H478" t="n">
         <v>16523</v>
@@ -14260,7 +14260,7 @@
         <v>3.40400004386902</v>
       </c>
       <c r="G479" t="n">
-        <v>2.75258278846741</v>
+        <v>2.75258255004883</v>
       </c>
       <c r="H479" t="n">
         <v>44104</v>
@@ -14318,7 +14318,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>2.69274377822876</v>
+        <v>2.69274401664734</v>
       </c>
       <c r="H481" t="n">
         <v>53774</v>
@@ -14376,7 +14376,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.73317575454712</v>
+        <v>2.73317551612854</v>
       </c>
       <c r="H483" t="n">
         <v>13209</v>
@@ -14405,7 +14405,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G484" t="n">
-        <v>2.75419974327087</v>
+        <v>2.75419926643372</v>
       </c>
       <c r="H484" t="n">
         <v>28027</v>
@@ -14463,7 +14463,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064266204834</v>
       </c>
       <c r="H486" t="n">
         <v>33962</v>
@@ -14492,7 +14492,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G487" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064266204834</v>
       </c>
       <c r="H487" t="n">
         <v>64425</v>
@@ -14521,7 +14521,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G488" t="n">
-        <v>2.87064290046692</v>
+        <v>2.87064266204834</v>
       </c>
       <c r="H488" t="n">
         <v>43070</v>
@@ -14666,7 +14666,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H493" t="n">
         <v>35897</v>
@@ -14753,7 +14753,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H496" t="n">
         <v>27203</v>
@@ -14782,7 +14782,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G497" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H497" t="n">
         <v>17713</v>
@@ -14811,7 +14811,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H498" t="n">
         <v>4819</v>
@@ -14869,7 +14869,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G500" t="n">
-        <v>2.99355483055115</v>
+        <v>2.99355459213257</v>
       </c>
       <c r="H500" t="n">
         <v>24148</v>
@@ -14927,7 +14927,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.99840712547302</v>
+        <v>2.99840664863586</v>
       </c>
       <c r="H502" t="n">
         <v>19534</v>
@@ -14956,7 +14956,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G503" t="n">
-        <v>2.95959258079529</v>
+        <v>2.95959234237671</v>
       </c>
       <c r="H503" t="n">
         <v>20163</v>
@@ -14985,7 +14985,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G504" t="n">
-        <v>2.97253036499023</v>
+        <v>2.97253060340881</v>
       </c>
       <c r="H504" t="n">
         <v>26794</v>
@@ -15014,7 +15014,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G505" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H505" t="n">
         <v>20791</v>
@@ -15043,7 +15043,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H506" t="n">
         <v>25108</v>
@@ -15072,7 +15072,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H507" t="n">
         <v>9640</v>
@@ -15101,7 +15101,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G508" t="n">
-        <v>2.96444439888</v>
+        <v>2.96444392204285</v>
       </c>
       <c r="H508" t="n">
         <v>14705</v>
@@ -15130,7 +15130,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G509" t="n">
-        <v>2.98870348930359</v>
+        <v>2.98870301246643</v>
       </c>
       <c r="H509" t="n">
         <v>34208</v>
@@ -15159,7 +15159,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H510" t="n">
         <v>18206</v>
@@ -15246,7 +15246,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G513" t="n">
-        <v>3.02428293228149</v>
+        <v>3.02428317070007</v>
       </c>
       <c r="H513" t="n">
         <v>32857</v>
@@ -15275,7 +15275,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G514" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H514" t="n">
         <v>21697</v>
@@ -15333,7 +15333,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>3.00406694412231</v>
+        <v>3.00406718254089</v>
       </c>
       <c r="H516" t="n">
         <v>21937</v>
@@ -15362,7 +15362,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G517" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H517" t="n">
         <v>30008</v>
@@ -15391,7 +15391,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662798881531</v>
       </c>
       <c r="H518" t="n">
         <v>34740</v>
@@ -15420,7 +15420,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="n">
-        <v>3.08897352218628</v>
+        <v>3.08897399902344</v>
       </c>
       <c r="H519" t="n">
         <v>42643</v>
@@ -15449,7 +15449,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="n">
-        <v>3.08897352218628</v>
+        <v>3.08897399902344</v>
       </c>
       <c r="H520" t="n">
         <v>95749</v>
@@ -15478,7 +15478,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>3.16175055503845</v>
+        <v>3.16175007820129</v>
       </c>
       <c r="H521" t="n">
         <v>147513</v>
@@ -15507,7 +15507,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G522" t="n">
-        <v>3.14962077140808</v>
+        <v>3.1496205329895</v>
       </c>
       <c r="H522" t="n">
         <v>45939</v>
@@ -15536,7 +15536,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705972671509</v>
       </c>
       <c r="H523" t="n">
         <v>65958</v>
@@ -15594,7 +15594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G525" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H525" t="n">
         <v>23093</v>
@@ -15710,7 +15710,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H529" t="n">
         <v>31820</v>
@@ -15884,7 +15884,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G535" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H535" t="n">
         <v>16675</v>
@@ -15913,7 +15913,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G536" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H536" t="n">
         <v>30939</v>
@@ -15942,7 +15942,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.89894533157349</v>
+        <v>2.89894509315491</v>
       </c>
       <c r="H537" t="n">
         <v>43032</v>
@@ -15971,7 +15971,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>2.9151177406311</v>
+        <v>2.91511750221252</v>
       </c>
       <c r="H538" t="n">
         <v>26193</v>
@@ -16000,7 +16000,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>2.89894533157349</v>
+        <v>2.89894509315491</v>
       </c>
       <c r="H539" t="n">
         <v>13819</v>
@@ -16058,7 +16058,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H541" t="n">
         <v>15012</v>
@@ -16087,7 +16087,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>2.8140389919281</v>
+        <v>2.81403875350952</v>
       </c>
       <c r="H542" t="n">
         <v>15169</v>
@@ -16174,7 +16174,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G545" t="n">
-        <v>3.0081102848053</v>
+        <v>3.00811052322388</v>
       </c>
       <c r="H545" t="n">
         <v>13019</v>
@@ -16203,7 +16203,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G546" t="n">
-        <v>3.06875801086426</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H546" t="n">
         <v>37276</v>
@@ -16232,7 +16232,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G547" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H547" t="n">
         <v>29420</v>
@@ -16261,7 +16261,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H548" t="n">
         <v>19728</v>
@@ -16290,7 +16290,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>3.01215314865112</v>
+        <v>3.0121533870697</v>
       </c>
       <c r="H549" t="n">
         <v>22631</v>
@@ -16319,7 +16319,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.01215314865112</v>
+        <v>3.0121533870697</v>
       </c>
       <c r="H550" t="n">
         <v>8795</v>
@@ -16435,7 +16435,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G554" t="n">
-        <v>2.88681578636169</v>
+        <v>2.88681554794312</v>
       </c>
       <c r="H554" t="n">
         <v>37669</v>
@@ -16464,7 +16464,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.85851335525513</v>
+        <v>2.85851359367371</v>
       </c>
       <c r="H555" t="n">
         <v>15320</v>
@@ -16522,7 +16522,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H557" t="n">
         <v>36584</v>
@@ -16609,7 +16609,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G560" t="n">
-        <v>3.02023935317993</v>
+        <v>3.02023959159851</v>
       </c>
       <c r="H560" t="n">
         <v>22138</v>
@@ -16783,7 +16783,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G566" t="n">
-        <v>3.00406694412231</v>
+        <v>3.00406718254089</v>
       </c>
       <c r="H566" t="n">
         <v>26784</v>
@@ -16812,7 +16812,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>2.96363544464111</v>
+        <v>2.96363520622253</v>
       </c>
       <c r="H567" t="n">
         <v>14348</v>
@@ -16841,7 +16841,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G568" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H568" t="n">
         <v>33482</v>
@@ -16870,7 +16870,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H569" t="n">
         <v>20729</v>
@@ -16899,7 +16899,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G570" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H570" t="n">
         <v>12542</v>
@@ -16928,7 +16928,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.97980833053589</v>
+        <v>2.97980809211731</v>
       </c>
       <c r="H571" t="n">
         <v>12871</v>
@@ -16957,7 +16957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G572" t="n">
-        <v>2.95150637626648</v>
+        <v>2.95150589942932</v>
       </c>
       <c r="H572" t="n">
         <v>14977</v>
@@ -16986,7 +16986,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H573" t="n">
         <v>29946</v>
@@ -17015,7 +17015,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G574" t="n">
-        <v>3.0081102848053</v>
+        <v>3.00811052322388</v>
       </c>
       <c r="H574" t="n">
         <v>34804</v>
@@ -17044,7 +17044,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>2.98385119438171</v>
+        <v>2.98385143280029</v>
       </c>
       <c r="H575" t="n">
         <v>72092</v>
@@ -17073,7 +17073,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>2.9676787853241</v>
+        <v>2.96767854690552</v>
       </c>
       <c r="H576" t="n">
         <v>19331</v>
@@ -17131,7 +17131,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>3.02023935317993</v>
+        <v>3.02023959159851</v>
       </c>
       <c r="H578" t="n">
         <v>35878</v>
@@ -17160,7 +17160,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G579" t="n">
-        <v>3.08088731765747</v>
+        <v>3.08088707923889</v>
       </c>
       <c r="H579" t="n">
         <v>44576</v>
@@ -17189,7 +17189,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G580" t="n">
-        <v>3.06875801086426</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H580" t="n">
         <v>37210</v>
@@ -17218,7 +17218,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H581" t="n">
         <v>51320</v>
@@ -17247,7 +17247,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H582" t="n">
         <v>14099</v>
@@ -17276,7 +17276,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G583" t="n">
-        <v>3.08088731765747</v>
+        <v>3.08088707923889</v>
       </c>
       <c r="H583" t="n">
         <v>8012</v>
@@ -17305,7 +17305,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G584" t="n">
-        <v>3.0849301815033</v>
+        <v>3.08493065834045</v>
       </c>
       <c r="H584" t="n">
         <v>11079</v>
@@ -17363,7 +17363,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>3.06875801086426</v>
+        <v>3.06875777244568</v>
       </c>
       <c r="H586" t="n">
         <v>12611</v>
@@ -17392,7 +17392,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>3.0647144317627</v>
+        <v>3.06471419334412</v>
       </c>
       <c r="H587" t="n">
         <v>40607</v>
@@ -17421,7 +17421,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G588" t="n">
-        <v>3.04045510292053</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H588" t="n">
         <v>28278</v>
@@ -17450,7 +17450,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>3.0728006362915</v>
+        <v>3.07280087471008</v>
       </c>
       <c r="H589" t="n">
         <v>141960</v>
@@ -17537,7 +17537,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G592" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749122619629</v>
       </c>
       <c r="H592" t="n">
         <v>11711</v>
@@ -17566,7 +17566,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G593" t="n">
-        <v>3.13749146461487</v>
+        <v>3.13749122619629</v>
       </c>
       <c r="H593" t="n">
         <v>18941</v>
@@ -17624,7 +17624,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G595" t="n">
-        <v>3.0849301815033</v>
+        <v>3.08493065834045</v>
       </c>
       <c r="H595" t="n">
         <v>33246</v>
@@ -17740,7 +17740,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>3.22644090652466</v>
+        <v>3.22644114494324</v>
       </c>
       <c r="H599" t="n">
         <v>44669</v>
@@ -17769,7 +17769,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G600" t="n">
-        <v>3.18196606636047</v>
+        <v>3.18196630477905</v>
       </c>
       <c r="H600" t="n">
         <v>36836</v>
@@ -17856,7 +17856,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G603" t="n">
-        <v>3.21431159973145</v>
+        <v>3.21431112289429</v>
       </c>
       <c r="H603" t="n">
         <v>21035</v>
@@ -17914,7 +17914,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>3.11727571487427</v>
+        <v>3.11727547645569</v>
       </c>
       <c r="H605" t="n">
         <v>16652</v>
@@ -18001,7 +18001,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.17490530014038</v>
+        <v>3.17490553855896</v>
       </c>
       <c r="H608" t="n">
         <v>10245</v>
@@ -18059,7 +18059,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G610" t="n">
-        <v>3.14204716682434</v>
+        <v>3.14204740524292</v>
       </c>
       <c r="H610" t="n">
         <v>35670</v>
@@ -18175,7 +18175,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="n">
-        <v>3.02293682098389</v>
+        <v>3.02293705940247</v>
       </c>
       <c r="H614" t="n">
         <v>74809</v>
@@ -18204,7 +18204,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>3.05579471588135</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H615" t="n">
         <v>8889</v>
@@ -18233,7 +18233,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>3.07633090019226</v>
+        <v>3.07633113861084</v>
       </c>
       <c r="H616" t="n">
         <v>11007</v>
@@ -18262,7 +18262,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="n">
-        <v>3.13794016838074</v>
+        <v>3.13793992996216</v>
       </c>
       <c r="H617" t="n">
         <v>25576</v>
@@ -18349,7 +18349,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G620" t="n">
-        <v>3.0393660068512</v>
+        <v>3.03936576843262</v>
       </c>
       <c r="H620" t="n">
         <v>108303</v>
@@ -18378,7 +18378,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="n">
-        <v>3.05579471588135</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H621" t="n">
         <v>34890</v>
@@ -18436,7 +18436,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>3.1174042224884</v>
+        <v>3.11740398406982</v>
       </c>
       <c r="H623" t="n">
         <v>39985</v>
@@ -18465,7 +18465,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>3.1174042224884</v>
+        <v>3.11740398406982</v>
       </c>
       <c r="H624" t="n">
         <v>56705</v>
@@ -18552,7 +18552,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>3.05990195274353</v>
+        <v>3.05990242958069</v>
       </c>
       <c r="H627" t="n">
         <v>27358</v>
@@ -18610,7 +18610,7 @@
         <v>3.75</v>
       </c>
       <c r="G629" t="n">
-        <v>3.08043837547302</v>
+        <v>3.0804386138916</v>
       </c>
       <c r="H629" t="n">
         <v>20075</v>
@@ -18697,7 +18697,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G632" t="n">
-        <v>3.08865261077881</v>
+        <v>3.08865284919739</v>
       </c>
       <c r="H632" t="n">
         <v>27479</v>
@@ -18813,7 +18813,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>3.0681164264679</v>
+        <v>3.06811690330505</v>
       </c>
       <c r="H636" t="n">
         <v>9875</v>
@@ -18842,7 +18842,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>3.10097479820251</v>
+        <v>3.10097503662109</v>
       </c>
       <c r="H637" t="n">
         <v>55066</v>
@@ -19016,7 +19016,7 @@
         <v>3.75</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08043837547302</v>
+        <v>3.0804386138916</v>
       </c>
       <c r="H643" t="n">
         <v>9594</v>
@@ -19074,7 +19074,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>3.1461546421051</v>
+        <v>3.14615440368652</v>
       </c>
       <c r="H645" t="n">
         <v>21823</v>
@@ -19103,7 +19103,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>3.1461546421051</v>
+        <v>3.14615440368652</v>
       </c>
       <c r="H646" t="n">
         <v>5310</v>
@@ -19277,7 +19277,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>3.25294280052185</v>
+        <v>3.25294303894043</v>
       </c>
       <c r="H652" t="n">
         <v>25210</v>
@@ -19306,7 +19306,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>3.24062132835388</v>
+        <v>3.2406210899353</v>
       </c>
       <c r="H653" t="n">
         <v>22467</v>
@@ -19422,7 +19422,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G657" t="n">
-        <v>3.41723299026489</v>
+        <v>3.41723275184631</v>
       </c>
       <c r="H657" t="n">
         <v>159806</v>
@@ -19480,7 +19480,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>3.35973167419434</v>
+        <v>3.35973143577576</v>
       </c>
       <c r="H659" t="n">
         <v>76457</v>
@@ -19509,7 +19509,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="n">
-        <v>3.46652007102966</v>
+        <v>3.4665195941925</v>
       </c>
       <c r="H660" t="n">
         <v>178638</v>
@@ -19538,7 +19538,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G661" t="n">
-        <v>3.37616086006165</v>
+        <v>3.37616038322449</v>
       </c>
       <c r="H661" t="n">
         <v>771474</v>
@@ -19567,7 +19567,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>3.40901827812195</v>
+        <v>3.40901851654053</v>
       </c>
       <c r="H662" t="n">
         <v>49274</v>
@@ -19596,7 +19596,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>3.44187688827515</v>
+        <v>3.44187664985657</v>
       </c>
       <c r="H663" t="n">
         <v>198699</v>
@@ -19625,7 +19625,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.44187688827515</v>
+        <v>3.44187664985657</v>
       </c>
       <c r="H664" t="n">
         <v>37222</v>
@@ -19654,7 +19654,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="n">
-        <v>3.40080404281616</v>
+        <v>3.40080428123474</v>
       </c>
       <c r="H665" t="n">
         <v>30309</v>
@@ -19683,7 +19683,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>3.38437485694885</v>
+        <v>3.38437461853027</v>
       </c>
       <c r="H666" t="n">
         <v>18534</v>
@@ -19712,7 +19712,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>3.31455183029175</v>
+        <v>3.31455159187317</v>
       </c>
       <c r="H667" t="n">
         <v>39198</v>
@@ -19770,7 +19770,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>3.3063371181488</v>
+        <v>3.30633759498596</v>
       </c>
       <c r="H669" t="n">
         <v>28585</v>
@@ -19828,7 +19828,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>3.35973167419434</v>
+        <v>3.35973143577576</v>
       </c>
       <c r="H671" t="n">
         <v>31771</v>
@@ -19857,7 +19857,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>3.24062132835388</v>
+        <v>3.2406210899353</v>
       </c>
       <c r="H672" t="n">
         <v>62324</v>
@@ -19973,7 +19973,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>3.26937222480774</v>
+        <v>3.26937198638916</v>
       </c>
       <c r="H676" t="n">
         <v>11711</v>
@@ -20060,7 +20060,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G679" t="n">
-        <v>3.21187090873718</v>
+        <v>3.2118706703186</v>
       </c>
       <c r="H679" t="n">
         <v>7737</v>
@@ -20147,7 +20147,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>3.32687330245972</v>
+        <v>3.32687377929688</v>
       </c>
       <c r="H682" t="n">
         <v>18076</v>
@@ -20176,7 +20176,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G683" t="n">
-        <v>3.4993782043457</v>
+        <v>3.49937844276428</v>
       </c>
       <c r="H683" t="n">
         <v>123793</v>
@@ -20205,7 +20205,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.51169943809509</v>
+        <v>3.51169967651367</v>
       </c>
       <c r="H684" t="n">
         <v>122153</v>
@@ -20292,7 +20292,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>3.50759267807007</v>
+        <v>3.50759291648865</v>
       </c>
       <c r="H687" t="n">
         <v>48640</v>
@@ -20321,7 +20321,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="n">
-        <v>3.58563017845154</v>
+        <v>3.58562994003296</v>
       </c>
       <c r="H688" t="n">
         <v>104807</v>
@@ -20379,7 +20379,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="n">
-        <v>3.49116373062134</v>
+        <v>3.49116349220276</v>
       </c>
       <c r="H690" t="n">
         <v>24637</v>
@@ -20437,7 +20437,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>3.70063376426697</v>
+        <v>3.70063400268555</v>
       </c>
       <c r="H692" t="n">
         <v>240141</v>
@@ -20466,7 +20466,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>3.80331468582153</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H693" t="n">
         <v>166131</v>
@@ -20524,7 +20524,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H695" t="n">
         <v>99219</v>
@@ -20553,7 +20553,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G696" t="n">
-        <v>3.60616636276245</v>
+        <v>3.60616683959961</v>
       </c>
       <c r="H696" t="n">
         <v>72075</v>
@@ -20582,7 +20582,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.71706247329712</v>
+        <v>3.71706223487854</v>
       </c>
       <c r="H697" t="n">
         <v>63187</v>
@@ -20611,7 +20611,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>3.70063376426697</v>
+        <v>3.70063400268555</v>
       </c>
       <c r="H698" t="n">
         <v>38470</v>
@@ -20640,7 +20640,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G699" t="n">
-        <v>3.74581360816956</v>
+        <v>3.74581265449524</v>
       </c>
       <c r="H699" t="n">
         <v>33160</v>
@@ -20669,7 +20669,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G700" t="n">
-        <v>3.7211697101593</v>
+        <v>3.72116994857788</v>
       </c>
       <c r="H700" t="n">
         <v>52446</v>
@@ -20698,7 +20698,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>3.75813460350037</v>
+        <v>3.75813484191895</v>
       </c>
       <c r="H701" t="n">
         <v>61208</v>
@@ -20727,7 +20727,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>3.83617305755615</v>
+        <v>3.83617281913757</v>
       </c>
       <c r="H702" t="n">
         <v>109153</v>
@@ -20756,7 +20756,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G703" t="n">
-        <v>3.82795810699463</v>
+        <v>3.82795834541321</v>
       </c>
       <c r="H703" t="n">
         <v>54742</v>
@@ -20785,7 +20785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>3.86081600189209</v>
+        <v>3.86081576347351</v>
       </c>
       <c r="H704" t="n">
         <v>73408</v>
@@ -20814,7 +20814,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G705" t="n">
-        <v>3.97992634773254</v>
+        <v>3.97992587089539</v>
       </c>
       <c r="H705" t="n">
         <v>192175</v>
@@ -20843,7 +20843,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>3.93474650382996</v>
+        <v>3.93474698066711</v>
       </c>
       <c r="H706" t="n">
         <v>142470</v>
@@ -20872,7 +20872,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="n">
-        <v>3.8443865776062</v>
+        <v>3.84438681602478</v>
       </c>
       <c r="H707" t="n">
         <v>138036</v>
@@ -20901,7 +20901,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>3.80331468582153</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H708" t="n">
         <v>105500</v>
@@ -20930,7 +20930,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>3.78688621520996</v>
+        <v>3.7868857383728</v>
       </c>
       <c r="H709" t="n">
         <v>40785</v>
@@ -20988,7 +20988,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867078781128</v>
       </c>
       <c r="H711" t="n">
         <v>108765</v>
@@ -21017,7 +21017,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="n">
-        <v>3.71295475959778</v>
+        <v>3.71295547485352</v>
       </c>
       <c r="H712" t="n">
         <v>30961</v>
@@ -21046,7 +21046,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78277921676636</v>
+        <v>3.7827787399292</v>
       </c>
       <c r="H713" t="n">
         <v>86200</v>
@@ -21075,7 +21075,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79510021209717</v>
+        <v>3.79509997367859</v>
       </c>
       <c r="H714" t="n">
         <v>15542</v>
@@ -21104,7 +21104,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G715" t="n">
-        <v>3.75813460350037</v>
+        <v>3.75813484191895</v>
       </c>
       <c r="H715" t="n">
         <v>24403</v>
@@ -21162,7 +21162,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867078781128</v>
       </c>
       <c r="H717" t="n">
         <v>37906</v>
@@ -21191,7 +21191,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H718" t="n">
         <v>69227</v>
@@ -21220,7 +21220,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G719" t="n">
-        <v>3.7211697101593</v>
+        <v>3.72116994857788</v>
       </c>
       <c r="H719" t="n">
         <v>48205</v>
@@ -21249,7 +21249,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G720" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H720" t="n">
         <v>34708</v>
@@ -21278,7 +21278,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H721" t="n">
         <v>50647</v>
@@ -21336,7 +21336,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G723" t="n">
-        <v>3.81974411010742</v>
+        <v>3.81974339485168</v>
       </c>
       <c r="H723" t="n">
         <v>107484</v>
@@ -21365,7 +21365,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>3.86903047561646</v>
+        <v>3.86903071403503</v>
       </c>
       <c r="H724" t="n">
         <v>78387</v>
@@ -21394,7 +21394,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G725" t="n">
-        <v>3.90599584579468</v>
+        <v>3.90599632263184</v>
       </c>
       <c r="H725" t="n">
         <v>38151</v>
@@ -21423,7 +21423,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>3.9183177947998</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H726" t="n">
         <v>134986</v>
@@ -21452,7 +21452,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>3.9183177947998</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H727" t="n">
         <v>82607</v>
@@ -21481,7 +21481,7 @@
         <v>4.66499996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>3.83206605911255</v>
+        <v>3.83206510543823</v>
       </c>
       <c r="H728" t="n">
         <v>39212</v>
@@ -21510,7 +21510,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G729" t="n">
-        <v>3.79099225997925</v>
+        <v>3.79099273681641</v>
       </c>
       <c r="H729" t="n">
         <v>43175</v>
@@ -21539,7 +21539,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>3.83617305755615</v>
+        <v>3.83617281913757</v>
       </c>
       <c r="H730" t="n">
         <v>32787</v>
@@ -21568,7 +21568,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G731" t="n">
-        <v>3.77045702934265</v>
+        <v>3.77045655250549</v>
       </c>
       <c r="H731" t="n">
         <v>18187</v>
@@ -21597,7 +21597,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H732" t="n">
         <v>33541</v>
@@ -21626,7 +21626,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>3.76224207878113</v>
+        <v>3.76224184036255</v>
       </c>
       <c r="H733" t="n">
         <v>41957</v>
@@ -21655,7 +21655,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>3.6842041015625</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H734" t="n">
         <v>31529</v>
@@ -21742,7 +21742,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G737" t="n">
-        <v>3.59795212745667</v>
+        <v>3.59795260429382</v>
       </c>
       <c r="H737" t="n">
         <v>45226</v>
@@ -21800,7 +21800,7 @@
         <v>4.25</v>
       </c>
       <c r="G739" t="n">
-        <v>3.49116373062134</v>
+        <v>3.49116349220276</v>
       </c>
       <c r="H739" t="n">
         <v>76142</v>
@@ -21887,7 +21887,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G742" t="n">
-        <v>3.60616636276245</v>
+        <v>3.60616683959961</v>
       </c>
       <c r="H742" t="n">
         <v>62698</v>
@@ -21916,7 +21916,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>3.6267032623291</v>
+        <v>3.62670278549194</v>
       </c>
       <c r="H743" t="n">
         <v>33077</v>
@@ -21945,7 +21945,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H744" t="n">
         <v>69787</v>
@@ -22003,7 +22003,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H746" t="n">
         <v>38382</v>
@@ -22061,7 +22061,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867078781128</v>
       </c>
       <c r="H748" t="n">
         <v>166234</v>
@@ -22090,7 +22090,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="n">
-        <v>3.69652581214905</v>
+        <v>3.69652676582336</v>
       </c>
       <c r="H749" t="n">
         <v>52912</v>
@@ -22119,7 +22119,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="n">
-        <v>3.63902473449707</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H750" t="n">
         <v>155173</v>
@@ -22148,7 +22148,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="n">
-        <v>3.6267032623291</v>
+        <v>3.62670278549194</v>
       </c>
       <c r="H751" t="n">
         <v>10478</v>
@@ -22177,7 +22177,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="n">
-        <v>3.56920146942139</v>
+        <v>3.56920123100281</v>
       </c>
       <c r="H752" t="n">
         <v>67819</v>
@@ -22235,7 +22235,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>3.63902473449707</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H754" t="n">
         <v>101246</v>
@@ -22264,7 +22264,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.63902473449707</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H755" t="n">
         <v>21557</v>
@@ -22293,7 +22293,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="n">
-        <v>3.62259554862976</v>
+        <v>3.62259578704834</v>
       </c>
       <c r="H756" t="n">
         <v>15999</v>
@@ -22322,7 +22322,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>3.60205960273743</v>
+        <v>3.60205936431885</v>
       </c>
       <c r="H757" t="n">
         <v>20408</v>
@@ -22351,7 +22351,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H758" t="n">
         <v>12169</v>
@@ -22409,7 +22409,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G760" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H760" t="n">
         <v>42084</v>
@@ -22438,7 +22438,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59795212745667</v>
+        <v>3.59795260429382</v>
       </c>
       <c r="H761" t="n">
         <v>69033</v>
@@ -22467,7 +22467,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G762" t="n">
-        <v>3.61438155174255</v>
+        <v>3.6143810749054</v>
       </c>
       <c r="H762" t="n">
         <v>26366</v>
@@ -22496,7 +22496,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="n">
-        <v>3.63902473449707</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H763" t="n">
         <v>36511</v>
@@ -22554,7 +22554,7 @@
         <v>4.53499984741211</v>
       </c>
       <c r="G765" t="n">
-        <v>3.72527718544006</v>
+        <v>3.72527694702148</v>
       </c>
       <c r="H765" t="n">
         <v>33032</v>
@@ -22583,7 +22583,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="n">
-        <v>3.70474076271057</v>
+        <v>3.70474147796631</v>
       </c>
       <c r="H766" t="n">
         <v>203274</v>
@@ -22612,7 +22612,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G767" t="n">
-        <v>3.61848902702332</v>
+        <v>3.618488073349</v>
       </c>
       <c r="H767" t="n">
         <v>70522</v>
@@ -22757,7 +22757,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="n">
-        <v>3.63902473449707</v>
+        <v>3.63902401924133</v>
       </c>
       <c r="H772" t="n">
         <v>27013</v>
@@ -22844,7 +22844,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.58152341842651</v>
+        <v>3.58152318000793</v>
       </c>
       <c r="H775" t="n">
         <v>34176</v>
@@ -22873,7 +22873,7 @@
         <v>4.5</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69652581214905</v>
+        <v>3.69652676582336</v>
       </c>
       <c r="H776" t="n">
         <v>190049</v>
@@ -22902,7 +22902,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G777" t="n">
-        <v>3.80331468582153</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H777" t="n">
         <v>32135</v>
@@ -22931,7 +22931,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G778" t="n">
-        <v>3.77456378936768</v>
+        <v>3.77456426620483</v>
       </c>
       <c r="H778" t="n">
         <v>20632</v>
@@ -22960,7 +22960,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G779" t="n">
-        <v>3.81974411010742</v>
+        <v>3.81974339485168</v>
       </c>
       <c r="H779" t="n">
         <v>22277</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="n">
-        <v>3.8115291595459</v>
+        <v>3.81152892112732</v>
       </c>
       <c r="H780" t="n">
         <v>11208</v>
@@ -23018,7 +23018,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>3.77867126464844</v>
+        <v>3.77867078781128</v>
       </c>
       <c r="H781" t="n">
         <v>27055</v>
@@ -23047,7 +23047,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G782" t="n">
-        <v>3.85260248184204</v>
+        <v>3.85260128974915</v>
       </c>
       <c r="H782" t="n">
         <v>102037</v>
@@ -23076,7 +23076,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>3.92242455482483</v>
+        <v>3.92242527008057</v>
       </c>
       <c r="H783" t="n">
         <v>29806</v>
@@ -23105,7 +23105,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>3.93474650382996</v>
+        <v>3.93474698066711</v>
       </c>
       <c r="H784" t="n">
         <v>66709</v>
@@ -23134,7 +23134,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G785" t="n">
-        <v>4.00046300888062</v>
+        <v>4.00046253204346</v>
       </c>
       <c r="H785" t="n">
         <v>34090</v>
@@ -23192,7 +23192,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G787" t="n">
-        <v>4.08260774612427</v>
+        <v>4.08260679244995</v>
       </c>
       <c r="H787" t="n">
         <v>68041</v>
@@ -23250,7 +23250,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>4.14832353591919</v>
+        <v>4.14832448959351</v>
       </c>
       <c r="H789" t="n">
         <v>91901</v>
@@ -23366,7 +23366,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H793" t="n">
         <v>168992</v>
@@ -23395,7 +23395,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H794" t="n">
         <v>137854</v>
@@ -23453,7 +23453,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G796" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H796" t="n">
         <v>31628</v>
@@ -23482,7 +23482,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>4.00867748260498</v>
+        <v>4.00867700576782</v>
       </c>
       <c r="H797" t="n">
         <v>68646</v>
@@ -23511,7 +23511,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G798" t="n">
-        <v>3.99224781990051</v>
+        <v>3.99224829673767</v>
       </c>
       <c r="H798" t="n">
         <v>11876</v>
@@ -23627,7 +23627,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G802" t="n">
-        <v>3.99635529518127</v>
+        <v>3.99635577201843</v>
       </c>
       <c r="H802" t="n">
         <v>35324</v>
@@ -23656,7 +23656,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G803" t="n">
-        <v>3.99224781990051</v>
+        <v>3.99224829673767</v>
       </c>
       <c r="H803" t="n">
         <v>28200</v>
@@ -23714,7 +23714,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G805" t="n">
-        <v>3.99224781990051</v>
+        <v>3.99224829673767</v>
       </c>
       <c r="H805" t="n">
         <v>37583</v>
@@ -23743,7 +23743,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>4.17296695709229</v>
+        <v>4.17296743392944</v>
       </c>
       <c r="H806" t="n">
         <v>68680</v>
@@ -23772,7 +23772,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>4.30439901351929</v>
+        <v>4.30439853668213</v>
       </c>
       <c r="H807" t="n">
         <v>103293</v>
@@ -23801,7 +23801,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G808" t="n">
-        <v>4.42761754989624</v>
+        <v>4.42761707305908</v>
       </c>
       <c r="H808" t="n">
         <v>249509</v>
@@ -23859,7 +23859,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>4.48511838912964</v>
+        <v>4.48511791229248</v>
       </c>
       <c r="H810" t="n">
         <v>99785</v>
@@ -23888,7 +23888,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>4.38654470443726</v>
+        <v>4.38654375076294</v>
       </c>
       <c r="H811" t="n">
         <v>220416</v>
@@ -23917,7 +23917,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.48511838912964</v>
+        <v>4.48511791229248</v>
       </c>
       <c r="H812" t="n">
         <v>158616</v>
@@ -23946,7 +23946,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G813" t="n">
-        <v>4.52619075775146</v>
+        <v>4.52619123458862</v>
       </c>
       <c r="H813" t="n">
         <v>139773</v>
@@ -23975,7 +23975,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G814" t="n">
-        <v>4.57547807693481</v>
+        <v>4.57547855377197</v>
       </c>
       <c r="H814" t="n">
         <v>185638</v>
@@ -24062,7 +24062,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G817" t="n">
-        <v>4.57547807693481</v>
+        <v>4.57547855377197</v>
       </c>
       <c r="H817" t="n">
         <v>34360</v>
@@ -24120,7 +24120,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>4.58369207382202</v>
+        <v>4.58369302749634</v>
       </c>
       <c r="H819" t="n">
         <v>21467</v>
@@ -24149,7 +24149,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>4.56726264953613</v>
+        <v>4.56726360321045</v>
       </c>
       <c r="H820" t="n">
         <v>15095</v>
@@ -24178,7 +24178,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>4.53440570831299</v>
+        <v>4.53440523147583</v>
       </c>
       <c r="H821" t="n">
         <v>77444</v>
@@ -24207,7 +24207,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G822" t="n">
-        <v>4.35368633270264</v>
+        <v>4.35368728637695</v>
       </c>
       <c r="H822" t="n">
         <v>61762</v>
@@ -24236,7 +24236,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>4.34547185897827</v>
+        <v>4.34547233581543</v>
       </c>
       <c r="H823" t="n">
         <v>26602</v>
@@ -24265,7 +24265,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G824" t="n">
-        <v>4.37833023071289</v>
+        <v>4.37832927703857</v>
       </c>
       <c r="H824" t="n">
         <v>64270</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.39475870132446</v>
+        <v>4.39475917816162</v>
       </c>
       <c r="H825" t="n">
         <v>34656</v>
@@ -24526,7 +24526,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.35368633270264</v>
+        <v>4.35368728637695</v>
       </c>
       <c r="H833" t="n">
         <v>82546</v>
@@ -24555,7 +24555,7 @@
         <v>5.25</v>
       </c>
       <c r="G834" t="n">
-        <v>4.31261396408081</v>
+        <v>4.31261348724365</v>
       </c>
       <c r="H834" t="n">
         <v>68016</v>
@@ -24584,7 +24584,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G835" t="n">
-        <v>4.43583106994629</v>
+        <v>4.43583154678345</v>
       </c>
       <c r="H835" t="n">
         <v>176046</v>
@@ -24613,7 +24613,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>4.48511838912964</v>
+        <v>4.48511791229248</v>
       </c>
       <c r="H836" t="n">
         <v>44298</v>
@@ -24642,7 +24642,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G837" t="n">
-        <v>4.52619075775146</v>
+        <v>4.52619123458862</v>
       </c>
       <c r="H837" t="n">
         <v>35573</v>
@@ -24671,7 +24671,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>4.65762281417847</v>
+        <v>4.65762329101562</v>
       </c>
       <c r="H838" t="n">
         <v>101495</v>
@@ -24700,7 +24700,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G839" t="n">
-        <v>4.70691013336182</v>
+        <v>4.70690965652466</v>
       </c>
       <c r="H839" t="n">
         <v>61079</v>
@@ -24729,7 +24729,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G840" t="n">
-        <v>4.64119434356689</v>
+        <v>4.64119386672974</v>
       </c>
       <c r="H840" t="n">
         <v>45963</v>
@@ -24787,7 +24787,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.55904960632324</v>
+        <v>4.55904912948608</v>
       </c>
       <c r="H842" t="n">
         <v>31144</v>
@@ -24816,7 +24816,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.55904960632324</v>
+        <v>4.55904912948608</v>
       </c>
       <c r="H843" t="n">
         <v>17460</v>
@@ -24845,7 +24845,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>4.48511838912964</v>
+        <v>4.48511791229248</v>
       </c>
       <c r="H844" t="n">
         <v>22395</v>
@@ -24903,7 +24903,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>4.48511838912964</v>
+        <v>4.48511791229248</v>
       </c>
       <c r="H846" t="n">
         <v>21794</v>
@@ -25048,7 +25048,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G851" t="n">
-        <v>4.38654470443726</v>
+        <v>4.38654375076294</v>
       </c>
       <c r="H851" t="n">
         <v>33576</v>
@@ -25106,7 +25106,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G853" t="n">
-        <v>4.39475870132446</v>
+        <v>4.39475917816162</v>
       </c>
       <c r="H853" t="n">
         <v>26033</v>
@@ -25135,7 +25135,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G854" t="n">
-        <v>4.32082891464233</v>
+        <v>4.32082843780518</v>
       </c>
       <c r="H854" t="n">
         <v>47263</v>
@@ -25164,7 +25164,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G855" t="n">
-        <v>4.32082891464233</v>
+        <v>4.32082843780518</v>
       </c>
       <c r="H855" t="n">
         <v>22155</v>
@@ -25193,7 +25193,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.29618549346924</v>
+        <v>4.29618453979492</v>
       </c>
       <c r="H856" t="n">
         <v>40838</v>
@@ -25222,7 +25222,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.28797006607056</v>
+        <v>4.2879695892334</v>
       </c>
       <c r="H857" t="n">
         <v>47715</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H859" t="n">
         <v>42714</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H860" t="n">
         <v>14810</v>
@@ -25367,7 +25367,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G862" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H862" t="n">
         <v>65534</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H863" t="n">
         <v>47863</v>
@@ -25454,7 +25454,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G865" t="n">
-        <v>4.21306562423706</v>
+        <v>4.21306610107422</v>
       </c>
       <c r="H865" t="n">
         <v>52335</v>
@@ -25483,7 +25483,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G866" t="n">
-        <v>4.1794285774231</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H866" t="n">
         <v>53889</v>
@@ -25512,7 +25512,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23829364776611</v>
+        <v>4.23829412460327</v>
       </c>
       <c r="H867" t="n">
         <v>20899</v>
@@ -25541,7 +25541,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>4.22147512435913</v>
+        <v>4.22147560119629</v>
       </c>
       <c r="H868" t="n">
         <v>27277</v>
@@ -25570,7 +25570,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G869" t="n">
-        <v>4.28874969482422</v>
+        <v>4.28874921798706</v>
       </c>
       <c r="H869" t="n">
         <v>51924</v>
@@ -25599,7 +25599,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>4.25511169433594</v>
+        <v>4.25511264801025</v>
       </c>
       <c r="H870" t="n">
         <v>48746</v>
@@ -25686,7 +25686,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H873" t="n">
         <v>58805</v>
@@ -25715,7 +25715,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H874" t="n">
         <v>14233</v>
@@ -25831,7 +25831,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G878" t="n">
-        <v>4.35602331161499</v>
+        <v>4.35602378845215</v>
       </c>
       <c r="H878" t="n">
         <v>26051</v>
@@ -25860,7 +25860,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H879" t="n">
         <v>24765</v>
@@ -25947,7 +25947,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G882" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H882" t="n">
         <v>25721</v>
@@ -25976,7 +25976,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G883" t="n">
-        <v>4.25511169433594</v>
+        <v>4.25511264801025</v>
       </c>
       <c r="H883" t="n">
         <v>185372</v>
@@ -26005,7 +26005,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>4.1415867805481</v>
+        <v>4.14158582687378</v>
       </c>
       <c r="H884" t="n">
         <v>38616</v>
@@ -26034,7 +26034,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G885" t="n">
-        <v>4.17522430419922</v>
+        <v>4.17522382736206</v>
       </c>
       <c r="H885" t="n">
         <v>71067</v>
@@ -26063,7 +26063,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G886" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487991333008</v>
       </c>
       <c r="H886" t="n">
         <v>76899</v>
@@ -26121,7 +26121,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G888" t="n">
-        <v>3.99862813949585</v>
+        <v>3.99862861633301</v>
       </c>
       <c r="H888" t="n">
         <v>138542</v>
@@ -26208,7 +26208,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>3.86407876014709</v>
+        <v>3.86407899856567</v>
       </c>
       <c r="H891" t="n">
         <v>164930</v>
@@ -26237,7 +26237,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>3.90612578392029</v>
+        <v>3.90612530708313</v>
       </c>
       <c r="H892" t="n">
         <v>65812</v>
@@ -26295,7 +26295,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.85987424850464</v>
+        <v>3.85987448692322</v>
       </c>
       <c r="H894" t="n">
         <v>35895</v>
@@ -26324,7 +26324,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>3.88089752197266</v>
+        <v>3.88089799880981</v>
       </c>
       <c r="H895" t="n">
         <v>65152</v>
@@ -26353,7 +26353,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G896" t="n">
-        <v>3.8766930103302</v>
+        <v>3.87669324874878</v>
       </c>
       <c r="H896" t="n">
         <v>16496</v>
@@ -26382,7 +26382,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H897" t="n">
         <v>93698</v>
@@ -26411,7 +26411,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>3.90612578392029</v>
+        <v>3.90612530708313</v>
       </c>
       <c r="H898" t="n">
         <v>27432</v>
@@ -26440,7 +26440,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G899" t="n">
-        <v>3.84305644035339</v>
+        <v>3.84305572509766</v>
       </c>
       <c r="H899" t="n">
         <v>20737</v>
@@ -26469,7 +26469,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G900" t="n">
-        <v>3.86407876014709</v>
+        <v>3.86407899856567</v>
       </c>
       <c r="H900" t="n">
         <v>83258</v>
@@ -26527,7 +26527,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G902" t="n">
-        <v>4.00283336639404</v>
+        <v>4.00283288955688</v>
       </c>
       <c r="H902" t="n">
         <v>58188</v>
@@ -26556,7 +26556,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G903" t="n">
-        <v>4.02385568618774</v>
+        <v>4.0238561630249</v>
       </c>
       <c r="H903" t="n">
         <v>47622</v>
@@ -26585,7 +26585,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G904" t="n">
-        <v>4.1794285774231</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H904" t="n">
         <v>124527</v>
@@ -26614,7 +26614,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>4.17101907730103</v>
+        <v>4.17101955413818</v>
       </c>
       <c r="H905" t="n">
         <v>138288</v>
@@ -26701,7 +26701,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>3.94396805763245</v>
+        <v>3.94396710395813</v>
       </c>
       <c r="H908" t="n">
         <v>146640</v>
@@ -26730,7 +26730,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>3.75896215438843</v>
+        <v>3.75896239280701</v>
       </c>
       <c r="H909" t="n">
         <v>112580</v>
@@ -26788,7 +26788,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>3.80521392822266</v>
+        <v>3.80521368980408</v>
       </c>
       <c r="H911" t="n">
         <v>41711</v>
@@ -26846,7 +26846,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91873979568481</v>
+        <v>3.91873955726624</v>
       </c>
       <c r="H913" t="n">
         <v>95858</v>
@@ -26904,7 +26904,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>3.85146522521973</v>
+        <v>3.85146474838257</v>
       </c>
       <c r="H915" t="n">
         <v>58796</v>
@@ -26933,7 +26933,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>3.80521392822266</v>
+        <v>3.80521368980408</v>
       </c>
       <c r="H916" t="n">
         <v>31648</v>
@@ -26962,7 +26962,7 @@
         <v>4.5</v>
       </c>
       <c r="G917" t="n">
-        <v>3.78419089317322</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H917" t="n">
         <v>18106</v>
@@ -27020,7 +27020,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G919" t="n">
-        <v>3.63702774047852</v>
+        <v>3.63702750205994</v>
       </c>
       <c r="H919" t="n">
         <v>43334</v>
@@ -27049,7 +27049,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441349029541</v>
       </c>
       <c r="H920" t="n">
         <v>59927</v>
@@ -27194,7 +27194,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G925" t="n">
-        <v>3.58236718177795</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H925" t="n">
         <v>14205</v>
@@ -27223,7 +27223,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.64123225212097</v>
+        <v>3.64123249053955</v>
       </c>
       <c r="H926" t="n">
         <v>20911</v>
@@ -27281,7 +27281,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G928" t="n">
-        <v>3.86828398704529</v>
+        <v>3.86828327178955</v>
       </c>
       <c r="H928" t="n">
         <v>29744</v>
@@ -27310,7 +27310,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>3.77578067779541</v>
+        <v>3.77578163146973</v>
       </c>
       <c r="H929" t="n">
         <v>66248</v>
@@ -27368,7 +27368,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.76316738128662</v>
+        <v>3.7631676197052</v>
       </c>
       <c r="H931" t="n">
         <v>100882</v>
@@ -27484,7 +27484,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G935" t="n">
-        <v>3.65384650230408</v>
+        <v>3.65384602546692</v>
       </c>
       <c r="H935" t="n">
         <v>28600</v>
@@ -27513,7 +27513,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>3.63282346725464</v>
+        <v>3.63282322883606</v>
       </c>
       <c r="H936" t="n">
         <v>17927</v>
@@ -27542,7 +27542,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>3.52350211143494</v>
+        <v>3.52350234985352</v>
       </c>
       <c r="H937" t="n">
         <v>99290</v>
@@ -27716,7 +27716,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441349029541</v>
       </c>
       <c r="H943" t="n">
         <v>74050</v>
@@ -27774,7 +27774,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.76316738128662</v>
+        <v>3.7631676197052</v>
       </c>
       <c r="H945" t="n">
         <v>65323</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>3.70850682258606</v>
+        <v>3.70850706100464</v>
       </c>
       <c r="H947" t="n">
         <v>16961</v>
@@ -27919,7 +27919,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G950" t="n">
-        <v>3.58236718177795</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H950" t="n">
         <v>25708</v>
@@ -27977,7 +27977,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>3.59498119354248</v>
+        <v>3.59498071670532</v>
       </c>
       <c r="H952" t="n">
         <v>29620</v>
@@ -28035,7 +28035,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G954" t="n">
-        <v>3.63282346725464</v>
+        <v>3.63282322883606</v>
       </c>
       <c r="H954" t="n">
         <v>27595</v>
@@ -28064,7 +28064,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>3.5403208732605</v>
+        <v>3.54032039642334</v>
       </c>
       <c r="H955" t="n">
         <v>41593</v>
@@ -28151,7 +28151,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>3.57816243171692</v>
+        <v>3.57816290855408</v>
       </c>
       <c r="H958" t="n">
         <v>20043</v>
@@ -28209,7 +28209,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>3.55293440818787</v>
+        <v>3.55293488502502</v>
       </c>
       <c r="H960" t="n">
         <v>28716</v>
@@ -28267,7 +28267,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G962" t="n">
-        <v>3.65384650230408</v>
+        <v>3.65384602546692</v>
       </c>
       <c r="H962" t="n">
         <v>34756</v>
@@ -28412,7 +28412,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G967" t="n">
-        <v>3.87248826026917</v>
+        <v>3.87248849868774</v>
       </c>
       <c r="H967" t="n">
         <v>98632</v>
@@ -28470,7 +28470,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G969" t="n">
-        <v>3.84726023674011</v>
+        <v>3.84726047515869</v>
       </c>
       <c r="H969" t="n">
         <v>29124</v>
@@ -28499,7 +28499,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85146522521973</v>
+        <v>3.85146474838257</v>
       </c>
       <c r="H970" t="n">
         <v>35812</v>
@@ -28528,7 +28528,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G971" t="n">
-        <v>3.88089752197266</v>
+        <v>3.88089799880981</v>
       </c>
       <c r="H971" t="n">
         <v>36901</v>
@@ -28557,7 +28557,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H972" t="n">
         <v>52932</v>
@@ -28615,7 +28615,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>3.92714905738831</v>
+        <v>3.92714953422546</v>
       </c>
       <c r="H974" t="n">
         <v>60311</v>
@@ -28673,7 +28673,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G976" t="n">
-        <v>4.05328941345215</v>
+        <v>4.05328893661499</v>
       </c>
       <c r="H976" t="n">
         <v>72505</v>
@@ -28702,7 +28702,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G977" t="n">
-        <v>4.15420007705688</v>
+        <v>4.15420055389404</v>
       </c>
       <c r="H977" t="n">
         <v>70913</v>
@@ -28731,7 +28731,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G978" t="n">
-        <v>4.15840482711792</v>
+        <v>4.15840530395508</v>
       </c>
       <c r="H978" t="n">
         <v>104738</v>
@@ -28760,7 +28760,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>4.33920574188232</v>
+        <v>4.33920526504517</v>
       </c>
       <c r="H979" t="n">
         <v>141471</v>
@@ -28789,7 +28789,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>4.25511169433594</v>
+        <v>4.25511264801025</v>
       </c>
       <c r="H980" t="n">
         <v>60835</v>
@@ -28818,7 +28818,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>4.28874969482422</v>
+        <v>4.28874921798706</v>
       </c>
       <c r="H981" t="n">
         <v>45213</v>
@@ -28934,7 +28934,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G985" t="n">
-        <v>4.48216342926025</v>
+        <v>4.48216390609741</v>
       </c>
       <c r="H985" t="n">
         <v>121569</v>
@@ -28963,7 +28963,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G986" t="n">
-        <v>4.39807033538818</v>
+        <v>4.39806985855103</v>
       </c>
       <c r="H986" t="n">
         <v>34439</v>
@@ -29021,7 +29021,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G988" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H988" t="n">
         <v>168462</v>
@@ -29079,7 +29079,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G990" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H990" t="n">
         <v>72376</v>
@@ -29108,7 +29108,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G991" t="n">
-        <v>4.33920574188232</v>
+        <v>4.33920526504517</v>
       </c>
       <c r="H991" t="n">
         <v>75354</v>
@@ -29166,7 +29166,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G993" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H993" t="n">
         <v>33595</v>
@@ -29224,7 +29224,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G995" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H995" t="n">
         <v>97656</v>
@@ -29253,7 +29253,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G996" t="n">
-        <v>4.67557764053345</v>
+        <v>4.67557811737061</v>
       </c>
       <c r="H996" t="n">
         <v>413404</v>
@@ -29282,7 +29282,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G997" t="n">
-        <v>4.70921564102173</v>
+        <v>4.70921516418457</v>
       </c>
       <c r="H997" t="n">
         <v>207895</v>
@@ -29340,7 +29340,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>4.54943752288818</v>
+        <v>4.54943799972534</v>
       </c>
       <c r="H999" t="n">
         <v>155283</v>
@@ -29369,7 +29369,7 @@
         <v>5.5</v>
       </c>
       <c r="G1000" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1000" t="n">
         <v>96233</v>
@@ -29427,7 +29427,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1002" t="n">
         <v>75122</v>
@@ -29456,7 +29456,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1003" t="n">
         <v>47533</v>
@@ -29572,7 +29572,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.39807033538818</v>
+        <v>4.39806985855103</v>
       </c>
       <c r="H1007" t="n">
         <v>120553</v>
@@ -29601,7 +29601,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.46534490585327</v>
+        <v>4.46534538269043</v>
       </c>
       <c r="H1008" t="n">
         <v>238585</v>
@@ -29659,7 +29659,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H1010" t="n">
         <v>60835</v>
@@ -29746,7 +29746,7 @@
         <v>5.25</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41488933563232</v>
+        <v>4.41488885879517</v>
       </c>
       <c r="H1013" t="n">
         <v>30335</v>
@@ -29804,7 +29804,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H1015" t="n">
         <v>17780</v>
@@ -29891,7 +29891,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H1018" t="n">
         <v>21777</v>
@@ -29949,7 +29949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284183502197</v>
       </c>
       <c r="H1020" t="n">
         <v>43906</v>
@@ -29978,7 +29978,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1021" t="n">
-        <v>4.45693588256836</v>
+        <v>4.45693635940552</v>
       </c>
       <c r="H1021" t="n">
         <v>29205</v>
@@ -30036,7 +30036,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.66716909408569</v>
+        <v>4.66716957092285</v>
       </c>
       <c r="H1023" t="n">
         <v>78529</v>
@@ -30065,7 +30065,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1024" t="n">
         <v>28268</v>
@@ -30152,7 +30152,7 @@
         <v>5.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.6251220703125</v>
+        <v>4.62512159347534</v>
       </c>
       <c r="H1027" t="n">
         <v>38338</v>
@@ -30297,7 +30297,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1032" t="n">
         <v>19972</v>
@@ -30384,7 +30384,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1035" t="n">
-        <v>4.35602331161499</v>
+        <v>4.35602378845215</v>
       </c>
       <c r="H1035" t="n">
         <v>19977</v>
@@ -30413,7 +30413,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1036" t="n">
-        <v>4.14579057693481</v>
+        <v>4.14579105377197</v>
       </c>
       <c r="H1036" t="n">
         <v>87006</v>
@@ -30529,7 +30529,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.21306562423706</v>
+        <v>4.21306610107422</v>
       </c>
       <c r="H1040" t="n">
         <v>14580</v>
@@ -30558,7 +30558,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1041" t="n">
-        <v>4.27193117141724</v>
+        <v>4.27193021774292</v>
       </c>
       <c r="H1041" t="n">
         <v>18713</v>
@@ -30587,7 +30587,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.17101907730103</v>
+        <v>4.17101955413818</v>
       </c>
       <c r="H1042" t="n">
         <v>65972</v>
@@ -30616,7 +30616,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1043" t="n">
-        <v>4.14579057693481</v>
+        <v>4.14579105377197</v>
       </c>
       <c r="H1043" t="n">
         <v>33212</v>
@@ -30645,7 +30645,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>4.30556774139404</v>
+        <v>4.3055682182312</v>
       </c>
       <c r="H1044" t="n">
         <v>27804</v>
@@ -30674,7 +30674,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1045" t="n">
-        <v>4.38966131210327</v>
+        <v>4.38966035842896</v>
       </c>
       <c r="H1045" t="n">
         <v>37700</v>
@@ -30732,7 +30732,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1047" t="n">
         <v>436016</v>
@@ -30790,7 +30790,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.54102849960327</v>
+        <v>4.54102897644043</v>
       </c>
       <c r="H1049" t="n">
         <v>28796</v>
@@ -30848,7 +30848,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H1051" t="n">
         <v>25958</v>
@@ -30877,7 +30877,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1052" t="n">
-        <v>4.49898242950439</v>
+        <v>4.49898195266724</v>
       </c>
       <c r="H1052" t="n">
         <v>39312</v>
@@ -30906,7 +30906,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487991333008</v>
       </c>
       <c r="H1053" t="n">
         <v>152414</v>
@@ -30935,7 +30935,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.0280613899231</v>
+        <v>4.02806091308594</v>
       </c>
       <c r="H1054" t="n">
         <v>87604</v>
@@ -30964,7 +30964,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1055" t="n">
-        <v>4.04487943649292</v>
+        <v>4.04487991333008</v>
       </c>
       <c r="H1055" t="n">
         <v>294922</v>
@@ -31022,7 +31022,7 @@
         <v>4.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.78419089317322</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H1057" t="n">
         <v>100789</v>
@@ -31051,7 +31051,7 @@
         <v>4.5</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.78419089317322</v>
+        <v>3.78419065475464</v>
       </c>
       <c r="H1058" t="n">
         <v>46961</v>
@@ -31080,7 +31080,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.6706645488739</v>
+        <v>3.67066502571106</v>
       </c>
       <c r="H1059" t="n">
         <v>45415</v>
@@ -31109,7 +31109,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.59498119354248</v>
+        <v>3.59498071670532</v>
       </c>
       <c r="H1060" t="n">
         <v>98196</v>
@@ -31167,7 +31167,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.29224610328674</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1062" t="n">
         <v>83038</v>
@@ -31196,7 +31196,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.24178981781006</v>
+        <v>3.24179005622864</v>
       </c>
       <c r="H1063" t="n">
         <v>77522</v>
@@ -31254,7 +31254,7 @@
         <v>3.75</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1065" t="n">
         <v>78435</v>
@@ -31399,7 +31399,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.67416167259216</v>
+        <v>2.67416143417358</v>
       </c>
       <c r="H1070" t="n">
         <v>30926</v>
@@ -31428,7 +31428,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.61109137535095</v>
+        <v>2.61109161376953</v>
       </c>
       <c r="H1071" t="n">
         <v>53793</v>
@@ -31486,7 +31486,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.55643081665039</v>
+        <v>2.55643129348755</v>
       </c>
       <c r="H1073" t="n">
         <v>102932</v>
@@ -31515,7 +31515,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.66575217247009</v>
+        <v>2.66575241088867</v>
       </c>
       <c r="H1074" t="n">
         <v>70432</v>
@@ -31573,7 +31573,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.75404977798462</v>
+        <v>2.7540500164032</v>
       </c>
       <c r="H1076" t="n">
         <v>49244</v>
@@ -31602,7 +31602,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.64472889900208</v>
+        <v>2.6447286605835</v>
       </c>
       <c r="H1077" t="n">
         <v>47482</v>
@@ -31718,7 +31718,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.72882175445557</v>
+        <v>2.72882199287415</v>
       </c>
       <c r="H1081" t="n">
         <v>47993</v>
@@ -31747,7 +31747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.64893364906311</v>
+        <v>2.64893341064453</v>
       </c>
       <c r="H1082" t="n">
         <v>39845</v>
@@ -31776,7 +31776,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.65313863754272</v>
+        <v>2.65313816070557</v>
       </c>
       <c r="H1083" t="n">
         <v>58343</v>
@@ -31805,7 +31805,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.79189157485962</v>
+        <v>2.79189205169678</v>
       </c>
       <c r="H1084" t="n">
         <v>378419</v>
@@ -31834,7 +31834,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.82973384857178</v>
+        <v>2.8297336101532</v>
       </c>
       <c r="H1085" t="n">
         <v>42050</v>
@@ -31863,7 +31863,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.86757612228394</v>
+        <v>2.86757564544678</v>
       </c>
       <c r="H1086" t="n">
         <v>74383</v>
@@ -31921,7 +31921,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1088" t="n">
         <v>43109</v>
@@ -31979,7 +31979,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.87598514556885</v>
+        <v>2.87598538398743</v>
       </c>
       <c r="H1090" t="n">
         <v>99582</v>
@@ -32008,7 +32008,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1091" t="n">
         <v>12591</v>
@@ -32037,7 +32037,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.91803169250488</v>
+        <v>2.9180314540863</v>
       </c>
       <c r="H1092" t="n">
         <v>30394</v>
@@ -32066,7 +32066,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.91803169250488</v>
+        <v>2.9180314540863</v>
       </c>
       <c r="H1093" t="n">
         <v>14421</v>
@@ -32095,7 +32095,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1094" t="n">
         <v>44042</v>
@@ -32124,7 +32124,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.94746446609497</v>
+        <v>2.94746398925781</v>
       </c>
       <c r="H1095" t="n">
         <v>24986</v>
@@ -32153,7 +32153,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1096" t="n">
         <v>16579</v>
@@ -32182,7 +32182,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.88439440727234</v>
+        <v>2.88439464569092</v>
       </c>
       <c r="H1097" t="n">
         <v>16136</v>
@@ -32211,7 +32211,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1098" t="n">
         <v>8697</v>
@@ -32240,7 +32240,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91382670402527</v>
+        <v>2.91382694244385</v>
       </c>
       <c r="H1099" t="n">
         <v>11932</v>
@@ -32269,7 +32269,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.88859891891479</v>
+        <v>2.88859868049622</v>
       </c>
       <c r="H1100" t="n">
         <v>10088</v>
@@ -32298,7 +32298,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1101" t="n">
         <v>15640</v>
@@ -32327,7 +32327,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.88018989562988</v>
+        <v>2.8801896572113</v>
       </c>
       <c r="H1102" t="n">
         <v>34379</v>
@@ -32356,7 +32356,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.03996634483337</v>
+        <v>3.03996658325195</v>
       </c>
       <c r="H1103" t="n">
         <v>107338</v>
@@ -32385,7 +32385,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.97689652442932</v>
+        <v>2.9768967628479</v>
       </c>
       <c r="H1104" t="n">
         <v>41109</v>
@@ -32414,7 +32414,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.98530578613281</v>
+        <v>2.98530602455139</v>
       </c>
       <c r="H1105" t="n">
         <v>51255</v>
@@ -32443,7 +32443,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.01894283294678</v>
+        <v>3.01894307136536</v>
       </c>
       <c r="H1106" t="n">
         <v>7512</v>
@@ -32472,7 +32472,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06519460678101</v>
+        <v>3.06519436836243</v>
       </c>
       <c r="H1107" t="n">
         <v>4348</v>
@@ -32559,7 +32559,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.96848750114441</v>
+        <v>2.96848773956299</v>
       </c>
       <c r="H1110" t="n">
         <v>10213</v>
@@ -32588,7 +32588,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>3.02735233306885</v>
+        <v>3.02735257148743</v>
       </c>
       <c r="H1111" t="n">
         <v>23141</v>
@@ -32617,7 +32617,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.98530578613281</v>
+        <v>2.98530602455139</v>
       </c>
       <c r="H1112" t="n">
         <v>12893</v>
@@ -32675,7 +32675,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1114" t="n">
-        <v>3.17872023582458</v>
+        <v>3.17872047424316</v>
       </c>
       <c r="H1114" t="n">
         <v>30466</v>
@@ -32704,7 +32704,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.09462714195251</v>
+        <v>3.09462738037109</v>
       </c>
       <c r="H1115" t="n">
         <v>483852</v>
@@ -32733,7 +32733,7 @@
         <v>3.75</v>
       </c>
       <c r="G1116" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1116" t="n">
         <v>16895</v>
@@ -32762,7 +32762,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.08201336860657</v>
+        <v>3.08201313018799</v>
       </c>
       <c r="H1117" t="n">
         <v>31713</v>
@@ -32791,7 +32791,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.11565065383911</v>
+        <v>3.11565017700195</v>
       </c>
       <c r="H1118" t="n">
         <v>31970</v>
@@ -32820,7 +32820,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.06939935684204</v>
+        <v>3.06939911842346</v>
       </c>
       <c r="H1119" t="n">
         <v>81350</v>
@@ -32849,7 +32849,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1120" t="n">
-        <v>3.0525803565979</v>
+        <v>3.05258059501648</v>
       </c>
       <c r="H1120" t="n">
         <v>87073</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.15349221229553</v>
+        <v>3.15349245071411</v>
       </c>
       <c r="H1121" t="n">
         <v>125597</v>
@@ -32907,7 +32907,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.23758506774902</v>
+        <v>3.2375853061676</v>
       </c>
       <c r="H1122" t="n">
         <v>41019</v>
@@ -32936,7 +32936,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.31326961517334</v>
+        <v>3.31326937675476</v>
       </c>
       <c r="H1123" t="n">
         <v>33940</v>
@@ -32965,7 +32965,7 @@
         <v>4</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.36372542381287</v>
+        <v>3.36372518539429</v>
       </c>
       <c r="H1124" t="n">
         <v>69055</v>
@@ -33023,7 +33023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.38895344734192</v>
+        <v>3.38895320892334</v>
       </c>
       <c r="H1126" t="n">
         <v>117823</v>
@@ -33052,7 +33052,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.4057719707489</v>
+        <v>3.40577173233032</v>
       </c>
       <c r="H1127" t="n">
         <v>28852</v>
@@ -33168,7 +33168,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.29224610328674</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1131" t="n">
         <v>38417</v>
@@ -33226,7 +33226,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.30485987663269</v>
+        <v>3.30486011505127</v>
       </c>
       <c r="H1133" t="n">
         <v>9929</v>
@@ -33255,7 +33255,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1134" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963185310364</v>
       </c>
       <c r="H1134" t="n">
         <v>191541</v>
@@ -33313,7 +33313,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.31326961517334</v>
+        <v>3.31326937675476</v>
       </c>
       <c r="H1136" t="n">
         <v>55970</v>
@@ -33371,7 +33371,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.29224610328674</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1138" t="n">
         <v>118323</v>
@@ -33400,7 +33400,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.35531568527222</v>
+        <v>3.3553159236908</v>
       </c>
       <c r="H1139" t="n">
         <v>353213</v>
@@ -33429,7 +33429,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G1140" t="n">
-        <v>3.36792969703674</v>
+        <v>3.3679301738739</v>
       </c>
       <c r="H1140" t="n">
         <v>16770</v>
@@ -33458,7 +33458,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.37213444709778</v>
+        <v>3.37213468551636</v>
       </c>
       <c r="H1141" t="n">
         <v>74328</v>
@@ -33487,7 +33487,7 @@
         <v>4</v>
       </c>
       <c r="G1142" t="n">
-        <v>3.36372542381287</v>
+        <v>3.36372518539429</v>
       </c>
       <c r="H1142" t="n">
         <v>25882</v>
@@ -33545,7 +33545,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.5403208732605</v>
+        <v>3.54032039642334</v>
       </c>
       <c r="H1144" t="n">
         <v>31349</v>
@@ -33574,7 +33574,7 @@
         <v>4.25</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.67881679534912</v>
+        <v>3.67881727218628</v>
       </c>
       <c r="H1145" t="n">
         <v>32568</v>
@@ -33632,7 +33632,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.55330467224121</v>
+        <v>3.55330443382263</v>
       </c>
       <c r="H1147" t="n">
         <v>68563</v>
@@ -33690,7 +33690,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1149" t="n">
-        <v>3.44510459899902</v>
+        <v>3.44510436058044</v>
       </c>
       <c r="H1149" t="n">
         <v>17936</v>
@@ -33748,7 +33748,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854339599609</v>
       </c>
       <c r="H1151" t="n">
         <v>12775</v>
@@ -33777,7 +33777,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854339599609</v>
       </c>
       <c r="H1152" t="n">
         <v>25808</v>
@@ -33806,7 +33806,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1153" t="n">
         <v>7570</v>
@@ -33835,7 +33835,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.2892951965332</v>
+        <v>3.28929543495178</v>
       </c>
       <c r="H1154" t="n">
         <v>52863</v>
@@ -33864,7 +33864,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.31526374816895</v>
+        <v>3.31526350975037</v>
       </c>
       <c r="H1155" t="n">
         <v>18868</v>
@@ -33893,7 +33893,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1156" t="n">
-        <v>3.34555959701538</v>
+        <v>3.34555983543396</v>
       </c>
       <c r="H1156" t="n">
         <v>8521</v>
@@ -34038,7 +34038,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>3.21139097213745</v>
+        <v>3.21139121055603</v>
       </c>
       <c r="H1161" t="n">
         <v>13813</v>
@@ -34125,7 +34125,7 @@
         <v>3.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.02961397171021</v>
+        <v>3.02961421012878</v>
       </c>
       <c r="H1164" t="n">
         <v>28095</v>
@@ -34241,7 +34241,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.18542289733887</v>
+        <v>3.18542313575745</v>
       </c>
       <c r="H1168" t="n">
         <v>60306</v>
@@ -34328,7 +34328,7 @@
         <v>3.625</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.13781476020813</v>
+        <v>3.13781452178955</v>
       </c>
       <c r="H1171" t="n">
         <v>37987</v>
@@ -34386,7 +34386,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>3.0988621711731</v>
+        <v>3.09886240959167</v>
       </c>
       <c r="H1173" t="n">
         <v>26812</v>
@@ -34705,7 +34705,7 @@
         <v>3.5</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.02961397171021</v>
+        <v>3.02961421012878</v>
       </c>
       <c r="H1184" t="n">
         <v>10267</v>
@@ -34734,7 +34734,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.98200559616089</v>
+        <v>2.98200607299805</v>
       </c>
       <c r="H1185" t="n">
         <v>22437</v>
@@ -34821,7 +34821,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.91708540916443</v>
+        <v>2.91708564758301</v>
       </c>
       <c r="H1188" t="n">
         <v>19683</v>
@@ -34850,7 +34850,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1189" t="n">
         <v>17643</v>
@@ -34995,7 +34995,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.02528619766235</v>
+        <v>3.02528595924377</v>
       </c>
       <c r="H1194" t="n">
         <v>32076</v>
@@ -35024,7 +35024,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.0036461353302</v>
+        <v>3.00364589691162</v>
       </c>
       <c r="H1195" t="n">
         <v>8450</v>
@@ -35169,7 +35169,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.77426099777222</v>
+        <v>2.77426075935364</v>
       </c>
       <c r="H1200" t="n">
         <v>14812</v>
@@ -35198,7 +35198,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.77426099777222</v>
+        <v>2.77426075935364</v>
       </c>
       <c r="H1201" t="n">
         <v>11373</v>
@@ -35401,7 +35401,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.73530888557434</v>
+        <v>2.73530912399292</v>
       </c>
       <c r="H1208" t="n">
         <v>14973</v>
@@ -35488,7 +35488,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.85649347305298</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1211" t="n">
         <v>27706</v>
@@ -35517,7 +35517,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1212" t="n">
         <v>28258</v>
@@ -35546,7 +35546,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.85649347305298</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1213" t="n">
         <v>27427</v>
@@ -35575,7 +35575,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.0036461353302</v>
+        <v>3.00364589691162</v>
       </c>
       <c r="H1214" t="n">
         <v>29476</v>
@@ -35604,7 +35604,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.89977335929871</v>
+        <v>2.89977359771729</v>
       </c>
       <c r="H1215" t="n">
         <v>17211</v>
@@ -35720,7 +35720,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.76127672195435</v>
+        <v>2.76127696037292</v>
       </c>
       <c r="H1219" t="n">
         <v>16948</v>
@@ -35981,7 +35981,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.52756404876709</v>
+        <v>2.52756381034851</v>
       </c>
       <c r="H1228" t="n">
         <v>38593</v>
@@ -36039,7 +36039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.51025176048279</v>
+        <v>2.51025199890137</v>
       </c>
       <c r="H1230" t="n">
         <v>25737</v>
@@ -36097,7 +36097,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.52756404876709</v>
+        <v>2.52756381034851</v>
       </c>
       <c r="H1232" t="n">
         <v>24638</v>
@@ -36184,7 +36184,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.85649347305298</v>
+        <v>2.8564932346344</v>
       </c>
       <c r="H1235" t="n">
         <v>61256</v>
@@ -36242,7 +36242,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.90842962265015</v>
+        <v>2.90842938423157</v>
       </c>
       <c r="H1237" t="n">
         <v>60379</v>
@@ -36271,7 +36271,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.89111733436584</v>
+        <v>2.89111757278442</v>
       </c>
       <c r="H1238" t="n">
         <v>43412</v>
@@ -36387,7 +36387,7 @@
         <v>3.625</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.13781476020813</v>
+        <v>3.13781452178955</v>
       </c>
       <c r="H1242" t="n">
         <v>286519</v>
@@ -36474,7 +36474,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>3.0988621711731</v>
+        <v>3.09886240959167</v>
       </c>
       <c r="H1245" t="n">
         <v>58577</v>
@@ -36619,7 +36619,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12483048439026</v>
+        <v>3.12483024597168</v>
       </c>
       <c r="H1250" t="n">
         <v>43905</v>
@@ -36677,7 +36677,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.22004699707031</v>
+        <v>3.22004723548889</v>
       </c>
       <c r="H1252" t="n">
         <v>180885</v>
@@ -36764,7 +36764,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1255" t="n">
-        <v>3.31526374816895</v>
+        <v>3.31526350975037</v>
       </c>
       <c r="H1255" t="n">
         <v>104398</v>
@@ -36851,7 +36851,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.41048002243042</v>
+        <v>3.410480260849</v>
       </c>
       <c r="H1258" t="n">
         <v>37054</v>
@@ -36880,7 +36880,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1259" t="n">
         <v>47087</v>
@@ -36909,7 +36909,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.37585616111755</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1260" t="n">
         <v>50431</v>
@@ -36938,7 +36938,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1261" t="n">
-        <v>3.38451194763184</v>
+        <v>3.38451170921326</v>
       </c>
       <c r="H1261" t="n">
         <v>41887</v>
@@ -36967,7 +36967,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.4191358089447</v>
+        <v>3.41913604736328</v>
       </c>
       <c r="H1262" t="n">
         <v>34624</v>
@@ -36996,7 +36996,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.436448097229</v>
+        <v>3.43644833564758</v>
       </c>
       <c r="H1263" t="n">
         <v>51384</v>
@@ -37083,7 +37083,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.4191358089447</v>
+        <v>3.41913604736328</v>
       </c>
       <c r="H1266" t="n">
         <v>38075</v>
@@ -37112,7 +37112,7 @@
         <v>3.875</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.35421586036682</v>
+        <v>3.35421562194824</v>
       </c>
       <c r="H1267" t="n">
         <v>46313</v>
@@ -37141,7 +37141,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.47972798347473</v>
+        <v>3.47972822189331</v>
       </c>
       <c r="H1268" t="n">
         <v>293768</v>
@@ -37228,7 +37228,7 @@
         <v>4.25</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.67881679534912</v>
+        <v>3.67881727218628</v>
       </c>
       <c r="H1271" t="n">
         <v>52340</v>
@@ -37257,7 +37257,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>3.64419317245483</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1272" t="n">
         <v>61245</v>
@@ -37286,7 +37286,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1273" t="n">
         <v>44391</v>
@@ -37315,7 +37315,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1274" t="n">
         <v>37048</v>
@@ -37344,7 +37344,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.72209739685059</v>
+        <v>3.72209763526917</v>
       </c>
       <c r="H1275" t="n">
         <v>48291</v>
@@ -37373,7 +37373,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.64419317245483</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1276" t="n">
         <v>24944</v>
@@ -37402,7 +37402,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.57927298545837</v>
+        <v>3.57927322387695</v>
       </c>
       <c r="H1277" t="n">
         <v>32707</v>
@@ -37431,7 +37431,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.58360075950623</v>
+        <v>3.58360028266907</v>
       </c>
       <c r="H1278" t="n">
         <v>7637</v>
@@ -37460,7 +37460,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1279" t="n">
-        <v>3.57494497299194</v>
+        <v>3.57494473457336</v>
       </c>
       <c r="H1279" t="n">
         <v>24582</v>
@@ -37547,7 +37547,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.5316641330719</v>
+        <v>3.53166437149048</v>
       </c>
       <c r="H1282" t="n">
         <v>18636</v>
@@ -37663,7 +37663,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1286" t="n">
-        <v>3.44510459899902</v>
+        <v>3.44510436058044</v>
       </c>
       <c r="H1286" t="n">
         <v>32240</v>
@@ -37692,7 +37692,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1287" t="n">
-        <v>3.436448097229</v>
+        <v>3.43644833564758</v>
       </c>
       <c r="H1287" t="n">
         <v>22323</v>
@@ -37721,7 +37721,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>3.49704051017761</v>
+        <v>3.49704027175903</v>
       </c>
       <c r="H1288" t="n">
         <v>26429</v>
@@ -37750,7 +37750,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1289" t="n">
-        <v>3.44510459899902</v>
+        <v>3.44510436058044</v>
       </c>
       <c r="H1289" t="n">
         <v>36096</v>
@@ -37779,7 +37779,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1290" t="n">
-        <v>3.41048002243042</v>
+        <v>3.410480260849</v>
       </c>
       <c r="H1290" t="n">
         <v>5711</v>
@@ -37808,7 +37808,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1291" t="n">
-        <v>3.41048002243042</v>
+        <v>3.410480260849</v>
       </c>
       <c r="H1291" t="n">
         <v>9392</v>
@@ -37953,7 +37953,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.47972798347473</v>
+        <v>3.47972822189331</v>
       </c>
       <c r="H1296" t="n">
         <v>55820</v>
@@ -38011,7 +38011,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1298" t="n">
-        <v>3.50136828422546</v>
+        <v>3.50136852264404</v>
       </c>
       <c r="H1298" t="n">
         <v>334044</v>
@@ -38040,7 +38040,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.49704051017761</v>
+        <v>3.49704027175903</v>
       </c>
       <c r="H1299" t="n">
         <v>38928</v>
@@ -38069,7 +38069,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.5316641330719</v>
+        <v>3.53166437149048</v>
       </c>
       <c r="H1300" t="n">
         <v>13827</v>
@@ -38185,7 +38185,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.50136828422546</v>
+        <v>3.50136852264404</v>
       </c>
       <c r="H1304" t="n">
         <v>73237</v>
@@ -38272,7 +38272,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.66583323478699</v>
+        <v>3.66583347320557</v>
       </c>
       <c r="H1307" t="n">
         <v>53680</v>
@@ -38301,7 +38301,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.6615047454834</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1308" t="n">
         <v>14769</v>
@@ -38330,7 +38330,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.6528491973877</v>
+        <v>3.65284895896912</v>
       </c>
       <c r="H1309" t="n">
         <v>21085</v>
@@ -38359,7 +38359,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1310" t="n">
-        <v>3.62688088417053</v>
+        <v>3.62688112258911</v>
       </c>
       <c r="H1310" t="n">
         <v>13519</v>
@@ -38388,7 +38388,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.6615047454834</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1311" t="n">
         <v>35922</v>
@@ -38417,7 +38417,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.69612956047058</v>
+        <v>3.69612908363342</v>
       </c>
       <c r="H1312" t="n">
         <v>21893</v>
@@ -38446,7 +38446,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.75672149658203</v>
+        <v>3.75672197341919</v>
       </c>
       <c r="H1313" t="n">
         <v>17797</v>
@@ -38475,7 +38475,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.62688088417053</v>
+        <v>3.62688112258911</v>
       </c>
       <c r="H1314" t="n">
         <v>40501</v>
@@ -38504,7 +38504,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.60524106025696</v>
+        <v>3.60524082183838</v>
       </c>
       <c r="H1315" t="n">
         <v>18680</v>
@@ -38533,7 +38533,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.67016100883484</v>
+        <v>3.67016124725342</v>
       </c>
       <c r="H1316" t="n">
         <v>18719</v>
@@ -38591,7 +38591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.6615047454834</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1318" t="n">
         <v>19255</v>
@@ -38620,7 +38620,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.70045733451843</v>
+        <v>3.70045709609985</v>
       </c>
       <c r="H1319" t="n">
         <v>16480</v>
@@ -38649,7 +38649,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.70045733451843</v>
+        <v>3.70045709609985</v>
       </c>
       <c r="H1320" t="n">
         <v>33947</v>
@@ -38707,7 +38707,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.69180107116699</v>
+        <v>3.69180154800415</v>
       </c>
       <c r="H1322" t="n">
         <v>21036</v>
@@ -38736,7 +38736,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.6398651599884</v>
+        <v>3.63986492156982</v>
       </c>
       <c r="H1323" t="n">
         <v>28422</v>
@@ -38794,7 +38794,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.64419317245483</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1325" t="n">
         <v>19724</v>
@@ -38881,7 +38881,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.57494497299194</v>
+        <v>3.57494473457336</v>
       </c>
       <c r="H1328" t="n">
         <v>44132</v>
@@ -38910,7 +38910,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.5403208732605</v>
+        <v>3.54032039642334</v>
       </c>
       <c r="H1329" t="n">
         <v>12171</v>
@@ -38939,7 +38939,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.47972798347473</v>
+        <v>3.47972822189331</v>
       </c>
       <c r="H1330" t="n">
         <v>31279</v>
@@ -38997,7 +38997,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.5230085849762</v>
+        <v>3.52300882339478</v>
       </c>
       <c r="H1332" t="n">
         <v>80474</v>
@@ -39026,7 +39026,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.62688088417053</v>
+        <v>3.62688112258911</v>
       </c>
       <c r="H1333" t="n">
         <v>62690</v>
@@ -39055,7 +39055,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.64419317245483</v>
+        <v>3.64419293403625</v>
       </c>
       <c r="H1334" t="n">
         <v>227618</v>
@@ -39084,7 +39084,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.58792853355408</v>
+        <v>3.58792877197266</v>
       </c>
       <c r="H1335" t="n">
         <v>817038</v>
@@ -39142,7 +39142,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.63120889663696</v>
+        <v>3.63120913505554</v>
       </c>
       <c r="H1337" t="n">
         <v>162714</v>
@@ -39200,7 +39200,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.70478534698486</v>
+        <v>3.70478582382202</v>
       </c>
       <c r="H1339" t="n">
         <v>37701</v>
@@ -39229,7 +39229,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.75672149658203</v>
+        <v>3.75672197341919</v>
       </c>
       <c r="H1340" t="n">
         <v>106019</v>
@@ -39316,7 +39316,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.91253066062927</v>
+        <v>3.91253042221069</v>
       </c>
       <c r="H1343" t="n">
         <v>53369</v>
@@ -39345,7 +39345,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.92568922042847</v>
+        <v>3.92568874359131</v>
       </c>
       <c r="H1344" t="n">
         <v>82068</v>
@@ -39548,7 +39548,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.05289030075073</v>
+        <v>4.05288982391357</v>
       </c>
       <c r="H1351" t="n">
         <v>28011</v>
@@ -39635,7 +39635,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.98271036148071</v>
+        <v>3.9827094078064</v>
       </c>
       <c r="H1354" t="n">
         <v>94059</v>
@@ -39693,7 +39693,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1356" t="n">
         <v>107419</v>
@@ -39751,7 +39751,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.96955156326294</v>
+        <v>3.96955108642578</v>
       </c>
       <c r="H1358" t="n">
         <v>48171</v>
@@ -39780,7 +39780,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.0002555847168</v>
+        <v>4.00025463104248</v>
       </c>
       <c r="H1359" t="n">
         <v>55834</v>
@@ -39896,7 +39896,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.89059901237488</v>
+        <v>3.8905987739563</v>
       </c>
       <c r="H1363" t="n">
         <v>29461</v>
@@ -39925,7 +39925,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.91691637039185</v>
+        <v>3.91691660881042</v>
       </c>
       <c r="H1364" t="n">
         <v>14269</v>
@@ -39983,7 +39983,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1366" t="n">
         <v>23565</v>
@@ -40012,7 +40012,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.87744045257568</v>
+        <v>3.8774402141571</v>
       </c>
       <c r="H1367" t="n">
         <v>33068</v>
@@ -40099,7 +40099,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.87744045257568</v>
+        <v>3.8774402141571</v>
       </c>
       <c r="H1370" t="n">
         <v>38364</v>
@@ -40128,7 +40128,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.88182687759399</v>
+        <v>3.88182663917542</v>
       </c>
       <c r="H1371" t="n">
         <v>39514</v>
@@ -40157,7 +40157,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.88182687759399</v>
+        <v>3.88182663917542</v>
       </c>
       <c r="H1372" t="n">
         <v>221869</v>
@@ -40186,7 +40186,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.92568922042847</v>
+        <v>3.92568874359131</v>
       </c>
       <c r="H1373" t="n">
         <v>28128</v>
@@ -40215,7 +40215,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.95639276504517</v>
+        <v>3.95639324188232</v>
       </c>
       <c r="H1374" t="n">
         <v>105079</v>
@@ -40244,7 +40244,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.99148321151733</v>
+        <v>3.99148273468018</v>
       </c>
       <c r="H1375" t="n">
         <v>83917</v>
@@ -40447,7 +40447,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.97393822669983</v>
+        <v>3.97393774986267</v>
       </c>
       <c r="H1382" t="n">
         <v>31872</v>
@@ -40505,7 +40505,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.10552549362183</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1384" t="n">
         <v>114987</v>
@@ -40534,7 +40534,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.10552549362183</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1385" t="n">
         <v>70506</v>
@@ -40563,7 +40563,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.12307024002075</v>
+        <v>4.12306976318359</v>
       </c>
       <c r="H1386" t="n">
         <v>86135</v>
@@ -40592,7 +40592,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.0616626739502</v>
+        <v>4.06166219711304</v>
       </c>
       <c r="H1387" t="n">
         <v>51964</v>
@@ -40621,7 +40621,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1388" t="n">
-        <v>4.0616626739502</v>
+        <v>4.06166219711304</v>
       </c>
       <c r="H1388" t="n">
         <v>64581</v>
@@ -40650,7 +40650,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.03534555435181</v>
+        <v>4.03534460067749</v>
       </c>
       <c r="H1389" t="n">
         <v>36588</v>
@@ -40708,7 +40708,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.95200681686401</v>
+        <v>3.95200634002686</v>
       </c>
       <c r="H1391" t="n">
         <v>16896</v>
@@ -40737,7 +40737,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.93446183204651</v>
+        <v>3.93446135520935</v>
       </c>
       <c r="H1392" t="n">
         <v>88740</v>
@@ -40795,7 +40795,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1394" t="n">
-        <v>4.10552549362183</v>
+        <v>4.10552501678467</v>
       </c>
       <c r="H1394" t="n">
         <v>234889</v>
@@ -40882,7 +40882,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.12307024002075</v>
+        <v>4.12306976318359</v>
       </c>
       <c r="H1397" t="n">
         <v>13344</v>
@@ -40911,7 +40911,7 @@
         <v>4.75</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.16693162918091</v>
+        <v>4.16693210601807</v>
       </c>
       <c r="H1398" t="n">
         <v>39796</v>
@@ -40969,7 +40969,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.11429786682129</v>
+        <v>4.11429691314697</v>
       </c>
       <c r="H1400" t="n">
         <v>49469</v>
@@ -41114,7 +41114,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.82480573654175</v>
+        <v>3.82480525970459</v>
       </c>
       <c r="H1405" t="n">
         <v>22741</v>
@@ -41143,7 +41143,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.79848742485046</v>
+        <v>3.79848790168762</v>
       </c>
       <c r="H1406" t="n">
         <v>16201</v>
@@ -41172,7 +41172,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.79410171508789</v>
+        <v>3.79410147666931</v>
       </c>
       <c r="H1407" t="n">
         <v>67590</v>
@@ -41259,7 +41259,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.58794832229614</v>
+        <v>3.58794808387756</v>
       </c>
       <c r="H1410" t="n">
         <v>22462</v>
@@ -41288,7 +41288,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.75023913383484</v>
+        <v>3.75023889541626</v>
       </c>
       <c r="H1411" t="n">
         <v>54658</v>
@@ -41375,7 +41375,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.91253066062927</v>
+        <v>3.91253042221069</v>
       </c>
       <c r="H1414" t="n">
         <v>28276</v>
@@ -41404,7 +41404,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.79848742485046</v>
+        <v>3.79848790168762</v>
       </c>
       <c r="H1415" t="n">
         <v>26744</v>
@@ -41491,7 +41491,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.9081437587738</v>
+        <v>3.90814399719238</v>
       </c>
       <c r="H1418" t="n">
         <v>69967</v>
@@ -41549,7 +41549,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G1420" t="n">
-        <v>3.95200681686401</v>
+        <v>3.95200634002686</v>
       </c>
       <c r="H1420" t="n">
         <v>30064</v>
@@ -41607,7 +41607,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1422" t="n">
         <v>19394</v>
@@ -41694,7 +41694,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.91691637039185</v>
+        <v>3.91691660881042</v>
       </c>
       <c r="H1425" t="n">
         <v>15425</v>
@@ -41723,7 +41723,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1426" t="n">
-        <v>3.93884754180908</v>
+        <v>3.93884801864624</v>
       </c>
       <c r="H1426" t="n">
         <v>17704</v>
@@ -41752,7 +41752,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.95639276504517</v>
+        <v>3.95639324188232</v>
       </c>
       <c r="H1427" t="n">
         <v>12378</v>
@@ -41810,7 +41810,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.89059901237488</v>
+        <v>3.8905987739563</v>
       </c>
       <c r="H1429" t="n">
         <v>20043</v>
@@ -41839,7 +41839,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.82480573654175</v>
+        <v>3.82480525970459</v>
       </c>
       <c r="H1430" t="n">
         <v>16207</v>
@@ -41868,7 +41868,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.88182687759399</v>
+        <v>3.88182663917542</v>
       </c>
       <c r="H1431" t="n">
         <v>25145</v>
@@ -41984,7 +41984,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.9081437587738</v>
+        <v>3.90814399719238</v>
       </c>
       <c r="H1435" t="n">
         <v>22582</v>
@@ -42158,7 +42158,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.88621282577515</v>
+        <v>3.88621306419373</v>
       </c>
       <c r="H1441" t="n">
         <v>31839</v>
@@ -42187,7 +42187,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.88621282577515</v>
+        <v>3.88621306419373</v>
       </c>
       <c r="H1442" t="n">
         <v>11973</v>
@@ -42216,7 +42216,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>3.89498543739319</v>
+        <v>3.89498519897461</v>
       </c>
       <c r="H1443" t="n">
         <v>22458</v>
@@ -42245,7 +42245,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1444" t="n">
-        <v>4.03534555435181</v>
+        <v>4.03534460067749</v>
       </c>
       <c r="H1444" t="n">
         <v>36796</v>
@@ -42303,7 +42303,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.95639276504517</v>
+        <v>3.95639324188232</v>
       </c>
       <c r="H1446" t="n">
         <v>25409</v>
@@ -42332,7 +42332,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.93446183204651</v>
+        <v>3.93446135520935</v>
       </c>
       <c r="H1447" t="n">
         <v>48699</v>
@@ -42361,7 +42361,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.95639276504517</v>
+        <v>3.95639324188232</v>
       </c>
       <c r="H1448" t="n">
         <v>17459</v>
@@ -42390,7 +42390,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.0616626739502</v>
+        <v>4.06166219711304</v>
       </c>
       <c r="H1449" t="n">
         <v>32404</v>
@@ -42419,7 +42419,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.01341438293457</v>
+        <v>4.01341390609741</v>
       </c>
       <c r="H1450" t="n">
         <v>15103</v>
@@ -42506,7 +42506,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.12307024002075</v>
+        <v>4.12306976318359</v>
       </c>
       <c r="H1453" t="n">
         <v>25172</v>
@@ -42535,7 +42535,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.00464200973511</v>
+        <v>4.00464153289795</v>
       </c>
       <c r="H1454" t="n">
         <v>29105</v>
@@ -42593,7 +42593,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.13622856140137</v>
+        <v>4.13622903823853</v>
       </c>
       <c r="H1456" t="n">
         <v>26452</v>
@@ -42622,7 +42622,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1457" t="n">
-        <v>4.17570447921753</v>
+        <v>4.17570543289185</v>
       </c>
       <c r="H1457" t="n">
         <v>34032</v>
@@ -42651,7 +42651,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.15377330780029</v>
+        <v>4.15377378463745</v>
       </c>
       <c r="H1458" t="n">
         <v>22649</v>
@@ -42767,7 +42767,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.01341438293457</v>
+        <v>4.01341390609741</v>
       </c>
       <c r="H1462" t="n">
         <v>8627</v>
@@ -42796,7 +42796,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.99148321151733</v>
+        <v>3.99148273468018</v>
       </c>
       <c r="H1463" t="n">
         <v>13521</v>
@@ -42854,7 +42854,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.11429786682129</v>
+        <v>4.11429691314697</v>
       </c>
       <c r="H1465" t="n">
         <v>11238</v>
@@ -42970,7 +42970,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1469" t="n">
-        <v>4.1581597328186</v>
+        <v>4.15816020965576</v>
       </c>
       <c r="H1469" t="n">
         <v>8104</v>
@@ -43086,7 +43086,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.20202255249023</v>
+        <v>4.20202207565308</v>
       </c>
       <c r="H1473" t="n">
         <v>29042</v>
@@ -43144,7 +43144,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.34238195419312</v>
+        <v>4.34238243103027</v>
       </c>
       <c r="H1475" t="n">
         <v>36122</v>
@@ -43202,7 +43202,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.43887948989868</v>
+        <v>4.43887996673584</v>
       </c>
       <c r="H1477" t="n">
         <v>50769</v>
@@ -43231,7 +43231,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.45642375946045</v>
+        <v>4.45642423629761</v>
       </c>
       <c r="H1478" t="n">
         <v>26090</v>
@@ -43260,7 +43260,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1479" t="n">
-        <v>4.46519660949707</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1479" t="n">
         <v>16097</v>
@@ -43289,7 +43289,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.41256189346313</v>
+        <v>4.41256284713745</v>
       </c>
       <c r="H1480" t="n">
         <v>46344</v>
@@ -43434,7 +43434,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1485" t="n">
-        <v>4.39501714706421</v>
+        <v>4.39501762390137</v>
       </c>
       <c r="H1485" t="n">
         <v>24688</v>
@@ -43463,7 +43463,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.41256189346313</v>
+        <v>4.41256284713745</v>
       </c>
       <c r="H1486" t="n">
         <v>41871</v>
@@ -43492,7 +43492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.42133474349976</v>
+        <v>4.42133522033691</v>
       </c>
       <c r="H1487" t="n">
         <v>19669</v>
@@ -43521,7 +43521,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1488" t="n">
-        <v>4.39501714706421</v>
+        <v>4.39501762390137</v>
       </c>
       <c r="H1488" t="n">
         <v>43372</v>
@@ -43666,7 +43666,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.51783180236816</v>
+        <v>4.51783132553101</v>
       </c>
       <c r="H1493" t="n">
         <v>33847</v>
@@ -43753,7 +43753,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1496" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1496" t="n">
         <v>59614</v>
@@ -43782,7 +43782,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1497" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1497" t="n">
         <v>45722</v>
@@ -43840,7 +43840,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1499" t="n">
-        <v>4.39501714706421</v>
+        <v>4.39501762390137</v>
       </c>
       <c r="H1499" t="n">
         <v>22226</v>
@@ -43869,7 +43869,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1500" t="n">
-        <v>4.29851913452148</v>
+        <v>4.29851961135864</v>
       </c>
       <c r="H1500" t="n">
         <v>42771</v>
@@ -43898,7 +43898,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1501" t="n">
-        <v>4.35554075241089</v>
+        <v>4.35554170608521</v>
       </c>
       <c r="H1501" t="n">
         <v>50486</v>
@@ -44014,7 +44014,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1505" t="n">
-        <v>4.46519660949707</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1505" t="n">
         <v>56559</v>
@@ -44043,7 +44043,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1506" t="n">
-        <v>4.49151468276978</v>
+        <v>4.49151420593262</v>
       </c>
       <c r="H1506" t="n">
         <v>29573</v>
@@ -44072,7 +44072,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1507" t="n">
-        <v>4.54414892196655</v>
+        <v>4.54414939880371</v>
       </c>
       <c r="H1507" t="n">
         <v>74370</v>
@@ -44130,7 +44130,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1509" t="n">
-        <v>4.55292224884033</v>
+        <v>4.55292177200317</v>
       </c>
       <c r="H1509" t="n">
         <v>39944</v>
@@ -44159,7 +44159,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1510" t="n">
-        <v>4.55292224884033</v>
+        <v>4.55292177200317</v>
       </c>
       <c r="H1510" t="n">
         <v>43181</v>
@@ -44188,7 +44188,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1511" t="n">
-        <v>4.51783180236816</v>
+        <v>4.51783132553101</v>
       </c>
       <c r="H1511" t="n">
         <v>23008</v>
@@ -44246,7 +44246,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1513" t="n">
-        <v>4.65819215774536</v>
+        <v>4.6581916809082</v>
       </c>
       <c r="H1513" t="n">
         <v>68965</v>
@@ -44275,7 +44275,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1514" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1514" t="n">
         <v>37612</v>
@@ -44362,7 +44362,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1517" t="n">
-        <v>4.78100681304932</v>
+        <v>4.78100633621216</v>
       </c>
       <c r="H1517" t="n">
         <v>112154</v>
@@ -44449,7 +44449,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.03540897369385</v>
+        <v>5.03540849685669</v>
       </c>
       <c r="H1520" t="n">
         <v>118116</v>
@@ -44478,7 +44478,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1521" t="n">
-        <v>5.20208549499512</v>
+        <v>5.20208597183228</v>
       </c>
       <c r="H1521" t="n">
         <v>130419</v>
@@ -44565,7 +44565,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1524" t="n">
-        <v>5.05295419692993</v>
+        <v>5.05295372009277</v>
       </c>
       <c r="H1524" t="n">
         <v>126230</v>
@@ -44594,7 +44594,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1525" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1525" t="n">
         <v>94660</v>
@@ -44623,7 +44623,7 @@
         <v>5.75</v>
       </c>
       <c r="G1526" t="n">
-        <v>5.04418134689331</v>
+        <v>5.04418087005615</v>
       </c>
       <c r="H1526" t="n">
         <v>57227</v>
@@ -44652,7 +44652,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.14945125579834</v>
+        <v>5.14945077896118</v>
       </c>
       <c r="H1527" t="n">
         <v>147453</v>
@@ -44739,7 +44739,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1530" t="n">
-        <v>5.35999059677124</v>
+        <v>5.35999155044556</v>
       </c>
       <c r="H1530" t="n">
         <v>88930</v>
@@ -44768,7 +44768,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.38630819320679</v>
+        <v>5.38630771636963</v>
       </c>
       <c r="H1531" t="n">
         <v>88528</v>
@@ -44971,7 +44971,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1538" t="n">
         <v>121540</v>
@@ -45029,7 +45029,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.98277425765991</v>
+        <v>4.98277378082275</v>
       </c>
       <c r="H1540" t="n">
         <v>44589</v>
@@ -45087,7 +45087,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1542" t="n">
-        <v>4.65819215774536</v>
+        <v>4.6581916809082</v>
       </c>
       <c r="H1542" t="n">
         <v>138270</v>
@@ -45145,7 +45145,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1544" t="n">
-        <v>4.78100681304932</v>
+        <v>4.78100633621216</v>
       </c>
       <c r="H1544" t="n">
         <v>18251</v>
@@ -45203,7 +45203,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.6494197845459</v>
+        <v>4.64941930770874</v>
       </c>
       <c r="H1546" t="n">
         <v>24508</v>
@@ -45261,7 +45261,7 @@
         <v>5.5</v>
       </c>
       <c r="G1548" t="n">
-        <v>4.82486915588379</v>
+        <v>4.82486963272095</v>
       </c>
       <c r="H1548" t="n">
         <v>56796</v>
@@ -45290,7 +45290,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.73714447021484</v>
+        <v>4.73714399337769</v>
       </c>
       <c r="H1549" t="n">
         <v>25756</v>
@@ -45319,7 +45319,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1550" t="n">
-        <v>4.93891191482544</v>
+        <v>4.93891143798828</v>
       </c>
       <c r="H1550" t="n">
         <v>97294</v>
@@ -45377,7 +45377,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1552" t="n">
-        <v>4.79855155944824</v>
+        <v>4.7985520362854</v>
       </c>
       <c r="H1552" t="n">
         <v>60085</v>
@@ -45464,7 +45464,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1555" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1555" t="n">
         <v>105080</v>
@@ -45493,7 +45493,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.93013954162598</v>
+        <v>4.93013906478882</v>
       </c>
       <c r="H1556" t="n">
         <v>107233</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.82486915588379</v>
+        <v>4.82486963272095</v>
       </c>
       <c r="H1558" t="n">
         <v>69670</v>
@@ -45667,7 +45667,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.6494197845459</v>
+        <v>4.64941930770874</v>
       </c>
       <c r="H1562" t="n">
         <v>39032</v>
@@ -45696,7 +45696,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1563" t="n">
-        <v>4.64064693450928</v>
+        <v>4.64064645767212</v>
       </c>
       <c r="H1563" t="n">
         <v>18667</v>
@@ -45754,7 +45754,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.51783180236816</v>
+        <v>4.51783132553101</v>
       </c>
       <c r="H1565" t="n">
         <v>76720</v>
@@ -45812,7 +45812,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.55292224884033</v>
+        <v>4.55292177200317</v>
       </c>
       <c r="H1567" t="n">
         <v>20954</v>
@@ -45870,7 +45870,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.43010711669922</v>
+        <v>4.43010759353638</v>
       </c>
       <c r="H1569" t="n">
         <v>74132</v>
@@ -45899,7 +45899,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.32483673095703</v>
+        <v>4.32483720779419</v>
       </c>
       <c r="H1570" t="n">
         <v>67064</v>
@@ -45928,7 +45928,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.2722020149231</v>
+        <v>4.27220249176025</v>
       </c>
       <c r="H1571" t="n">
         <v>83986</v>
@@ -46015,7 +46015,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1574" t="n">
-        <v>4.29851913452148</v>
+        <v>4.29851961135864</v>
       </c>
       <c r="H1574" t="n">
         <v>88377</v>
@@ -46160,7 +46160,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.46519660949707</v>
+        <v>4.46519708633423</v>
       </c>
       <c r="H1579" t="n">
         <v>44797</v>
@@ -46218,7 +46218,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.49151468276978</v>
+        <v>4.49151420593262</v>
       </c>
       <c r="H1581" t="n">
         <v>32307</v>
@@ -46247,7 +46247,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.75468921661377</v>
+        <v>4.75468873977661</v>
       </c>
       <c r="H1582" t="n">
         <v>34531</v>
@@ -46276,7 +46276,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.66696405410767</v>
+        <v>4.66696453094482</v>
       </c>
       <c r="H1583" t="n">
         <v>50824</v>
@@ -46363,7 +46363,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.85995960235596</v>
+        <v>4.8599591255188</v>
       </c>
       <c r="H1586" t="n">
         <v>43056</v>
@@ -46392,7 +46392,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>4.85995960235596</v>
+        <v>4.8599591255188</v>
       </c>
       <c r="H1587" t="n">
         <v>35009</v>
@@ -46421,7 +46421,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1588" t="n">
-        <v>5.00909185409546</v>
+        <v>5.0090913772583</v>
       </c>
       <c r="H1588" t="n">
         <v>44967</v>
@@ -46479,7 +46479,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1590" t="n">
-        <v>5.11436080932617</v>
+        <v>5.11436128616333</v>
       </c>
       <c r="H1590" t="n">
         <v>40558</v>
@@ -46508,7 +46508,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1591" t="n">
-        <v>5.19331359863281</v>
+        <v>5.19331407546997</v>
       </c>
       <c r="H1591" t="n">
         <v>32996</v>
@@ -46595,7 +46595,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1594" t="n">
-        <v>5.19331359863281</v>
+        <v>5.19331407546997</v>
       </c>
       <c r="H1594" t="n">
         <v>29439</v>
@@ -46624,7 +46624,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>5.14945125579834</v>
+        <v>5.14945077896118</v>
       </c>
       <c r="H1595" t="n">
         <v>22727</v>
@@ -46653,7 +46653,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1596" t="n">
-        <v>5.17576837539673</v>
+        <v>5.17576885223389</v>
       </c>
       <c r="H1596" t="n">
         <v>21731</v>
@@ -46740,7 +46740,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1599" t="n">
-        <v>5.43894290924072</v>
+        <v>5.43894243240356</v>
       </c>
       <c r="H1599" t="n">
         <v>45303</v>
@@ -46769,7 +46769,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1600" t="n">
-        <v>5.43894290924072</v>
+        <v>5.43894243240356</v>
       </c>
       <c r="H1600" t="n">
         <v>73046</v>
@@ -46798,7 +46798,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1601" t="n">
-        <v>5.5091233253479</v>
+        <v>5.50912380218506</v>
       </c>
       <c r="H1601" t="n">
         <v>60060</v>
@@ -46885,7 +46885,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>5.4213981628418</v>
+        <v>5.42139768600464</v>
       </c>
       <c r="H1604" t="n">
         <v>15962</v>
@@ -46914,7 +46914,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1605" t="n">
         <v>28457</v>
@@ -46943,7 +46943,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1606" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1606" t="n">
         <v>39120</v>
@@ -46972,7 +46972,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1607" t="n">
-        <v>5.34982824325562</v>
+        <v>5.34982872009277</v>
       </c>
       <c r="H1607" t="n">
         <v>26086</v>
@@ -47001,7 +47001,7 @@
         <v>6</v>
       </c>
       <c r="G1608" t="n">
-        <v>5.36772155761719</v>
+        <v>5.36772108078003</v>
       </c>
       <c r="H1608" t="n">
         <v>22051</v>
@@ -47030,7 +47030,7 @@
         <v>6</v>
       </c>
       <c r="G1609" t="n">
-        <v>5.36772155761719</v>
+        <v>5.36772108078003</v>
       </c>
       <c r="H1609" t="n">
         <v>40350</v>
@@ -47117,7 +47117,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>5.68083810806274</v>
+        <v>5.68083763122559</v>
       </c>
       <c r="H1612" t="n">
         <v>24162</v>
@@ -47146,7 +47146,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1613" t="n">
-        <v>5.5376992225647</v>
+        <v>5.53769874572754</v>
       </c>
       <c r="H1613" t="n">
         <v>35547</v>
@@ -47204,7 +47204,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1615" t="n">
         <v>61746</v>
@@ -47262,7 +47262,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1617" t="n">
-        <v>5.51086044311523</v>
+        <v>5.51085996627808</v>
       </c>
       <c r="H1617" t="n">
         <v>52926</v>
@@ -47320,7 +47320,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>5.69872999191284</v>
+        <v>5.69873046875</v>
       </c>
       <c r="H1619" t="n">
         <v>40676</v>
@@ -47378,7 +47378,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1621" t="n">
-        <v>5.76135444641113</v>
+        <v>5.76135396957397</v>
       </c>
       <c r="H1621" t="n">
         <v>26305</v>
@@ -47407,7 +47407,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1622" t="n">
-        <v>5.80608415603638</v>
+        <v>5.80608463287354</v>
       </c>
       <c r="H1622" t="n">
         <v>17292</v>
@@ -47581,7 +47581,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1628" t="n">
-        <v>5.91343975067139</v>
+        <v>5.91344022750854</v>
       </c>
       <c r="H1628" t="n">
         <v>17658</v>
@@ -47668,7 +47668,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1631" t="n">
-        <v>5.78819227218628</v>
+        <v>5.78819274902344</v>
       </c>
       <c r="H1631" t="n">
         <v>23406</v>
@@ -47726,7 +47726,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.56453704833984</v>
+        <v>5.564537525177</v>
       </c>
       <c r="H1633" t="n">
         <v>10116</v>
@@ -47813,7 +47813,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1636" t="n">
-        <v>5.55559110641479</v>
+        <v>5.55559062957764</v>
       </c>
       <c r="H1636" t="n">
         <v>21394</v>
@@ -47842,7 +47842,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.57348394393921</v>
+        <v>5.57348346710205</v>
       </c>
       <c r="H1637" t="n">
         <v>25849</v>
@@ -47871,7 +47871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1638" t="n">
-        <v>5.54664516448975</v>
+        <v>5.54664468765259</v>
       </c>
       <c r="H1638" t="n">
         <v>25632</v>
@@ -47900,7 +47900,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.56453704833984</v>
+        <v>5.564537525177</v>
       </c>
       <c r="H1639" t="n">
         <v>27932</v>
@@ -47929,7 +47929,7 @@
         <v>6</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.36772155761719</v>
+        <v>5.36772108078003</v>
       </c>
       <c r="H1640" t="n">
         <v>40504</v>
@@ -47958,7 +47958,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1641" t="n">
-        <v>5.3140435218811</v>
+        <v>5.31404399871826</v>
       </c>
       <c r="H1641" t="n">
         <v>23288</v>
@@ -48016,7 +48016,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1643" t="n">
-        <v>5.22458171844482</v>
+        <v>5.22458219528198</v>
       </c>
       <c r="H1643" t="n">
         <v>26122</v>
@@ -48074,7 +48074,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1645" t="n">
-        <v>5.23352861404419</v>
+        <v>5.23352813720703</v>
       </c>
       <c r="H1645" t="n">
         <v>33148</v>
@@ -48103,7 +48103,7 @@
         <v>6</v>
       </c>
       <c r="G1646" t="n">
-        <v>5.36772155761719</v>
+        <v>5.36772108078003</v>
       </c>
       <c r="H1646" t="n">
         <v>16237</v>
@@ -48132,7 +48132,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1647" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1647" t="n">
         <v>20118</v>
@@ -48190,7 +48190,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1649" t="n">
-        <v>5.27825880050659</v>
+        <v>5.27825927734375</v>
       </c>
       <c r="H1649" t="n">
         <v>25880</v>
@@ -48219,7 +48219,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1650" t="n">
-        <v>5.23352861404419</v>
+        <v>5.23352813720703</v>
       </c>
       <c r="H1650" t="n">
         <v>14298</v>
@@ -48248,7 +48248,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>5.22458171844482</v>
+        <v>5.22458219528198</v>
       </c>
       <c r="H1651" t="n">
         <v>10662</v>
@@ -48277,7 +48277,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1652" t="n">
-        <v>5.25142049789429</v>
+        <v>5.25142002105713</v>
       </c>
       <c r="H1652" t="n">
         <v>6670</v>
@@ -48335,7 +48335,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1654" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1654" t="n">
         <v>3429</v>
@@ -48480,7 +48480,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1659" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092744827271</v>
       </c>
       <c r="H1659" t="n">
         <v>14998</v>
@@ -48509,7 +48509,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1660" t="n">
-        <v>4.97408771514893</v>
+        <v>4.97408819198608</v>
       </c>
       <c r="H1660" t="n">
         <v>4940</v>
@@ -48538,7 +48538,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.92935705184937</v>
+        <v>4.92935752868652</v>
       </c>
       <c r="H1661" t="n">
         <v>7539</v>
@@ -48567,7 +48567,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1662" t="n">
-        <v>4.91146516799927</v>
+        <v>4.91146469116211</v>
       </c>
       <c r="H1662" t="n">
         <v>4990</v>
@@ -48596,7 +48596,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1663" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1663" t="n">
         <v>4884</v>
@@ -48625,7 +48625,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1664" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1664" t="n">
         <v>3654</v>
@@ -48654,7 +48654,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1665" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1665" t="n">
         <v>1766</v>
@@ -48683,7 +48683,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1666" t="n">
-        <v>5.02776527404785</v>
+        <v>5.02776479721069</v>
       </c>
       <c r="H1666" t="n">
         <v>2209</v>
@@ -48712,7 +48712,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1667" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1667" t="n">
         <v>3351</v>
@@ -48915,7 +48915,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1674" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1674" t="n">
         <v>32862</v>
@@ -49002,7 +49002,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1677" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1677" t="n">
         <v>61662</v>
@@ -49031,7 +49031,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1678" t="n">
-        <v>5.35877466201782</v>
+        <v>5.35877513885498</v>
       </c>
       <c r="H1678" t="n">
         <v>48833</v>
@@ -49089,7 +49089,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1680" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1680" t="n">
         <v>3893</v>
@@ -49118,7 +49118,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1681" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1681" t="n">
         <v>2943</v>
@@ -49147,7 +49147,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1682" t="n">
-        <v>5.22458171844482</v>
+        <v>5.22458219528198</v>
       </c>
       <c r="H1682" t="n">
         <v>8677</v>
@@ -49408,7 +49408,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1691" t="n">
-        <v>4.83989477157593</v>
+        <v>4.83989524841309</v>
       </c>
       <c r="H1691" t="n">
         <v>13122</v>
@@ -49495,7 +49495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1694" t="n">
-        <v>4.79516410827637</v>
+        <v>4.79516458511353</v>
       </c>
       <c r="H1694" t="n">
         <v>14660</v>
@@ -49524,7 +49524,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1695" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1695" t="n">
         <v>11114</v>
@@ -49553,7 +49553,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1696" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1696" t="n">
         <v>46629</v>
@@ -49582,7 +49582,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.75043249130249</v>
+        <v>4.75043296813965</v>
       </c>
       <c r="H1697" t="n">
         <v>12083</v>
@@ -49669,7 +49669,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.652024269104</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1700" t="n">
         <v>8433</v>
@@ -49698,7 +49698,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1701" t="n">
-        <v>4.59834766387939</v>
+        <v>4.59834718704224</v>
       </c>
       <c r="H1701" t="n">
         <v>15687</v>
@@ -49727,7 +49727,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1702" t="n">
-        <v>4.48204755783081</v>
+        <v>4.48204803466797</v>
       </c>
       <c r="H1702" t="n">
         <v>32468</v>
@@ -49756,7 +49756,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.61623954772949</v>
+        <v>4.61624002456665</v>
       </c>
       <c r="H1703" t="n">
         <v>10989</v>
@@ -49843,7 +49843,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1706" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1706" t="n">
         <v>30524</v>
@@ -49872,7 +49872,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1707" t="n">
-        <v>4.652024269104</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1707" t="n">
         <v>24304</v>
@@ -49930,7 +49930,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1709" t="n">
-        <v>4.652024269104</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1709" t="n">
         <v>18865</v>
@@ -49959,7 +49959,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1710" t="n">
-        <v>4.62518644332886</v>
+        <v>4.6251859664917</v>
       </c>
       <c r="H1710" t="n">
         <v>18413</v>
@@ -50104,7 +50104,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1715" t="n">
-        <v>4.59834766387939</v>
+        <v>4.59834718704224</v>
       </c>
       <c r="H1715" t="n">
         <v>16437</v>
@@ -50307,7 +50307,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1722" t="n">
-        <v>4.48204755783081</v>
+        <v>4.48204803466797</v>
       </c>
       <c r="H1722" t="n">
         <v>10490</v>
@@ -50481,7 +50481,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1728" t="n">
-        <v>4.39258527755737</v>
+        <v>4.39258480072021</v>
       </c>
       <c r="H1728" t="n">
         <v>11987</v>
@@ -50626,7 +50626,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1733" t="n">
-        <v>4.40600490570068</v>
+        <v>4.40600442886353</v>
       </c>
       <c r="H1733" t="n">
         <v>19415</v>
@@ -50713,7 +50713,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1736" t="n">
-        <v>4.31206941604614</v>
+        <v>4.3120698928833</v>
       </c>
       <c r="H1736" t="n">
         <v>23962</v>
@@ -50829,7 +50829,7 @@
         <v>4.875</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.36127328872681</v>
+        <v>4.36127281188965</v>
       </c>
       <c r="H1740" t="n">
         <v>10091</v>
@@ -50858,7 +50858,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1741" t="n">
-        <v>4.27628421783447</v>
+        <v>4.27628469467163</v>
       </c>
       <c r="H1741" t="n">
         <v>16027</v>
@@ -50916,7 +50916,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1743" t="n">
-        <v>4.11525297164917</v>
+        <v>4.11525249481201</v>
       </c>
       <c r="H1743" t="n">
         <v>94018</v>
@@ -51148,7 +51148,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1751" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1751" t="n">
         <v>17367</v>
@@ -51177,7 +51177,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>4.73254108428955</v>
+        <v>4.73254060745239</v>
       </c>
       <c r="H1752" t="n">
         <v>15553</v>
@@ -51264,7 +51264,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1755" t="n">
-        <v>4.652024269104</v>
+        <v>4.65202474594116</v>
       </c>
       <c r="H1755" t="n">
         <v>12664</v>
@@ -51293,7 +51293,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1756" t="n">
         <v>11240</v>
@@ -51351,7 +51351,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1758" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1758" t="n">
         <v>45839</v>
@@ -51380,7 +51380,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1759" t="n">
-        <v>5.06355047225952</v>
+        <v>5.06354999542236</v>
       </c>
       <c r="H1759" t="n">
         <v>9338</v>
@@ -51409,7 +51409,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1760" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092744827271</v>
       </c>
       <c r="H1760" t="n">
         <v>46326</v>
@@ -51467,7 +51467,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1762" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1762" t="n">
         <v>17489</v>
@@ -51496,7 +51496,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1763" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092744827271</v>
       </c>
       <c r="H1763" t="n">
         <v>15553</v>
@@ -51554,7 +51554,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1765" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1765" t="n">
         <v>16423</v>
@@ -51612,7 +51612,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1767" t="n">
-        <v>5.27825880050659</v>
+        <v>5.27825927734375</v>
       </c>
       <c r="H1767" t="n">
         <v>22888</v>
@@ -51670,7 +51670,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1769" t="n">
-        <v>5.26036691665649</v>
+        <v>5.26036739349365</v>
       </c>
       <c r="H1769" t="n">
         <v>11761</v>
@@ -51699,7 +51699,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1770" t="n">
-        <v>5.25142049789429</v>
+        <v>5.25142002105713</v>
       </c>
       <c r="H1770" t="n">
         <v>14837</v>
@@ -51786,7 +51786,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.86673402786255</v>
+        <v>4.86673355102539</v>
       </c>
       <c r="H1773" t="n">
         <v>21989</v>
@@ -51873,7 +51873,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1776" t="n">
-        <v>5.07249641418457</v>
+        <v>5.07249593734741</v>
       </c>
       <c r="H1776" t="n">
         <v>5907</v>
@@ -51902,7 +51902,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1777" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1777" t="n">
         <v>7772</v>
@@ -51931,7 +51931,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1778" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1778" t="n">
         <v>5909</v>
@@ -51960,7 +51960,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1779" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1779" t="n">
         <v>8483</v>
@@ -51989,7 +51989,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.70570230484009</v>
+        <v>4.70570278167725</v>
       </c>
       <c r="H1780" t="n">
         <v>77215</v>
@@ -52047,7 +52047,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.75043249130249</v>
+        <v>4.75043296813965</v>
       </c>
       <c r="H1782" t="n">
         <v>6784</v>
@@ -52163,7 +52163,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1786" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1786" t="n">
         <v>7645</v>
@@ -52250,7 +52250,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1789" t="n">
-        <v>4.85778713226318</v>
+        <v>4.85778760910034</v>
       </c>
       <c r="H1789" t="n">
         <v>18301</v>
@@ -52482,7 +52482,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.83989477157593</v>
+        <v>4.83989524841309</v>
       </c>
       <c r="H1797" t="n">
         <v>3037</v>
@@ -52569,7 +52569,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1800" t="n">
-        <v>4.77727222442627</v>
+        <v>4.77727174758911</v>
       </c>
       <c r="H1800" t="n">
         <v>20596</v>
@@ -52743,7 +52743,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1806" t="n">
-        <v>4.83989477157593</v>
+        <v>4.83989524841309</v>
       </c>
       <c r="H1806" t="n">
         <v>10263</v>
@@ -52801,7 +52801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1808" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1808" t="n">
         <v>30637</v>
@@ -52830,7 +52830,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1809" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1809" t="n">
         <v>25456</v>
@@ -52859,7 +52859,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1810" t="n">
         <v>5265</v>
@@ -52888,7 +52888,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1811" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1811" t="n">
         <v>17032</v>
@@ -52917,7 +52917,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1812" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1812" t="n">
         <v>44688</v>
@@ -52946,7 +52946,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>5.0098729133606</v>
+        <v>5.00987339019775</v>
       </c>
       <c r="H1813" t="n">
         <v>24148</v>
@@ -52975,7 +52975,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.97408771514893</v>
+        <v>4.97408819198608</v>
       </c>
       <c r="H1814" t="n">
         <v>12241</v>
@@ -53120,7 +53120,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1819" t="n">
         <v>39832</v>
@@ -53236,7 +53236,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1823" t="n">
         <v>5146</v>
@@ -53294,7 +53294,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1825" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092744827271</v>
       </c>
       <c r="H1825" t="n">
         <v>33072</v>
@@ -53497,7 +53497,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.97408771514893</v>
+        <v>4.97408819198608</v>
       </c>
       <c r="H1832" t="n">
         <v>20783</v>
@@ -53526,7 +53526,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1833" t="n">
         <v>11546</v>
@@ -53555,7 +53555,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1834" t="n">
-        <v>5.00092649459839</v>
+        <v>5.00092744827271</v>
       </c>
       <c r="H1834" t="n">
         <v>23025</v>
@@ -53613,7 +53613,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1836" t="n">
         <v>13665</v>
@@ -53642,7 +53642,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.96514225006104</v>
+        <v>4.96514272689819</v>
       </c>
       <c r="H1837" t="n">
         <v>10041</v>
@@ -53758,7 +53758,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1841" t="n">
-        <v>5.02776527404785</v>
+        <v>5.02776479721069</v>
       </c>
       <c r="H1841" t="n">
         <v>12032</v>
@@ -53787,7 +53787,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1842" t="n">
-        <v>5.06355047225952</v>
+        <v>5.06354999542236</v>
       </c>
       <c r="H1842" t="n">
         <v>17490</v>
@@ -53845,7 +53845,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1844" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1844" t="n">
         <v>8797</v>
@@ -53903,7 +53903,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1846" t="n">
-        <v>5.02776527404785</v>
+        <v>5.02776479721069</v>
       </c>
       <c r="H1846" t="n">
         <v>9167</v>
@@ -53932,7 +53932,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1847" t="n">
-        <v>5.07249641418457</v>
+        <v>5.07249593734741</v>
       </c>
       <c r="H1847" t="n">
         <v>7429</v>
@@ -54019,7 +54019,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G1850" t="n">
-        <v>5.07249641418457</v>
+        <v>5.07249593734741</v>
       </c>
       <c r="H1850" t="n">
         <v>5078</v>
@@ -54048,7 +54048,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1851" t="n">
-        <v>5.08144283294678</v>
+        <v>5.08144235610962</v>
       </c>
       <c r="H1851" t="n">
         <v>10038</v>
@@ -54077,7 +54077,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1852" t="n">
-        <v>5.12617349624634</v>
+        <v>5.12617301940918</v>
       </c>
       <c r="H1852" t="n">
         <v>4188</v>
@@ -54106,7 +54106,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1853" t="n">
-        <v>5.12617349624634</v>
+        <v>5.12617301940918</v>
       </c>
       <c r="H1853" t="n">
         <v>6700</v>
@@ -54135,7 +54135,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1854" t="n">
-        <v>5.11722755432129</v>
+        <v>5.11722707748413</v>
       </c>
       <c r="H1854" t="n">
         <v>8009</v>
@@ -54164,7 +54164,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1855" t="n">
-        <v>5.16195869445801</v>
+        <v>5.16195821762085</v>
       </c>
       <c r="H1855" t="n">
         <v>7158</v>
@@ -54193,7 +54193,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1856" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1856" t="n">
         <v>18091</v>
@@ -54251,7 +54251,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1858" t="n">
-        <v>5.29615163803101</v>
+        <v>5.29615116119385</v>
       </c>
       <c r="H1858" t="n">
         <v>6450</v>
@@ -80096,6 +80096,35 @@
         <v>43545</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>4.85500001907349</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>4.65500020980835</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>25125</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BAN.MI.xlsx
+++ b/data/BAN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59127044677734</v>
+        <v>3.59127020835876</v>
       </c>
       <c r="H2" t="n">
         <v>72929</v>
@@ -456,7 +456,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G3" t="n">
-        <v>3.60514187812805</v>
+        <v>3.60514235496521</v>
       </c>
       <c r="H3" t="n">
         <v>46376</v>
@@ -514,7 +514,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G5" t="n">
-        <v>3.38935780525208</v>
+        <v>3.38935732841492</v>
       </c>
       <c r="H5" t="n">
         <v>181917</v>
@@ -543,7 +543,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G6" t="n">
-        <v>3.34620046615601</v>
+        <v>3.34620118141174</v>
       </c>
       <c r="H6" t="n">
         <v>71336</v>
@@ -572,7 +572,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G7" t="n">
-        <v>3.28608965873718</v>
+        <v>3.28608989715576</v>
       </c>
       <c r="H7" t="n">
         <v>56010</v>
@@ -601,7 +601,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G8" t="n">
-        <v>3.37240290641785</v>
+        <v>3.37240314483643</v>
       </c>
       <c r="H8" t="n">
         <v>62861</v>
@@ -630,7 +630,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.39089941978455</v>
+        <v>3.39089894294739</v>
       </c>
       <c r="H9" t="n">
         <v>38098</v>
@@ -688,7 +688,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35853099822998</v>
+        <v>3.35853123664856</v>
       </c>
       <c r="H11" t="n">
         <v>95260</v>
@@ -717,7 +717,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G12" t="n">
-        <v>3.31229209899902</v>
+        <v>3.31229162216187</v>
       </c>
       <c r="H12" t="n">
         <v>77310</v>
@@ -746,7 +746,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G13" t="n">
-        <v>3.33695340156555</v>
+        <v>3.33695268630981</v>
       </c>
       <c r="H13" t="n">
         <v>58756</v>
@@ -775,7 +775,7 @@
         <v>3.95799994468689</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05026793479919</v>
+        <v>3.05026745796204</v>
       </c>
       <c r="H14" t="n">
         <v>232026</v>
@@ -804,7 +804,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G15" t="n">
-        <v>3.17203211784363</v>
+        <v>3.17203235626221</v>
       </c>
       <c r="H15" t="n">
         <v>196273</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.22135376930237</v>
+        <v>3.22135400772095</v>
       </c>
       <c r="H16" t="n">
         <v>58469</v>
@@ -862,7 +862,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G17" t="n">
-        <v>3.14428758621216</v>
+        <v>3.1442883014679</v>
       </c>
       <c r="H17" t="n">
         <v>52350</v>
@@ -891,7 +891,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G18" t="n">
-        <v>3.19823431968689</v>
+        <v>3.19823455810547</v>
       </c>
       <c r="H18" t="n">
         <v>61482</v>
@@ -920,7 +920,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G19" t="n">
-        <v>3.12579250335693</v>
+        <v>3.12579274177551</v>
       </c>
       <c r="H19" t="n">
         <v>16969</v>
@@ -949,7 +949,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G20" t="n">
-        <v>3.06722235679626</v>
+        <v>3.06722211837769</v>
       </c>
       <c r="H20" t="n">
         <v>38321</v>
@@ -1065,7 +1065,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G24" t="n">
-        <v>3.00556969642639</v>
+        <v>3.00556993484497</v>
       </c>
       <c r="H24" t="n">
         <v>130754</v>
@@ -1094,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>3.08263564109802</v>
+        <v>3.08263540267944</v>
       </c>
       <c r="H25" t="n">
         <v>43277</v>
@@ -1123,7 +1123,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G26" t="n">
-        <v>2.98553228378296</v>
+        <v>2.98553252220154</v>
       </c>
       <c r="H26" t="n">
         <v>72543</v>
@@ -1152,7 +1152,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G27" t="n">
-        <v>2.86685132980347</v>
+        <v>2.86685109138489</v>
       </c>
       <c r="H27" t="n">
         <v>119521</v>
@@ -1181,7 +1181,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>2.85143780708313</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H28" t="n">
         <v>67495</v>
@@ -1239,7 +1239,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76666498184204</v>
+        <v>2.76666522026062</v>
       </c>
       <c r="H30" t="n">
         <v>152737</v>
@@ -1268,7 +1268,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G31" t="n">
-        <v>2.69422364234924</v>
+        <v>2.69422316551208</v>
       </c>
       <c r="H31" t="n">
         <v>107730</v>
@@ -1297,7 +1297,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G32" t="n">
-        <v>2.69576454162598</v>
+        <v>2.69576478004456</v>
       </c>
       <c r="H32" t="n">
         <v>156635</v>
@@ -1355,7 +1355,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G34" t="n">
-        <v>2.85143780708313</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H34" t="n">
         <v>57855</v>
@@ -1413,7 +1413,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86685132980347</v>
+        <v>2.86685109138489</v>
       </c>
       <c r="H36" t="n">
         <v>30589</v>
@@ -1442,7 +1442,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G37" t="n">
-        <v>2.91925573348999</v>
+        <v>2.91925597190857</v>
       </c>
       <c r="H37" t="n">
         <v>20925</v>
@@ -1471,7 +1471,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G38" t="n">
-        <v>2.89921879768372</v>
+        <v>2.89921855926514</v>
       </c>
       <c r="H38" t="n">
         <v>57547</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.85143780708313</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H39" t="n">
         <v>25330</v>
@@ -1529,7 +1529,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.85143780708313</v>
+        <v>2.85143804550171</v>
       </c>
       <c r="H40" t="n">
         <v>31248</v>
@@ -1558,7 +1558,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93004488945007</v>
+        <v>2.93004536628723</v>
       </c>
       <c r="H41" t="n">
         <v>36631</v>
@@ -1587,7 +1587,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G42" t="n">
-        <v>2.99478030204773</v>
+        <v>2.99478054046631</v>
       </c>
       <c r="H42" t="n">
         <v>55878</v>
@@ -1645,7 +1645,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G44" t="n">
-        <v>3.0040283203125</v>
+        <v>3.00402855873108</v>
       </c>
       <c r="H44" t="n">
         <v>22788</v>
@@ -1674,7 +1674,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G45" t="n">
-        <v>2.90075993537903</v>
+        <v>2.90075969696045</v>
       </c>
       <c r="H45" t="n">
         <v>67040</v>
@@ -1732,7 +1732,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9439172744751</v>
+        <v>2.94391703605652</v>
       </c>
       <c r="H47" t="n">
         <v>29987</v>
@@ -1761,7 +1761,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G48" t="n">
-        <v>2.913090467453</v>
+        <v>2.91309022903442</v>
       </c>
       <c r="H48" t="n">
         <v>23813</v>
@@ -1877,7 +1877,7 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08263564109802</v>
+        <v>3.08263540267944</v>
       </c>
       <c r="H52" t="n">
         <v>21452</v>
@@ -1964,7 +1964,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G55" t="n">
-        <v>3.07030510902405</v>
+        <v>3.07030487060547</v>
       </c>
       <c r="H55" t="n">
         <v>14032</v>
@@ -1993,7 +1993,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>3.14428758621216</v>
+        <v>3.1442883014679</v>
       </c>
       <c r="H56" t="n">
         <v>126601</v>
@@ -2022,7 +2022,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G57" t="n">
-        <v>3.22135376930237</v>
+        <v>3.22135400772095</v>
       </c>
       <c r="H57" t="n">
         <v>62497</v>
@@ -2051,7 +2051,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G58" t="n">
-        <v>3.16432547569275</v>
+        <v>3.16432523727417</v>
       </c>
       <c r="H58" t="n">
         <v>30025</v>
@@ -2080,7 +2080,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G59" t="n">
-        <v>3.26759314537048</v>
+        <v>3.26759386062622</v>
       </c>
       <c r="H59" t="n">
         <v>68882</v>
@@ -2109,7 +2109,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.23676729202271</v>
+        <v>3.23676753044128</v>
       </c>
       <c r="H60" t="n">
         <v>54892</v>
@@ -2196,7 +2196,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14428758621216</v>
+        <v>3.1442883014679</v>
       </c>
       <c r="H63" t="n">
         <v>22488</v>
@@ -2225,7 +2225,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05951595306396</v>
+        <v>3.05951571464539</v>
       </c>
       <c r="H64" t="n">
         <v>70519</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.12887477874756</v>
+        <v>3.12887525558472</v>
       </c>
       <c r="H65" t="n">
         <v>34918</v>
@@ -2283,7 +2283,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G66" t="n">
-        <v>3.13504004478455</v>
+        <v>3.13504076004028</v>
       </c>
       <c r="H66" t="n">
         <v>37530</v>
@@ -2312,7 +2312,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G67" t="n">
-        <v>3.03793740272522</v>
+        <v>3.0379376411438</v>
       </c>
       <c r="H67" t="n">
         <v>20927</v>
@@ -2341,7 +2341,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G68" t="n">
-        <v>3.04718542098999</v>
+        <v>3.04718494415283</v>
       </c>
       <c r="H68" t="n">
         <v>20107</v>
@@ -2370,7 +2370,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G69" t="n">
-        <v>3.07492876052856</v>
+        <v>3.07492923736572</v>
       </c>
       <c r="H69" t="n">
         <v>21306</v>
@@ -2428,7 +2428,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>2.93621063232422</v>
+        <v>2.93620991706848</v>
       </c>
       <c r="H71" t="n">
         <v>17654</v>
@@ -2457,7 +2457,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G72" t="n">
-        <v>2.8976776599884</v>
+        <v>2.89767742156982</v>
       </c>
       <c r="H72" t="n">
         <v>32000</v>
@@ -2486,7 +2486,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G73" t="n">
-        <v>3.02868914604187</v>
+        <v>3.02868962287903</v>
       </c>
       <c r="H73" t="n">
         <v>10988</v>
@@ -2515,7 +2515,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>2.90538358688354</v>
+        <v>2.9053840637207</v>
       </c>
       <c r="H74" t="n">
         <v>47297</v>
@@ -2573,7 +2573,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G76" t="n">
-        <v>2.81290483474731</v>
+        <v>2.81290555000305</v>
       </c>
       <c r="H76" t="n">
         <v>95558</v>
@@ -2602,7 +2602,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G77" t="n">
-        <v>2.84835505485535</v>
+        <v>2.84835529327393</v>
       </c>
       <c r="H77" t="n">
         <v>24243</v>
@@ -2631,7 +2631,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G78" t="n">
-        <v>2.92233872413635</v>
+        <v>2.92233848571777</v>
       </c>
       <c r="H78" t="n">
         <v>48703</v>
@@ -2718,7 +2718,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G81" t="n">
-        <v>2.86530923843384</v>
+        <v>2.865309715271</v>
       </c>
       <c r="H81" t="n">
         <v>52337</v>
@@ -2747,7 +2747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.85914492607117</v>
+        <v>2.85914444923401</v>
       </c>
       <c r="H82" t="n">
         <v>23339</v>
@@ -2776,7 +2776,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>2.79749202728271</v>
+        <v>2.79749178886414</v>
       </c>
       <c r="H83" t="n">
         <v>43312</v>
@@ -2805,7 +2805,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G84" t="n">
-        <v>2.7543351650238</v>
+        <v>2.75433468818665</v>
       </c>
       <c r="H84" t="n">
         <v>21266</v>
@@ -2834,7 +2834,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G85" t="n">
-        <v>2.7543351650238</v>
+        <v>2.75433468818665</v>
       </c>
       <c r="H85" t="n">
         <v>24473</v>
@@ -2892,7 +2892,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G87" t="n">
-        <v>2.74200415611267</v>
+        <v>2.74200439453125</v>
       </c>
       <c r="H87" t="n">
         <v>25791</v>
@@ -2979,7 +2979,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G90" t="n">
-        <v>2.62486410140991</v>
+        <v>2.62486433982849</v>
       </c>
       <c r="H90" t="n">
         <v>31513</v>
@@ -3008,7 +3008,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>2.6572322845459</v>
+        <v>2.65723180770874</v>
       </c>
       <c r="H91" t="n">
         <v>18592</v>
@@ -3037,7 +3037,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.70501255989075</v>
+        <v>2.70501279830933</v>
       </c>
       <c r="H92" t="n">
         <v>35213</v>
@@ -3066,7 +3066,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>2.72042608261108</v>
+        <v>2.7204258441925</v>
       </c>
       <c r="H93" t="n">
         <v>19766</v>
@@ -3095,7 +3095,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G94" t="n">
-        <v>2.66647958755493</v>
+        <v>2.66647982597351</v>
       </c>
       <c r="H94" t="n">
         <v>45599</v>
@@ -3124,7 +3124,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>2.53546762466431</v>
+        <v>2.53546786308289</v>
       </c>
       <c r="H95" t="n">
         <v>173451</v>
@@ -3153,7 +3153,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48152160644531</v>
+        <v>2.48152184486389</v>
       </c>
       <c r="H96" t="n">
         <v>102059</v>
@@ -3211,7 +3211,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>2.42757534980774</v>
+        <v>2.42757558822632</v>
       </c>
       <c r="H98" t="n">
         <v>26401</v>
@@ -3240,7 +3240,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G99" t="n">
-        <v>2.46610879898071</v>
+        <v>2.46610856056213</v>
       </c>
       <c r="H99" t="n">
         <v>80928</v>
@@ -3269,7 +3269,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55043363571167</v>
+        <v>2.55043315887451</v>
       </c>
       <c r="H100" t="n">
         <v>23573</v>
@@ -3298,7 +3298,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.53293228149414</v>
+        <v>2.53293204307556</v>
       </c>
       <c r="H101" t="n">
         <v>61597</v>
@@ -3327,7 +3327,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.50588464736938</v>
+        <v>2.50588440895081</v>
       </c>
       <c r="H102" t="n">
         <v>52729</v>
@@ -3385,7 +3385,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.55361533164978</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H104" t="n">
         <v>41372</v>
@@ -3443,7 +3443,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G106" t="n">
-        <v>2.5265679359436</v>
+        <v>2.52656817436218</v>
       </c>
       <c r="H106" t="n">
         <v>37323</v>
@@ -3472,7 +3472,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G107" t="n">
-        <v>2.5265679359436</v>
+        <v>2.52656817436218</v>
       </c>
       <c r="H107" t="n">
         <v>41652</v>
@@ -3530,7 +3530,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G109" t="n">
-        <v>2.66339707374573</v>
+        <v>2.66339755058289</v>
       </c>
       <c r="H109" t="n">
         <v>176680</v>
@@ -3559,7 +3559,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H110" t="n">
         <v>125977</v>
@@ -3588,7 +3588,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.74454045295715</v>
+        <v>2.74453973770142</v>
       </c>
       <c r="H111" t="n">
         <v>312957</v>
@@ -3617,7 +3617,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G112" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H112" t="n">
         <v>290102</v>
@@ -3675,7 +3675,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.50588464736938</v>
+        <v>2.50588440895081</v>
       </c>
       <c r="H114" t="n">
         <v>83369</v>
@@ -3704,7 +3704,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>2.39451193809509</v>
+        <v>2.39451169967651</v>
       </c>
       <c r="H115" t="n">
         <v>82760</v>
@@ -3733,7 +3733,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>2.34678053855896</v>
+        <v>2.34678101539612</v>
       </c>
       <c r="H116" t="n">
         <v>57327</v>
@@ -3762,7 +3762,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>2.39451193809509</v>
+        <v>2.39451169967651</v>
       </c>
       <c r="H117" t="n">
         <v>48701</v>
@@ -3791,7 +3791,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>2.34678053855896</v>
+        <v>2.34678101539612</v>
       </c>
       <c r="H118" t="n">
         <v>55466</v>
@@ -3820,7 +3820,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G119" t="n">
-        <v>2.45019817352295</v>
+        <v>2.45019793510437</v>
       </c>
       <c r="H119" t="n">
         <v>187802</v>
@@ -3849,7 +3849,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G120" t="n">
-        <v>2.42315053939819</v>
+        <v>2.42315030097961</v>
       </c>
       <c r="H120" t="n">
         <v>40122</v>
@@ -3936,7 +3936,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G123" t="n">
-        <v>2.4549708366394</v>
+        <v>2.45497131347656</v>
       </c>
       <c r="H123" t="n">
         <v>154366</v>
@@ -3965,7 +3965,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35473585128784</v>
+        <v>2.35473561286926</v>
       </c>
       <c r="H124" t="n">
         <v>319100</v>
@@ -3994,7 +3994,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14790081977844</v>
+        <v>2.14790058135986</v>
       </c>
       <c r="H125" t="n">
         <v>176396</v>
@@ -4052,7 +4052,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G127" t="n">
-        <v>2.2465455532074</v>
+        <v>2.24654531478882</v>
       </c>
       <c r="H127" t="n">
         <v>83605</v>
@@ -4110,7 +4110,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G129" t="n">
-        <v>2.30700492858887</v>
+        <v>2.30700516700745</v>
       </c>
       <c r="H129" t="n">
         <v>136895</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.32291531562805</v>
+        <v>2.32291507720947</v>
       </c>
       <c r="H130" t="n">
         <v>32482</v>
@@ -4168,7 +4168,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.24336290359497</v>
+        <v>2.24336314201355</v>
       </c>
       <c r="H131" t="n">
         <v>19361</v>
@@ -4197,7 +4197,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G132" t="n">
-        <v>2.14630961418152</v>
+        <v>2.1463098526001</v>
       </c>
       <c r="H132" t="n">
         <v>157907</v>
@@ -4226,7 +4226,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G133" t="n">
-        <v>2.17813038825989</v>
+        <v>2.17813062667847</v>
       </c>
       <c r="H133" t="n">
         <v>87599</v>
@@ -4255,7 +4255,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>2.23540806770325</v>
+        <v>2.23540782928467</v>
       </c>
       <c r="H134" t="n">
         <v>81622</v>
@@ -4284,7 +4284,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25609111785889</v>
+        <v>2.25609135627747</v>
       </c>
       <c r="H135" t="n">
         <v>36502</v>
@@ -4313,7 +4313,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G136" t="n">
-        <v>2.28154826164246</v>
+        <v>2.28154802322388</v>
       </c>
       <c r="H136" t="n">
         <v>119374</v>
@@ -4342,7 +4342,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G137" t="n">
-        <v>2.28632092475891</v>
+        <v>2.28632116317749</v>
       </c>
       <c r="H137" t="n">
         <v>96462</v>
@@ -4400,7 +4400,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>2.27041077613831</v>
+        <v>2.27041101455688</v>
       </c>
       <c r="H139" t="n">
         <v>22031</v>
@@ -4429,7 +4429,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G140" t="n">
-        <v>2.27041077613831</v>
+        <v>2.27041101455688</v>
       </c>
       <c r="H140" t="n">
         <v>51795</v>
@@ -4458,7 +4458,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G141" t="n">
-        <v>2.33087038993835</v>
+        <v>2.33087062835693</v>
       </c>
       <c r="H141" t="n">
         <v>33609</v>
@@ -4574,7 +4574,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G145" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H145" t="n">
         <v>74728</v>
@@ -4603,7 +4603,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G146" t="n">
-        <v>2.83522939682007</v>
+        <v>2.83522915840149</v>
       </c>
       <c r="H146" t="n">
         <v>321439</v>
@@ -4632,7 +4632,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G147" t="n">
-        <v>2.77795195579529</v>
+        <v>2.77795171737671</v>
       </c>
       <c r="H147" t="n">
         <v>193727</v>
@@ -4661,7 +4661,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H148" t="n">
         <v>65327</v>
@@ -4690,7 +4690,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G149" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H149" t="n">
         <v>491545</v>
@@ -4777,7 +4777,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G152" t="n">
-        <v>2.55361533164978</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H152" t="n">
         <v>45450</v>
@@ -4806,7 +4806,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G153" t="n">
-        <v>2.55043363571167</v>
+        <v>2.55043315887451</v>
       </c>
       <c r="H153" t="n">
         <v>144787</v>
@@ -4922,7 +4922,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G157" t="n">
-        <v>2.51861262321472</v>
+        <v>2.5186128616333</v>
       </c>
       <c r="H157" t="n">
         <v>42162</v>
@@ -4980,7 +4980,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G159" t="n">
-        <v>2.51224851608276</v>
+        <v>2.51224827766418</v>
       </c>
       <c r="H159" t="n">
         <v>72706</v>
@@ -5183,7 +5183,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G166" t="n">
-        <v>2.58066296577454</v>
+        <v>2.58066320419312</v>
       </c>
       <c r="H166" t="n">
         <v>115779</v>
@@ -5241,7 +5241,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>2.58066296577454</v>
+        <v>2.58066320419312</v>
       </c>
       <c r="H168" t="n">
         <v>37331</v>
@@ -5270,7 +5270,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.59020972251892</v>
+        <v>2.59020948410034</v>
       </c>
       <c r="H169" t="n">
         <v>13943</v>
@@ -5299,7 +5299,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G170" t="n">
-        <v>2.59657335281372</v>
+        <v>2.5965735912323</v>
       </c>
       <c r="H170" t="n">
         <v>50663</v>
@@ -5328,7 +5328,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G171" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225440979004</v>
       </c>
       <c r="H171" t="n">
         <v>48256</v>
@@ -5386,7 +5386,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G173" t="n">
-        <v>2.63475871086121</v>
+        <v>2.63475823402405</v>
       </c>
       <c r="H173" t="n">
         <v>113264</v>
@@ -5415,7 +5415,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.69839954376221</v>
+        <v>2.69839978218079</v>
       </c>
       <c r="H174" t="n">
         <v>40940</v>
@@ -5444,7 +5444,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G175" t="n">
-        <v>2.73340249061584</v>
+        <v>2.73340320587158</v>
       </c>
       <c r="H175" t="n">
         <v>109716</v>
@@ -5473,7 +5473,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G176" t="n">
-        <v>2.73340249061584</v>
+        <v>2.73340320587158</v>
       </c>
       <c r="H176" t="n">
         <v>20242</v>
@@ -5502,7 +5502,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G177" t="n">
-        <v>2.76045036315918</v>
+        <v>2.76045060157776</v>
       </c>
       <c r="H177" t="n">
         <v>60761</v>
@@ -5531,7 +5531,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.70476412773132</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H178" t="n">
         <v>27763</v>
@@ -5676,7 +5676,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G183" t="n">
-        <v>2.70953679084778</v>
+        <v>2.70953726768494</v>
       </c>
       <c r="H183" t="n">
         <v>54185</v>
@@ -5705,7 +5705,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G184" t="n">
-        <v>2.64907765388489</v>
+        <v>2.64907741546631</v>
       </c>
       <c r="H184" t="n">
         <v>14160</v>
@@ -5734,7 +5734,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G185" t="n">
-        <v>2.66976118087769</v>
+        <v>2.66976070404053</v>
       </c>
       <c r="H185" t="n">
         <v>14080</v>
@@ -5792,7 +5792,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G187" t="n">
-        <v>2.7111279964447</v>
+        <v>2.71112847328186</v>
       </c>
       <c r="H187" t="n">
         <v>39220</v>
@@ -5850,7 +5850,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>2.64907765388489</v>
+        <v>2.64907741546631</v>
       </c>
       <c r="H189" t="n">
         <v>47560</v>
@@ -5879,7 +5879,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G190" t="n">
-        <v>2.63794016838074</v>
+        <v>2.63794088363647</v>
       </c>
       <c r="H190" t="n">
         <v>53442</v>
@@ -5908,7 +5908,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G191" t="n">
-        <v>2.61089277267456</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H191" t="n">
         <v>9182</v>
@@ -5937,7 +5937,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.59180021286011</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H192" t="n">
         <v>29200</v>
@@ -5995,7 +5995,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G194" t="n">
-        <v>2.54247856140137</v>
+        <v>2.54247808456421</v>
       </c>
       <c r="H194" t="n">
         <v>27987</v>
@@ -6024,7 +6024,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G195" t="n">
-        <v>2.55361533164978</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H195" t="n">
         <v>12196</v>
@@ -6053,7 +6053,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>2.56157064437866</v>
+        <v>2.56157088279724</v>
       </c>
       <c r="H196" t="n">
         <v>30767</v>
@@ -6111,7 +6111,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>2.55361533164978</v>
+        <v>2.55361557006836</v>
       </c>
       <c r="H198" t="n">
         <v>11245</v>
@@ -6140,7 +6140,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G199" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930156707764</v>
       </c>
       <c r="H199" t="n">
         <v>6143</v>
@@ -6198,7 +6198,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G201" t="n">
-        <v>2.63157653808594</v>
+        <v>2.63157629966736</v>
       </c>
       <c r="H201" t="n">
         <v>48572</v>
@@ -6227,7 +6227,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G202" t="n">
-        <v>2.54725170135498</v>
+        <v>2.54725122451782</v>
       </c>
       <c r="H202" t="n">
         <v>36814</v>
@@ -6285,7 +6285,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G204" t="n">
-        <v>2.62043881416321</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H204" t="n">
         <v>8159</v>
@@ -6343,7 +6343,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.70476412773132</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H206" t="n">
         <v>52437</v>
@@ -6372,7 +6372,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>2.69680905342102</v>
+        <v>2.69680881500244</v>
       </c>
       <c r="H207" t="n">
         <v>9998</v>
@@ -6401,7 +6401,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>2.66817021369934</v>
+        <v>2.66817045211792</v>
       </c>
       <c r="H208" t="n">
         <v>47680</v>
@@ -6430,7 +6430,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H209" t="n">
         <v>24860</v>
@@ -6459,7 +6459,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>2.76840543746948</v>
+        <v>2.76840591430664</v>
       </c>
       <c r="H210" t="n">
         <v>76075</v>
@@ -6488,7 +6488,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G211" t="n">
-        <v>2.68567156791687</v>
+        <v>2.68567109107971</v>
       </c>
       <c r="H211" t="n">
         <v>106947</v>
@@ -6575,7 +6575,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G214" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089866638184</v>
       </c>
       <c r="H214" t="n">
         <v>41273</v>
@@ -6604,7 +6604,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089866638184</v>
       </c>
       <c r="H215" t="n">
         <v>9359</v>
@@ -6662,7 +6662,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>2.63316750526428</v>
+        <v>2.6331672668457</v>
       </c>
       <c r="H217" t="n">
         <v>19269</v>
@@ -6749,7 +6749,7 @@
         <v>3.21399998664856</v>
       </c>
       <c r="G220" t="n">
-        <v>2.55679726600647</v>
+        <v>2.55679750442505</v>
       </c>
       <c r="H220" t="n">
         <v>41230</v>
@@ -6778,7 +6778,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G221" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H221" t="n">
         <v>43595</v>
@@ -6836,7 +6836,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G223" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H223" t="n">
         <v>18854</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H224" t="n">
         <v>33279</v>
@@ -6923,7 +6923,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G226" t="n">
-        <v>2.56793451309204</v>
+        <v>2.56793475151062</v>
       </c>
       <c r="H226" t="n">
         <v>41172</v>
@@ -6981,7 +6981,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G228" t="n">
-        <v>2.53929567337036</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H228" t="n">
         <v>26610</v>
@@ -7010,7 +7010,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G229" t="n">
-        <v>2.50588464736938</v>
+        <v>2.50588440895081</v>
       </c>
       <c r="H229" t="n">
         <v>14019</v>
@@ -7068,7 +7068,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G231" t="n">
-        <v>2.49952006340027</v>
+        <v>2.49951982498169</v>
       </c>
       <c r="H231" t="n">
         <v>16357</v>
@@ -7184,7 +7184,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>2.41519498825073</v>
+        <v>2.41519522666931</v>
       </c>
       <c r="H235" t="n">
         <v>57120</v>
@@ -7213,7 +7213,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G236" t="n">
-        <v>2.41519498825073</v>
+        <v>2.41519522666931</v>
       </c>
       <c r="H236" t="n">
         <v>18231</v>
@@ -7242,7 +7242,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>2.35473585128784</v>
+        <v>2.35473561286926</v>
       </c>
       <c r="H237" t="n">
         <v>69110</v>
@@ -7271,7 +7271,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G238" t="n">
-        <v>2.44860744476318</v>
+        <v>2.44860672950745</v>
       </c>
       <c r="H238" t="n">
         <v>62898</v>
@@ -7300,7 +7300,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>2.50588464736938</v>
+        <v>2.50588440895081</v>
       </c>
       <c r="H239" t="n">
         <v>18391</v>
@@ -7358,7 +7358,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G241" t="n">
-        <v>2.50588464736938</v>
+        <v>2.50588440895081</v>
       </c>
       <c r="H241" t="n">
         <v>70052</v>
@@ -7387,7 +7387,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G242" t="n">
-        <v>2.53929567337036</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H242" t="n">
         <v>14106</v>
@@ -7416,7 +7416,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G243" t="n">
-        <v>2.53929567337036</v>
+        <v>2.53929615020752</v>
       </c>
       <c r="H243" t="n">
         <v>21628</v>
@@ -7445,7 +7445,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G244" t="n">
-        <v>2.52975034713745</v>
+        <v>2.52974987030029</v>
       </c>
       <c r="H244" t="n">
         <v>12347</v>
@@ -7474,7 +7474,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G245" t="n">
-        <v>2.57588982582092</v>
+        <v>2.5758900642395</v>
       </c>
       <c r="H245" t="n">
         <v>38786</v>
@@ -7677,7 +7677,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G252" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930156707764</v>
       </c>
       <c r="H252" t="n">
         <v>9879</v>
@@ -7706,7 +7706,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G253" t="n">
-        <v>2.59975576400757</v>
+        <v>2.59975552558899</v>
       </c>
       <c r="H253" t="n">
         <v>45016</v>
@@ -7735,7 +7735,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G254" t="n">
-        <v>2.61248397827148</v>
+        <v>2.61248373985291</v>
       </c>
       <c r="H254" t="n">
         <v>26246</v>
@@ -7764,7 +7764,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G255" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930156707764</v>
       </c>
       <c r="H255" t="n">
         <v>17200</v>
@@ -7793,7 +7793,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>2.63316750526428</v>
+        <v>2.6331672668457</v>
       </c>
       <c r="H256" t="n">
         <v>3048</v>
@@ -7851,7 +7851,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H258" t="n">
         <v>80602</v>
@@ -7880,7 +7880,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>2.7524950504303</v>
+        <v>2.75249528884888</v>
       </c>
       <c r="H259" t="n">
         <v>50582</v>
@@ -7909,7 +7909,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G260" t="n">
-        <v>2.7238564491272</v>
+        <v>2.72385621070862</v>
       </c>
       <c r="H260" t="n">
         <v>42845</v>
@@ -7938,7 +7938,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71271944046021</v>
+        <v>2.71271920204163</v>
       </c>
       <c r="H261" t="n">
         <v>30939</v>
@@ -7967,7 +7967,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G262" t="n">
-        <v>2.719083070755</v>
+        <v>2.71908354759216</v>
       </c>
       <c r="H262" t="n">
         <v>25385</v>
@@ -8083,7 +8083,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G266" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089866638184</v>
       </c>
       <c r="H266" t="n">
         <v>13826</v>
@@ -8112,7 +8112,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G267" t="n">
-        <v>2.71431016921997</v>
+        <v>2.71431040763855</v>
       </c>
       <c r="H267" t="n">
         <v>19300</v>
@@ -8141,7 +8141,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G268" t="n">
-        <v>2.70635533332825</v>
+        <v>2.70635509490967</v>
       </c>
       <c r="H268" t="n">
         <v>26397</v>
@@ -8170,7 +8170,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G269" t="n">
-        <v>2.70635533332825</v>
+        <v>2.70635509490967</v>
       </c>
       <c r="H269" t="n">
         <v>22982</v>
@@ -8228,7 +8228,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G271" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H271" t="n">
         <v>41308</v>
@@ -8257,7 +8257,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G272" t="n">
-        <v>2.63157653808594</v>
+        <v>2.63157629966736</v>
       </c>
       <c r="H272" t="n">
         <v>44211</v>
@@ -8286,7 +8286,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G273" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H273" t="n">
         <v>35545</v>
@@ -8315,7 +8315,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G274" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.62521195411682</v>
+        <v>2.62521243095398</v>
       </c>
       <c r="H275" t="n">
         <v>42217</v>
@@ -8489,7 +8489,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G280" t="n">
-        <v>2.59180021286011</v>
+        <v>2.59180045127869</v>
       </c>
       <c r="H280" t="n">
         <v>23457</v>
@@ -8605,7 +8605,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.68089818954468</v>
+        <v>2.68089866638184</v>
       </c>
       <c r="H284" t="n">
         <v>57420</v>
@@ -8663,7 +8663,7 @@
         <v>3.37800002098083</v>
       </c>
       <c r="G286" t="n">
-        <v>2.68726277351379</v>
+        <v>2.68726229667664</v>
       </c>
       <c r="H286" t="n">
         <v>17879</v>
@@ -8721,7 +8721,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>2.70476412773132</v>
+        <v>2.70476388931274</v>
       </c>
       <c r="H288" t="n">
         <v>50895</v>
@@ -8750,7 +8750,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G289" t="n">
-        <v>2.72067451477051</v>
+        <v>2.72067427635193</v>
       </c>
       <c r="H289" t="n">
         <v>25565</v>
@@ -8779,7 +8779,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G290" t="n">
-        <v>2.68885374069214</v>
+        <v>2.68885350227356</v>
       </c>
       <c r="H290" t="n">
         <v>82866</v>
@@ -8837,7 +8837,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G292" t="n">
-        <v>2.63316750526428</v>
+        <v>2.6331672668457</v>
       </c>
       <c r="H292" t="n">
         <v>71797</v>
@@ -8866,7 +8866,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G293" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H293" t="n">
         <v>34605</v>
@@ -8895,7 +8895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G294" t="n">
-        <v>2.66498804092407</v>
+        <v>2.66498827934265</v>
       </c>
       <c r="H294" t="n">
         <v>25347</v>
@@ -8953,7 +8953,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G296" t="n">
-        <v>2.62043881416321</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H296" t="n">
         <v>18722</v>
@@ -9011,7 +9011,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G298" t="n">
-        <v>2.58225417137146</v>
+        <v>2.58225440979004</v>
       </c>
       <c r="H298" t="n">
         <v>32196</v>
@@ -9127,7 +9127,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.59339165687561</v>
+        <v>2.59339118003845</v>
       </c>
       <c r="H302" t="n">
         <v>13538</v>
@@ -9156,7 +9156,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G303" t="n">
-        <v>2.61089277267456</v>
+        <v>2.61089301109314</v>
       </c>
       <c r="H303" t="n">
         <v>10504</v>
@@ -9214,7 +9214,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G305" t="n">
-        <v>2.60930180549622</v>
+        <v>2.60930156707764</v>
       </c>
       <c r="H305" t="n">
         <v>49411</v>
@@ -9272,7 +9272,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G307" t="n">
-        <v>2.63794016838074</v>
+        <v>2.63794088363647</v>
       </c>
       <c r="H307" t="n">
         <v>62268</v>
@@ -9301,7 +9301,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G308" t="n">
-        <v>2.61248397827148</v>
+        <v>2.61248373985291</v>
       </c>
       <c r="H308" t="n">
         <v>66425</v>
@@ -9359,7 +9359,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G310" t="n">
-        <v>2.62043881416321</v>
+        <v>2.62043905258179</v>
       </c>
       <c r="H310" t="n">
         <v>89281</v>
@@ -9388,7 +9388,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G311" t="n">
-        <v>2.64112234115601</v>
+        <v>2.64112257957458</v>
       </c>
       <c r="H311" t="n">
         <v>41340</v>
@@ -9417,7 +9417,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G312" t="n">
-        <v>2.66817021369934</v>
+        <v>2.66817045211792</v>
       </c>
       <c r="H312" t="n">
         <v>57404</v>
@@ -9446,7 +9446,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>2.74454045295715</v>
+        <v>2.74453973770142</v>
       </c>
       <c r="H313" t="n">
         <v>87119</v>
@@ -9475,7 +9475,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G314" t="n">
-        <v>2.86068558692932</v>
+        <v>2.8606858253479</v>
       </c>
       <c r="H314" t="n">
         <v>698828</v>
@@ -9504,7 +9504,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H315" t="n">
         <v>207351</v>
@@ -9533,7 +9533,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93546462059021</v>
+        <v>2.93546438217163</v>
       </c>
       <c r="H316" t="n">
         <v>182578</v>
@@ -9591,7 +9591,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G318" t="n">
-        <v>2.90682601928711</v>
+        <v>2.90682578086853</v>
       </c>
       <c r="H318" t="n">
         <v>132386</v>
@@ -9678,7 +9678,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H321" t="n">
         <v>95397</v>
@@ -9707,7 +9707,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H322" t="n">
         <v>104092</v>
@@ -9736,7 +9736,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87182307243347</v>
+        <v>2.87182283401489</v>
       </c>
       <c r="H323" t="n">
         <v>35190</v>
@@ -9765,7 +9765,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G324" t="n">
-        <v>2.86068558692932</v>
+        <v>2.8606858253479</v>
       </c>
       <c r="H324" t="n">
         <v>27671</v>
@@ -9794,7 +9794,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>2.83681988716125</v>
+        <v>2.83682012557983</v>
       </c>
       <c r="H325" t="n">
         <v>158724</v>
@@ -9823,7 +9823,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G326" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H326" t="n">
         <v>89204</v>
@@ -9910,7 +9910,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G329" t="n">
-        <v>2.81772780418396</v>
+        <v>2.81772804260254</v>
       </c>
       <c r="H329" t="n">
         <v>82116</v>
@@ -9939,7 +9939,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>2.81454586982727</v>
+        <v>2.81454563140869</v>
       </c>
       <c r="H330" t="n">
         <v>69337</v>
@@ -10055,7 +10055,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G334" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H334" t="n">
         <v>92029</v>
@@ -10084,7 +10084,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H335" t="n">
         <v>53661</v>
@@ -10142,7 +10142,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H337" t="n">
         <v>70066</v>
@@ -10200,7 +10200,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.85750365257263</v>
+        <v>2.85750341415405</v>
       </c>
       <c r="H339" t="n">
         <v>238858</v>
@@ -10229,7 +10229,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G340" t="n">
-        <v>2.85273051261902</v>
+        <v>2.85273027420044</v>
       </c>
       <c r="H340" t="n">
         <v>51846</v>
@@ -10287,7 +10287,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G342" t="n">
-        <v>2.82409191131592</v>
+        <v>2.82409167289734</v>
       </c>
       <c r="H342" t="n">
         <v>125438</v>
@@ -10316,7 +10316,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G343" t="n">
-        <v>2.85432147979736</v>
+        <v>2.85432171821594</v>
       </c>
       <c r="H343" t="n">
         <v>124053</v>
@@ -10345,7 +10345,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G344" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H344" t="n">
         <v>89264</v>
@@ -10432,7 +10432,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G347" t="n">
-        <v>2.889324426651</v>
+        <v>2.88932490348816</v>
       </c>
       <c r="H347" t="n">
         <v>90670</v>
@@ -10461,7 +10461,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G348" t="n">
-        <v>2.87977814674377</v>
+        <v>2.87977838516235</v>
       </c>
       <c r="H348" t="n">
         <v>136711</v>
@@ -10577,7 +10577,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G352" t="n">
-        <v>2.93228268623352</v>
+        <v>2.93228244781494</v>
       </c>
       <c r="H352" t="n">
         <v>138348</v>
@@ -10606,7 +10606,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G353" t="n">
-        <v>2.91637182235718</v>
+        <v>2.91637206077576</v>
       </c>
       <c r="H353" t="n">
         <v>182186</v>
@@ -10635,7 +10635,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G354" t="n">
-        <v>2.94341969490051</v>
+        <v>2.94341993331909</v>
       </c>
       <c r="H354" t="n">
         <v>80424</v>
@@ -10693,7 +10693,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G356" t="n">
-        <v>3.05015897750854</v>
+        <v>3.05015921592712</v>
       </c>
       <c r="H356" t="n">
         <v>57659</v>
@@ -10722,7 +10722,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G357" t="n">
-        <v>3.10191130638123</v>
+        <v>3.10191178321838</v>
       </c>
       <c r="H357" t="n">
         <v>147407</v>
@@ -10838,7 +10838,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G361" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H361" t="n">
         <v>119655</v>
@@ -10867,7 +10867,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G362" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H362" t="n">
         <v>67746</v>
@@ -10896,7 +10896,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G363" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H363" t="n">
         <v>54604</v>
@@ -10925,7 +10925,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G364" t="n">
-        <v>3.11323213577271</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H364" t="n">
         <v>34631</v>
@@ -11099,7 +11099,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G370" t="n">
-        <v>3.10352873802185</v>
+        <v>3.10352897644043</v>
       </c>
       <c r="H370" t="n">
         <v>81503</v>
@@ -11215,7 +11215,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G374" t="n">
-        <v>2.91916060447693</v>
+        <v>2.91916108131409</v>
       </c>
       <c r="H374" t="n">
         <v>188128</v>
@@ -11273,7 +11273,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G376" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H376" t="n">
         <v>38680</v>
@@ -11302,7 +11302,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G377" t="n">
-        <v>2.96929597854614</v>
+        <v>2.96929574012756</v>
       </c>
       <c r="H377" t="n">
         <v>24588</v>
@@ -11331,7 +11331,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G378" t="n">
-        <v>2.96120953559875</v>
+        <v>2.96120977401733</v>
       </c>
       <c r="H378" t="n">
         <v>38971</v>
@@ -11389,7 +11389,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G380" t="n">
-        <v>2.96120953559875</v>
+        <v>2.96120977401733</v>
       </c>
       <c r="H380" t="n">
         <v>35420</v>
@@ -11418,7 +11418,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G381" t="n">
-        <v>2.92724680900574</v>
+        <v>2.92724704742432</v>
       </c>
       <c r="H381" t="n">
         <v>55506</v>
@@ -11476,7 +11476,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G383" t="n">
-        <v>2.87549471855164</v>
+        <v>2.87549495697021</v>
       </c>
       <c r="H383" t="n">
         <v>35865</v>
@@ -11505,7 +11505,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G384" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328479766846</v>
       </c>
       <c r="H384" t="n">
         <v>31658</v>
@@ -11563,7 +11563,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G386" t="n">
-        <v>3.02266597747803</v>
+        <v>3.02266550064087</v>
       </c>
       <c r="H386" t="n">
         <v>111467</v>
@@ -11592,7 +11592,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G387" t="n">
-        <v>3.02104830741882</v>
+        <v>3.0210485458374</v>
       </c>
       <c r="H387" t="n">
         <v>12744</v>
@@ -11621,7 +11621,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G388" t="n">
-        <v>3.04207301139832</v>
+        <v>3.04207324981689</v>
       </c>
       <c r="H388" t="n">
         <v>35930</v>
@@ -11650,7 +11650,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G389" t="n">
-        <v>3.04530715942383</v>
+        <v>3.04530739784241</v>
       </c>
       <c r="H389" t="n">
         <v>32337</v>
@@ -11708,7 +11708,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G391" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H391" t="n">
         <v>49004</v>
@@ -11766,7 +11766,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>3.14557790756226</v>
+        <v>3.14557766914368</v>
       </c>
       <c r="H393" t="n">
         <v>58156</v>
@@ -11824,7 +11824,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G395" t="n">
-        <v>3.16498517990112</v>
+        <v>3.16498494148254</v>
       </c>
       <c r="H395" t="n">
         <v>152673</v>
@@ -11882,7 +11882,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G397" t="n">
-        <v>3.22482347488403</v>
+        <v>3.22482371330261</v>
       </c>
       <c r="H397" t="n">
         <v>116628</v>
@@ -11911,7 +11911,7 @@
         <v>4.00400018692017</v>
       </c>
       <c r="G398" t="n">
-        <v>3.23776173591614</v>
+        <v>3.23776197433472</v>
       </c>
       <c r="H398" t="n">
         <v>119030</v>
@@ -12056,7 +12056,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G403" t="n">
-        <v>3.12617015838623</v>
+        <v>3.12617039680481</v>
       </c>
       <c r="H403" t="n">
         <v>58341</v>
@@ -12085,7 +12085,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>3.11323213577271</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H404" t="n">
         <v>51569</v>
@@ -12114,7 +12114,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>3.19409561157227</v>
+        <v>3.19409537315369</v>
       </c>
       <c r="H405" t="n">
         <v>91838</v>
@@ -12143,7 +12143,7 @@
         <v>3.75</v>
       </c>
       <c r="G406" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H406" t="n">
         <v>155468</v>
@@ -12172,7 +12172,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G407" t="n">
-        <v>3.09220814704895</v>
+        <v>3.09220790863037</v>
       </c>
       <c r="H407" t="n">
         <v>101028</v>
@@ -12201,7 +12201,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G408" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H408" t="n">
         <v>42013</v>
@@ -12259,7 +12259,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G410" t="n">
-        <v>3.0841212272644</v>
+        <v>3.08412146568298</v>
       </c>
       <c r="H410" t="n">
         <v>32920</v>
@@ -12288,7 +12288,7 @@
         <v>3.75</v>
       </c>
       <c r="G411" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H411" t="n">
         <v>55958</v>
@@ -12317,7 +12317,7 @@
         <v>3.75</v>
       </c>
       <c r="G412" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H412" t="n">
         <v>136507</v>
@@ -12375,7 +12375,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H414" t="n">
         <v>65128</v>
@@ -12404,7 +12404,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G415" t="n">
-        <v>3.01943111419678</v>
+        <v>3.0194308757782</v>
       </c>
       <c r="H415" t="n">
         <v>8634</v>
@@ -12433,7 +12433,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G416" t="n">
-        <v>3.11323213577271</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H416" t="n">
         <v>101420</v>
@@ -12491,7 +12491,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G418" t="n">
-        <v>3.05015897750854</v>
+        <v>3.05015921592712</v>
       </c>
       <c r="H418" t="n">
         <v>11880</v>
@@ -12520,7 +12520,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G419" t="n">
-        <v>3.04530715942383</v>
+        <v>3.04530739784241</v>
       </c>
       <c r="H419" t="n">
         <v>10728</v>
@@ -12549,7 +12549,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H420" t="n">
         <v>52757</v>
@@ -12636,7 +12636,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G423" t="n">
-        <v>3.02913451194763</v>
+        <v>3.02913475036621</v>
       </c>
       <c r="H423" t="n">
         <v>46896</v>
@@ -12694,7 +12694,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G425" t="n">
-        <v>3.0259006023407</v>
+        <v>3.02590036392212</v>
       </c>
       <c r="H425" t="n">
         <v>42343</v>
@@ -12752,7 +12752,7 @@
         <v>3.75</v>
       </c>
       <c r="G427" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H427" t="n">
         <v>23627</v>
@@ -12810,7 +12810,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>3.0436897277832</v>
+        <v>3.04368996620178</v>
       </c>
       <c r="H429" t="n">
         <v>15285</v>
@@ -12839,7 +12839,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G430" t="n">
-        <v>3.03883814811707</v>
+        <v>3.03883838653564</v>
       </c>
       <c r="H430" t="n">
         <v>46094</v>
@@ -12955,7 +12955,7 @@
         <v>3.80800008773804</v>
       </c>
       <c r="G434" t="n">
-        <v>3.07927012443542</v>
+        <v>3.079270362854</v>
       </c>
       <c r="H434" t="n">
         <v>22989</v>
@@ -12984,7 +12984,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G435" t="n">
-        <v>3.06309700012207</v>
+        <v>3.06309723854065</v>
       </c>
       <c r="H435" t="n">
         <v>4662</v>
@@ -13042,7 +13042,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G437" t="n">
-        <v>3.07441782951355</v>
+        <v>3.07441806793213</v>
       </c>
       <c r="H437" t="n">
         <v>53196</v>
@@ -13071,7 +13071,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G438" t="n">
-        <v>3.09059047698975</v>
+        <v>3.0905909538269</v>
       </c>
       <c r="H438" t="n">
         <v>71142</v>
@@ -13100,7 +13100,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>3.11323213577271</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H439" t="n">
         <v>36940</v>
@@ -13129,7 +13129,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G440" t="n">
-        <v>3.14557790756226</v>
+        <v>3.14557766914368</v>
       </c>
       <c r="H440" t="n">
         <v>45982</v>
@@ -13158,7 +13158,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G441" t="n">
-        <v>3.10352873802185</v>
+        <v>3.10352897644043</v>
       </c>
       <c r="H441" t="n">
         <v>27948</v>
@@ -13216,7 +13216,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G443" t="n">
-        <v>3.11646676063538</v>
+        <v>3.11646699905396</v>
       </c>
       <c r="H443" t="n">
         <v>51853</v>
@@ -13245,7 +13245,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H444" t="n">
         <v>73276</v>
@@ -13303,7 +13303,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G446" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H446" t="n">
         <v>30672</v>
@@ -13332,7 +13332,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H447" t="n">
         <v>38185</v>
@@ -13361,7 +13361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G448" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H448" t="n">
         <v>7499</v>
@@ -13390,7 +13390,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H449" t="n">
         <v>21094</v>
@@ -13419,7 +13419,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G450" t="n">
-        <v>3.03560376167297</v>
+        <v>3.03560352325439</v>
       </c>
       <c r="H450" t="n">
         <v>23747</v>
@@ -13477,7 +13477,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G452" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662775039673</v>
       </c>
       <c r="H452" t="n">
         <v>18836</v>
@@ -13564,7 +13564,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G455" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662775039673</v>
       </c>
       <c r="H455" t="n">
         <v>20763</v>
@@ -13593,7 +13593,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G456" t="n">
-        <v>3.01943111419678</v>
+        <v>3.0194308757782</v>
       </c>
       <c r="H456" t="n">
         <v>33701</v>
@@ -13738,7 +13738,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G461" t="n">
-        <v>3.02428317070007</v>
+        <v>3.02428269386292</v>
       </c>
       <c r="H461" t="n">
         <v>43036</v>
@@ -13767,7 +13767,7 @@
         <v>3.75</v>
       </c>
       <c r="G462" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H462" t="n">
         <v>26960</v>
@@ -13796,7 +13796,7 @@
         <v>3.75</v>
       </c>
       <c r="G463" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H463" t="n">
         <v>36742</v>
@@ -13941,7 +13941,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G468" t="n">
-        <v>2.82050800323486</v>
+        <v>2.82050752639771</v>
       </c>
       <c r="H468" t="n">
         <v>38921</v>
@@ -13970,7 +13970,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G469" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H469" t="n">
         <v>29990</v>
@@ -13999,7 +13999,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H470" t="n">
         <v>14253</v>
@@ -14028,7 +14028,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G471" t="n">
-        <v>2.84961819648743</v>
+        <v>2.84961867332458</v>
       </c>
       <c r="H471" t="n">
         <v>23748</v>
@@ -14057,7 +14057,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G472" t="n">
-        <v>2.89328455924988</v>
+        <v>2.89328479766846</v>
       </c>
       <c r="H472" t="n">
         <v>73459</v>
@@ -14086,7 +14086,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G473" t="n">
-        <v>2.88358092308044</v>
+        <v>2.88358116149902</v>
       </c>
       <c r="H473" t="n">
         <v>34493</v>
@@ -14144,7 +14144,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G475" t="n">
-        <v>2.90298843383789</v>
+        <v>2.90298795700073</v>
       </c>
       <c r="H475" t="n">
         <v>8119</v>
@@ -14202,7 +14202,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G477" t="n">
-        <v>2.78007626533508</v>
+        <v>2.7800760269165</v>
       </c>
       <c r="H477" t="n">
         <v>64051</v>
@@ -14289,7 +14289,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G480" t="n">
-        <v>2.81889033317566</v>
+        <v>2.81889057159424</v>
       </c>
       <c r="H480" t="n">
         <v>79093</v>
@@ -14347,7 +14347,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.74934840202332</v>
+        <v>2.74934816360474</v>
       </c>
       <c r="H482" t="n">
         <v>54279</v>
@@ -14376,7 +14376,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.73317575454712</v>
+        <v>2.73317551612854</v>
       </c>
       <c r="H483" t="n">
         <v>13209</v>
@@ -14550,7 +14550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.91107416152954</v>
+        <v>2.91107439994812</v>
       </c>
       <c r="H489" t="n">
         <v>28572</v>
@@ -14608,7 +14608,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G491" t="n">
-        <v>2.90783953666687</v>
+        <v>2.90784001350403</v>
       </c>
       <c r="H491" t="n">
         <v>93467</v>
@@ -14637,7 +14637,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G492" t="n">
-        <v>2.91107416152954</v>
+        <v>2.91107439994812</v>
       </c>
       <c r="H492" t="n">
         <v>17258</v>
@@ -14695,7 +14695,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99032044410706</v>
+        <v>2.99032020568848</v>
       </c>
       <c r="H494" t="n">
         <v>72971</v>
@@ -14724,7 +14724,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G495" t="n">
-        <v>2.97576522827148</v>
+        <v>2.97576546669006</v>
       </c>
       <c r="H495" t="n">
         <v>23653</v>
@@ -14840,7 +14840,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H499" t="n">
         <v>19062</v>
@@ -14927,7 +14927,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.99840688705444</v>
+        <v>2.99840664863586</v>
       </c>
       <c r="H502" t="n">
         <v>19534</v>
@@ -15014,7 +15014,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G505" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H505" t="n">
         <v>20791</v>
@@ -15159,7 +15159,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H510" t="n">
         <v>18206</v>
@@ -15188,7 +15188,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G511" t="n">
-        <v>2.97576522827148</v>
+        <v>2.97576546669006</v>
       </c>
       <c r="H511" t="n">
         <v>20741</v>
@@ -15246,7 +15246,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G513" t="n">
-        <v>3.02428317070007</v>
+        <v>3.02428269386292</v>
       </c>
       <c r="H513" t="n">
         <v>32857</v>
@@ -15275,7 +15275,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G514" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H514" t="n">
         <v>21697</v>
@@ -15333,7 +15333,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>3.00406670570374</v>
+        <v>3.00406694412231</v>
       </c>
       <c r="H516" t="n">
         <v>21937</v>
@@ -15362,7 +15362,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G517" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H517" t="n">
         <v>30008</v>
@@ -15391,7 +15391,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G518" t="n">
-        <v>3.05662822723389</v>
+        <v>3.05662775039673</v>
       </c>
       <c r="H518" t="n">
         <v>34740</v>
@@ -15420,7 +15420,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G519" t="n">
-        <v>3.08897352218628</v>
+        <v>3.0889732837677</v>
       </c>
       <c r="H519" t="n">
         <v>42643</v>
@@ -15449,7 +15449,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G520" t="n">
-        <v>3.08897352218628</v>
+        <v>3.0889732837677</v>
       </c>
       <c r="H520" t="n">
         <v>95749</v>
@@ -15507,7 +15507,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G522" t="n">
-        <v>3.14962077140808</v>
+        <v>3.14962029457092</v>
       </c>
       <c r="H522" t="n">
         <v>45939</v>
@@ -15536,7 +15536,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G523" t="n">
-        <v>3.09705996513367</v>
+        <v>3.09705948829651</v>
       </c>
       <c r="H523" t="n">
         <v>65958</v>
@@ -15565,7 +15565,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>3.11323213577271</v>
+        <v>3.11323237419128</v>
       </c>
       <c r="H524" t="n">
         <v>23639</v>
@@ -15594,7 +15594,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G525" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H525" t="n">
         <v>23093</v>
@@ -15623,7 +15623,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G526" t="n">
-        <v>3.10918927192688</v>
+        <v>3.10918951034546</v>
       </c>
       <c r="H526" t="n">
         <v>22353</v>
@@ -15652,7 +15652,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G527" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H527" t="n">
         <v>17842</v>
@@ -15681,7 +15681,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G528" t="n">
-        <v>3.12536191940308</v>
+        <v>3.1253616809845</v>
       </c>
       <c r="H528" t="n">
         <v>6994</v>
@@ -15710,7 +15710,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>3.12131881713867</v>
+        <v>3.12131857872009</v>
       </c>
       <c r="H529" t="n">
         <v>31820</v>
@@ -15739,7 +15739,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>3.18600940704346</v>
+        <v>3.1860089302063</v>
       </c>
       <c r="H530" t="n">
         <v>29603</v>
@@ -15797,7 +15797,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>3.00002431869507</v>
+        <v>3.00002384185791</v>
       </c>
       <c r="H532" t="n">
         <v>35802</v>
@@ -15826,7 +15826,7 @@
         <v>3.75</v>
       </c>
       <c r="G533" t="n">
-        <v>3.03236889839172</v>
+        <v>3.0323691368103</v>
       </c>
       <c r="H533" t="n">
         <v>19859</v>
@@ -15884,7 +15884,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G535" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H535" t="n">
         <v>16675</v>
@@ -15942,7 +15942,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894533157349</v>
       </c>
       <c r="H537" t="n">
         <v>43032</v>
@@ -16000,7 +16000,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G539" t="n">
-        <v>2.89894509315491</v>
+        <v>2.89894533157349</v>
       </c>
       <c r="H539" t="n">
         <v>13819</v>
@@ -16029,7 +16029,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.86255669593811</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H540" t="n">
         <v>15401</v>
@@ -16058,7 +16058,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H541" t="n">
         <v>15012</v>
@@ -16087,7 +16087,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>2.81403851509094</v>
+        <v>2.81403875350952</v>
       </c>
       <c r="H542" t="n">
         <v>15169</v>
@@ -16116,7 +16116,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.86255669593811</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H543" t="n">
         <v>7373</v>
@@ -16232,7 +16232,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G547" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H547" t="n">
         <v>29420</v>
@@ -16261,7 +16261,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H548" t="n">
         <v>19728</v>
@@ -16290,7 +16290,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G549" t="n">
-        <v>3.0121533870697</v>
+        <v>3.01215362548828</v>
       </c>
       <c r="H549" t="n">
         <v>22631</v>
@@ -16319,7 +16319,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>3.0121533870697</v>
+        <v>3.01215362548828</v>
       </c>
       <c r="H550" t="n">
         <v>8795</v>
@@ -16464,7 +16464,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.85851311683655</v>
+        <v>2.85851359367371</v>
       </c>
       <c r="H555" t="n">
         <v>15320</v>
@@ -16493,7 +16493,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>2.86255669593811</v>
+        <v>2.86255645751953</v>
       </c>
       <c r="H556" t="n">
         <v>683</v>
@@ -16522,7 +16522,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.84638381004333</v>
+        <v>2.84638404846191</v>
       </c>
       <c r="H557" t="n">
         <v>36584</v>
@@ -16551,7 +16551,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>2.91107416152954</v>
+        <v>2.91107439994812</v>
       </c>
       <c r="H558" t="n">
         <v>15867</v>
@@ -16580,7 +16580,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.97576522827148</v>
+        <v>2.97576546669006</v>
       </c>
       <c r="H559" t="n">
         <v>10615</v>
@@ -16609,7 +16609,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G560" t="n">
-        <v>3.02023959159851</v>
+        <v>3.02023983001709</v>
       </c>
       <c r="H560" t="n">
         <v>22138</v>
@@ -16696,7 +16696,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G563" t="n">
-        <v>2.91107416152954</v>
+        <v>2.91107439994812</v>
       </c>
       <c r="H563" t="n">
         <v>19539</v>
@@ -16783,7 +16783,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G566" t="n">
-        <v>3.00406670570374</v>
+        <v>3.00406694412231</v>
       </c>
       <c r="H566" t="n">
         <v>26784</v>
@@ -16812,7 +16812,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G567" t="n">
-        <v>2.96363544464111</v>
+        <v>2.96363520622253</v>
       </c>
       <c r="H567" t="n">
         <v>14348</v>
@@ -16870,7 +16870,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G569" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H569" t="n">
         <v>20729</v>
@@ -16928,7 +16928,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>2.97980856895447</v>
+        <v>2.97980833053589</v>
       </c>
       <c r="H571" t="n">
         <v>12871</v>
@@ -17131,7 +17131,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G578" t="n">
-        <v>3.02023959159851</v>
+        <v>3.02023983001709</v>
       </c>
       <c r="H578" t="n">
         <v>35878</v>
@@ -17218,7 +17218,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.9919376373291</v>
+        <v>2.99193787574768</v>
       </c>
       <c r="H581" t="n">
         <v>51320</v>
@@ -17247,7 +17247,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H582" t="n">
         <v>14099</v>
@@ -17334,7 +17334,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H585" t="n">
         <v>48226</v>
@@ -17421,7 +17421,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G588" t="n">
-        <v>3.04045534133911</v>
+        <v>3.04045557975769</v>
       </c>
       <c r="H588" t="n">
         <v>28278</v>
@@ -17508,7 +17508,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G591" t="n">
-        <v>3.1051459312439</v>
+        <v>3.10514616966248</v>
       </c>
       <c r="H591" t="n">
         <v>22626</v>
@@ -17595,7 +17595,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>3.12536191940308</v>
+        <v>3.1253616809845</v>
       </c>
       <c r="H594" t="n">
         <v>4292</v>
@@ -17682,7 +17682,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G597" t="n">
-        <v>3.19409561157227</v>
+        <v>3.19409537315369</v>
       </c>
       <c r="H597" t="n">
         <v>252878</v>
@@ -17769,7 +17769,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G600" t="n">
-        <v>3.18196606636047</v>
+        <v>3.18196630477905</v>
       </c>
       <c r="H600" t="n">
         <v>36836</v>
@@ -17798,7 +17798,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G601" t="n">
-        <v>3.20622491836548</v>
+        <v>3.20622515678406</v>
       </c>
       <c r="H601" t="n">
         <v>22587</v>
@@ -17885,7 +17885,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G604" t="n">
-        <v>3.17792296409607</v>
+        <v>3.17792320251465</v>
       </c>
       <c r="H604" t="n">
         <v>36810</v>
@@ -17914,7 +17914,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>3.11727547645569</v>
+        <v>3.11727571487427</v>
       </c>
       <c r="H605" t="n">
         <v>16652</v>
@@ -17943,7 +17943,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G606" t="n">
-        <v>3.17792296409607</v>
+        <v>3.17792320251465</v>
       </c>
       <c r="H606" t="n">
         <v>55869</v>
@@ -17972,7 +17972,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G607" t="n">
-        <v>3.10918927192688</v>
+        <v>3.10918951034546</v>
       </c>
       <c r="H607" t="n">
         <v>19269</v>
@@ -18001,7 +18001,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G608" t="n">
-        <v>3.17490530014038</v>
+        <v>3.1749050617218</v>
       </c>
       <c r="H608" t="n">
         <v>10245</v>
@@ -18088,7 +18088,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G611" t="n">
-        <v>3.12151074409485</v>
+        <v>3.12151098251343</v>
       </c>
       <c r="H611" t="n">
         <v>26208</v>
@@ -18117,7 +18117,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G612" t="n">
-        <v>3.15436887741089</v>
+        <v>3.15436911582947</v>
       </c>
       <c r="H612" t="n">
         <v>23103</v>
@@ -18175,7 +18175,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G614" t="n">
-        <v>3.02293682098389</v>
+        <v>3.02293729782104</v>
       </c>
       <c r="H614" t="n">
         <v>74809</v>
@@ -18204,7 +18204,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G615" t="n">
-        <v>3.05579519271851</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H615" t="n">
         <v>8889</v>
@@ -18233,7 +18233,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>3.07633137702942</v>
+        <v>3.07633066177368</v>
       </c>
       <c r="H616" t="n">
         <v>11007</v>
@@ -18262,7 +18262,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G617" t="n">
-        <v>3.13793992996216</v>
+        <v>3.13793969154358</v>
       </c>
       <c r="H617" t="n">
         <v>25576</v>
@@ -18320,7 +18320,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G619" t="n">
-        <v>3.17901253700256</v>
+        <v>3.17901206016541</v>
       </c>
       <c r="H619" t="n">
         <v>18705</v>
@@ -18349,7 +18349,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G620" t="n">
-        <v>3.0393660068512</v>
+        <v>3.03936624526978</v>
       </c>
       <c r="H620" t="n">
         <v>108303</v>
@@ -18378,7 +18378,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G621" t="n">
-        <v>3.05579519271851</v>
+        <v>3.05579495429993</v>
       </c>
       <c r="H621" t="n">
         <v>34890</v>
@@ -18407,7 +18407,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G622" t="n">
-        <v>3.00650787353516</v>
+        <v>3.00650811195374</v>
       </c>
       <c r="H622" t="n">
         <v>72011</v>
@@ -18436,7 +18436,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>3.11740350723267</v>
+        <v>3.11740374565125</v>
       </c>
       <c r="H623" t="n">
         <v>39985</v>
@@ -18465,7 +18465,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>3.11740350723267</v>
+        <v>3.11740374565125</v>
       </c>
       <c r="H624" t="n">
         <v>56705</v>
@@ -18581,7 +18581,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H628" t="n">
         <v>42645</v>
@@ -18610,7 +18610,7 @@
         <v>3.75</v>
       </c>
       <c r="G629" t="n">
-        <v>3.08043813705444</v>
+        <v>3.08043837547302</v>
       </c>
       <c r="H629" t="n">
         <v>20075</v>
@@ -18639,7 +18639,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H630" t="n">
         <v>7374</v>
@@ -18668,7 +18668,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G631" t="n">
-        <v>3.07222414016724</v>
+        <v>3.07222390174866</v>
       </c>
       <c r="H631" t="n">
         <v>12824</v>
@@ -18726,7 +18726,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G633" t="n">
-        <v>3.1050820350647</v>
+        <v>3.10508155822754</v>
       </c>
       <c r="H633" t="n">
         <v>62139</v>
@@ -18784,7 +18784,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G635" t="n">
-        <v>3.0188295841217</v>
+        <v>3.01882982254028</v>
       </c>
       <c r="H635" t="n">
         <v>12728</v>
@@ -18813,7 +18813,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G636" t="n">
-        <v>3.06811666488647</v>
+        <v>3.06811690330505</v>
       </c>
       <c r="H636" t="n">
         <v>9875</v>
@@ -18842,7 +18842,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G637" t="n">
-        <v>3.10097503662109</v>
+        <v>3.10097455978394</v>
       </c>
       <c r="H637" t="n">
         <v>55066</v>
@@ -18871,7 +18871,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>3.0434730052948</v>
+        <v>3.04347324371338</v>
       </c>
       <c r="H638" t="n">
         <v>11711</v>
@@ -18900,7 +18900,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G639" t="n">
-        <v>3.09276056289673</v>
+        <v>3.09276032447815</v>
       </c>
       <c r="H639" t="n">
         <v>8567</v>
@@ -18929,7 +18929,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G640" t="n">
-        <v>3.12561845779419</v>
+        <v>3.12561821937561</v>
       </c>
       <c r="H640" t="n">
         <v>13830</v>
@@ -18958,7 +18958,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G641" t="n">
-        <v>3.12561845779419</v>
+        <v>3.12561821937561</v>
       </c>
       <c r="H641" t="n">
         <v>18851</v>
@@ -18987,7 +18987,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G642" t="n">
-        <v>3.12561845779419</v>
+        <v>3.12561821937561</v>
       </c>
       <c r="H642" t="n">
         <v>1266</v>
@@ -19016,7 +19016,7 @@
         <v>3.75</v>
       </c>
       <c r="G643" t="n">
-        <v>3.08043813705444</v>
+        <v>3.08043837547302</v>
       </c>
       <c r="H643" t="n">
         <v>9594</v>
@@ -19045,7 +19045,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G644" t="n">
-        <v>3.12151074409485</v>
+        <v>3.12151098251343</v>
       </c>
       <c r="H644" t="n">
         <v>22875</v>
@@ -19161,7 +19161,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G648" t="n">
-        <v>3.12561845779419</v>
+        <v>3.12561821937561</v>
       </c>
       <c r="H648" t="n">
         <v>8213</v>
@@ -19190,7 +19190,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G649" t="n">
-        <v>3.15436887741089</v>
+        <v>3.15436911582947</v>
       </c>
       <c r="H649" t="n">
         <v>17423</v>
@@ -19248,7 +19248,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G651" t="n">
-        <v>3.19544172286987</v>
+        <v>3.19544148445129</v>
       </c>
       <c r="H651" t="n">
         <v>16643</v>
@@ -19364,7 +19364,7 @@
         <v>4</v>
       </c>
       <c r="G655" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H655" t="n">
         <v>730994</v>
@@ -19393,7 +19393,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>3.35151672363281</v>
+        <v>3.35151696205139</v>
       </c>
       <c r="H656" t="n">
         <v>87001</v>
@@ -19451,7 +19451,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>3.35151672363281</v>
+        <v>3.35151696205139</v>
       </c>
       <c r="H658" t="n">
         <v>95736</v>
@@ -19480,7 +19480,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>3.35973215103149</v>
+        <v>3.35973167419434</v>
       </c>
       <c r="H659" t="n">
         <v>76457</v>
@@ -19509,7 +19509,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G660" t="n">
-        <v>3.46652030944824</v>
+        <v>3.46652007102966</v>
       </c>
       <c r="H660" t="n">
         <v>178638</v>
@@ -19538,7 +19538,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G661" t="n">
-        <v>3.37616086006165</v>
+        <v>3.37616038322449</v>
       </c>
       <c r="H661" t="n">
         <v>771474</v>
@@ -19596,7 +19596,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G663" t="n">
-        <v>3.44187688827515</v>
+        <v>3.44187664985657</v>
       </c>
       <c r="H663" t="n">
         <v>198699</v>
@@ -19625,7 +19625,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G664" t="n">
-        <v>3.44187688827515</v>
+        <v>3.44187664985657</v>
       </c>
       <c r="H664" t="n">
         <v>37222</v>
@@ -19654,7 +19654,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G665" t="n">
-        <v>3.40080380439758</v>
+        <v>3.40080404281616</v>
       </c>
       <c r="H665" t="n">
         <v>30309</v>
@@ -19683,7 +19683,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G666" t="n">
-        <v>3.38437485694885</v>
+        <v>3.38437509536743</v>
       </c>
       <c r="H666" t="n">
         <v>18534</v>
@@ -19712,7 +19712,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>3.31455183029175</v>
+        <v>3.31455159187317</v>
       </c>
       <c r="H667" t="n">
         <v>39198</v>
@@ -19741,7 +19741,7 @@
         <v>4</v>
       </c>
       <c r="G668" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H668" t="n">
         <v>25975</v>
@@ -19770,7 +19770,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>3.30633735656738</v>
+        <v>3.30633759498596</v>
       </c>
       <c r="H669" t="n">
         <v>28585</v>
@@ -19828,7 +19828,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G671" t="n">
-        <v>3.35973215103149</v>
+        <v>3.35973167419434</v>
       </c>
       <c r="H671" t="n">
         <v>31771</v>
@@ -19915,7 +19915,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>3.24883556365967</v>
+        <v>3.24883532524109</v>
       </c>
       <c r="H674" t="n">
         <v>28539</v>
@@ -19973,7 +19973,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G676" t="n">
-        <v>3.26937174797058</v>
+        <v>3.26937198638916</v>
       </c>
       <c r="H676" t="n">
         <v>11711</v>
@@ -20031,7 +20031,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>3.24883556365967</v>
+        <v>3.24883532524109</v>
       </c>
       <c r="H678" t="n">
         <v>14565</v>
@@ -20118,7 +20118,7 @@
         <v>4</v>
       </c>
       <c r="G681" t="n">
-        <v>3.28580093383789</v>
+        <v>3.28580117225647</v>
       </c>
       <c r="H681" t="n">
         <v>75753</v>
@@ -20147,7 +20147,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G682" t="n">
-        <v>3.32687401771545</v>
+        <v>3.32687377929688</v>
       </c>
       <c r="H682" t="n">
         <v>18076</v>
@@ -20176,7 +20176,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G683" t="n">
-        <v>3.49937844276428</v>
+        <v>3.4993782043457</v>
       </c>
       <c r="H683" t="n">
         <v>123793</v>
@@ -20205,7 +20205,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.51170015335083</v>
+        <v>3.51169943809509</v>
       </c>
       <c r="H684" t="n">
         <v>122153</v>
@@ -20234,7 +20234,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>3.47473454475403</v>
+        <v>3.47473430633545</v>
       </c>
       <c r="H685" t="n">
         <v>79386</v>
@@ -20263,7 +20263,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G686" t="n">
-        <v>3.50348496437073</v>
+        <v>3.50348520278931</v>
       </c>
       <c r="H686" t="n">
         <v>53010</v>
@@ -20292,7 +20292,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>3.50759267807007</v>
+        <v>3.50759243965149</v>
       </c>
       <c r="H687" t="n">
         <v>48640</v>
@@ -20321,7 +20321,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G688" t="n">
-        <v>3.58563017845154</v>
+        <v>3.58563041687012</v>
       </c>
       <c r="H688" t="n">
         <v>104807</v>
@@ -20379,7 +20379,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="n">
-        <v>3.49116349220276</v>
+        <v>3.49116373062134</v>
       </c>
       <c r="H690" t="n">
         <v>24637</v>
@@ -20408,7 +20408,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G691" t="n">
-        <v>3.54455828666687</v>
+        <v>3.54455804824829</v>
       </c>
       <c r="H691" t="n">
         <v>144454</v>
@@ -20437,7 +20437,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>3.70063376426697</v>
+        <v>3.70063328742981</v>
       </c>
       <c r="H692" t="n">
         <v>240141</v>
@@ -20466,7 +20466,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>3.80331492424011</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H693" t="n">
         <v>166131</v>
@@ -20495,7 +20495,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H694" t="n">
         <v>169087</v>
@@ -20524,7 +20524,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G695" t="n">
-        <v>3.68420433998108</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H695" t="n">
         <v>99219</v>
@@ -20582,7 +20582,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.71706175804138</v>
+        <v>3.71706295013428</v>
       </c>
       <c r="H697" t="n">
         <v>63187</v>
@@ -20611,7 +20611,7 @@
         <v>4.50500011444092</v>
       </c>
       <c r="G698" t="n">
-        <v>3.70063376426697</v>
+        <v>3.70063328742981</v>
       </c>
       <c r="H698" t="n">
         <v>38470</v>
@@ -20669,7 +20669,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G700" t="n">
-        <v>3.72116994857788</v>
+        <v>3.72117042541504</v>
       </c>
       <c r="H700" t="n">
         <v>52446</v>
@@ -20727,7 +20727,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G702" t="n">
-        <v>3.83617258071899</v>
+        <v>3.83617305755615</v>
       </c>
       <c r="H702" t="n">
         <v>109153</v>
@@ -20756,7 +20756,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G703" t="n">
-        <v>3.82795858383179</v>
+        <v>3.82795810699463</v>
       </c>
       <c r="H703" t="n">
         <v>54742</v>
@@ -20785,7 +20785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>3.86081600189209</v>
+        <v>3.86081647872925</v>
       </c>
       <c r="H704" t="n">
         <v>73408</v>
@@ -20814,7 +20814,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G705" t="n">
-        <v>3.97992658615112</v>
+        <v>3.97992563247681</v>
       </c>
       <c r="H705" t="n">
         <v>192175</v>
@@ -20872,7 +20872,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G707" t="n">
-        <v>3.8443865776062</v>
+        <v>3.84438705444336</v>
       </c>
       <c r="H707" t="n">
         <v>138036</v>
@@ -20901,7 +20901,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>3.80331492424011</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H708" t="n">
         <v>105500</v>
@@ -20930,7 +20930,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>3.78688549995422</v>
+        <v>3.78688597679138</v>
       </c>
       <c r="H709" t="n">
         <v>40785</v>
@@ -20959,7 +20959,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759937286377</v>
       </c>
       <c r="H710" t="n">
         <v>53135</v>
@@ -20988,7 +20988,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G711" t="n">
-        <v>3.7786705493927</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H711" t="n">
         <v>108765</v>
@@ -21017,7 +21017,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G712" t="n">
-        <v>3.71295499801636</v>
+        <v>3.71295571327209</v>
       </c>
       <c r="H712" t="n">
         <v>30961</v>
@@ -21075,7 +21075,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79510045051575</v>
+        <v>3.79509997367859</v>
       </c>
       <c r="H714" t="n">
         <v>15542</v>
@@ -21133,7 +21133,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>3.6554536819458</v>
+        <v>3.65545344352722</v>
       </c>
       <c r="H716" t="n">
         <v>26171</v>
@@ -21162,7 +21162,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>3.7786705493927</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H717" t="n">
         <v>37906</v>
@@ -21191,7 +21191,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224279403687</v>
       </c>
       <c r="H718" t="n">
         <v>69227</v>
@@ -21220,7 +21220,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G719" t="n">
-        <v>3.72116994857788</v>
+        <v>3.72117042541504</v>
       </c>
       <c r="H719" t="n">
         <v>48205</v>
@@ -21249,7 +21249,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G720" t="n">
-        <v>3.68420433998108</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H720" t="n">
         <v>34708</v>
@@ -21278,7 +21278,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H721" t="n">
         <v>50647</v>
@@ -21307,7 +21307,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G722" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759937286377</v>
       </c>
       <c r="H722" t="n">
         <v>55674</v>
@@ -21423,7 +21423,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>3.91831803321838</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H726" t="n">
         <v>134986</v>
@@ -21452,7 +21452,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>3.91831803321838</v>
+        <v>3.91831755638123</v>
       </c>
       <c r="H727" t="n">
         <v>82607</v>
@@ -21539,7 +21539,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>3.83617258071899</v>
+        <v>3.83617305755615</v>
       </c>
       <c r="H730" t="n">
         <v>32787</v>
@@ -21568,7 +21568,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G731" t="n">
-        <v>3.77045655250549</v>
+        <v>3.77045702934265</v>
       </c>
       <c r="H731" t="n">
         <v>18187</v>
@@ -21597,7 +21597,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224279403687</v>
       </c>
       <c r="H732" t="n">
         <v>33541</v>
@@ -21626,7 +21626,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>3.76224231719971</v>
+        <v>3.76224279403687</v>
       </c>
       <c r="H733" t="n">
         <v>41957</v>
@@ -21655,7 +21655,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>3.68420433998108</v>
+        <v>3.68420481681824</v>
       </c>
       <c r="H734" t="n">
         <v>31529</v>
@@ -21684,7 +21684,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G735" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H735" t="n">
         <v>140609</v>
@@ -21713,7 +21713,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>3.58973813056946</v>
+        <v>3.58973789215088</v>
       </c>
       <c r="H736" t="n">
         <v>43867</v>
@@ -21742,7 +21742,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G737" t="n">
-        <v>3.59795260429382</v>
+        <v>3.59795212745667</v>
       </c>
       <c r="H737" t="n">
         <v>45226</v>
@@ -21800,7 +21800,7 @@
         <v>4.25</v>
       </c>
       <c r="G739" t="n">
-        <v>3.49116349220276</v>
+        <v>3.49116373062134</v>
       </c>
       <c r="H739" t="n">
         <v>76142</v>
@@ -21916,7 +21916,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>3.62670302391052</v>
+        <v>3.6267032623291</v>
       </c>
       <c r="H743" t="n">
         <v>33077</v>
@@ -21945,7 +21945,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G744" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H744" t="n">
         <v>69787</v>
@@ -21974,7 +21974,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G745" t="n">
-        <v>3.56509470939636</v>
+        <v>3.5650942325592</v>
       </c>
       <c r="H745" t="n">
         <v>26747</v>
@@ -22003,7 +22003,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G746" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H746" t="n">
         <v>38382</v>
@@ -22032,7 +22032,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G747" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759937286377</v>
       </c>
       <c r="H747" t="n">
         <v>117156</v>
@@ -22061,7 +22061,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G748" t="n">
-        <v>3.7786705493927</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H748" t="n">
         <v>166234</v>
@@ -22090,7 +22090,7 @@
         <v>4.5</v>
       </c>
       <c r="G749" t="n">
-        <v>3.69652581214905</v>
+        <v>3.69652605056763</v>
       </c>
       <c r="H749" t="n">
         <v>52912</v>
@@ -22119,7 +22119,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G750" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902473449707</v>
       </c>
       <c r="H750" t="n">
         <v>155173</v>
@@ -22148,7 +22148,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G751" t="n">
-        <v>3.62670302391052</v>
+        <v>3.6267032623291</v>
       </c>
       <c r="H751" t="n">
         <v>10478</v>
@@ -22177,7 +22177,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G752" t="n">
-        <v>3.56920146942139</v>
+        <v>3.56920170783997</v>
       </c>
       <c r="H752" t="n">
         <v>67819</v>
@@ -22206,7 +22206,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G753" t="n">
-        <v>3.64313149452209</v>
+        <v>3.64313197135925</v>
       </c>
       <c r="H753" t="n">
         <v>47802</v>
@@ -22235,7 +22235,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902473449707</v>
       </c>
       <c r="H754" t="n">
         <v>101246</v>
@@ -22264,7 +22264,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G755" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902473449707</v>
       </c>
       <c r="H755" t="n">
         <v>21557</v>
@@ -22293,7 +22293,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G756" t="n">
-        <v>3.62259578704834</v>
+        <v>3.62259602546692</v>
       </c>
       <c r="H756" t="n">
         <v>15999</v>
@@ -22322,7 +22322,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G757" t="n">
-        <v>3.60205984115601</v>
+        <v>3.60205936431885</v>
       </c>
       <c r="H757" t="n">
         <v>20408</v>
@@ -22351,7 +22351,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H758" t="n">
         <v>12169</v>
@@ -22380,7 +22380,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G759" t="n">
-        <v>3.6554536819458</v>
+        <v>3.65545344352722</v>
       </c>
       <c r="H759" t="n">
         <v>30287</v>
@@ -22409,7 +22409,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G760" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H760" t="n">
         <v>42084</v>
@@ -22438,7 +22438,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G761" t="n">
-        <v>3.59795260429382</v>
+        <v>3.59795212745667</v>
       </c>
       <c r="H761" t="n">
         <v>69033</v>
@@ -22467,7 +22467,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G762" t="n">
-        <v>3.6143810749054</v>
+        <v>3.61438131332397</v>
       </c>
       <c r="H762" t="n">
         <v>26366</v>
@@ -22496,7 +22496,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G763" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902473449707</v>
       </c>
       <c r="H763" t="n">
         <v>36511</v>
@@ -22525,7 +22525,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G764" t="n">
-        <v>3.73759889602661</v>
+        <v>3.73759937286377</v>
       </c>
       <c r="H764" t="n">
         <v>23380</v>
@@ -22583,7 +22583,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G766" t="n">
-        <v>3.70474100112915</v>
+        <v>3.70474052429199</v>
       </c>
       <c r="H766" t="n">
         <v>203274</v>
@@ -22612,7 +22612,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G767" t="n">
-        <v>3.61848831176758</v>
+        <v>3.61848902702332</v>
       </c>
       <c r="H767" t="n">
         <v>70522</v>
@@ -22641,7 +22641,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G768" t="n">
-        <v>3.6554536819458</v>
+        <v>3.65545344352722</v>
       </c>
       <c r="H768" t="n">
         <v>32231</v>
@@ -22670,7 +22670,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>3.6554536819458</v>
+        <v>3.65545344352722</v>
       </c>
       <c r="H769" t="n">
         <v>21973</v>
@@ -22699,7 +22699,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G770" t="n">
-        <v>3.65134620666504</v>
+        <v>3.65134644508362</v>
       </c>
       <c r="H770" t="n">
         <v>64992</v>
@@ -22728,7 +22728,7 @@
         <v>4.46500015258789</v>
       </c>
       <c r="G771" t="n">
-        <v>3.66777563095093</v>
+        <v>3.66777586936951</v>
       </c>
       <c r="H771" t="n">
         <v>29437</v>
@@ -22757,7 +22757,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G772" t="n">
-        <v>3.63902449607849</v>
+        <v>3.63902473449707</v>
       </c>
       <c r="H772" t="n">
         <v>27013</v>
@@ -22844,7 +22844,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G775" t="n">
-        <v>3.58152294158936</v>
+        <v>3.58152318000793</v>
       </c>
       <c r="H775" t="n">
         <v>34176</v>
@@ -22873,7 +22873,7 @@
         <v>4.5</v>
       </c>
       <c r="G776" t="n">
-        <v>3.69652581214905</v>
+        <v>3.69652605056763</v>
       </c>
       <c r="H776" t="n">
         <v>190049</v>
@@ -22902,7 +22902,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G777" t="n">
-        <v>3.80331492424011</v>
+        <v>3.80331444740295</v>
       </c>
       <c r="H777" t="n">
         <v>32135</v>
@@ -22989,7 +22989,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G780" t="n">
-        <v>3.81152963638306</v>
+        <v>3.81153011322021</v>
       </c>
       <c r="H780" t="n">
         <v>11208</v>
@@ -23018,7 +23018,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G781" t="n">
-        <v>3.7786705493927</v>
+        <v>3.77867102622986</v>
       </c>
       <c r="H781" t="n">
         <v>27055</v>
@@ -23221,7 +23221,7 @@
         <v>5</v>
       </c>
       <c r="G788" t="n">
-        <v>4.10725164413452</v>
+        <v>4.10725116729736</v>
       </c>
       <c r="H788" t="n">
         <v>112810</v>
@@ -23337,7 +23337,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G792" t="n">
-        <v>4.01278448104858</v>
+        <v>4.01278495788574</v>
       </c>
       <c r="H792" t="n">
         <v>21474</v>
@@ -23540,7 +23540,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G799" t="n">
-        <v>4.01278448104858</v>
+        <v>4.01278495788574</v>
       </c>
       <c r="H799" t="n">
         <v>32863</v>
@@ -23569,7 +23569,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G800" t="n">
-        <v>4.05796384811401</v>
+        <v>4.05796480178833</v>
       </c>
       <c r="H800" t="n">
         <v>40001</v>
@@ -23598,7 +23598,7 @@
         <v>4.875</v>
       </c>
       <c r="G801" t="n">
-        <v>4.00457048416138</v>
+        <v>4.00457000732422</v>
       </c>
       <c r="H801" t="n">
         <v>32198</v>
@@ -23685,7 +23685,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G804" t="n">
-        <v>3.97581958770752</v>
+        <v>3.97581911087036</v>
       </c>
       <c r="H804" t="n">
         <v>38310</v>
@@ -23743,7 +23743,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>4.1729679107666</v>
+        <v>4.17296743392944</v>
       </c>
       <c r="H806" t="n">
         <v>68680</v>
@@ -23772,7 +23772,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G807" t="n">
-        <v>4.30439901351929</v>
+        <v>4.30439949035645</v>
       </c>
       <c r="H807" t="n">
         <v>103293</v>
@@ -23830,7 +23830,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G809" t="n">
-        <v>4.40297365188599</v>
+        <v>4.40297317504883</v>
       </c>
       <c r="H809" t="n">
         <v>91379</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>4.60012149810791</v>
+        <v>4.60012102127075</v>
       </c>
       <c r="H815" t="n">
         <v>215464</v>
@@ -24033,7 +24033,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G816" t="n">
-        <v>4.60012149810791</v>
+        <v>4.60012102127075</v>
       </c>
       <c r="H816" t="n">
         <v>58892</v>
@@ -24091,7 +24091,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>4.60012149810791</v>
+        <v>4.60012102127075</v>
       </c>
       <c r="H818" t="n">
         <v>25431</v>
@@ -24120,7 +24120,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G819" t="n">
-        <v>4.58369255065918</v>
+        <v>4.58369302749634</v>
       </c>
       <c r="H819" t="n">
         <v>21467</v>
@@ -24178,7 +24178,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>4.53440523147583</v>
+        <v>4.53440570831299</v>
       </c>
       <c r="H821" t="n">
         <v>77444</v>
@@ -24207,7 +24207,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G822" t="n">
-        <v>4.35368633270264</v>
+        <v>4.35368585586548</v>
       </c>
       <c r="H822" t="n">
         <v>61762</v>
@@ -24236,7 +24236,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G823" t="n">
-        <v>4.34547138214111</v>
+        <v>4.34547185897827</v>
       </c>
       <c r="H823" t="n">
         <v>26602</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.39475917816162</v>
+        <v>4.39475870132446</v>
       </c>
       <c r="H825" t="n">
         <v>34656</v>
@@ -24323,7 +24323,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G826" t="n">
-        <v>4.45226049423218</v>
+        <v>4.45226001739502</v>
       </c>
       <c r="H826" t="n">
         <v>92106</v>
@@ -24352,7 +24352,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G827" t="n">
-        <v>4.45226049423218</v>
+        <v>4.45226001739502</v>
       </c>
       <c r="H827" t="n">
         <v>122475</v>
@@ -24439,7 +24439,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G830" t="n">
-        <v>4.50976181030273</v>
+        <v>4.50976228713989</v>
       </c>
       <c r="H830" t="n">
         <v>34366</v>
@@ -24526,7 +24526,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.35368633270264</v>
+        <v>4.35368585586548</v>
       </c>
       <c r="H833" t="n">
         <v>82546</v>
@@ -24671,7 +24671,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>4.65762281417847</v>
+        <v>4.65762329101562</v>
       </c>
       <c r="H838" t="n">
         <v>101495</v>
@@ -24700,7 +24700,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G839" t="n">
-        <v>4.70691013336182</v>
+        <v>4.70691061019897</v>
       </c>
       <c r="H839" t="n">
         <v>61079</v>
@@ -24729,7 +24729,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G840" t="n">
-        <v>4.64119434356689</v>
+        <v>4.64119386672974</v>
       </c>
       <c r="H840" t="n">
         <v>45963</v>
@@ -24758,7 +24758,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G841" t="n">
-        <v>4.59190654754639</v>
+        <v>4.5919075012207</v>
       </c>
       <c r="H841" t="n">
         <v>100209</v>
@@ -24787,7 +24787,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.55904817581177</v>
+        <v>4.55904865264893</v>
       </c>
       <c r="H842" t="n">
         <v>31144</v>
@@ -24816,7 +24816,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.55904817581177</v>
+        <v>4.55904865264893</v>
       </c>
       <c r="H843" t="n">
         <v>17460</v>
@@ -24961,7 +24961,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G848" t="n">
-        <v>4.50976181030273</v>
+        <v>4.50976228713989</v>
       </c>
       <c r="H848" t="n">
         <v>59088</v>
@@ -24990,7 +24990,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>4.45226049423218</v>
+        <v>4.45226001739502</v>
       </c>
       <c r="H849" t="n">
         <v>11805</v>
@@ -25106,7 +25106,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G853" t="n">
-        <v>4.39475917816162</v>
+        <v>4.39475870132446</v>
       </c>
       <c r="H853" t="n">
         <v>26033</v>
@@ -25193,7 +25193,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>4.29618453979492</v>
+        <v>4.29618501663208</v>
       </c>
       <c r="H856" t="n">
         <v>40838</v>
@@ -25222,7 +25222,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.28797006607056</v>
+        <v>4.28797054290771</v>
       </c>
       <c r="H857" t="n">
         <v>47715</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H859" t="n">
         <v>42714</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H860" t="n">
         <v>14810</v>
@@ -25338,7 +25338,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G861" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329883575439</v>
       </c>
       <c r="H861" t="n">
         <v>12608</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H863" t="n">
         <v>47863</v>
@@ -25454,7 +25454,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G865" t="n">
-        <v>4.2130651473999</v>
+        <v>4.21306562423706</v>
       </c>
       <c r="H865" t="n">
         <v>52335</v>
@@ -25483,7 +25483,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G866" t="n">
-        <v>4.17942762374878</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H866" t="n">
         <v>53889</v>
@@ -25512,7 +25512,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>4.23829317092896</v>
+        <v>4.23829364776611</v>
       </c>
       <c r="H867" t="n">
         <v>20899</v>
@@ -25686,7 +25686,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G873" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H873" t="n">
         <v>58805</v>
@@ -25715,7 +25715,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G874" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H874" t="n">
         <v>14233</v>
@@ -25773,7 +25773,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G876" t="n">
-        <v>4.26352167129517</v>
+        <v>4.26352119445801</v>
       </c>
       <c r="H876" t="n">
         <v>9240</v>
@@ -25860,7 +25860,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G879" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H879" t="n">
         <v>24765</v>
@@ -26005,7 +26005,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G884" t="n">
-        <v>4.14158725738525</v>
+        <v>4.14158630371094</v>
       </c>
       <c r="H884" t="n">
         <v>38616</v>
@@ -26092,7 +26092,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>3.96078634262085</v>
+        <v>3.96078586578369</v>
       </c>
       <c r="H887" t="n">
         <v>207235</v>
@@ -26179,7 +26179,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94817280769348</v>
+        <v>3.94817233085632</v>
       </c>
       <c r="H890" t="n">
         <v>44423</v>
@@ -26295,7 +26295,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G894" t="n">
-        <v>3.85987424850464</v>
+        <v>3.8598747253418</v>
       </c>
       <c r="H894" t="n">
         <v>35895</v>
@@ -26324,7 +26324,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>3.88089752197266</v>
+        <v>3.88089799880981</v>
       </c>
       <c r="H895" t="n">
         <v>65152</v>
@@ -26382,7 +26382,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>3.92714858055115</v>
+        <v>3.92714905738831</v>
       </c>
       <c r="H897" t="n">
         <v>93698</v>
@@ -26440,7 +26440,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G899" t="n">
-        <v>3.84305572509766</v>
+        <v>3.84305644035339</v>
       </c>
       <c r="H899" t="n">
         <v>20737</v>
@@ -26498,7 +26498,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.98601412773132</v>
+        <v>3.98601460456848</v>
       </c>
       <c r="H901" t="n">
         <v>70917</v>
@@ -26556,7 +26556,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G903" t="n">
-        <v>4.02385663986206</v>
+        <v>4.0238561630249</v>
       </c>
       <c r="H903" t="n">
         <v>47622</v>
@@ -26585,7 +26585,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G904" t="n">
-        <v>4.17942762374878</v>
+        <v>4.17942810058594</v>
       </c>
       <c r="H904" t="n">
         <v>124527</v>
@@ -26643,7 +26643,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G906" t="n">
-        <v>4.22988414764404</v>
+        <v>4.22988367080688</v>
       </c>
       <c r="H906" t="n">
         <v>68752</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.20465707778931</v>
+        <v>4.20465660095215</v>
       </c>
       <c r="H907" t="n">
         <v>181979</v>
@@ -26701,7 +26701,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G908" t="n">
-        <v>3.94396805763245</v>
+        <v>3.94396758079529</v>
       </c>
       <c r="H908" t="n">
         <v>146640</v>
@@ -26730,7 +26730,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>3.75896215438843</v>
+        <v>3.75896263122559</v>
       </c>
       <c r="H909" t="n">
         <v>112580</v>
@@ -26759,7 +26759,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79260063171387</v>
+        <v>3.79260015487671</v>
       </c>
       <c r="H910" t="n">
         <v>75174</v>
@@ -26788,7 +26788,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>3.80521368980408</v>
+        <v>3.80521416664124</v>
       </c>
       <c r="H911" t="n">
         <v>41711</v>
@@ -26817,7 +26817,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G912" t="n">
-        <v>3.98601412773132</v>
+        <v>3.98601460456848</v>
       </c>
       <c r="H912" t="n">
         <v>85224</v>
@@ -26875,7 +26875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G914" t="n">
-        <v>3.93555808067322</v>
+        <v>3.93555855751038</v>
       </c>
       <c r="H914" t="n">
         <v>69549</v>
@@ -26904,7 +26904,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G915" t="n">
-        <v>3.85146546363831</v>
+        <v>3.85146498680115</v>
       </c>
       <c r="H915" t="n">
         <v>58796</v>
@@ -26933,7 +26933,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G916" t="n">
-        <v>3.80521368980408</v>
+        <v>3.80521416664124</v>
       </c>
       <c r="H916" t="n">
         <v>31648</v>
@@ -26991,7 +26991,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G918" t="n">
-        <v>3.6916880607605</v>
+        <v>3.69168829917908</v>
       </c>
       <c r="H918" t="n">
         <v>28446</v>
@@ -27049,7 +27049,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441325187683</v>
       </c>
       <c r="H920" t="n">
         <v>59927</v>
@@ -27078,7 +27078,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G921" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H921" t="n">
         <v>22149</v>
@@ -27107,7 +27107,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G922" t="n">
-        <v>3.60759544372559</v>
+        <v>3.60759520530701</v>
       </c>
       <c r="H922" t="n">
         <v>27438</v>
@@ -27136,7 +27136,7 @@
         <v>4.31500005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.6286187171936</v>
+        <v>3.62861824035645</v>
       </c>
       <c r="H923" t="n">
         <v>30278</v>
@@ -27194,7 +27194,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G925" t="n">
-        <v>3.58236765861511</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H925" t="n">
         <v>14205</v>
@@ -27223,7 +27223,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>3.64123225212097</v>
+        <v>3.64123201370239</v>
       </c>
       <c r="H926" t="n">
         <v>20911</v>
@@ -27252,7 +27252,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G927" t="n">
-        <v>3.73373484611511</v>
+        <v>3.73373460769653</v>
       </c>
       <c r="H927" t="n">
         <v>59457</v>
@@ -27310,7 +27310,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>3.77578139305115</v>
+        <v>3.77578091621399</v>
       </c>
       <c r="H929" t="n">
         <v>66248</v>
@@ -27339,7 +27339,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G930" t="n">
-        <v>3.7043023109436</v>
+        <v>3.70430254936218</v>
       </c>
       <c r="H930" t="n">
         <v>32087</v>
@@ -27368,7 +27368,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G931" t="n">
-        <v>3.76316714286804</v>
+        <v>3.76316738128662</v>
       </c>
       <c r="H931" t="n">
         <v>100882</v>
@@ -27397,7 +27397,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G932" t="n">
-        <v>3.70009756088257</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H932" t="n">
         <v>23120</v>
@@ -27426,7 +27426,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>3.61600470542908</v>
+        <v>3.6160044670105</v>
       </c>
       <c r="H933" t="n">
         <v>37511</v>
@@ -27455,7 +27455,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>3.61600470542908</v>
+        <v>3.6160044670105</v>
       </c>
       <c r="H934" t="n">
         <v>27320</v>
@@ -27571,7 +27571,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G938" t="n">
-        <v>3.70009756088257</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H938" t="n">
         <v>45841</v>
@@ -27629,7 +27629,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G940" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H940" t="n">
         <v>27931</v>
@@ -27658,7 +27658,7 @@
         <v>4.25</v>
       </c>
       <c r="G941" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H941" t="n">
         <v>38506</v>
@@ -27687,7 +27687,7 @@
         <v>4.25</v>
       </c>
       <c r="G942" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H942" t="n">
         <v>119394</v>
@@ -27716,7 +27716,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G943" t="n">
-        <v>3.62441372871399</v>
+        <v>3.62441325187683</v>
       </c>
       <c r="H943" t="n">
         <v>74050</v>
@@ -27774,7 +27774,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G945" t="n">
-        <v>3.76316714286804</v>
+        <v>3.76316738128662</v>
       </c>
       <c r="H945" t="n">
         <v>65323</v>
@@ -27803,7 +27803,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>3.70009756088257</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H946" t="n">
         <v>42387</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>3.70850658416748</v>
+        <v>3.70850682258606</v>
       </c>
       <c r="H947" t="n">
         <v>16961</v>
@@ -27890,7 +27890,7 @@
         <v>4.25</v>
       </c>
       <c r="G949" t="n">
-        <v>3.57395768165588</v>
+        <v>3.57395792007446</v>
       </c>
       <c r="H949" t="n">
         <v>21673</v>
@@ -27919,7 +27919,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G950" t="n">
-        <v>3.58236765861511</v>
+        <v>3.58236742019653</v>
       </c>
       <c r="H950" t="n">
         <v>25708</v>
@@ -27948,7 +27948,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G951" t="n">
-        <v>3.5907769203186</v>
+        <v>3.59077644348145</v>
       </c>
       <c r="H951" t="n">
         <v>11470</v>
@@ -28006,7 +28006,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>3.70009756088257</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H953" t="n">
         <v>62364</v>
@@ -28064,7 +28064,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>3.54032039642334</v>
+        <v>3.54032063484192</v>
       </c>
       <c r="H955" t="n">
         <v>41593</v>
@@ -28093,7 +28093,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G956" t="n">
-        <v>3.4982738494873</v>
+        <v>3.49827408790588</v>
       </c>
       <c r="H956" t="n">
         <v>19244</v>
@@ -28122,7 +28122,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G957" t="n">
-        <v>3.56554818153381</v>
+        <v>3.56554841995239</v>
       </c>
       <c r="H957" t="n">
         <v>24322</v>
@@ -28151,7 +28151,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G958" t="n">
-        <v>3.57816243171692</v>
+        <v>3.5781626701355</v>
       </c>
       <c r="H958" t="n">
         <v>20043</v>
@@ -28238,7 +28238,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>3.5907769203186</v>
+        <v>3.59077644348145</v>
       </c>
       <c r="H961" t="n">
         <v>24349</v>
@@ -28296,7 +28296,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.60759544372559</v>
+        <v>3.60759520530701</v>
       </c>
       <c r="H963" t="n">
         <v>21774</v>
@@ -28325,7 +28325,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G964" t="n">
-        <v>3.59918594360352</v>
+        <v>3.59918618202209</v>
       </c>
       <c r="H964" t="n">
         <v>44956</v>
@@ -28354,7 +28354,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G965" t="n">
-        <v>3.70009756088257</v>
+        <v>3.70009779930115</v>
       </c>
       <c r="H965" t="n">
         <v>68023</v>
@@ -28412,7 +28412,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G967" t="n">
-        <v>3.87248873710632</v>
+        <v>3.87248826026917</v>
       </c>
       <c r="H967" t="n">
         <v>98632</v>
@@ -28441,7 +28441,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G968" t="n">
-        <v>3.81782817840576</v>
+        <v>3.8178277015686</v>
       </c>
       <c r="H968" t="n">
         <v>70923</v>
@@ -28499,7 +28499,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>3.85146546363831</v>
+        <v>3.85146498680115</v>
       </c>
       <c r="H970" t="n">
         <v>35812</v>
@@ -28528,7 +28528,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G971" t="n">
-        <v>3.88089752197266</v>
+        <v>3.88089799880981</v>
       </c>
       <c r="H971" t="n">
         <v>36901</v>
@@ -28557,7 +28557,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G972" t="n">
-        <v>3.92714858055115</v>
+        <v>3.92714905738831</v>
       </c>
       <c r="H972" t="n">
         <v>52932</v>
@@ -28586,7 +28586,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G973" t="n">
-        <v>3.93135404586792</v>
+        <v>3.93135356903076</v>
       </c>
       <c r="H973" t="n">
         <v>32131</v>
@@ -28615,7 +28615,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>3.92714858055115</v>
+        <v>3.92714905738831</v>
       </c>
       <c r="H974" t="n">
         <v>60311</v>
@@ -28644,7 +28644,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G975" t="n">
-        <v>4.01124238967896</v>
+        <v>4.0112419128418</v>
       </c>
       <c r="H975" t="n">
         <v>60010</v>
@@ -28673,7 +28673,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G976" t="n">
-        <v>4.05328893661499</v>
+        <v>4.05328845977783</v>
       </c>
       <c r="H976" t="n">
         <v>72505</v>
@@ -28731,7 +28731,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G978" t="n">
-        <v>4.15840530395508</v>
+        <v>4.15840435028076</v>
       </c>
       <c r="H978" t="n">
         <v>104738</v>
@@ -28876,7 +28876,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G983" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329883575439</v>
       </c>
       <c r="H983" t="n">
         <v>86583</v>
@@ -28905,7 +28905,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G984" t="n">
-        <v>4.49057340621948</v>
+        <v>4.49057292938232</v>
       </c>
       <c r="H984" t="n">
         <v>101974</v>
@@ -28934,7 +28934,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G985" t="n">
-        <v>4.48216342926025</v>
+        <v>4.48216390609741</v>
       </c>
       <c r="H985" t="n">
         <v>121569</v>
@@ -28992,7 +28992,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G987" t="n">
-        <v>4.42329835891724</v>
+        <v>4.42329883575439</v>
       </c>
       <c r="H987" t="n">
         <v>79916</v>
@@ -29253,7 +29253,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G996" t="n">
-        <v>4.67557811737061</v>
+        <v>4.67557764053345</v>
       </c>
       <c r="H996" t="n">
         <v>413404</v>
@@ -29311,7 +29311,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G998" t="n">
-        <v>4.59989356994629</v>
+        <v>4.59989309310913</v>
       </c>
       <c r="H998" t="n">
         <v>233224</v>
@@ -29398,7 +29398,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.61671304702759</v>
+        <v>4.61671209335327</v>
       </c>
       <c r="H1001" t="n">
         <v>207996</v>
@@ -29427,7 +29427,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1002" t="n">
         <v>75122</v>
@@ -29456,7 +29456,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1003" t="n">
         <v>47533</v>
@@ -29485,7 +29485,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.58307552337646</v>
+        <v>4.58307504653931</v>
       </c>
       <c r="H1004" t="n">
         <v>68308</v>
@@ -29514,7 +29514,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.60830307006836</v>
+        <v>4.60830354690552</v>
       </c>
       <c r="H1005" t="n">
         <v>64087</v>
@@ -29543,7 +29543,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.57466602325439</v>
+        <v>4.57466650009155</v>
       </c>
       <c r="H1006" t="n">
         <v>65039</v>
@@ -29601,7 +29601,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.46534585952759</v>
+        <v>4.46534538269043</v>
       </c>
       <c r="H1008" t="n">
         <v>238585</v>
@@ -29717,7 +29717,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852590560913</v>
       </c>
       <c r="H1012" t="n">
         <v>79806</v>
@@ -29746,7 +29746,7 @@
         <v>5.25</v>
       </c>
       <c r="G1013" t="n">
-        <v>4.41488933563232</v>
+        <v>4.41488885879517</v>
       </c>
       <c r="H1013" t="n">
         <v>30335</v>
@@ -29804,7 +29804,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H1015" t="n">
         <v>17780</v>
@@ -29833,7 +29833,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852590560913</v>
       </c>
       <c r="H1016" t="n">
         <v>24939</v>
@@ -29862,7 +29862,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852590560913</v>
       </c>
       <c r="H1017" t="n">
         <v>14038</v>
@@ -29920,7 +29920,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.43170833587646</v>
+        <v>4.43170738220215</v>
       </c>
       <c r="H1019" t="n">
         <v>24998</v>
@@ -29949,7 +29949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1020" t="n">
-        <v>4.37284231185913</v>
+        <v>4.37284278869629</v>
       </c>
       <c r="H1020" t="n">
         <v>43906</v>
@@ -30007,7 +30007,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.60830307006836</v>
+        <v>4.60830354690552</v>
       </c>
       <c r="H1022" t="n">
         <v>88961</v>
@@ -30036,7 +30036,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.66716861724854</v>
+        <v>4.66716909408569</v>
       </c>
       <c r="H1023" t="n">
         <v>78529</v>
@@ -30065,7 +30065,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.59148454666138</v>
+        <v>4.59148502349854</v>
       </c>
       <c r="H1024" t="n">
         <v>28268</v>
@@ -30094,7 +30094,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.56625652313232</v>
+        <v>4.56625699996948</v>
       </c>
       <c r="H1025" t="n">
         <v>23465</v>
@@ -30123,7 +30123,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.51580047607422</v>
+        <v>4.51580142974854</v>
       </c>
       <c r="H1026" t="n">
         <v>28134</v>
@@ -30210,7 +30210,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.57466602325439</v>
+        <v>4.57466650009155</v>
       </c>
       <c r="H1029" t="n">
         <v>18151</v>
@@ -30239,7 +30239,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.57466602325439</v>
+        <v>4.57466650009155</v>
       </c>
       <c r="H1030" t="n">
         <v>12557</v>
@@ -30268,7 +30268,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>4.44852638244629</v>
+        <v>4.44852590560913</v>
       </c>
       <c r="H1031" t="n">
         <v>41499</v>
@@ -30471,7 +30471,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1038" t="n">
-        <v>4.11215448379517</v>
+        <v>4.11215400695801</v>
       </c>
       <c r="H1038" t="n">
         <v>37621</v>
@@ -30500,7 +30500,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1039" t="n">
-        <v>4.22988414764404</v>
+        <v>4.22988367080688</v>
       </c>
       <c r="H1039" t="n">
         <v>28178</v>
@@ -30529,7 +30529,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1040" t="n">
-        <v>4.2130651473999</v>
+        <v>4.21306562423706</v>
       </c>
       <c r="H1040" t="n">
         <v>14580</v>
@@ -30761,7 +30761,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1048" t="n">
-        <v>4.56625652313232</v>
+        <v>4.56625699996948</v>
       </c>
       <c r="H1048" t="n">
         <v>628680</v>
@@ -30935,7 +30935,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.02806043624878</v>
+        <v>4.02806091308594</v>
       </c>
       <c r="H1054" t="n">
         <v>87604</v>
@@ -31080,7 +31080,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.67066478729248</v>
+        <v>3.67066502571106</v>
       </c>
       <c r="H1059" t="n">
         <v>45415</v>
@@ -31138,7 +31138,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.39736199378967</v>
+        <v>3.39736223220825</v>
       </c>
       <c r="H1061" t="n">
         <v>100807</v>
@@ -31167,7 +31167,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.29224562644958</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1062" t="n">
         <v>83038</v>
@@ -31196,7 +31196,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.24179005622864</v>
+        <v>3.24178981781006</v>
       </c>
       <c r="H1063" t="n">
         <v>77522</v>
@@ -31225,7 +31225,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.09883189201355</v>
+        <v>3.09883165359497</v>
       </c>
       <c r="H1064" t="n">
         <v>66132</v>
@@ -31312,7 +31312,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.85496187210083</v>
+        <v>2.85496139526367</v>
       </c>
       <c r="H1067" t="n">
         <v>105436</v>
@@ -31428,7 +31428,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.61109161376953</v>
+        <v>2.61109137535095</v>
       </c>
       <c r="H1071" t="n">
         <v>53793</v>
@@ -31486,7 +31486,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.55643105506897</v>
+        <v>2.55643081665039</v>
       </c>
       <c r="H1073" t="n">
         <v>102932</v>
@@ -31602,7 +31602,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.64472889900208</v>
+        <v>2.6447286605835</v>
       </c>
       <c r="H1077" t="n">
         <v>47482</v>
@@ -31689,7 +31689,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.70779848098755</v>
+        <v>2.70779871940613</v>
       </c>
       <c r="H1080" t="n">
         <v>66327</v>
@@ -31718,7 +31718,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.72882199287415</v>
+        <v>2.72882175445557</v>
       </c>
       <c r="H1081" t="n">
         <v>47993</v>
@@ -31747,7 +31747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.64893388748169</v>
+        <v>2.64893364906311</v>
       </c>
       <c r="H1082" t="n">
         <v>39845</v>
@@ -31805,7 +31805,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.79189157485962</v>
+        <v>2.7918918132782</v>
       </c>
       <c r="H1084" t="n">
         <v>378419</v>
@@ -31834,7 +31834,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.82973408699036</v>
+        <v>2.82973384857178</v>
       </c>
       <c r="H1085" t="n">
         <v>42050</v>
@@ -31863,7 +31863,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.8675754070282</v>
+        <v>2.86757588386536</v>
       </c>
       <c r="H1086" t="n">
         <v>74383</v>
@@ -31921,7 +31921,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1088" t="n">
         <v>43109</v>
@@ -31979,7 +31979,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.87598490715027</v>
+        <v>2.87598466873169</v>
       </c>
       <c r="H1090" t="n">
         <v>99582</v>
@@ -32008,7 +32008,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.88018941879272</v>
+        <v>2.88018989562988</v>
       </c>
       <c r="H1091" t="n">
         <v>12591</v>
@@ -32037,7 +32037,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.91803169250488</v>
+        <v>2.91803193092346</v>
       </c>
       <c r="H1092" t="n">
         <v>30394</v>
@@ -32066,7 +32066,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.91803169250488</v>
+        <v>2.91803193092346</v>
       </c>
       <c r="H1093" t="n">
         <v>14421</v>
@@ -32095,7 +32095,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1094" t="n">
         <v>44042</v>
@@ -32124,7 +32124,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.94746422767639</v>
+        <v>2.94746375083923</v>
       </c>
       <c r="H1095" t="n">
         <v>24986</v>
@@ -32153,7 +32153,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.88018941879272</v>
+        <v>2.88018989562988</v>
       </c>
       <c r="H1096" t="n">
         <v>16579</v>
@@ -32211,7 +32211,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.90121293067932</v>
+        <v>2.90121269226074</v>
       </c>
       <c r="H1098" t="n">
         <v>8697</v>
@@ -32240,7 +32240,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.91382670402527</v>
+        <v>2.91382694244385</v>
       </c>
       <c r="H1099" t="n">
         <v>11932</v>
@@ -32269,7 +32269,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.88859891891479</v>
+        <v>2.88859915733337</v>
       </c>
       <c r="H1100" t="n">
         <v>10088</v>
@@ -32298,7 +32298,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.88018941879272</v>
+        <v>2.88018989562988</v>
       </c>
       <c r="H1101" t="n">
         <v>15640</v>
@@ -32327,7 +32327,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.88018941879272</v>
+        <v>2.88018989562988</v>
       </c>
       <c r="H1102" t="n">
         <v>34379</v>
@@ -32385,7 +32385,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.9768967628479</v>
+        <v>2.97689652442932</v>
       </c>
       <c r="H1104" t="n">
         <v>41109</v>
@@ -32472,7 +32472,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.06519460678101</v>
+        <v>3.06519436836243</v>
       </c>
       <c r="H1107" t="n">
         <v>4348</v>
@@ -32646,7 +32646,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.12405920028687</v>
+        <v>3.12405967712402</v>
       </c>
       <c r="H1113" t="n">
         <v>30715</v>
@@ -32704,7 +32704,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1115" t="n">
-        <v>3.09462714195251</v>
+        <v>3.09462738037109</v>
       </c>
       <c r="H1115" t="n">
         <v>483852</v>
@@ -32762,7 +32762,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>3.08201289176941</v>
+        <v>3.08201313018799</v>
       </c>
       <c r="H1117" t="n">
         <v>31713</v>
@@ -32791,7 +32791,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.11565017700195</v>
+        <v>3.11565041542053</v>
       </c>
       <c r="H1118" t="n">
         <v>31970</v>
@@ -32820,7 +32820,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.06939959526062</v>
+        <v>3.06939911842346</v>
       </c>
       <c r="H1119" t="n">
         <v>81350</v>
@@ -32936,7 +32936,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.31326937675476</v>
+        <v>3.31326913833618</v>
       </c>
       <c r="H1123" t="n">
         <v>33940</v>
@@ -32994,7 +32994,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.40997648239136</v>
+        <v>3.40997624397278</v>
       </c>
       <c r="H1125" t="n">
         <v>96671</v>
@@ -33023,7 +33023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.38895320892334</v>
+        <v>3.38895297050476</v>
       </c>
       <c r="H1126" t="n">
         <v>117823</v>
@@ -33052,7 +33052,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1127" t="n">
-        <v>3.4057719707489</v>
+        <v>3.40577173233032</v>
       </c>
       <c r="H1127" t="n">
         <v>28852</v>
@@ -33168,7 +33168,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.29224562644958</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1131" t="n">
         <v>38417</v>
@@ -33197,7 +33197,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.30906438827515</v>
+        <v>3.30906462669373</v>
       </c>
       <c r="H1132" t="n">
         <v>20072</v>
@@ -33226,7 +33226,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.30485987663269</v>
+        <v>3.30486011505127</v>
       </c>
       <c r="H1133" t="n">
         <v>9929</v>
@@ -33284,7 +33284,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.30065488815308</v>
+        <v>3.30065536499023</v>
       </c>
       <c r="H1135" t="n">
         <v>30588</v>
@@ -33313,7 +33313,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1136" t="n">
-        <v>3.31326937675476</v>
+        <v>3.31326913833618</v>
       </c>
       <c r="H1136" t="n">
         <v>55970</v>
@@ -33342,7 +33342,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>3.30906438827515</v>
+        <v>3.30906462669373</v>
       </c>
       <c r="H1137" t="n">
         <v>62999</v>
@@ -33371,7 +33371,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.29224562644958</v>
+        <v>3.29224586486816</v>
       </c>
       <c r="H1138" t="n">
         <v>118323</v>
@@ -33400,7 +33400,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1139" t="n">
-        <v>3.35531568527222</v>
+        <v>3.3553159236908</v>
       </c>
       <c r="H1139" t="n">
         <v>353213</v>
@@ -33458,7 +33458,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1141" t="n">
-        <v>3.37213468551636</v>
+        <v>3.37213444709778</v>
       </c>
       <c r="H1141" t="n">
         <v>74328</v>
@@ -33516,7 +33516,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.5907769203186</v>
+        <v>3.59077644348145</v>
       </c>
       <c r="H1143" t="n">
         <v>68123</v>
@@ -33545,7 +33545,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1144" t="n">
-        <v>3.54032039642334</v>
+        <v>3.54032063484192</v>
       </c>
       <c r="H1144" t="n">
         <v>31349</v>
@@ -33632,7 +33632,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>3.55330467224121</v>
+        <v>3.55330491065979</v>
       </c>
       <c r="H1147" t="n">
         <v>68563</v>
@@ -33719,7 +33719,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.42779231071472</v>
+        <v>3.42779207229614</v>
       </c>
       <c r="H1150" t="n">
         <v>15298</v>
@@ -33748,7 +33748,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1151" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1151" t="n">
         <v>12775</v>
@@ -33777,7 +33777,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.35854363441467</v>
+        <v>3.35854387283325</v>
       </c>
       <c r="H1152" t="n">
         <v>25808</v>
@@ -33806,7 +33806,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.3758556842804</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1153" t="n">
         <v>7570</v>
@@ -34212,7 +34212,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1167" t="n">
         <v>39750</v>
@@ -34270,7 +34270,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1169" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1169" t="n">
         <v>42338</v>
@@ -34299,7 +34299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1170" t="n">
         <v>11674</v>
@@ -34328,7 +34328,7 @@
         <v>3.625</v>
       </c>
       <c r="G1171" t="n">
-        <v>3.13781452178955</v>
+        <v>3.13781476020813</v>
       </c>
       <c r="H1171" t="n">
         <v>37987</v>
@@ -34357,7 +34357,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1172" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1172" t="n">
         <v>44555</v>
@@ -34415,7 +34415,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1174" t="n">
         <v>16845</v>
@@ -34444,7 +34444,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1175" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1175" t="n">
         <v>11249</v>
@@ -34473,7 +34473,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1176" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1176" t="n">
         <v>14163</v>
@@ -34502,7 +34502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1177" t="n">
-        <v>3.09020638465881</v>
+        <v>3.09020662307739</v>
       </c>
       <c r="H1177" t="n">
         <v>13797</v>
@@ -34676,7 +34676,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.97767806053162</v>
+        <v>2.9776782989502</v>
       </c>
       <c r="H1183" t="n">
         <v>18449</v>
@@ -34995,7 +34995,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.02528595924377</v>
+        <v>3.02528619766235</v>
       </c>
       <c r="H1194" t="n">
         <v>32076</v>
@@ -35024,7 +35024,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.00364637374878</v>
+        <v>3.0036461353302</v>
       </c>
       <c r="H1195" t="n">
         <v>8450</v>
@@ -35053,7 +35053,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.97767806053162</v>
+        <v>2.9776782989502</v>
       </c>
       <c r="H1196" t="n">
         <v>10571</v>
@@ -35169,7 +35169,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.77426099777222</v>
+        <v>2.77426075935364</v>
       </c>
       <c r="H1200" t="n">
         <v>14812</v>
@@ -35198,7 +35198,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.77426099777222</v>
+        <v>2.77426075935364</v>
       </c>
       <c r="H1201" t="n">
         <v>11373</v>
@@ -35256,7 +35256,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.7439649105072</v>
+        <v>2.74396514892578</v>
       </c>
       <c r="H1203" t="n">
         <v>13783</v>
@@ -35285,7 +35285,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.71799683570862</v>
+        <v>2.71799659729004</v>
       </c>
       <c r="H1204" t="n">
         <v>20689</v>
@@ -35314,7 +35314,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.75262093544006</v>
+        <v>2.75262117385864</v>
       </c>
       <c r="H1205" t="n">
         <v>14823</v>
@@ -35343,7 +35343,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.78724503517151</v>
+        <v>2.78724527359009</v>
       </c>
       <c r="H1206" t="n">
         <v>18322</v>
@@ -35430,7 +35430,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.78724503517151</v>
+        <v>2.78724527359009</v>
       </c>
       <c r="H1209" t="n">
         <v>11104</v>
@@ -35575,7 +35575,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.00364637374878</v>
+        <v>3.0036461353302</v>
       </c>
       <c r="H1214" t="n">
         <v>29476</v>
@@ -35807,7 +35807,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.70068454742432</v>
+        <v>2.70068430900574</v>
       </c>
       <c r="H1222" t="n">
         <v>24653</v>
@@ -35836,7 +35836,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.66606044769287</v>
+        <v>2.66606020927429</v>
       </c>
       <c r="H1223" t="n">
         <v>27695</v>
@@ -36039,7 +36039,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.51025199890137</v>
+        <v>2.51025176048279</v>
       </c>
       <c r="H1230" t="n">
         <v>25737</v>
@@ -36068,7 +36068,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.4972677230835</v>
+        <v>2.49726796150208</v>
       </c>
       <c r="H1231" t="n">
         <v>24442</v>
@@ -36126,7 +36126,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.44100308418274</v>
+        <v>2.44100332260132</v>
       </c>
       <c r="H1233" t="n">
         <v>71628</v>
@@ -36271,7 +36271,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.891117811203</v>
+        <v>2.89111757278442</v>
       </c>
       <c r="H1238" t="n">
         <v>43412</v>
@@ -36387,7 +36387,7 @@
         <v>3.625</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.13781452178955</v>
+        <v>3.13781476020813</v>
       </c>
       <c r="H1242" t="n">
         <v>286519</v>
@@ -36416,7 +36416,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1243" t="n">
         <v>42158</v>
@@ -36445,7 +36445,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1244" t="n">
         <v>82441</v>
@@ -36532,7 +36532,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1247" t="n">
         <v>61470</v>
@@ -36561,7 +36561,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1248" t="n">
-        <v>3.10319042205811</v>
+        <v>3.10319066047668</v>
       </c>
       <c r="H1248" t="n">
         <v>43730</v>
@@ -36590,7 +36590,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>3.10319042205811</v>
+        <v>3.10319066047668</v>
       </c>
       <c r="H1249" t="n">
         <v>33292</v>
@@ -36619,7 +36619,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1250" t="n">
-        <v>3.12483072280884</v>
+        <v>3.12483048439026</v>
       </c>
       <c r="H1250" t="n">
         <v>43905</v>
@@ -36648,7 +36648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1251" t="n">
-        <v>3.1161744594574</v>
+        <v>3.11617422103882</v>
       </c>
       <c r="H1251" t="n">
         <v>44851</v>
@@ -36706,7 +36706,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.22870326042175</v>
+        <v>3.22870302200317</v>
       </c>
       <c r="H1253" t="n">
         <v>120927</v>
@@ -36793,7 +36793,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1256" t="n">
-        <v>3.40615177154541</v>
+        <v>3.40615200996399</v>
       </c>
       <c r="H1256" t="n">
         <v>82291</v>
@@ -36880,7 +36880,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.3758556842804</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1259" t="n">
         <v>47087</v>
@@ -36909,7 +36909,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.3758556842804</v>
+        <v>3.37585592269897</v>
       </c>
       <c r="H1260" t="n">
         <v>50431</v>
@@ -36967,7 +36967,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.41913604736328</v>
+        <v>3.4191358089447</v>
       </c>
       <c r="H1262" t="n">
         <v>34624</v>
@@ -37083,7 +37083,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.41913604736328</v>
+        <v>3.4191358089447</v>
       </c>
       <c r="H1266" t="n">
         <v>38075</v>
@@ -37112,7 +37112,7 @@
         <v>3.875</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.35421586036682</v>
+        <v>3.35421562194824</v>
       </c>
       <c r="H1267" t="n">
         <v>46313</v>
@@ -37286,7 +37286,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1273" t="n">
-        <v>3.67016053199768</v>
+        <v>3.67016077041626</v>
       </c>
       <c r="H1273" t="n">
         <v>44391</v>
@@ -37315,7 +37315,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1274" t="n">
-        <v>3.67016053199768</v>
+        <v>3.67016077041626</v>
       </c>
       <c r="H1274" t="n">
         <v>37048</v>
@@ -37344,7 +37344,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.72209739685059</v>
+        <v>3.72209763526917</v>
       </c>
       <c r="H1275" t="n">
         <v>48291</v>
@@ -37402,7 +37402,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.57927322387695</v>
+        <v>3.57927298545837</v>
       </c>
       <c r="H1277" t="n">
         <v>32707</v>
@@ -37547,7 +37547,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>3.53166437149048</v>
+        <v>3.5316641330719</v>
       </c>
       <c r="H1282" t="n">
         <v>18636</v>
@@ -38069,7 +38069,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.53166437149048</v>
+        <v>3.5316641330719</v>
       </c>
       <c r="H1300" t="n">
         <v>13827</v>
@@ -38301,7 +38301,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1308" t="n">
         <v>14769</v>
@@ -38330,7 +38330,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1309" t="n">
-        <v>3.6528491973877</v>
+        <v>3.65284895896912</v>
       </c>
       <c r="H1309" t="n">
         <v>21085</v>
@@ -38388,7 +38388,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1311" t="n">
         <v>35922</v>
@@ -38504,7 +38504,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1315" t="n">
-        <v>3.60524129867554</v>
+        <v>3.60524106025696</v>
       </c>
       <c r="H1315" t="n">
         <v>18680</v>
@@ -38533,7 +38533,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.67016053199768</v>
+        <v>3.67016077041626</v>
       </c>
       <c r="H1316" t="n">
         <v>18719</v>
@@ -38562,7 +38562,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.68747353553772</v>
+        <v>3.6874737739563</v>
       </c>
       <c r="H1317" t="n">
         <v>37495</v>
@@ -38591,7 +38591,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.66150498390198</v>
+        <v>3.66150522232056</v>
       </c>
       <c r="H1318" t="n">
         <v>19255</v>
@@ -38620,7 +38620,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045757293701</v>
       </c>
       <c r="H1319" t="n">
         <v>16480</v>
@@ -38649,7 +38649,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.70045781135559</v>
+        <v>3.70045757293701</v>
       </c>
       <c r="H1320" t="n">
         <v>33947</v>
@@ -38678,7 +38678,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.68314504623413</v>
+        <v>3.68314528465271</v>
       </c>
       <c r="H1321" t="n">
         <v>14847</v>
@@ -38852,7 +38852,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1327" t="n">
-        <v>3.68314504623413</v>
+        <v>3.68314528465271</v>
       </c>
       <c r="H1327" t="n">
         <v>15723</v>
@@ -38910,7 +38910,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.5403208732605</v>
+        <v>3.54032063484192</v>
       </c>
       <c r="H1329" t="n">
         <v>12171</v>
@@ -39142,7 +39142,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.63120913505554</v>
+        <v>3.63120937347412</v>
       </c>
       <c r="H1337" t="n">
         <v>162714</v>
@@ -80154,6 +80154,35 @@
         <v>28728</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>4.78499984741211</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>4.66499996185303</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>4.76999998092651</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>4.76999998092651</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>14713</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
